--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G11">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G41">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G49">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G53">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G55">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G57">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G58">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G60">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G61">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N62">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G70">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="G96">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G100">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G103">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G116">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G137">

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G11">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G31">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G49">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G51">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G62">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G70">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="G96">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G103">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G116">

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G26">

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14366,10 +14366,10 @@
         <v>0</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC86">
         <v>0</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q107">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU153"/>
+  <dimension ref="A1:AU156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G11">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G42">
@@ -7151,17 +7151,17 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N42">
-        <v>4.11</v>
+        <v>2.04</v>
       </c>
       <c r="O42">
-        <v>3.62</v>
+        <v>3.26</v>
       </c>
       <c r="P42">
-        <v>1.79</v>
+        <v>3.54</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G43">
@@ -7314,17 +7314,17 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="O43">
-        <v>3.26</v>
+        <v>3.62</v>
       </c>
       <c r="P43">
-        <v>3.54</v>
+        <v>2.88</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="O44">
-        <v>3.62</v>
+        <v>2.91</v>
       </c>
       <c r="P44">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
+        <v>2.03</v>
+      </c>
+      <c r="AB44">
         <v>1.83</v>
-      </c>
-      <c r="AB44">
-        <v>1.93</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.83</v>
+        <v>1.48</v>
       </c>
       <c r="O45">
-        <v>2.91</v>
+        <v>4.6</v>
       </c>
       <c r="P45">
-        <v>2.57</v>
+        <v>5.36</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB45">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.48</v>
+        <v>2.73</v>
       </c>
       <c r="O46">
-        <v>4.6</v>
+        <v>3.02</v>
       </c>
       <c r="P46">
-        <v>5.36</v>
+        <v>2.58</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.73</v>
+        <v>1.74</v>
       </c>
       <c r="O47">
-        <v>3.02</v>
+        <v>3.68</v>
       </c>
       <c r="P47">
-        <v>2.58</v>
+        <v>4.3</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="O48">
-        <v>3.68</v>
+        <v>4.25</v>
       </c>
       <c r="P48">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB48">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="O49">
-        <v>4.25</v>
+        <v>3.54</v>
       </c>
       <c r="P49">
-        <v>4.34</v>
+        <v>3.15</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.09</v>
+        <v>2.92</v>
       </c>
       <c r="O50">
-        <v>3.54</v>
+        <v>3.74</v>
       </c>
       <c r="P50">
-        <v>3.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB50">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.92</v>
+        <v>4.11</v>
       </c>
       <c r="O51">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="P51">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G83">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G84">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G85">
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O86">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P86">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14366,10 +14366,10 @@
         <v>0</v>
       </c>
       <c r="AA86">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB86">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC86">
         <v>0</v>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-09-26 13:30:00</t>
+          <t>2026-09-26 13:00:00</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,22 +14774,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G89">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Deportivo Alavés W</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G90">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Deportivo Alavés W</t>
         </is>
       </c>
       <c r="G91">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G92">
@@ -15421,12 +15421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-09-26 13:45:00</t>
+          <t>2026-09-26 13:30:00</t>
         </is>
       </c>
     </row>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G94">
@@ -15747,12 +15747,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G95">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-09-26 14:00:00</t>
+          <t>2026-09-26 13:45:00</t>
         </is>
       </c>
     </row>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="G97">
@@ -16236,27 +16236,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G98">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-09-26 15:00:00</t>
+          <t>2026-09-26 14:00:00</t>
         </is>
       </c>
     </row>
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G103">
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G104">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-09-26 15:30:00</t>
+          <t>2026-09-26 15:00:00</t>
         </is>
       </c>
     </row>
@@ -17377,27 +17377,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G105">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-09-26 15:30:00</t>
+          <t>2026-09-26 15:00:00</t>
         </is>
       </c>
     </row>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="O107">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="P107">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G108">
@@ -18029,27 +18029,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-09-26 15:45:00</t>
+          <t>2026-09-26 15:30:00</t>
         </is>
       </c>
     </row>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G110">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-09-26 15:45:00</t>
+          <t>2026-09-26 15:30:00</t>
         </is>
       </c>
     </row>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G116">
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-09-26 16:00:00</t>
+          <t>2026-09-26 15:45:00</t>
         </is>
       </c>
     </row>
@@ -19496,27 +19496,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G118">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-09-26 16:00:00</t>
+          <t>2026-09-26 15:45:00</t>
         </is>
       </c>
     </row>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G119">
@@ -19822,12 +19822,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30:00</t>
+          <t>2026-09-26 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19985,12 +19985,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G121">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30:00</t>
+          <t>2026-09-26 16:00:00</t>
         </is>
       </c>
     </row>
@@ -20148,12 +20148,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G122">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-09-26 17:00:00</t>
+          <t>2026-09-26 16:30:00</t>
         </is>
       </c>
     </row>
@@ -20311,12 +20311,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G123">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-09-26 17:00:00</t>
+          <t>2026-09-26 16:30:00</t>
         </is>
       </c>
     </row>
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G124">
@@ -20637,12 +20637,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G125">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-09-26 18:30:00</t>
+          <t>2026-09-26 17:00:00</t>
         </is>
       </c>
     </row>
@@ -20800,12 +20800,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G126">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-09-26 19:00:00</t>
+          <t>2026-09-26 17:00:00</t>
         </is>
       </c>
     </row>
@@ -20963,27 +20963,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="G127">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:00</t>
+          <t>2026-09-26 17:00:00</t>
         </is>
       </c>
     </row>
@@ -21126,12 +21126,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G128">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:00</t>
+          <t>2026-09-26 18:30:00</t>
         </is>
       </c>
     </row>
@@ -21289,12 +21289,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G129">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-09-26 20:00:00</t>
+          <t>2026-09-26 19:00:00</t>
         </is>
       </c>
     </row>
@@ -21452,12 +21452,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G130">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-09-26 20:00:00</t>
+          <t>2026-09-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -21615,12 +21615,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G131">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-09-26 20:00:00</t>
+          <t>2026-09-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G133">
@@ -22104,12 +22104,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G134">
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-09-26 20:30:00</t>
+          <t>2026-09-26 20:00:00</t>
         </is>
       </c>
     </row>
@@ -22267,12 +22267,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G135">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>2026-09-26 20:30:00</t>
+          <t>2026-09-26 20:00:00</t>
         </is>
       </c>
     </row>
@@ -22430,12 +22430,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G136">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>2026-09-26 20:30:00</t>
+          <t>2026-09-26 20:00:00</t>
         </is>
       </c>
     </row>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G138">
@@ -22919,12 +22919,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G139">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>2026-09-26 21:30:00</t>
+          <t>2026-09-26 20:30:00</t>
         </is>
       </c>
     </row>
@@ -23082,7 +23082,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G140">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>2026-09-26 21:30:00</t>
+          <t>2026-09-26 20:30:00</t>
         </is>
       </c>
     </row>
@@ -23245,7 +23245,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G141">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>2026-09-26 21:30:00</t>
+          <t>2026-09-26 20:30:00</t>
         </is>
       </c>
     </row>
@@ -23413,7 +23413,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G144">
@@ -23897,12 +23897,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G145">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>2026-09-26 21:45:00</t>
+          <t>2026-09-26 21:30:00</t>
         </is>
       </c>
     </row>
@@ -24060,12 +24060,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G146">
@@ -24211,7 +24211,7 @@
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>2026-09-26 22:00:00</t>
+          <t>2026-09-26 21:30:00</t>
         </is>
       </c>
     </row>
@@ -24223,7 +24223,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G147">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>2026-09-26 22:30:00</t>
+          <t>2026-09-26 21:30:00</t>
         </is>
       </c>
     </row>
@@ -24386,12 +24386,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G148">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-09-26 23:00:00</t>
+          <t>2026-09-26 21:45:00</t>
         </is>
       </c>
     </row>
@@ -24549,7 +24549,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G149">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>2026-09-26 23:00:00</t>
+          <t>2026-09-26 22:00:00</t>
         </is>
       </c>
     </row>
@@ -24712,12 +24712,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G150">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>2026-09-26 23:00:00</t>
+          <t>2026-09-26 22:30:00</t>
         </is>
       </c>
     </row>
@@ -24875,12 +24875,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G151">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>2026-09-26 23:30:00</t>
+          <t>2026-09-26 23:00:00</t>
         </is>
       </c>
     </row>
@@ -25038,12 +25038,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G152">
@@ -25189,7 +25189,7 @@
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>2026-09-26 23:30:00</t>
+          <t>2026-09-26 23:00:00</t>
         </is>
       </c>
     </row>
@@ -25201,156 +25201,645 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>0</v>
+      </c>
+      <c r="Q153">
+        <v>0</v>
+      </c>
+      <c r="R153">
+        <v>0</v>
+      </c>
+      <c r="S153">
+        <v>0</v>
+      </c>
+      <c r="T153">
+        <v>0</v>
+      </c>
+      <c r="U153">
+        <v>0</v>
+      </c>
+      <c r="V153">
+        <v>0</v>
+      </c>
+      <c r="W153">
+        <v>0</v>
+      </c>
+      <c r="X153">
+        <v>0</v>
+      </c>
+      <c r="Y153">
+        <v>0</v>
+      </c>
+      <c r="Z153">
+        <v>0</v>
+      </c>
+      <c r="AA153">
+        <v>0</v>
+      </c>
+      <c r="AB153">
+        <v>0</v>
+      </c>
+      <c r="AC153">
+        <v>0</v>
+      </c>
+      <c r="AD153">
+        <v>0</v>
+      </c>
+      <c r="AE153">
+        <v>0</v>
+      </c>
+      <c r="AF153">
+        <v>0</v>
+      </c>
+      <c r="AG153">
+        <v>0</v>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ153">
+        <v>0</v>
+      </c>
+      <c r="AK153">
+        <v>0</v>
+      </c>
+      <c r="AL153">
+        <v>0</v>
+      </c>
+      <c r="AM153">
+        <v>-1</v>
+      </c>
+      <c r="AN153">
+        <v>-1</v>
+      </c>
+      <c r="AO153">
+        <v>-1</v>
+      </c>
+      <c r="AP153">
+        <v>-1</v>
+      </c>
+      <c r="AQ153">
+        <v>0</v>
+      </c>
+      <c r="AR153">
+        <v>0</v>
+      </c>
+      <c r="AS153">
+        <v>0</v>
+      </c>
+      <c r="AT153">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N154">
+        <v>0</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>0</v>
+      </c>
+      <c r="Q154">
+        <v>0</v>
+      </c>
+      <c r="R154">
+        <v>0</v>
+      </c>
+      <c r="S154">
+        <v>0</v>
+      </c>
+      <c r="T154">
+        <v>0</v>
+      </c>
+      <c r="U154">
+        <v>0</v>
+      </c>
+      <c r="V154">
+        <v>0</v>
+      </c>
+      <c r="W154">
+        <v>0</v>
+      </c>
+      <c r="X154">
+        <v>0</v>
+      </c>
+      <c r="Y154">
+        <v>0</v>
+      </c>
+      <c r="Z154">
+        <v>0</v>
+      </c>
+      <c r="AA154">
+        <v>0</v>
+      </c>
+      <c r="AB154">
+        <v>0</v>
+      </c>
+      <c r="AC154">
+        <v>0</v>
+      </c>
+      <c r="AD154">
+        <v>0</v>
+      </c>
+      <c r="AE154">
+        <v>0</v>
+      </c>
+      <c r="AF154">
+        <v>0</v>
+      </c>
+      <c r="AG154">
+        <v>0</v>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ154">
+        <v>0</v>
+      </c>
+      <c r="AK154">
+        <v>0</v>
+      </c>
+      <c r="AL154">
+        <v>0</v>
+      </c>
+      <c r="AM154">
+        <v>-1</v>
+      </c>
+      <c r="AN154">
+        <v>-1</v>
+      </c>
+      <c r="AO154">
+        <v>-1</v>
+      </c>
+      <c r="AP154">
+        <v>-1</v>
+      </c>
+      <c r="AQ154">
+        <v>0</v>
+      </c>
+      <c r="AR154">
+        <v>0</v>
+      </c>
+      <c r="AS154">
+        <v>0</v>
+      </c>
+      <c r="AT154">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N155">
+        <v>0</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155">
+        <v>0</v>
+      </c>
+      <c r="Q155">
+        <v>0</v>
+      </c>
+      <c r="R155">
+        <v>0</v>
+      </c>
+      <c r="S155">
+        <v>0</v>
+      </c>
+      <c r="T155">
+        <v>0</v>
+      </c>
+      <c r="U155">
+        <v>0</v>
+      </c>
+      <c r="V155">
+        <v>0</v>
+      </c>
+      <c r="W155">
+        <v>0</v>
+      </c>
+      <c r="X155">
+        <v>0</v>
+      </c>
+      <c r="Y155">
+        <v>0</v>
+      </c>
+      <c r="Z155">
+        <v>0</v>
+      </c>
+      <c r="AA155">
+        <v>0</v>
+      </c>
+      <c r="AB155">
+        <v>0</v>
+      </c>
+      <c r="AC155">
+        <v>0</v>
+      </c>
+      <c r="AD155">
+        <v>0</v>
+      </c>
+      <c r="AE155">
+        <v>0</v>
+      </c>
+      <c r="AF155">
+        <v>0</v>
+      </c>
+      <c r="AG155">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ155">
+        <v>0</v>
+      </c>
+      <c r="AK155">
+        <v>0</v>
+      </c>
+      <c r="AL155">
+        <v>0</v>
+      </c>
+      <c r="AM155">
+        <v>-1</v>
+      </c>
+      <c r="AN155">
+        <v>-1</v>
+      </c>
+      <c r="AO155">
+        <v>-1</v>
+      </c>
+      <c r="AP155">
+        <v>-1</v>
+      </c>
+      <c r="AQ155">
+        <v>0</v>
+      </c>
+      <c r="AR155">
+        <v>0</v>
+      </c>
+      <c r="AS155">
+        <v>0</v>
+      </c>
+      <c r="AT155">
+        <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
         <is>
           <t>SJ Earthquakes</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>Portland Timbers</t>
         </is>
       </c>
-      <c r="G153">
-        <v>0</v>
-      </c>
-      <c r="H153">
-        <v>0</v>
-      </c>
-      <c r="I153">
-        <v>0</v>
-      </c>
-      <c r="J153">
-        <v>0</v>
-      </c>
-      <c r="K153">
-        <v>0</v>
-      </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-      <c r="M153" t="inlineStr">
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N153">
-        <v>0</v>
-      </c>
-      <c r="O153">
-        <v>0</v>
-      </c>
-      <c r="P153">
-        <v>0</v>
-      </c>
-      <c r="Q153">
-        <v>0</v>
-      </c>
-      <c r="R153">
-        <v>0</v>
-      </c>
-      <c r="S153">
-        <v>0</v>
-      </c>
-      <c r="T153">
-        <v>0</v>
-      </c>
-      <c r="U153">
-        <v>0</v>
-      </c>
-      <c r="V153">
-        <v>0</v>
-      </c>
-      <c r="W153">
-        <v>0</v>
-      </c>
-      <c r="X153">
-        <v>0</v>
-      </c>
-      <c r="Y153">
-        <v>0</v>
-      </c>
-      <c r="Z153">
-        <v>0</v>
-      </c>
-      <c r="AA153">
-        <v>0</v>
-      </c>
-      <c r="AB153">
-        <v>0</v>
-      </c>
-      <c r="AC153">
-        <v>0</v>
-      </c>
-      <c r="AD153">
-        <v>0</v>
-      </c>
-      <c r="AE153">
-        <v>0</v>
-      </c>
-      <c r="AF153">
-        <v>0</v>
-      </c>
-      <c r="AG153">
-        <v>0</v>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ153">
-        <v>0</v>
-      </c>
-      <c r="AK153">
-        <v>0</v>
-      </c>
-      <c r="AL153">
-        <v>0</v>
-      </c>
-      <c r="AM153">
-        <v>-1</v>
-      </c>
-      <c r="AN153">
-        <v>-1</v>
-      </c>
-      <c r="AO153">
-        <v>-1</v>
-      </c>
-      <c r="AP153">
-        <v>-1</v>
-      </c>
-      <c r="AQ153">
-        <v>0</v>
-      </c>
-      <c r="AR153">
-        <v>0</v>
-      </c>
-      <c r="AS153">
-        <v>0</v>
-      </c>
-      <c r="AT153">
-        <v>0</v>
-      </c>
-      <c r="AU153" t="inlineStr">
+      <c r="N156">
+        <v>0</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+      <c r="P156">
+        <v>0</v>
+      </c>
+      <c r="Q156">
+        <v>0</v>
+      </c>
+      <c r="R156">
+        <v>0</v>
+      </c>
+      <c r="S156">
+        <v>0</v>
+      </c>
+      <c r="T156">
+        <v>0</v>
+      </c>
+      <c r="U156">
+        <v>0</v>
+      </c>
+      <c r="V156">
+        <v>0</v>
+      </c>
+      <c r="W156">
+        <v>0</v>
+      </c>
+      <c r="X156">
+        <v>0</v>
+      </c>
+      <c r="Y156">
+        <v>0</v>
+      </c>
+      <c r="Z156">
+        <v>0</v>
+      </c>
+      <c r="AA156">
+        <v>0</v>
+      </c>
+      <c r="AB156">
+        <v>0</v>
+      </c>
+      <c r="AC156">
+        <v>0</v>
+      </c>
+      <c r="AD156">
+        <v>0</v>
+      </c>
+      <c r="AE156">
+        <v>0</v>
+      </c>
+      <c r="AF156">
+        <v>0</v>
+      </c>
+      <c r="AG156">
+        <v>0</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ156">
+        <v>0</v>
+      </c>
+      <c r="AK156">
+        <v>0</v>
+      </c>
+      <c r="AL156">
+        <v>0</v>
+      </c>
+      <c r="AM156">
+        <v>-1</v>
+      </c>
+      <c r="AN156">
+        <v>-1</v>
+      </c>
+      <c r="AO156">
+        <v>-1</v>
+      </c>
+      <c r="AP156">
+        <v>-1</v>
+      </c>
+      <c r="AQ156">
+        <v>0</v>
+      </c>
+      <c r="AR156">
+        <v>0</v>
+      </c>
+      <c r="AS156">
+        <v>0</v>
+      </c>
+      <c r="AT156">
+        <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
         <is>
           <t>2026-09-26 23:30:00</t>
         </is>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q11">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G105">

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="P10">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="O11">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22685,10 +22685,10 @@
         <v>0</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE137">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22842,10 +22842,10 @@
         <v>0</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23011,10 +23011,10 @@
         <v>0</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD139">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23174,10 +23174,10 @@
         <v>0</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD140">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23337,10 +23337,10 @@
         <v>0</v>
       </c>
       <c r="AC141">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD141">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE141">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23663,10 +23663,10 @@
         <v>0</v>
       </c>
       <c r="AC143">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD143">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23826,10 +23826,10 @@
         <v>0</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD144">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -23989,10 +23989,10 @@
         <v>0</v>
       </c>
       <c r="AC145">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD145">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24152,10 +24152,10 @@
         <v>0</v>
       </c>
       <c r="AC146">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD146">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24315,10 +24315,10 @@
         <v>0</v>
       </c>
       <c r="AC147">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD147">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE147">
         <v>0</v>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24804,10 +24804,10 @@
         <v>0</v>
       </c>
       <c r="AC150">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD150">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G151">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G153">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25456,10 +25456,10 @@
         <v>0</v>
       </c>
       <c r="AC154">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD154">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE154">
         <v>0</v>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O155">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25613,10 +25613,10 @@
         <v>0</v>
       </c>
       <c r="AA155">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB155">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC155">
         <v>0</v>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25782,10 +25782,10 @@
         <v>0</v>
       </c>
       <c r="AC156">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD156">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE156">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="O7">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P8">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB8">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="O9">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="P9">
-        <v>2.09</v>
+        <v>2.49</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="O10">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="P11">
-        <v>2.47</v>
+        <v>3.1</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O40">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="P40">
-        <v>4.79</v>
+        <v>4.49</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="O41">
-        <v>3.88</v>
+        <v>3.98</v>
       </c>
       <c r="P41">
-        <v>4.49</v>
+        <v>4.79</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.92</v>
+        <v>4.11</v>
       </c>
       <c r="O50">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="P50">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>4.11</v>
+        <v>2.92</v>
       </c>
       <c r="O51">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="P51">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB51">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G70">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G121">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G134">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="O140">
-        <v>4.01</v>
+        <v>4.09</v>
       </c>
       <c r="P140">
-        <v>3.23</v>
+        <v>2.44</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23174,10 +23174,10 @@
         <v>0</v>
       </c>
       <c r="AC140">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AD140">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="O141">
-        <v>4.09</v>
+        <v>4.01</v>
       </c>
       <c r="P141">
-        <v>2.44</v>
+        <v>3.23</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23337,10 +23337,10 @@
         <v>0</v>
       </c>
       <c r="AC141">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AD141">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE141">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.39</v>
+        <v>2.19</v>
       </c>
       <c r="O145">
-        <v>5.47</v>
+        <v>3.86</v>
       </c>
       <c r="P145">
-        <v>7.9</v>
+        <v>3.17</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -23989,10 +23989,10 @@
         <v>0</v>
       </c>
       <c r="AC145">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD145">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE145">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.19</v>
+        <v>1.39</v>
       </c>
       <c r="O147">
-        <v>3.86</v>
+        <v>5.47</v>
       </c>
       <c r="P147">
-        <v>3.17</v>
+        <v>7.9</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24315,10 +24315,10 @@
         <v>0</v>
       </c>
       <c r="AC147">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD147">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE147">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G153">

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G105">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G118">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="O144">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="P144">
-        <v>2.7</v>
+        <v>3.17</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="O145">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="P145">
-        <v>3.17</v>
+        <v>3.03</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="O146">
         <v>3.84</v>
       </c>
       <c r="P146">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="Q146">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O148">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="P148">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="Q148">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22027,10 +22027,10 @@
         <v>0</v>
       </c>
       <c r="AA133">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC133">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.5</v>
+        <v>1.39</v>
       </c>
       <c r="O146">
-        <v>3.84</v>
+        <v>5.47</v>
       </c>
       <c r="P146">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24152,10 +24152,10 @@
         <v>0</v>
       </c>
       <c r="AC146">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD146">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.39</v>
+        <v>2.5</v>
       </c>
       <c r="O147">
-        <v>5.47</v>
+        <v>3.84</v>
       </c>
       <c r="P147">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24315,10 +24315,10 @@
         <v>0</v>
       </c>
       <c r="AC147">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD147">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE147">
         <v>0</v>
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q153">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -12693,7 +12693,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N76">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21206,10 +21206,10 @@
         <v>0</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA128">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU156"/>
+  <dimension ref="A1:AU158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-09-26 09:30:00</t>
+          <t>2026-09-26 09:00:00</t>
         </is>
       </c>
     </row>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G26">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G27">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G28">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G31">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-26 10:00:00</t>
+          <t>2026-09-26 09:30:00</t>
         </is>
       </c>
     </row>
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G36">
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real SC</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-26 11:00:00</t>
+          <t>2026-09-26 10:00:00</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Real SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.74</v>
+        <v>3.62</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P39">
-        <v>3.94</v>
+        <v>1.88</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="O40">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>4.49</v>
+        <v>3.94</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O41">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="P41">
-        <v>4.79</v>
+        <v>4.49</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G42">
@@ -7151,17 +7151,17 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N42">
-        <v>2.04</v>
+        <v>1.55</v>
       </c>
       <c r="O42">
-        <v>3.26</v>
+        <v>3.98</v>
       </c>
       <c r="P42">
-        <v>3.54</v>
+        <v>4.79</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G43">
@@ -7314,17 +7314,17 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="O43">
-        <v>3.62</v>
+        <v>3.26</v>
       </c>
       <c r="P43">
-        <v>2.88</v>
+        <v>3.54</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="O44">
-        <v>2.91</v>
+        <v>3.62</v>
       </c>
       <c r="P44">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AB44">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.48</v>
+        <v>2.83</v>
       </c>
       <c r="O45">
-        <v>4.6</v>
+        <v>2.91</v>
       </c>
       <c r="P45">
-        <v>5.36</v>
+        <v>2.57</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.73</v>
+        <v>1.48</v>
       </c>
       <c r="O46">
-        <v>3.02</v>
+        <v>4.6</v>
       </c>
       <c r="P46">
-        <v>2.58</v>
+        <v>5.36</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.74</v>
+        <v>2.73</v>
       </c>
       <c r="O47">
-        <v>3.68</v>
+        <v>3.02</v>
       </c>
       <c r="P47">
-        <v>4.3</v>
+        <v>2.58</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="O48">
-        <v>4.25</v>
+        <v>3.68</v>
       </c>
       <c r="P48">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="O49">
-        <v>3.54</v>
+        <v>4.25</v>
       </c>
       <c r="P49">
-        <v>3.15</v>
+        <v>4.34</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>4.11</v>
+        <v>2.09</v>
       </c>
       <c r="O50">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="P50">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8501,7 +8501,7 @@
         <v>1.83</v>
       </c>
       <c r="AB50">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.92</v>
+        <v>4.11</v>
       </c>
       <c r="O51">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="P51">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -8743,22 +8743,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8906,22 +8906,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G53">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G54">
@@ -9107,17 +9107,17 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.58</v>
+        <v>1.57</v>
       </c>
       <c r="O55">
-        <v>3.48</v>
+        <v>4.15</v>
       </c>
       <c r="P55">
-        <v>2.5</v>
+        <v>5.21</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.4</v>
+        <v>2.58</v>
       </c>
       <c r="O56">
-        <v>5</v>
+        <v>3.48</v>
       </c>
       <c r="P56">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G57">
@@ -9596,17 +9596,17 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,17 +9922,17 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O59">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P59">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G60">
@@ -10085,17 +10085,17 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G62">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G63">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G65">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G66">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-09-26 11:15:00</t>
+          <t>2026-09-26 11:00:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G67">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-09-26 11:30:00</t>
+          <t>2026-09-26 11:00:00</t>
         </is>
       </c>
     </row>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11432,10 +11432,10 @@
         <v>0</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-09-26 11:30:00</t>
+          <t>2026-09-26 11:15:00</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G72">
@@ -12161,27 +12161,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G73">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-09-26 12:00:00</t>
+          <t>2026-09-26 11:30:00</t>
         </is>
       </c>
     </row>
@@ -12324,12 +12324,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G74">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2026-09-26 12:00:00</t>
+          <t>2026-09-26 11:30:00</t>
         </is>
       </c>
     </row>
@@ -12487,27 +12487,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G75">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-09-26 12:15:00</t>
+          <t>2026-09-26 12:00:00</t>
         </is>
       </c>
     </row>
@@ -12650,27 +12650,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G76">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N76">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-09-26 12:30:00</t>
+          <t>2026-09-26 12:00:00</t>
         </is>
       </c>
     </row>
@@ -12813,12 +12813,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G77">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-09-26 12:30:00</t>
+          <t>2026-09-26 12:15:00</t>
         </is>
       </c>
     </row>
@@ -12981,22 +12981,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G78">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N78">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G79">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G80">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G81">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G82">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G83">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-09-26 13:00:00</t>
+          <t>2026-09-26 12:30:00</t>
         </is>
       </c>
     </row>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G84">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-09-26 13:00:00</t>
+          <t>2026-09-26 12:30:00</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G85">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O86">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P86">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB87">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-09-26 13:30:00</t>
+          <t>2026-09-26 13:00:00</t>
         </is>
       </c>
     </row>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="O88">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="P88">
-        <v>5.25</v>
+        <v>3.14</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB88">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-09-26 13:30:00</t>
+          <t>2026-09-26 13:00:00</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14855,10 +14855,10 @@
         <v>0</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC89">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="O90">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="P90">
-        <v>2.96</v>
+        <v>5.25</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15018,10 +15018,10 @@
         <v>0</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC90">
         <v>0</v>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Deportivo Alavés W</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G91">
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Deportivo Alavés W</t>
         </is>
       </c>
       <c r="G93">
@@ -15584,12 +15584,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G94">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-09-26 13:45:00</t>
+          <t>2026-09-26 13:30:00</t>
         </is>
       </c>
     </row>
@@ -15747,12 +15747,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G95">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-09-26 13:45:00</t>
+          <t>2026-09-26 13:30:00</t>
         </is>
       </c>
     </row>
@@ -15910,12 +15910,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G96">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-09-26 14:00:00</t>
+          <t>2026-09-26 13:45:00</t>
         </is>
       </c>
     </row>
@@ -16073,12 +16073,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G97">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-09-26 14:00:00</t>
+          <t>2026-09-26 13:45:00</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="G98">
@@ -16399,27 +16399,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="G99">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-09-26 15:00:00</t>
+          <t>2026-09-26 14:00:00</t>
         </is>
       </c>
     </row>
@@ -16562,12 +16562,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G100">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-09-26 15:00:00</t>
+          <t>2026-09-26 14:00:00</t>
         </is>
       </c>
     </row>
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G105">
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G106">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-09-26 15:30:00</t>
+          <t>2026-09-26 15:00:00</t>
         </is>
       </c>
     </row>
@@ -17703,27 +17703,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G107">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-09-26 15:30:00</t>
+          <t>2026-09-26 15:00:00</t>
         </is>
       </c>
     </row>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>4.88</v>
+        <v>1.77</v>
       </c>
       <c r="O109">
-        <v>4.19</v>
+        <v>2.91</v>
       </c>
       <c r="P109">
-        <v>1.56</v>
+        <v>5.05</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18109,10 +18109,10 @@
         <v>0</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA109">
         <v>0</v>
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G110">
@@ -18355,27 +18355,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-09-26 15:45:00</t>
+          <t>2026-09-26 15:30:00</t>
         </is>
       </c>
     </row>
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G112">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-09-26 15:45:00</t>
+          <t>2026-09-26 15:30:00</t>
         </is>
       </c>
     </row>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G118">
@@ -19659,27 +19659,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-09-26 16:00:00</t>
+          <t>2026-09-26 15:45:00</t>
         </is>
       </c>
     </row>
@@ -19822,27 +19822,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-09-26 16:00:00</t>
+          <t>2026-09-26 15:45:00</t>
         </is>
       </c>
     </row>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20065,10 +20065,10 @@
         <v>0</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA121">
         <v>0</v>
@@ -20148,12 +20148,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20228,10 +20228,10 @@
         <v>0</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA122">
         <v>0</v>
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30:00</t>
+          <t>2026-09-26 16:00:00</t>
         </is>
       </c>
     </row>
@@ -20311,12 +20311,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>7.23</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20397,10 +20397,10 @@
         <v>0</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC123">
         <v>0</v>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30:00</t>
+          <t>2026-09-26 16:00:00</t>
         </is>
       </c>
     </row>
@@ -20474,12 +20474,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G124">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-09-26 17:00:00</t>
+          <t>2026-09-26 16:30:00</t>
         </is>
       </c>
     </row>
@@ -20637,12 +20637,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G125">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-09-26 17:00:00</t>
+          <t>2026-09-26 16:30:00</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,22 +20968,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G127">
@@ -21126,12 +21126,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O128">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P128">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21206,10 +21206,10 @@
         <v>0</v>
       </c>
       <c r="Y128">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z128">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA128">
         <v>0</v>
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-09-26 18:30:00</t>
+          <t>2026-09-26 17:00:00</t>
         </is>
       </c>
     </row>
@@ -21289,27 +21289,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="G129">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-09-26 19:00:00</t>
+          <t>2026-09-26 17:00:00</t>
         </is>
       </c>
     </row>
@@ -21452,12 +21452,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21532,10 +21532,10 @@
         <v>0</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA130">
         <v>0</v>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:00</t>
+          <t>2026-09-26 18:30:00</t>
         </is>
       </c>
     </row>
@@ -21615,12 +21615,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21695,10 +21695,10 @@
         <v>0</v>
       </c>
       <c r="Y131">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z131">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA131">
         <v>0</v>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:00</t>
+          <t>2026-09-26 19:00:00</t>
         </is>
       </c>
     </row>
@@ -21778,12 +21778,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O132">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="P132">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2026-09-26 20:00:00</t>
+          <t>2026-09-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="O133">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="P133">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22027,10 +22027,10 @@
         <v>0</v>
       </c>
       <c r="AA133">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AB133">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AC133">
         <v>0</v>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-09-26 20:00:00</t>
+          <t>2026-09-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22353,10 +22353,10 @@
         <v>0</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC135">
         <v>0</v>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22593,12 +22593,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="O137">
-        <v>3.98</v>
+        <v>2.79</v>
       </c>
       <c r="P137">
-        <v>2.51</v>
+        <v>4.38</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22673,10 +22673,10 @@
         <v>0</v>
       </c>
       <c r="Y137">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z137">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA137">
         <v>0</v>
@@ -22685,10 +22685,10 @@
         <v>0</v>
       </c>
       <c r="AC137">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD137">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE137">
         <v>0</v>
@@ -22744,7 +22744,7 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>2026-09-26 20:30:00</t>
+          <t>2026-09-26 20:00:00</t>
         </is>
       </c>
     </row>
@@ -22756,12 +22756,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O138">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P138">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22842,10 +22842,10 @@
         <v>0</v>
       </c>
       <c r="AA138">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB138">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC138">
         <v>0</v>
@@ -22907,7 +22907,7 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>2026-09-26 20:30:00</t>
+          <t>2026-09-26 20:00:00</t>
         </is>
       </c>
     </row>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.55</v>
+        <v>2.62</v>
       </c>
       <c r="O139">
-        <v>4.8</v>
+        <v>3.98</v>
       </c>
       <c r="P139">
-        <v>5.58</v>
+        <v>2.51</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23011,10 +23011,10 @@
         <v>0</v>
       </c>
       <c r="AC139">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AD139">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AE139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="O140">
-        <v>4.09</v>
+        <v>3.73</v>
       </c>
       <c r="P140">
-        <v>2.44</v>
+        <v>2.83</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23168,16 +23168,16 @@
         <v>0</v>
       </c>
       <c r="AA140">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC140">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD140">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="O141">
-        <v>4.01</v>
+        <v>4.8</v>
       </c>
       <c r="P141">
-        <v>3.23</v>
+        <v>5.58</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23337,10 +23337,10 @@
         <v>0</v>
       </c>
       <c r="AC141">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AD141">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AE141">
         <v>0</v>
@@ -23408,12 +23408,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23500,10 +23500,10 @@
         <v>0</v>
       </c>
       <c r="AC142">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD142">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE142">
         <v>0</v>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-09-26 21:30:00</t>
+          <t>2026-09-26 20:30:00</t>
         </is>
       </c>
     </row>
@@ -23571,7 +23571,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.5</v>
+        <v>2.66</v>
       </c>
       <c r="O143">
-        <v>4.8</v>
+        <v>4.09</v>
       </c>
       <c r="P143">
-        <v>6.36</v>
+        <v>2.44</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23663,10 +23663,10 @@
         <v>0</v>
       </c>
       <c r="AC143">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AD143">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AE143">
         <v>0</v>
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-09-26 21:30:00</t>
+          <t>2026-09-26 20:30:00</t>
         </is>
       </c>
     </row>
@@ -23739,7 +23739,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.19</v>
+        <v>2.99</v>
       </c>
       <c r="O144">
-        <v>3.86</v>
+        <v>3.2</v>
       </c>
       <c r="P144">
-        <v>3.17</v>
+        <v>2.18</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23820,16 +23820,16 @@
         <v>0</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC144">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD144">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.27</v>
+        <v>1.5</v>
       </c>
       <c r="O145">
-        <v>3.84</v>
+        <v>4.8</v>
       </c>
       <c r="P145">
-        <v>3.03</v>
+        <v>6.36</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -23992,7 +23992,7 @@
         <v>2.25</v>
       </c>
       <c r="AD145">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.39</v>
+        <v>2.19</v>
       </c>
       <c r="O146">
-        <v>5.47</v>
+        <v>3.86</v>
       </c>
       <c r="P146">
-        <v>7.9</v>
+        <v>3.17</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24152,10 +24152,10 @@
         <v>0</v>
       </c>
       <c r="AC146">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD146">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="O147">
         <v>3.84</v>
       </c>
       <c r="P147">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24386,12 +24386,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="O148">
-        <v>4.36</v>
+        <v>5.47</v>
       </c>
       <c r="P148">
-        <v>4.59</v>
+        <v>7.9</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24478,10 +24478,10 @@
         <v>0</v>
       </c>
       <c r="AC148">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD148">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE148">
         <v>0</v>
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-09-26 21:45:00</t>
+          <t>2026-09-26 21:30:00</t>
         </is>
       </c>
     </row>
@@ -24549,12 +24549,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O149">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24641,10 +24641,10 @@
         <v>0</v>
       </c>
       <c r="AC149">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD149">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE149">
         <v>0</v>
@@ -24700,7 +24700,7 @@
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>2026-09-26 22:00:00</t>
+          <t>2026-09-26 21:30:00</t>
         </is>
       </c>
     </row>
@@ -24712,12 +24712,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.16</v>
+        <v>1.5</v>
       </c>
       <c r="O150">
-        <v>3.94</v>
+        <v>4.36</v>
       </c>
       <c r="P150">
-        <v>3.18</v>
+        <v>4.59</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24804,10 +24804,10 @@
         <v>0</v>
       </c>
       <c r="AC150">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD150">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE150">
         <v>0</v>
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>2026-09-26 22:30:00</t>
+          <t>2026-09-26 21:45:00</t>
         </is>
       </c>
     </row>
@@ -24875,7 +24875,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -24961,10 +24961,10 @@
         <v>0</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC151">
         <v>0</v>
@@ -25026,7 +25026,7 @@
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>2026-09-26 23:00:00</t>
+          <t>2026-09-26 22:00:00</t>
         </is>
       </c>
     </row>
@@ -25038,12 +25038,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>3.09</v>
+        <v>2.16</v>
       </c>
       <c r="O152">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="P152">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25130,10 +25130,10 @@
         <v>0</v>
       </c>
       <c r="AC152">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD152">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE152">
         <v>0</v>
@@ -25189,7 +25189,7 @@
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>2026-09-26 23:00:00</t>
+          <t>2026-09-26 22:30:00</t>
         </is>
       </c>
     </row>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="O153">
-        <v>3.02</v>
+        <v>3.38</v>
       </c>
       <c r="P153">
-        <v>2.27</v>
+        <v>2.96</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25364,12 +25364,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.26</v>
+        <v>3.09</v>
       </c>
       <c r="O154">
-        <v>6.55</v>
+        <v>3.4</v>
       </c>
       <c r="P154">
-        <v>11.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25456,10 +25456,10 @@
         <v>0</v>
       </c>
       <c r="AC154">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD154">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE154">
         <v>0</v>
@@ -25515,7 +25515,7 @@
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>2026-09-26 23:30:00</t>
+          <t>2026-09-26 23:00:00</t>
         </is>
       </c>
     </row>
@@ -25527,12 +25527,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.26</v>
+        <v>3</v>
       </c>
       <c r="O155">
-        <v>3.77</v>
+        <v>3.02</v>
       </c>
       <c r="P155">
-        <v>3.09</v>
+        <v>2.27</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25613,10 +25613,10 @@
         <v>0</v>
       </c>
       <c r="AA155">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB155">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC155">
         <v>0</v>
@@ -25678,7 +25678,7 @@
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>2026-09-26 23:30:00</t>
+          <t>2026-09-26 23:00:00</t>
         </is>
       </c>
     </row>
@@ -25705,141 +25705,467 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N156">
+        <v>1.26</v>
+      </c>
+      <c r="O156">
+        <v>6.55</v>
+      </c>
+      <c r="P156">
+        <v>11.4</v>
+      </c>
+      <c r="Q156">
+        <v>0</v>
+      </c>
+      <c r="R156">
+        <v>0</v>
+      </c>
+      <c r="S156">
+        <v>0</v>
+      </c>
+      <c r="T156">
+        <v>0</v>
+      </c>
+      <c r="U156">
+        <v>0</v>
+      </c>
+      <c r="V156">
+        <v>0</v>
+      </c>
+      <c r="W156">
+        <v>0</v>
+      </c>
+      <c r="X156">
+        <v>0</v>
+      </c>
+      <c r="Y156">
+        <v>0</v>
+      </c>
+      <c r="Z156">
+        <v>0</v>
+      </c>
+      <c r="AA156">
+        <v>0</v>
+      </c>
+      <c r="AB156">
+        <v>0</v>
+      </c>
+      <c r="AC156">
+        <v>1.85</v>
+      </c>
+      <c r="AD156">
+        <v>1.82</v>
+      </c>
+      <c r="AE156">
+        <v>0</v>
+      </c>
+      <c r="AF156">
+        <v>0</v>
+      </c>
+      <c r="AG156">
+        <v>0</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ156">
+        <v>0</v>
+      </c>
+      <c r="AK156">
+        <v>0</v>
+      </c>
+      <c r="AL156">
+        <v>0</v>
+      </c>
+      <c r="AM156">
+        <v>-1</v>
+      </c>
+      <c r="AN156">
+        <v>-1</v>
+      </c>
+      <c r="AO156">
+        <v>-1</v>
+      </c>
+      <c r="AP156">
+        <v>-1</v>
+      </c>
+      <c r="AQ156">
+        <v>0</v>
+      </c>
+      <c r="AR156">
+        <v>0</v>
+      </c>
+      <c r="AS156">
+        <v>0</v>
+      </c>
+      <c r="AT156">
+        <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N157">
+        <v>2.26</v>
+      </c>
+      <c r="O157">
+        <v>3.77</v>
+      </c>
+      <c r="P157">
+        <v>3.09</v>
+      </c>
+      <c r="Q157">
+        <v>0</v>
+      </c>
+      <c r="R157">
+        <v>0</v>
+      </c>
+      <c r="S157">
+        <v>0</v>
+      </c>
+      <c r="T157">
+        <v>0</v>
+      </c>
+      <c r="U157">
+        <v>0</v>
+      </c>
+      <c r="V157">
+        <v>0</v>
+      </c>
+      <c r="W157">
+        <v>0</v>
+      </c>
+      <c r="X157">
+        <v>0</v>
+      </c>
+      <c r="Y157">
+        <v>0</v>
+      </c>
+      <c r="Z157">
+        <v>0</v>
+      </c>
+      <c r="AA157">
+        <v>1.58</v>
+      </c>
+      <c r="AB157">
+        <v>2.2</v>
+      </c>
+      <c r="AC157">
+        <v>0</v>
+      </c>
+      <c r="AD157">
+        <v>0</v>
+      </c>
+      <c r="AE157">
+        <v>0</v>
+      </c>
+      <c r="AF157">
+        <v>0</v>
+      </c>
+      <c r="AG157">
+        <v>0</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ157">
+        <v>0</v>
+      </c>
+      <c r="AK157">
+        <v>0</v>
+      </c>
+      <c r="AL157">
+        <v>0</v>
+      </c>
+      <c r="AM157">
+        <v>-1</v>
+      </c>
+      <c r="AN157">
+        <v>-1</v>
+      </c>
+      <c r="AO157">
+        <v>-1</v>
+      </c>
+      <c r="AP157">
+        <v>-1</v>
+      </c>
+      <c r="AQ157">
+        <v>0</v>
+      </c>
+      <c r="AR157">
+        <v>0</v>
+      </c>
+      <c r="AS157">
+        <v>0</v>
+      </c>
+      <c r="AT157">
+        <v>0</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
           <t>SJ Earthquakes</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>Portland Timbers</t>
         </is>
       </c>
-      <c r="G156">
-        <v>0</v>
-      </c>
-      <c r="H156">
-        <v>0</v>
-      </c>
-      <c r="I156">
-        <v>0</v>
-      </c>
-      <c r="J156">
-        <v>0</v>
-      </c>
-      <c r="K156">
-        <v>0</v>
-      </c>
-      <c r="L156">
-        <v>0</v>
-      </c>
-      <c r="M156" t="inlineStr">
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N156">
+      <c r="N158">
         <v>1.98</v>
       </c>
-      <c r="O156">
+      <c r="O158">
         <v>4.07</v>
       </c>
-      <c r="P156">
+      <c r="P158">
         <v>3.57</v>
       </c>
-      <c r="Q156">
-        <v>0</v>
-      </c>
-      <c r="R156">
-        <v>0</v>
-      </c>
-      <c r="S156">
-        <v>0</v>
-      </c>
-      <c r="T156">
-        <v>0</v>
-      </c>
-      <c r="U156">
-        <v>0</v>
-      </c>
-      <c r="V156">
-        <v>0</v>
-      </c>
-      <c r="W156">
-        <v>0</v>
-      </c>
-      <c r="X156">
-        <v>0</v>
-      </c>
-      <c r="Y156">
-        <v>0</v>
-      </c>
-      <c r="Z156">
-        <v>0</v>
-      </c>
-      <c r="AA156">
-        <v>0</v>
-      </c>
-      <c r="AB156">
-        <v>0</v>
-      </c>
-      <c r="AC156">
+      <c r="Q158">
+        <v>0</v>
+      </c>
+      <c r="R158">
+        <v>0</v>
+      </c>
+      <c r="S158">
+        <v>0</v>
+      </c>
+      <c r="T158">
+        <v>0</v>
+      </c>
+      <c r="U158">
+        <v>0</v>
+      </c>
+      <c r="V158">
+        <v>0</v>
+      </c>
+      <c r="W158">
+        <v>0</v>
+      </c>
+      <c r="X158">
+        <v>0</v>
+      </c>
+      <c r="Y158">
+        <v>0</v>
+      </c>
+      <c r="Z158">
+        <v>0</v>
+      </c>
+      <c r="AA158">
+        <v>0</v>
+      </c>
+      <c r="AB158">
+        <v>0</v>
+      </c>
+      <c r="AC158">
         <v>1.9</v>
       </c>
-      <c r="AD156">
+      <c r="AD158">
         <v>1.77</v>
       </c>
-      <c r="AE156">
-        <v>0</v>
-      </c>
-      <c r="AF156">
-        <v>0</v>
-      </c>
-      <c r="AG156">
-        <v>0</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ156">
-        <v>0</v>
-      </c>
-      <c r="AK156">
-        <v>0</v>
-      </c>
-      <c r="AL156">
-        <v>0</v>
-      </c>
-      <c r="AM156">
-        <v>-1</v>
-      </c>
-      <c r="AN156">
-        <v>-1</v>
-      </c>
-      <c r="AO156">
-        <v>-1</v>
-      </c>
-      <c r="AP156">
-        <v>-1</v>
-      </c>
-      <c r="AQ156">
-        <v>0</v>
-      </c>
-      <c r="AR156">
-        <v>0</v>
-      </c>
-      <c r="AS156">
-        <v>0</v>
-      </c>
-      <c r="AT156">
-        <v>0</v>
-      </c>
-      <c r="AU156" t="inlineStr">
+      <c r="AE158">
+        <v>0</v>
+      </c>
+      <c r="AF158">
+        <v>0</v>
+      </c>
+      <c r="AG158">
+        <v>0</v>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ158">
+        <v>0</v>
+      </c>
+      <c r="AK158">
+        <v>0</v>
+      </c>
+      <c r="AL158">
+        <v>0</v>
+      </c>
+      <c r="AM158">
+        <v>-1</v>
+      </c>
+      <c r="AN158">
+        <v>-1</v>
+      </c>
+      <c r="AO158">
+        <v>-1</v>
+      </c>
+      <c r="AP158">
+        <v>-1</v>
+      </c>
+      <c r="AQ158">
+        <v>0</v>
+      </c>
+      <c r="AR158">
+        <v>0</v>
+      </c>
+      <c r="AS158">
+        <v>0</v>
+      </c>
+      <c r="AT158">
+        <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
         <is>
           <t>2026-09-26 23:30:00</t>
         </is>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G107">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="O142">
-        <v>4.01</v>
+        <v>4.09</v>
       </c>
       <c r="P142">
-        <v>3.23</v>
+        <v>2.44</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23500,10 +23500,10 @@
         <v>0</v>
       </c>
       <c r="AC142">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AD142">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="O143">
-        <v>4.09</v>
+        <v>4.01</v>
       </c>
       <c r="P143">
-        <v>2.44</v>
+        <v>3.23</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23663,10 +23663,10 @@
         <v>0</v>
       </c>
       <c r="AC143">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AD143">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE143">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.48</v>
+        <v>2.73</v>
       </c>
       <c r="O46">
-        <v>4.6</v>
+        <v>3.02</v>
       </c>
       <c r="P46">
-        <v>5.36</v>
+        <v>2.58</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.73</v>
+        <v>1.74</v>
       </c>
       <c r="O47">
-        <v>3.02</v>
+        <v>3.68</v>
       </c>
       <c r="P47">
-        <v>2.58</v>
+        <v>4.3</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="O48">
-        <v>3.68</v>
+        <v>4.25</v>
       </c>
       <c r="P48">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB48">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="O49">
-        <v>4.25</v>
+        <v>3.54</v>
       </c>
       <c r="P49">
-        <v>4.34</v>
+        <v>3.15</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.09</v>
+        <v>4.11</v>
       </c>
       <c r="O50">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P50">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8501,7 +8501,7 @@
         <v>1.83</v>
       </c>
       <c r="AB50">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>4.11</v>
+        <v>2.92</v>
       </c>
       <c r="O51">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="P51">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB51">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.92</v>
+        <v>1.48</v>
       </c>
       <c r="O52">
-        <v>3.74</v>
+        <v>4.6</v>
       </c>
       <c r="P52">
-        <v>2.13</v>
+        <v>5.36</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G57">
@@ -9596,17 +9596,17 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N57">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P57">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,17 +9922,17 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G60">
@@ -10085,17 +10085,17 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N60">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G63">
@@ -10574,17 +10574,17 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q63">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -644,55 +644,55 @@
         <v>3.11</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,34 +807,34 @@
         <v>5.47</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AA3">
         <v>1.82</v>
@@ -843,19 +843,19 @@
         <v>1.94</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>4.87</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>2.55</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>2.03</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,34 +1459,34 @@
         <v>2.32</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AA7">
         <v>1.97</v>
@@ -1495,19 +1495,19 @@
         <v>1.79</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,34 +1622,34 @@
         <v>2.09</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA8">
         <v>1.99</v>
@@ -1658,19 +1658,19 @@
         <v>1.78</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>2.49</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>2.47</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>3.1</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>3.48</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>2.78</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>1.66</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4230,34 +4230,34 @@
         <v>3.08</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA24">
         <v>1.73</v>
@@ -4266,19 +4266,19 @@
         <v>1.95</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5697,34 +5697,34 @@
         <v>3.27</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA33">
         <v>1.93</v>
@@ -5733,19 +5733,19 @@
         <v>1.83</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6675,55 +6675,55 @@
         <v>1.88</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>3.94</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>4.49</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>4.79</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>3.54</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,34 +7490,34 @@
         <v>2.88</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA44">
         <v>1.83</v>
@@ -7526,19 +7526,19 @@
         <v>1.93</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="O45">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="P45">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA45">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AB45">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.73</v>
+        <v>1.74</v>
       </c>
       <c r="O46">
-        <v>3.02</v>
+        <v>3.68</v>
       </c>
       <c r="P46">
-        <v>2.58</v>
+        <v>4.3</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="O47">
-        <v>3.68</v>
+        <v>4.25</v>
       </c>
       <c r="P47">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA47">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AB47">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="O48">
-        <v>4.25</v>
+        <v>3.54</v>
       </c>
       <c r="P48">
-        <v>4.34</v>
+        <v>3.15</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.09</v>
+        <v>4.11</v>
       </c>
       <c r="O49">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P49">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
         <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>4.11</v>
+        <v>2.92</v>
       </c>
       <c r="O50">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="P50">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA50">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AB50">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.92</v>
+        <v>1.48</v>
       </c>
       <c r="O51">
-        <v>3.74</v>
+        <v>4.6</v>
       </c>
       <c r="P51">
-        <v>2.13</v>
+        <v>5.36</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.48</v>
+        <v>2.83</v>
       </c>
       <c r="O52">
-        <v>4.6</v>
+        <v>2.91</v>
       </c>
       <c r="P52">
-        <v>5.36</v>
+        <v>2.57</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G55">
@@ -9270,17 +9270,17 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N55">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O55">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P55">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G56">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N56">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="O56">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P56">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,17 +9922,17 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="O59">
-        <v>3.48</v>
+        <v>4.3</v>
       </c>
       <c r="P59">
-        <v>3.94</v>
+        <v>5</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G60">
@@ -10085,68 +10085,68 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G61">
@@ -10248,68 +10248,68 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G62">
@@ -10411,68 +10411,68 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>6.4</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -14825,34 +14825,34 @@
         <v>2.39</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AA89">
         <v>1.86</v>
@@ -14861,19 +14861,19 @@
         <v>1.91</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14988,34 +14988,34 @@
         <v>5.25</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA90">
         <v>2.25</v>
@@ -15024,19 +15024,19 @@
         <v>1.57</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15151,55 +15151,55 @@
         <v>0</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,55 +15314,55 @@
         <v>2.96</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18411,55 +18411,55 @@
         <v>1.56</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="O3">
-        <v>3.98</v>
+        <v>3.48</v>
       </c>
       <c r="P3">
-        <v>5.47</v>
+        <v>4.87</v>
       </c>
       <c r="Q3">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="R3">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T3">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="U3">
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z3">
-        <v>4.01</v>
+        <v>3.08</v>
       </c>
       <c r="AA3">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AB3">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AC3">
-        <v>2.66</v>
+        <v>3.48</v>
       </c>
       <c r="AD3">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.63</v>
+        <v>3.28</v>
       </c>
       <c r="O4">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="P4">
-        <v>4.87</v>
+        <v>2.03</v>
       </c>
       <c r="Q4">
-        <v>2.23</v>
+        <v>3.99</v>
       </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S4">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="U4">
-        <v>2.89</v>
+        <v>2.51</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z4">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AA4">
+        <v>1.88</v>
+      </c>
+      <c r="AB4">
+        <v>1.94</v>
+      </c>
+      <c r="AC4">
+        <v>3.07</v>
+      </c>
+      <c r="AD4">
+        <v>1.31</v>
+      </c>
+      <c r="AE4">
+        <v>1.09</v>
+      </c>
+      <c r="AF4">
+        <v>1.67</v>
+      </c>
+      <c r="AG4">
         <v>2.02</v>
-      </c>
-      <c r="AB4">
-        <v>1.77</v>
-      </c>
-      <c r="AC4">
-        <v>3.48</v>
-      </c>
-      <c r="AD4">
-        <v>1.22</v>
-      </c>
-      <c r="AE4">
-        <v>1.04</v>
-      </c>
-      <c r="AF4">
-        <v>1.85</v>
-      </c>
-      <c r="AG4">
-        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>2.05</v>
+        <v>1.27</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.32</v>
+        <v>3.14</v>
       </c>
       <c r="O5">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="P5">
-        <v>2.55</v>
+        <v>2.09</v>
       </c>
       <c r="Q5">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="R5">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S5">
         <v>1.33</v>
       </c>
       <c r="T5">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="U5">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z5">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="AB5">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="AC5">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AD5">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK5">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="O6">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="P6">
-        <v>2.03</v>
+        <v>2.49</v>
       </c>
       <c r="Q6">
-        <v>3.99</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U6">
-        <v>2.51</v>
+        <v>3.12</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="Z6">
-        <v>3.42</v>
+        <v>2.72</v>
       </c>
       <c r="AA6">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="AB6">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="AC6">
-        <v>3.07</v>
+        <v>4.33</v>
       </c>
       <c r="AD6">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AG6">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="P7">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="Q7">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S7">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T7">
-        <v>2.98</v>
+        <v>2.42</v>
       </c>
       <c r="U7">
-        <v>2.86</v>
+        <v>3.22</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z7">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="AA7">
-        <v>1.97</v>
+        <v>2.19</v>
       </c>
       <c r="AB7">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AC7">
-        <v>3.14</v>
+        <v>3.74</v>
       </c>
       <c r="AD7">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="O8">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>2.09</v>
+        <v>2.47</v>
       </c>
       <c r="Q8">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="R8">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z8">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AA8">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AB8">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AC8">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="AD8">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE8">
         <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG8">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK8">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,65 +1776,65 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.62</v>
+        <v>1.49</v>
       </c>
       <c r="O9">
-        <v>2.98</v>
+        <v>3.98</v>
       </c>
       <c r="P9">
-        <v>2.49</v>
+        <v>5.47</v>
       </c>
       <c r="Q9">
-        <v>3.3</v>
+        <v>1.99</v>
       </c>
       <c r="R9">
+        <v>2.28</v>
+      </c>
+      <c r="S9">
+        <v>1.32</v>
+      </c>
+      <c r="T9">
+        <v>3.2</v>
+      </c>
+      <c r="U9">
+        <v>2.57</v>
+      </c>
+      <c r="V9">
+        <v>1.48</v>
+      </c>
+      <c r="W9">
+        <v>1.11</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
+        <v>1.18</v>
+      </c>
+      <c r="Z9">
+        <v>4.01</v>
+      </c>
+      <c r="AA9">
+        <v>1.82</v>
+      </c>
+      <c r="AB9">
+        <v>1.94</v>
+      </c>
+      <c r="AC9">
+        <v>2.66</v>
+      </c>
+      <c r="AD9">
+        <v>1.41</v>
+      </c>
+      <c r="AE9">
+        <v>1.11</v>
+      </c>
+      <c r="AF9">
+        <v>1.71</v>
+      </c>
+      <c r="AG9">
         <v>2</v>
       </c>
-      <c r="S9">
-        <v>1.44</v>
-      </c>
-      <c r="T9">
-        <v>2.5</v>
-      </c>
-      <c r="U9">
-        <v>3.12</v>
-      </c>
-      <c r="V9">
-        <v>1.28</v>
-      </c>
-      <c r="W9">
-        <v>1.06</v>
-      </c>
-      <c r="X9">
-        <v>1.04</v>
-      </c>
-      <c r="Y9">
-        <v>1.4</v>
-      </c>
-      <c r="Z9">
-        <v>2.72</v>
-      </c>
-      <c r="AA9">
-        <v>2.29</v>
-      </c>
-      <c r="AB9">
-        <v>1.53</v>
-      </c>
-      <c r="AC9">
-        <v>4.33</v>
-      </c>
-      <c r="AD9">
-        <v>1.14</v>
-      </c>
-      <c r="AE9">
-        <v>1.01</v>
-      </c>
-      <c r="AF9">
-        <v>1.91</v>
-      </c>
-      <c r="AG9">
-        <v>1.73</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.36</v>
+        <v>2.21</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="Q10">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="R10">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="U10">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="V10">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z10">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="AA10">
+        <v>1.97</v>
+      </c>
+      <c r="AB10">
+        <v>1.79</v>
+      </c>
+      <c r="AC10">
+        <v>3.14</v>
+      </c>
+      <c r="AD10">
+        <v>1.27</v>
+      </c>
+      <c r="AE10">
+        <v>1.07</v>
+      </c>
+      <c r="AF10">
         <v>1.7</v>
       </c>
-      <c r="AB10">
-        <v>2.1</v>
-      </c>
-      <c r="AC10">
-        <v>2.77</v>
-      </c>
-      <c r="AD10">
-        <v>1.37</v>
-      </c>
-      <c r="AE10">
-        <v>1.11</v>
-      </c>
-      <c r="AF10">
-        <v>1.55</v>
-      </c>
       <c r="AG10">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="O11">
-        <v>2.99</v>
+        <v>3.38</v>
       </c>
       <c r="P11">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q11">
-        <v>3.13</v>
+        <v>2.93</v>
       </c>
       <c r="R11">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="S11">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>2.42</v>
+        <v>3.18</v>
       </c>
       <c r="U11">
-        <v>3.22</v>
+        <v>2.67</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
         <v>1.07</v>
@@ -2135,31 +2135,31 @@
         <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>2.74</v>
+        <v>3.72</v>
       </c>
       <c r="AA11">
-        <v>2.19</v>
+        <v>1.74</v>
       </c>
       <c r="AB11">
+        <v>2.02</v>
+      </c>
+      <c r="AC11">
+        <v>2.99</v>
+      </c>
+      <c r="AD11">
+        <v>1.32</v>
+      </c>
+      <c r="AE11">
+        <v>1.08</v>
+      </c>
+      <c r="AF11">
         <v>1.61</v>
       </c>
-      <c r="AC11">
-        <v>3.74</v>
-      </c>
-      <c r="AD11">
-        <v>1.19</v>
-      </c>
-      <c r="AE11">
-        <v>1.03</v>
-      </c>
-      <c r="AF11">
-        <v>1.84</v>
-      </c>
       <c r="AG11">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK11">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G18">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.62</v>
+        <v>1.6</v>
       </c>
       <c r="O39">
-        <v>3.68</v>
+        <v>3.88</v>
       </c>
       <c r="P39">
-        <v>1.88</v>
+        <v>4.49</v>
       </c>
       <c r="Q39">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R39">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S39">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="T39">
-        <v>3.12</v>
+        <v>3.46</v>
       </c>
       <c r="U39">
-        <v>2.48</v>
+        <v>2.19</v>
       </c>
       <c r="V39">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W39">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>3.82</v>
+        <v>4.55</v>
       </c>
       <c r="AA39">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AB39">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="AC39">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="AD39">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF39">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AG39">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK39">
-        <v>1.19</v>
+        <v>2.15</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="O40">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="P40">
-        <v>3.94</v>
+        <v>4.79</v>
       </c>
       <c r="Q40">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="R40">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="U40">
         <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W40">
         <v>1.13</v>
@@ -6862,31 +6862,31 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z40">
-        <v>3.9</v>
+        <v>4.18</v>
       </c>
       <c r="AA40">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB40">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC40">
         <v>2.56</v>
       </c>
       <c r="AD40">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
         <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK40">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.6</v>
+        <v>3.62</v>
       </c>
       <c r="O41">
-        <v>3.88</v>
+        <v>3.68</v>
       </c>
       <c r="P41">
-        <v>4.49</v>
+        <v>1.88</v>
       </c>
       <c r="Q41">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R41">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
+        <v>1.32</v>
+      </c>
+      <c r="T41">
+        <v>3.12</v>
+      </c>
+      <c r="U41">
+        <v>2.48</v>
+      </c>
+      <c r="V41">
+        <v>1.43</v>
+      </c>
+      <c r="W41">
+        <v>1.1</v>
+      </c>
+      <c r="X41">
+        <v>1.03</v>
+      </c>
+      <c r="Y41">
         <v>1.23</v>
       </c>
-      <c r="T41">
-        <v>3.46</v>
-      </c>
-      <c r="U41">
-        <v>2.19</v>
-      </c>
-      <c r="V41">
-        <v>1.57</v>
-      </c>
-      <c r="W41">
-        <v>1.13</v>
-      </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>1.2</v>
-      </c>
       <c r="Z41">
-        <v>4.55</v>
+        <v>3.82</v>
       </c>
       <c r="AA41">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AB41">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="AC41">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="AD41">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AE41">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AG41">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>2.15</v>
+        <v>1.19</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,31 +7155,31 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="O42">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>4.79</v>
+        <v>3.94</v>
       </c>
       <c r="Q42">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="R42">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="U42">
         <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
         <v>1.13</v>
@@ -7188,31 +7188,31 @@
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>4.18</v>
+        <v>3.9</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB42">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC42">
         <v>2.56</v>
       </c>
       <c r="AD42">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE42">
         <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK42">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G43">
@@ -7314,68 +7314,68 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43">
-        <v>2.04</v>
+        <v>4.11</v>
       </c>
       <c r="O43">
-        <v>3.26</v>
+        <v>3.62</v>
       </c>
       <c r="P43">
-        <v>3.54</v>
+        <v>1.79</v>
       </c>
       <c r="Q43">
-        <v>2.69</v>
+        <v>4.33</v>
       </c>
       <c r="R43">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="S43">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="T43">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="U43">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="V43">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AA43">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AB43">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AC43">
-        <v>3.76</v>
+        <v>2.92</v>
       </c>
       <c r="AD43">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AE43">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AG43">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK43">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,80 +7481,80 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.19</v>
+        <v>2.73</v>
       </c>
       <c r="O44">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="P44">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="Q44">
-        <v>2.43</v>
+        <v>3.18</v>
       </c>
       <c r="R44">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S44">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T44">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U44">
-        <v>2.47</v>
+        <v>2.96</v>
       </c>
       <c r="V44">
+        <v>1.4</v>
+      </c>
+      <c r="W44">
+        <v>1.06</v>
+      </c>
+      <c r="X44">
+        <v>1.03</v>
+      </c>
+      <c r="Y44">
+        <v>1.3</v>
+      </c>
+      <c r="Z44">
+        <v>3.2</v>
+      </c>
+      <c r="AA44">
+        <v>1.94</v>
+      </c>
+      <c r="AB44">
+        <v>1.8</v>
+      </c>
+      <c r="AC44">
+        <v>3.28</v>
+      </c>
+      <c r="AD44">
+        <v>1.25</v>
+      </c>
+      <c r="AE44">
+        <v>1.05</v>
+      </c>
+      <c r="AF44">
+        <v>1.73</v>
+      </c>
+      <c r="AG44">
+        <v>1.95</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>1.41</v>
+      </c>
+      <c r="AK44">
         <v>1.44</v>
-      </c>
-      <c r="W44">
-        <v>1.07</v>
-      </c>
-      <c r="X44">
-        <v>1.01</v>
-      </c>
-      <c r="Y44">
-        <v>1.22</v>
-      </c>
-      <c r="Z44">
-        <v>3.5</v>
-      </c>
-      <c r="AA44">
-        <v>1.83</v>
-      </c>
-      <c r="AB44">
-        <v>1.93</v>
-      </c>
-      <c r="AC44">
-        <v>2.83</v>
-      </c>
-      <c r="AD44">
-        <v>1.33</v>
-      </c>
-      <c r="AE44">
-        <v>1.12</v>
-      </c>
-      <c r="AF44">
-        <v>1.64</v>
-      </c>
-      <c r="AG44">
-        <v>2.13</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.27</v>
-      </c>
-      <c r="AK44">
-        <v>1.65</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.73</v>
+        <v>2.19</v>
       </c>
       <c r="O45">
-        <v>3.02</v>
+        <v>3.62</v>
       </c>
       <c r="P45">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="Q45">
-        <v>3.18</v>
+        <v>2.43</v>
       </c>
       <c r="R45">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="S45">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T45">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="U45">
-        <v>2.96</v>
+        <v>2.47</v>
       </c>
       <c r="V45">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z45">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA45">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB45">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC45">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD45">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE45">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF45">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG45">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AK45">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.74</v>
+        <v>2.09</v>
       </c>
       <c r="O46">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="P46">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q46">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="R46">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="S46">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T46">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U46">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V46">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W46">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA46">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AB46">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="AC46">
-        <v>3.01</v>
+        <v>2.77</v>
       </c>
       <c r="AD46">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AE46">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG46">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK46">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G47">
@@ -7966,68 +7966,68 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47">
-        <v>1.63</v>
+        <v>2.04</v>
       </c>
       <c r="O47">
-        <v>4.25</v>
+        <v>3.26</v>
       </c>
       <c r="P47">
-        <v>4.34</v>
+        <v>3.54</v>
       </c>
       <c r="Q47">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="R47">
-        <v>2.22</v>
+        <v>2.01</v>
       </c>
       <c r="S47">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="T47">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="U47">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="V47">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X47">
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z47">
-        <v>3.82</v>
+        <v>3</v>
       </c>
       <c r="AA47">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="AB47">
-        <v>2.06</v>
+        <v>1.61</v>
       </c>
       <c r="AC47">
-        <v>2.7</v>
+        <v>3.76</v>
       </c>
       <c r="AD47">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF47">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AG47">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK47">
-        <v>2.03</v>
+        <v>1.66</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.09</v>
+        <v>1.74</v>
       </c>
       <c r="O48">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="P48">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="Q48">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="R48">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="S48">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U48">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V48">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
+        <v>1.07</v>
+      </c>
+      <c r="X48">
+        <v>1</v>
+      </c>
+      <c r="Y48">
+        <v>1.22</v>
+      </c>
+      <c r="Z48">
+        <v>3.5</v>
+      </c>
+      <c r="AA48">
+        <v>1.91</v>
+      </c>
+      <c r="AB48">
+        <v>1.86</v>
+      </c>
+      <c r="AC48">
+        <v>3.01</v>
+      </c>
+      <c r="AD48">
+        <v>1.32</v>
+      </c>
+      <c r="AE48">
         <v>1.1</v>
       </c>
-      <c r="X48">
-        <v>1.02</v>
-      </c>
-      <c r="Y48">
-        <v>1.2</v>
-      </c>
-      <c r="Z48">
-        <v>4.33</v>
-      </c>
-      <c r="AA48">
-        <v>1.83</v>
-      </c>
-      <c r="AB48">
-        <v>2.03</v>
-      </c>
-      <c r="AC48">
-        <v>2.77</v>
-      </c>
-      <c r="AD48">
-        <v>1.43</v>
-      </c>
-      <c r="AE48">
-        <v>1.13</v>
-      </c>
       <c r="AF48">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK48">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,16 +8296,16 @@
         </is>
       </c>
       <c r="N49">
-        <v>4.11</v>
+        <v>2.83</v>
       </c>
       <c r="O49">
-        <v>3.62</v>
+        <v>2.91</v>
       </c>
       <c r="P49">
-        <v>1.79</v>
+        <v>2.57</v>
       </c>
       <c r="Q49">
-        <v>4.33</v>
+        <v>3.24</v>
       </c>
       <c r="R49">
         <v>2.25</v>
@@ -8314,13 +8314,13 @@
         <v>1.37</v>
       </c>
       <c r="T49">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="U49">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W49">
         <v>1.07</v>
@@ -8332,28 +8332,28 @@
         <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>3.5</v>
+        <v>4.07</v>
       </c>
       <c r="AA49">
+        <v>2.03</v>
+      </c>
+      <c r="AB49">
         <v>1.83</v>
       </c>
-      <c r="AB49">
-        <v>1.94</v>
-      </c>
       <c r="AC49">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AD49">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE49">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AK49">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.83</v>
+        <v>1.63</v>
       </c>
       <c r="O52">
-        <v>2.91</v>
+        <v>4.25</v>
       </c>
       <c r="P52">
-        <v>2.57</v>
+        <v>4.34</v>
       </c>
       <c r="Q52">
-        <v>3.24</v>
+        <v>2.2</v>
       </c>
       <c r="R52">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S52">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="T52">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U52">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="V52">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z52">
-        <v>4.07</v>
+        <v>3.82</v>
       </c>
       <c r="AA52">
+        <v>1.65</v>
+      </c>
+      <c r="AB52">
+        <v>2.06</v>
+      </c>
+      <c r="AC52">
+        <v>2.7</v>
+      </c>
+      <c r="AD52">
+        <v>1.36</v>
+      </c>
+      <c r="AE52">
+        <v>1.11</v>
+      </c>
+      <c r="AF52">
+        <v>1.67</v>
+      </c>
+      <c r="AG52">
+        <v>2.1</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>1.19</v>
+      </c>
+      <c r="AK52">
         <v>2.03</v>
-      </c>
-      <c r="AB52">
-        <v>1.83</v>
-      </c>
-      <c r="AC52">
-        <v>2.74</v>
-      </c>
-      <c r="AD52">
-        <v>1.35</v>
-      </c>
-      <c r="AE52">
-        <v>1.13</v>
-      </c>
-      <c r="AF52">
-        <v>1.6</v>
-      </c>
-      <c r="AG52">
-        <v>2.19</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.4</v>
-      </c>
-      <c r="AK52">
-        <v>1.43</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.75</v>
+        <v>1.76</v>
       </c>
       <c r="O56">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P56">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.76</v>
+        <v>2.13</v>
       </c>
       <c r="O57">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P57">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.13</v>
+        <v>1.62</v>
       </c>
       <c r="O58">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="P58">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,68 +9922,68 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N59">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="O59">
-        <v>4.3</v>
+        <v>3.48</v>
       </c>
       <c r="P59">
-        <v>5</v>
+        <v>3.94</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="O60">
-        <v>3.48</v>
+        <v>5</v>
       </c>
       <c r="P60">
-        <v>3.94</v>
+        <v>6.4</v>
       </c>
       <c r="Q60">
-        <v>2.39</v>
+        <v>1.74</v>
       </c>
       <c r="R60">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="S60">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="T60">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="U60">
-        <v>2.71</v>
+        <v>1.95</v>
       </c>
       <c r="V60">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="W60">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="X60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="Z60">
-        <v>3.05</v>
+        <v>5.85</v>
       </c>
       <c r="AA60">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="AB60">
-        <v>1.79</v>
+        <v>2.87</v>
       </c>
       <c r="AC60">
-        <v>3.44</v>
+        <v>2.02</v>
       </c>
       <c r="AD60">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="AE60">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AF60">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AG60">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK60">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G62">
@@ -10411,68 +10411,68 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N62">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="O62">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P62">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q62">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S62">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T62">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U62">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V62">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W62">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z62">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD62">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE62">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF62">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG62">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK62">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.4</v>
+        <v>2.58</v>
       </c>
       <c r="O63">
-        <v>5</v>
+        <v>3.48</v>
       </c>
       <c r="P63">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q63">
-        <v>1.74</v>
+        <v>2.75</v>
       </c>
       <c r="R63">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="S63">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="T63">
-        <v>4.3</v>
+        <v>3.08</v>
       </c>
       <c r="U63">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="V63">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="W63">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="Z63">
-        <v>5.85</v>
+        <v>4.05</v>
       </c>
       <c r="AA63">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB63">
-        <v>2.87</v>
+        <v>2.1</v>
       </c>
       <c r="AC63">
-        <v>2.02</v>
+        <v>2.52</v>
       </c>
       <c r="AD63">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="AE63">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AF63">
         <v>1.57</v>
       </c>
       <c r="AG63">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>3</v>
+        <v>1.46</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.53</v>
+        <v>1.7</v>
       </c>
       <c r="O103">
-        <v>3.6</v>
+        <v>4.45</v>
       </c>
       <c r="P103">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="Q103">
-        <v>3.11</v>
+        <v>2.08</v>
       </c>
       <c r="R103">
-        <v>2.36</v>
+        <v>2.73</v>
       </c>
       <c r="S103">
+        <v>1.15</v>
+      </c>
+      <c r="T103">
+        <v>5</v>
+      </c>
+      <c r="U103">
+        <v>1.73</v>
+      </c>
+      <c r="V103">
+        <v>2</v>
+      </c>
+      <c r="W103">
         <v>1.29</v>
       </c>
-      <c r="T103">
-        <v>3.26</v>
-      </c>
-      <c r="U103">
-        <v>2.32</v>
-      </c>
-      <c r="V103">
-        <v>1.53</v>
-      </c>
-      <c r="W103">
-        <v>1.12</v>
-      </c>
       <c r="X103">
+        <v>1</v>
+      </c>
+      <c r="Y103">
         <v>1.02</v>
       </c>
-      <c r="Y103">
-        <v>1.17</v>
-      </c>
       <c r="Z103">
-        <v>4.05</v>
+        <v>7.8</v>
       </c>
       <c r="AA103">
-        <v>1.68</v>
+        <v>1.2</v>
       </c>
       <c r="AB103">
-        <v>2.11</v>
+        <v>3.83</v>
       </c>
       <c r="AC103">
-        <v>2.56</v>
+        <v>1.62</v>
       </c>
       <c r="AD103">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="AE103">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="AF103">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AG103">
-        <v>2.34</v>
+        <v>3.42</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK103">
-        <v>1.45</v>
+        <v>2.07</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="O104">
-        <v>4.45</v>
+        <v>5.25</v>
       </c>
       <c r="P104">
-        <v>4</v>
+        <v>7.65</v>
       </c>
       <c r="Q104">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="R104">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="S104">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T104">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="U104">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="V104">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="W104">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="X104">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z104">
-        <v>7.8</v>
+        <v>6.45</v>
       </c>
       <c r="AA104">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AB104">
-        <v>3.83</v>
+        <v>2.92</v>
       </c>
       <c r="AC104">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AD104">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AE104">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AF104">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AG104">
-        <v>3.42</v>
+        <v>2.26</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK104">
-        <v>2.07</v>
+        <v>3.4</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="O105">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="P105">
-        <v>7.65</v>
+        <v>5.26</v>
       </c>
       <c r="Q105">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="R105">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S105">
         <v>1.2</v>
       </c>
       <c r="T105">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="U105">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V105">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="W105">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z105">
-        <v>6.45</v>
+        <v>6.15</v>
       </c>
       <c r="AA105">
+        <v>1.32</v>
+      </c>
+      <c r="AB105">
+        <v>3.1</v>
+      </c>
+      <c r="AC105">
+        <v>1.91</v>
+      </c>
+      <c r="AD105">
+        <v>1.82</v>
+      </c>
+      <c r="AE105">
         <v>1.31</v>
       </c>
-      <c r="AB105">
-        <v>2.92</v>
-      </c>
-      <c r="AC105">
-        <v>1.9</v>
-      </c>
-      <c r="AD105">
-        <v>1.83</v>
-      </c>
-      <c r="AE105">
-        <v>1.34</v>
-      </c>
       <c r="AF105">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG105">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AK105">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.41</v>
+        <v>1.9</v>
       </c>
       <c r="O106">
-        <v>4.6</v>
+        <v>3.78</v>
       </c>
       <c r="P106">
-        <v>5.26</v>
+        <v>3.07</v>
       </c>
       <c r="Q106">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="R106">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="S106">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="U106">
-        <v>1.99</v>
+        <v>2.21</v>
       </c>
       <c r="V106">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="W106">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Z106">
-        <v>6.15</v>
+        <v>4.7</v>
       </c>
       <c r="AA106">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AB106">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC106">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="AD106">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AE106">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AF106">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG106">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>2.42</v>
+        <v>1.81</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.9</v>
+        <v>2.53</v>
       </c>
       <c r="O107">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="P107">
-        <v>3.07</v>
+        <v>2.55</v>
       </c>
       <c r="Q107">
-        <v>2.4</v>
+        <v>3.11</v>
       </c>
       <c r="R107">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S107">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T107">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="U107">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="V107">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W107">
         <v>1.12</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
+        <v>1.17</v>
+      </c>
+      <c r="Z107">
+        <v>4.05</v>
+      </c>
+      <c r="AA107">
+        <v>1.68</v>
+      </c>
+      <c r="AB107">
+        <v>2.11</v>
+      </c>
+      <c r="AC107">
+        <v>2.56</v>
+      </c>
+      <c r="AD107">
+        <v>1.45</v>
+      </c>
+      <c r="AE107">
         <v>1.12</v>
       </c>
-      <c r="Z107">
-        <v>4.7</v>
-      </c>
-      <c r="AA107">
-        <v>1.57</v>
-      </c>
-      <c r="AB107">
-        <v>2.35</v>
-      </c>
-      <c r="AC107">
-        <v>2.33</v>
-      </c>
-      <c r="AD107">
-        <v>1.48</v>
-      </c>
-      <c r="AE107">
-        <v>1.16</v>
-      </c>
       <c r="AF107">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG107">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="AL107">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="O7">
-        <v>2.99</v>
+        <v>3.98</v>
       </c>
       <c r="P7">
-        <v>3.1</v>
+        <v>5.47</v>
       </c>
       <c r="Q7">
-        <v>3.13</v>
+        <v>1.99</v>
       </c>
       <c r="R7">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="S7">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="U7">
-        <v>3.22</v>
+        <v>2.57</v>
       </c>
       <c r="V7">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>2.74</v>
+        <v>4.01</v>
       </c>
       <c r="AA7">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="AB7">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>3.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD7">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AG7">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>1.48</v>
+        <v>2.21</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="P8">
-        <v>2.47</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
+        <v>3.13</v>
+      </c>
+      <c r="R8">
+        <v>1.98</v>
+      </c>
+      <c r="S8">
+        <v>1.45</v>
+      </c>
+      <c r="T8">
+        <v>2.42</v>
+      </c>
+      <c r="U8">
         <v>3.22</v>
       </c>
-      <c r="R8">
-        <v>2.17</v>
-      </c>
-      <c r="S8">
-        <v>1.3</v>
-      </c>
-      <c r="T8">
-        <v>3.2</v>
-      </c>
-      <c r="U8">
-        <v>2.45</v>
-      </c>
       <c r="V8">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>1.35</v>
+      </c>
+      <c r="Z8">
+        <v>2.74</v>
+      </c>
+      <c r="AA8">
+        <v>2.19</v>
+      </c>
+      <c r="AB8">
+        <v>1.61</v>
+      </c>
+      <c r="AC8">
+        <v>3.74</v>
+      </c>
+      <c r="AD8">
+        <v>1.19</v>
+      </c>
+      <c r="AE8">
         <v>1.03</v>
       </c>
-      <c r="Y8">
-        <v>1.17</v>
-      </c>
-      <c r="Z8">
-        <v>4</v>
-      </c>
-      <c r="AA8">
-        <v>1.7</v>
-      </c>
-      <c r="AB8">
-        <v>2.1</v>
-      </c>
-      <c r="AC8">
-        <v>2.77</v>
-      </c>
-      <c r="AD8">
-        <v>1.37</v>
-      </c>
-      <c r="AE8">
-        <v>1.11</v>
-      </c>
       <c r="AF8">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AG8">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,61 +1776,61 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.49</v>
+        <v>2.6</v>
       </c>
       <c r="O9">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>5.47</v>
+        <v>2.32</v>
       </c>
       <c r="Q9">
-        <v>1.99</v>
+        <v>3.2</v>
       </c>
       <c r="R9">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T9">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="U9">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="V9">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z9">
-        <v>4.01</v>
+        <v>3.43</v>
       </c>
       <c r="AA9">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AB9">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC9">
-        <v>2.66</v>
+        <v>3.14</v>
       </c>
       <c r="AD9">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG9">
         <v>2</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>2.21</v>
+        <v>1.38</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P10">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="Q10">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="R10">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="U10">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>3.43</v>
+        <v>3.72</v>
       </c>
       <c r="AA10">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AB10">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="AC10">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="AD10">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AK10">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O11">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="Q11">
-        <v>2.93</v>
+        <v>3.22</v>
       </c>
       <c r="R11">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AA11">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB11">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC11">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="AD11">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE11">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG11">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="O40">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>4.79</v>
+        <v>3.94</v>
       </c>
       <c r="Q40">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="U40">
         <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
         <v>1.13</v>
@@ -6862,31 +6862,31 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>4.18</v>
+        <v>3.9</v>
       </c>
       <c r="AA40">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB40">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC40">
         <v>2.56</v>
       </c>
       <c r="AD40">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE40">
         <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK40">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,31 +7155,31 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="P42">
-        <v>3.94</v>
+        <v>4.79</v>
       </c>
       <c r="Q42">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="U42">
         <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W42">
         <v>1.13</v>
@@ -7188,31 +7188,31 @@
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>3.9</v>
+        <v>4.18</v>
       </c>
       <c r="AA42">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC42">
         <v>2.56</v>
       </c>
       <c r="AD42">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
         <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG42">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK42">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,68 +7477,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44">
-        <v>2.73</v>
+        <v>2.04</v>
       </c>
       <c r="O44">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="P44">
-        <v>2.58</v>
+        <v>3.54</v>
       </c>
       <c r="Q44">
-        <v>3.18</v>
+        <v>2.69</v>
       </c>
       <c r="R44">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="S44">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T44">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="U44">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="V44">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
+        <v>1.02</v>
+      </c>
+      <c r="Y44">
+        <v>1.35</v>
+      </c>
+      <c r="Z44">
+        <v>3</v>
+      </c>
+      <c r="AA44">
+        <v>2.12</v>
+      </c>
+      <c r="AB44">
+        <v>1.61</v>
+      </c>
+      <c r="AC44">
+        <v>3.76</v>
+      </c>
+      <c r="AD44">
+        <v>1.19</v>
+      </c>
+      <c r="AE44">
         <v>1.03</v>
       </c>
-      <c r="Y44">
-        <v>1.3</v>
-      </c>
-      <c r="Z44">
-        <v>3.2</v>
-      </c>
-      <c r="AA44">
-        <v>1.94</v>
-      </c>
-      <c r="AB44">
-        <v>1.8</v>
-      </c>
-      <c r="AC44">
-        <v>3.28</v>
-      </c>
-      <c r="AD44">
-        <v>1.25</v>
-      </c>
-      <c r="AE44">
-        <v>1.05</v>
-      </c>
       <c r="AF44">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AG44">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="O46">
-        <v>3.54</v>
+        <v>4.25</v>
       </c>
       <c r="P46">
-        <v>3.15</v>
+        <v>4.34</v>
       </c>
       <c r="Q46">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="R46">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="S46">
         <v>1.26</v>
       </c>
       <c r="T46">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U46">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="V46">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W46">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z46">
-        <v>4.33</v>
+        <v>3.82</v>
       </c>
       <c r="AA46">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AB46">
+        <v>2.06</v>
+      </c>
+      <c r="AC46">
+        <v>2.7</v>
+      </c>
+      <c r="AD46">
+        <v>1.36</v>
+      </c>
+      <c r="AE46">
+        <v>1.11</v>
+      </c>
+      <c r="AF46">
+        <v>1.67</v>
+      </c>
+      <c r="AG46">
+        <v>2.1</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>1.19</v>
+      </c>
+      <c r="AK46">
         <v>2.03</v>
-      </c>
-      <c r="AC46">
-        <v>2.77</v>
-      </c>
-      <c r="AD46">
-        <v>1.43</v>
-      </c>
-      <c r="AE46">
-        <v>1.13</v>
-      </c>
-      <c r="AF46">
-        <v>1.55</v>
-      </c>
-      <c r="AG46">
-        <v>2.25</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.33</v>
-      </c>
-      <c r="AK46">
-        <v>1.65</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G47">
@@ -7966,84 +7966,84 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47">
-        <v>2.04</v>
+        <v>2.73</v>
       </c>
       <c r="O47">
-        <v>3.26</v>
+        <v>3.02</v>
       </c>
       <c r="P47">
-        <v>3.54</v>
+        <v>2.58</v>
       </c>
       <c r="Q47">
-        <v>2.69</v>
+        <v>3.18</v>
       </c>
       <c r="R47">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="S47">
+        <v>1.38</v>
+      </c>
+      <c r="T47">
+        <v>2.75</v>
+      </c>
+      <c r="U47">
+        <v>2.96</v>
+      </c>
+      <c r="V47">
+        <v>1.4</v>
+      </c>
+      <c r="W47">
+        <v>1.06</v>
+      </c>
+      <c r="X47">
+        <v>1.03</v>
+      </c>
+      <c r="Y47">
+        <v>1.3</v>
+      </c>
+      <c r="Z47">
+        <v>3.2</v>
+      </c>
+      <c r="AA47">
+        <v>1.94</v>
+      </c>
+      <c r="AB47">
+        <v>1.8</v>
+      </c>
+      <c r="AC47">
+        <v>3.28</v>
+      </c>
+      <c r="AD47">
+        <v>1.25</v>
+      </c>
+      <c r="AE47">
+        <v>1.05</v>
+      </c>
+      <c r="AF47">
+        <v>1.73</v>
+      </c>
+      <c r="AG47">
+        <v>1.95</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
         <v>1.41</v>
       </c>
-      <c r="T47">
-        <v>2.71</v>
-      </c>
-      <c r="U47">
-        <v>2.9</v>
-      </c>
-      <c r="V47">
-        <v>1.36</v>
-      </c>
-      <c r="W47">
-        <v>1.05</v>
-      </c>
-      <c r="X47">
-        <v>1.02</v>
-      </c>
-      <c r="Y47">
-        <v>1.35</v>
-      </c>
-      <c r="Z47">
-        <v>3</v>
-      </c>
-      <c r="AA47">
-        <v>2.12</v>
-      </c>
-      <c r="AB47">
-        <v>1.61</v>
-      </c>
-      <c r="AC47">
-        <v>3.76</v>
-      </c>
-      <c r="AD47">
-        <v>1.19</v>
-      </c>
-      <c r="AE47">
-        <v>1.03</v>
-      </c>
-      <c r="AF47">
-        <v>1.87</v>
-      </c>
-      <c r="AG47">
-        <v>1.83</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.29</v>
-      </c>
       <c r="AK47">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.74</v>
+        <v>2.09</v>
       </c>
       <c r="O48">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="P48">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q48">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="R48">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T48">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U48">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V48">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W48">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA48">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="AC48">
-        <v>3.01</v>
+        <v>2.77</v>
       </c>
       <c r="AD48">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AE48">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.83</v>
+        <v>1.74</v>
       </c>
       <c r="O49">
-        <v>2.91</v>
+        <v>3.68</v>
       </c>
       <c r="P49">
-        <v>2.57</v>
+        <v>4.3</v>
       </c>
       <c r="Q49">
-        <v>3.24</v>
+        <v>2.28</v>
       </c>
       <c r="R49">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S49">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="U49">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V49">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
         <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y49">
         <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>4.07</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AB49">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC49">
-        <v>2.74</v>
+        <v>3.01</v>
       </c>
       <c r="AD49">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG49">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK49">
-        <v>1.43</v>
+        <v>1.91</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O50">
-        <v>3.74</v>
+        <v>2.91</v>
       </c>
       <c r="P50">
-        <v>2.13</v>
+        <v>2.57</v>
       </c>
       <c r="Q50">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="R50">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="U50">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V50">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W50">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
         <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>4.2</v>
+        <v>4.07</v>
       </c>
       <c r="AA50">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="AB50">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AC50">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE50">
         <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AK50">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.48</v>
+        <v>2.92</v>
       </c>
       <c r="O51">
-        <v>4.6</v>
+        <v>3.74</v>
       </c>
       <c r="P51">
-        <v>5.36</v>
+        <v>2.13</v>
       </c>
       <c r="Q51">
-        <v>1.93</v>
+        <v>3.26</v>
       </c>
       <c r="R51">
+        <v>2.2</v>
+      </c>
+      <c r="S51">
+        <v>1.3</v>
+      </c>
+      <c r="T51">
+        <v>3.3</v>
+      </c>
+      <c r="U51">
         <v>2.45</v>
       </c>
-      <c r="S51">
-        <v>1.25</v>
-      </c>
-      <c r="T51">
-        <v>3.54</v>
-      </c>
-      <c r="U51">
-        <v>2.24</v>
-      </c>
       <c r="V51">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA51">
+        <v>1.69</v>
+      </c>
+      <c r="AB51">
+        <v>2.08</v>
+      </c>
+      <c r="AC51">
+        <v>2.7</v>
+      </c>
+      <c r="AD51">
+        <v>1.36</v>
+      </c>
+      <c r="AE51">
+        <v>1.13</v>
+      </c>
+      <c r="AF51">
         <v>1.58</v>
       </c>
-      <c r="AB51">
-        <v>2.19</v>
-      </c>
-      <c r="AC51">
-        <v>2.36</v>
-      </c>
-      <c r="AD51">
-        <v>1.47</v>
-      </c>
-      <c r="AE51">
-        <v>1.15</v>
-      </c>
-      <c r="AF51">
+      <c r="AG51">
+        <v>2.3</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.65</v>
       </c>
-      <c r="AG51">
-        <v>2.02</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.16</v>
-      </c>
       <c r="AK51">
-        <v>2.45</v>
+        <v>1.33</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="O52">
+        <v>4.6</v>
+      </c>
+      <c r="P52">
+        <v>5.36</v>
+      </c>
+      <c r="Q52">
+        <v>1.93</v>
+      </c>
+      <c r="R52">
+        <v>2.45</v>
+      </c>
+      <c r="S52">
+        <v>1.25</v>
+      </c>
+      <c r="T52">
+        <v>3.54</v>
+      </c>
+      <c r="U52">
+        <v>2.24</v>
+      </c>
+      <c r="V52">
+        <v>1.57</v>
+      </c>
+      <c r="W52">
+        <v>1.11</v>
+      </c>
+      <c r="X52">
+        <v>1.01</v>
+      </c>
+      <c r="Y52">
+        <v>1.18</v>
+      </c>
+      <c r="Z52">
         <v>4.25</v>
       </c>
-      <c r="P52">
-        <v>4.34</v>
-      </c>
-      <c r="Q52">
-        <v>2.2</v>
-      </c>
-      <c r="R52">
-        <v>2.22</v>
-      </c>
-      <c r="S52">
-        <v>1.26</v>
-      </c>
-      <c r="T52">
-        <v>3.2</v>
-      </c>
-      <c r="U52">
-        <v>2.42</v>
-      </c>
-      <c r="V52">
-        <v>1.48</v>
-      </c>
-      <c r="W52">
-        <v>1.08</v>
-      </c>
-      <c r="X52">
-        <v>1.02</v>
-      </c>
-      <c r="Y52">
-        <v>1.26</v>
-      </c>
-      <c r="Z52">
-        <v>3.82</v>
-      </c>
       <c r="AA52">
+        <v>1.58</v>
+      </c>
+      <c r="AB52">
+        <v>2.19</v>
+      </c>
+      <c r="AC52">
+        <v>2.36</v>
+      </c>
+      <c r="AD52">
+        <v>1.47</v>
+      </c>
+      <c r="AE52">
+        <v>1.15</v>
+      </c>
+      <c r="AF52">
         <v>1.65</v>
       </c>
-      <c r="AB52">
-        <v>2.06</v>
-      </c>
-      <c r="AC52">
-        <v>2.7</v>
-      </c>
-      <c r="AD52">
-        <v>1.36</v>
-      </c>
-      <c r="AE52">
-        <v>1.11</v>
-      </c>
-      <c r="AF52">
-        <v>1.67</v>
-      </c>
       <c r="AG52">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK52">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,68 +9922,68 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="O59">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P59">
-        <v>3.94</v>
+        <v>2.55</v>
       </c>
       <c r="Q59">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="R59">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S59">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T59">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U59">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="V59">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W59">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X59">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y59">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z59">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA59">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC59">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AD59">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE59">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF59">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG59">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK59">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,80 +10089,80 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="O60">
-        <v>5</v>
+        <v>3.48</v>
       </c>
       <c r="P60">
-        <v>6.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q60">
-        <v>1.74</v>
+        <v>2.39</v>
       </c>
       <c r="R60">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="S60">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="T60">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="U60">
-        <v>1.95</v>
+        <v>2.71</v>
       </c>
       <c r="V60">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="W60">
+        <v>1.06</v>
+      </c>
+      <c r="X60">
+        <v>1.03</v>
+      </c>
+      <c r="Y60">
+        <v>1.26</v>
+      </c>
+      <c r="Z60">
+        <v>3.05</v>
+      </c>
+      <c r="AA60">
+        <v>2.01</v>
+      </c>
+      <c r="AB60">
+        <v>1.79</v>
+      </c>
+      <c r="AC60">
+        <v>3.44</v>
+      </c>
+      <c r="AD60">
+        <v>1.26</v>
+      </c>
+      <c r="AE60">
+        <v>1.06</v>
+      </c>
+      <c r="AF60">
+        <v>1.82</v>
+      </c>
+      <c r="AG60">
+        <v>1.88</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
         <v>1.19</v>
       </c>
-      <c r="X60">
-        <v>1.01</v>
-      </c>
-      <c r="Y60">
-        <v>1.07</v>
-      </c>
-      <c r="Z60">
-        <v>5.85</v>
-      </c>
-      <c r="AA60">
-        <v>1.4</v>
-      </c>
-      <c r="AB60">
-        <v>2.87</v>
-      </c>
-      <c r="AC60">
-        <v>2.02</v>
-      </c>
-      <c r="AD60">
-        <v>1.77</v>
-      </c>
-      <c r="AE60">
-        <v>1.33</v>
-      </c>
-      <c r="AF60">
-        <v>1.57</v>
-      </c>
-      <c r="AG60">
-        <v>2.26</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ60">
-        <v>1.13</v>
-      </c>
       <c r="AK60">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G62">
@@ -10411,68 +10411,68 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N62">
+        <v>2.58</v>
+      </c>
+      <c r="O62">
+        <v>3.48</v>
+      </c>
+      <c r="P62">
+        <v>2.5</v>
+      </c>
+      <c r="Q62">
         <v>2.75</v>
       </c>
-      <c r="O62">
-        <v>3.4</v>
-      </c>
-      <c r="P62">
-        <v>2.55</v>
-      </c>
-      <c r="Q62">
-        <v>0</v>
-      </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.58</v>
+        <v>1.4</v>
       </c>
       <c r="O63">
-        <v>3.48</v>
+        <v>5</v>
       </c>
       <c r="P63">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q63">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="R63">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="S63">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="T63">
-        <v>3.08</v>
+        <v>4.3</v>
       </c>
       <c r="U63">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="V63">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="W63">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="Z63">
-        <v>4.05</v>
+        <v>5.85</v>
       </c>
       <c r="AA63">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>2.1</v>
+        <v>2.87</v>
       </c>
       <c r="AC63">
-        <v>2.52</v>
+        <v>2.02</v>
       </c>
       <c r="AD63">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="AE63">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AF63">
         <v>1.57</v>
       </c>
       <c r="AG63">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK63">
-        <v>1.46</v>
+        <v>3</v>
       </c>
       <c r="AL63">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="O7">
-        <v>3.98</v>
+        <v>2.99</v>
       </c>
       <c r="P7">
-        <v>5.47</v>
+        <v>3.1</v>
       </c>
       <c r="Q7">
-        <v>1.99</v>
+        <v>3.13</v>
       </c>
       <c r="R7">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="S7">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="T7">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="U7">
-        <v>2.57</v>
+        <v>3.22</v>
       </c>
       <c r="V7">
+        <v>1.35</v>
+      </c>
+      <c r="W7">
+        <v>1.07</v>
+      </c>
+      <c r="X7">
+        <v>1.04</v>
+      </c>
+      <c r="Y7">
+        <v>1.35</v>
+      </c>
+      <c r="Z7">
+        <v>2.74</v>
+      </c>
+      <c r="AA7">
+        <v>2.19</v>
+      </c>
+      <c r="AB7">
+        <v>1.61</v>
+      </c>
+      <c r="AC7">
+        <v>3.74</v>
+      </c>
+      <c r="AD7">
+        <v>1.19</v>
+      </c>
+      <c r="AE7">
+        <v>1.03</v>
+      </c>
+      <c r="AF7">
+        <v>1.84</v>
+      </c>
+      <c r="AG7">
+        <v>1.82</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.29</v>
+      </c>
+      <c r="AK7">
         <v>1.48</v>
-      </c>
-      <c r="W7">
-        <v>1.11</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.18</v>
-      </c>
-      <c r="Z7">
-        <v>4.01</v>
-      </c>
-      <c r="AA7">
-        <v>1.82</v>
-      </c>
-      <c r="AB7">
-        <v>1.94</v>
-      </c>
-      <c r="AC7">
-        <v>2.66</v>
-      </c>
-      <c r="AD7">
-        <v>1.41</v>
-      </c>
-      <c r="AE7">
-        <v>1.11</v>
-      </c>
-      <c r="AF7">
-        <v>1.71</v>
-      </c>
-      <c r="AG7">
-        <v>2</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.2</v>
-      </c>
-      <c r="AK7">
-        <v>2.21</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="O8">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q8">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="R8">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T8">
-        <v>2.42</v>
+        <v>2.98</v>
       </c>
       <c r="U8">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="V8">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
+        <v>1.05</v>
+      </c>
+      <c r="X8">
+        <v>1.01</v>
+      </c>
+      <c r="Y8">
+        <v>1.26</v>
+      </c>
+      <c r="Z8">
+        <v>3.43</v>
+      </c>
+      <c r="AA8">
+        <v>1.97</v>
+      </c>
+      <c r="AB8">
+        <v>1.79</v>
+      </c>
+      <c r="AC8">
+        <v>3.14</v>
+      </c>
+      <c r="AD8">
+        <v>1.27</v>
+      </c>
+      <c r="AE8">
         <v>1.07</v>
       </c>
-      <c r="X8">
-        <v>1.04</v>
-      </c>
-      <c r="Y8">
-        <v>1.35</v>
-      </c>
-      <c r="Z8">
-        <v>2.74</v>
-      </c>
-      <c r="AA8">
-        <v>2.19</v>
-      </c>
-      <c r="AB8">
-        <v>1.61</v>
-      </c>
-      <c r="AC8">
-        <v>3.74</v>
-      </c>
-      <c r="AD8">
-        <v>1.19</v>
-      </c>
-      <c r="AE8">
-        <v>1.03</v>
-      </c>
       <c r="AF8">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="Q9">
+        <v>3.22</v>
+      </c>
+      <c r="R9">
+        <v>2.17</v>
+      </c>
+      <c r="S9">
+        <v>1.3</v>
+      </c>
+      <c r="T9">
         <v>3.2</v>
       </c>
-      <c r="R9">
+      <c r="U9">
+        <v>2.45</v>
+      </c>
+      <c r="V9">
+        <v>1.49</v>
+      </c>
+      <c r="W9">
+        <v>1.11</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
+        <v>1.17</v>
+      </c>
+      <c r="Z9">
+        <v>4</v>
+      </c>
+      <c r="AA9">
+        <v>1.7</v>
+      </c>
+      <c r="AB9">
         <v>2.1</v>
       </c>
-      <c r="S9">
+      <c r="AC9">
+        <v>2.77</v>
+      </c>
+      <c r="AD9">
         <v>1.37</v>
       </c>
-      <c r="T9">
-        <v>2.98</v>
-      </c>
-      <c r="U9">
-        <v>2.86</v>
-      </c>
-      <c r="V9">
-        <v>1.37</v>
-      </c>
-      <c r="W9">
-        <v>1.05</v>
-      </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
-      <c r="Y9">
+      <c r="AE9">
+        <v>1.11</v>
+      </c>
+      <c r="AF9">
+        <v>1.55</v>
+      </c>
+      <c r="AG9">
+        <v>2.25</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.26</v>
       </c>
-      <c r="Z9">
-        <v>3.43</v>
-      </c>
-      <c r="AA9">
-        <v>1.97</v>
-      </c>
-      <c r="AB9">
-        <v>1.79</v>
-      </c>
-      <c r="AC9">
-        <v>3.14</v>
-      </c>
-      <c r="AD9">
-        <v>1.27</v>
-      </c>
-      <c r="AE9">
-        <v>1.07</v>
-      </c>
-      <c r="AF9">
-        <v>1.7</v>
-      </c>
-      <c r="AG9">
-        <v>2</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.28</v>
-      </c>
       <c r="AK9">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.32</v>
+        <v>1.49</v>
       </c>
       <c r="O10">
-        <v>3.38</v>
+        <v>3.98</v>
       </c>
       <c r="P10">
-        <v>2.55</v>
+        <v>5.47</v>
       </c>
       <c r="Q10">
-        <v>2.93</v>
+        <v>1.99</v>
       </c>
       <c r="R10">
         <v>2.28</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
+        <v>1.18</v>
+      </c>
+      <c r="Z10">
+        <v>4.01</v>
+      </c>
+      <c r="AA10">
+        <v>1.82</v>
+      </c>
+      <c r="AB10">
+        <v>1.94</v>
+      </c>
+      <c r="AC10">
+        <v>2.66</v>
+      </c>
+      <c r="AD10">
+        <v>1.41</v>
+      </c>
+      <c r="AE10">
+        <v>1.11</v>
+      </c>
+      <c r="AF10">
+        <v>1.71</v>
+      </c>
+      <c r="AG10">
+        <v>2</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.2</v>
       </c>
-      <c r="Z10">
-        <v>3.72</v>
-      </c>
-      <c r="AA10">
-        <v>1.74</v>
-      </c>
-      <c r="AB10">
-        <v>2.02</v>
-      </c>
-      <c r="AC10">
-        <v>2.99</v>
-      </c>
-      <c r="AD10">
-        <v>1.32</v>
-      </c>
-      <c r="AE10">
-        <v>1.08</v>
-      </c>
-      <c r="AF10">
-        <v>1.61</v>
-      </c>
-      <c r="AG10">
-        <v>2.12</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.44</v>
-      </c>
       <c r="AK10">
-        <v>1.5</v>
+        <v>2.21</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P11">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="Q11">
-        <v>3.22</v>
+        <v>2.93</v>
       </c>
       <c r="R11">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="V11">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="AA11">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB11">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC11">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="AD11">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE11">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AG11">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AK11">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="O40">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="P40">
-        <v>3.94</v>
+        <v>4.79</v>
       </c>
       <c r="Q40">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="R40">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="U40">
         <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W40">
         <v>1.13</v>
@@ -6862,31 +6862,31 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z40">
-        <v>3.9</v>
+        <v>4.18</v>
       </c>
       <c r="AA40">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB40">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC40">
         <v>2.56</v>
       </c>
       <c r="AD40">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
         <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK40">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.62</v>
+        <v>1.74</v>
       </c>
       <c r="O41">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>1.88</v>
+        <v>3.94</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="R41">
         <v>2.3</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T41">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U41">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AA41">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB41">
         <v>2.06</v>
       </c>
       <c r="AC41">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD41">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK41">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,61 +7155,61 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.55</v>
+        <v>3.62</v>
       </c>
       <c r="O42">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="P42">
-        <v>4.79</v>
+        <v>1.88</v>
       </c>
       <c r="Q42">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="R42">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
         <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V42">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z42">
-        <v>4.18</v>
+        <v>3.82</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB42">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC42">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD42">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG42">
         <v>2.1</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>2.14</v>
+        <v>1.19</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,77 +7644,77 @@
         </is>
       </c>
       <c r="N45">
+        <v>2.09</v>
+      </c>
+      <c r="O45">
+        <v>3.54</v>
+      </c>
+      <c r="P45">
+        <v>3.15</v>
+      </c>
+      <c r="Q45">
+        <v>2.75</v>
+      </c>
+      <c r="R45">
         <v>2.19</v>
       </c>
-      <c r="O45">
-        <v>3.62</v>
-      </c>
-      <c r="P45">
-        <v>2.88</v>
-      </c>
-      <c r="Q45">
-        <v>2.43</v>
-      </c>
-      <c r="R45">
-        <v>2.21</v>
-      </c>
       <c r="S45">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T45">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U45">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="V45">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W45">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z45">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA45">
         <v>1.83</v>
       </c>
       <c r="AB45">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AC45">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="AD45">
+        <v>1.43</v>
+      </c>
+      <c r="AE45">
+        <v>1.13</v>
+      </c>
+      <c r="AF45">
+        <v>1.55</v>
+      </c>
+      <c r="AG45">
+        <v>2.25</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
         <v>1.33</v>
-      </c>
-      <c r="AE45">
-        <v>1.12</v>
-      </c>
-      <c r="AF45">
-        <v>1.64</v>
-      </c>
-      <c r="AG45">
-        <v>2.13</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.27</v>
       </c>
       <c r="AK45">
         <v>1.65</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.63</v>
+        <v>2.19</v>
       </c>
       <c r="O46">
-        <v>4.25</v>
+        <v>3.62</v>
       </c>
       <c r="P46">
-        <v>4.34</v>
+        <v>2.88</v>
       </c>
       <c r="Q46">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="R46">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S46">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T46">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U46">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="V46">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AA46">
+        <v>1.83</v>
+      </c>
+      <c r="AB46">
+        <v>1.93</v>
+      </c>
+      <c r="AC46">
+        <v>2.83</v>
+      </c>
+      <c r="AD46">
+        <v>1.33</v>
+      </c>
+      <c r="AE46">
+        <v>1.12</v>
+      </c>
+      <c r="AF46">
+        <v>1.64</v>
+      </c>
+      <c r="AG46">
+        <v>2.13</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>1.27</v>
+      </c>
+      <c r="AK46">
         <v>1.65</v>
-      </c>
-      <c r="AB46">
-        <v>2.06</v>
-      </c>
-      <c r="AC46">
-        <v>2.7</v>
-      </c>
-      <c r="AD46">
-        <v>1.36</v>
-      </c>
-      <c r="AE46">
-        <v>1.11</v>
-      </c>
-      <c r="AF46">
-        <v>1.67</v>
-      </c>
-      <c r="AG46">
-        <v>2.1</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.19</v>
-      </c>
-      <c r="AK46">
-        <v>2.03</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.09</v>
+        <v>2.83</v>
       </c>
       <c r="O48">
-        <v>3.54</v>
+        <v>2.91</v>
       </c>
       <c r="P48">
-        <v>3.15</v>
+        <v>2.57</v>
       </c>
       <c r="Q48">
+        <v>3.24</v>
+      </c>
+      <c r="R48">
+        <v>2.25</v>
+      </c>
+      <c r="S48">
+        <v>1.37</v>
+      </c>
+      <c r="T48">
+        <v>2.7</v>
+      </c>
+      <c r="U48">
         <v>2.75</v>
       </c>
-      <c r="R48">
-        <v>2.19</v>
-      </c>
-      <c r="S48">
-        <v>1.26</v>
-      </c>
-      <c r="T48">
-        <v>3.4</v>
-      </c>
-      <c r="U48">
-        <v>2.32</v>
-      </c>
       <c r="V48">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>4.33</v>
+        <v>4.07</v>
       </c>
       <c r="AA48">
+        <v>2.03</v>
+      </c>
+      <c r="AB48">
         <v>1.83</v>
       </c>
-      <c r="AB48">
-        <v>2.03</v>
-      </c>
       <c r="AC48">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="AD48">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE48">
         <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK48">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="O50">
-        <v>2.91</v>
+        <v>3.74</v>
       </c>
       <c r="P50">
-        <v>2.57</v>
+        <v>2.13</v>
       </c>
       <c r="Q50">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V50">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
         <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="AA50">
-        <v>2.03</v>
+        <v>1.69</v>
       </c>
       <c r="AB50">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AC50">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD50">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
         <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG50">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AK50">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.92</v>
+        <v>1.48</v>
       </c>
       <c r="O51">
-        <v>3.74</v>
+        <v>4.6</v>
       </c>
       <c r="P51">
-        <v>2.13</v>
+        <v>5.36</v>
       </c>
       <c r="Q51">
-        <v>3.26</v>
+        <v>1.93</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="U51">
-        <v>2.45</v>
+        <v>2.24</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W51">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA51">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="AB51">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AC51">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF51">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.65</v>
+        <v>1.16</v>
       </c>
       <c r="AK51">
-        <v>1.33</v>
+        <v>2.45</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
+        <v>1.63</v>
+      </c>
+      <c r="O52">
+        <v>4.25</v>
+      </c>
+      <c r="P52">
+        <v>4.34</v>
+      </c>
+      <c r="Q52">
+        <v>2.2</v>
+      </c>
+      <c r="R52">
+        <v>2.22</v>
+      </c>
+      <c r="S52">
+        <v>1.26</v>
+      </c>
+      <c r="T52">
+        <v>3.2</v>
+      </c>
+      <c r="U52">
+        <v>2.42</v>
+      </c>
+      <c r="V52">
         <v>1.48</v>
       </c>
-      <c r="O52">
-        <v>4.6</v>
-      </c>
-      <c r="P52">
-        <v>5.36</v>
-      </c>
-      <c r="Q52">
-        <v>1.93</v>
-      </c>
-      <c r="R52">
-        <v>2.45</v>
-      </c>
-      <c r="S52">
-        <v>1.25</v>
-      </c>
-      <c r="T52">
-        <v>3.54</v>
-      </c>
-      <c r="U52">
-        <v>2.24</v>
-      </c>
-      <c r="V52">
-        <v>1.57</v>
-      </c>
       <c r="W52">
+        <v>1.08</v>
+      </c>
+      <c r="X52">
+        <v>1.02</v>
+      </c>
+      <c r="Y52">
+        <v>1.26</v>
+      </c>
+      <c r="Z52">
+        <v>3.82</v>
+      </c>
+      <c r="AA52">
+        <v>1.65</v>
+      </c>
+      <c r="AB52">
+        <v>2.06</v>
+      </c>
+      <c r="AC52">
+        <v>2.7</v>
+      </c>
+      <c r="AD52">
+        <v>1.36</v>
+      </c>
+      <c r="AE52">
         <v>1.11</v>
       </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.18</v>
-      </c>
-      <c r="Z52">
-        <v>4.25</v>
-      </c>
-      <c r="AA52">
-        <v>1.58</v>
-      </c>
-      <c r="AB52">
-        <v>2.19</v>
-      </c>
-      <c r="AC52">
-        <v>2.36</v>
-      </c>
-      <c r="AD52">
-        <v>1.47</v>
-      </c>
-      <c r="AE52">
-        <v>1.15</v>
-      </c>
       <c r="AF52">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG52">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="O60">
-        <v>3.48</v>
+        <v>4.15</v>
       </c>
       <c r="P60">
-        <v>3.94</v>
+        <v>5.21</v>
       </c>
       <c r="Q60">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="R60">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S60">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T60">
-        <v>2.9</v>
+        <v>3.26</v>
       </c>
       <c r="U60">
-        <v>2.71</v>
+        <v>2.31</v>
       </c>
       <c r="V60">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="W60">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X60">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z60">
-        <v>3.05</v>
+        <v>4.21</v>
       </c>
       <c r="AA60">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="AB60">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="AC60">
-        <v>3.44</v>
+        <v>2.53</v>
       </c>
       <c r="AD60">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AE60">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF60">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AG60">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK60">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.57</v>
+        <v>2.58</v>
       </c>
       <c r="O61">
-        <v>4.15</v>
+        <v>3.48</v>
       </c>
       <c r="P61">
-        <v>5.21</v>
+        <v>2.5</v>
       </c>
       <c r="Q61">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="R61">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S61">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T61">
-        <v>3.26</v>
+        <v>3.08</v>
       </c>
       <c r="U61">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="V61">
         <v>1.5</v>
       </c>
       <c r="W61">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X61">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
         <v>1.22</v>
       </c>
       <c r="Z61">
-        <v>4.21</v>
+        <v>4.05</v>
       </c>
       <c r="AA61">
         <v>1.65</v>
       </c>
       <c r="AB61">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC61">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="AD61">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE61">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF61">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AG61">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.58</v>
+        <v>1.89</v>
       </c>
       <c r="O62">
         <v>3.48</v>
       </c>
       <c r="P62">
-        <v>2.5</v>
+        <v>3.94</v>
       </c>
       <c r="Q62">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="R62">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="S62">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T62">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="U62">
-        <v>2.4</v>
+        <v>2.71</v>
       </c>
       <c r="V62">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W62">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z62">
-        <v>4.05</v>
+        <v>3.05</v>
       </c>
       <c r="AA62">
-        <v>1.65</v>
+        <v>2.01</v>
       </c>
       <c r="AB62">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AC62">
-        <v>2.52</v>
+        <v>3.44</v>
       </c>
       <c r="AD62">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AE62">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF62">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AG62">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK62">
-        <v>1.46</v>
+        <v>1.91</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -18737,55 +18737,55 @@
         <v>0</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G115">
@@ -19063,55 +19063,55 @@
         <v>0</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="O135">
-        <v>3.54</v>
+        <v>3.72</v>
       </c>
       <c r="P135">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22353,10 +22353,10 @@
         <v>0</v>
       </c>
       <c r="AA135">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB135">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="O136">
-        <v>3.72</v>
+        <v>3.54</v>
       </c>
       <c r="P136">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC136">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="O7">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q7">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="R7">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T7">
-        <v>2.42</v>
+        <v>2.98</v>
       </c>
       <c r="U7">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="V7">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
+        <v>1.05</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>1.26</v>
+      </c>
+      <c r="Z7">
+        <v>3.43</v>
+      </c>
+      <c r="AA7">
+        <v>1.97</v>
+      </c>
+      <c r="AB7">
+        <v>1.79</v>
+      </c>
+      <c r="AC7">
+        <v>3.14</v>
+      </c>
+      <c r="AD7">
+        <v>1.27</v>
+      </c>
+      <c r="AE7">
         <v>1.07</v>
       </c>
-      <c r="X7">
-        <v>1.04</v>
-      </c>
-      <c r="Y7">
-        <v>1.35</v>
-      </c>
-      <c r="Z7">
-        <v>2.74</v>
-      </c>
-      <c r="AA7">
-        <v>2.19</v>
-      </c>
-      <c r="AB7">
-        <v>1.61</v>
-      </c>
-      <c r="AC7">
-        <v>3.74</v>
-      </c>
-      <c r="AD7">
-        <v>1.19</v>
-      </c>
-      <c r="AE7">
-        <v>1.03</v>
-      </c>
       <c r="AF7">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="Q8">
+        <v>3.22</v>
+      </c>
+      <c r="R8">
+        <v>2.17</v>
+      </c>
+      <c r="S8">
+        <v>1.3</v>
+      </c>
+      <c r="T8">
         <v>3.2</v>
       </c>
-      <c r="R8">
+      <c r="U8">
+        <v>2.45</v>
+      </c>
+      <c r="V8">
+        <v>1.49</v>
+      </c>
+      <c r="W8">
+        <v>1.11</v>
+      </c>
+      <c r="X8">
+        <v>1.03</v>
+      </c>
+      <c r="Y8">
+        <v>1.17</v>
+      </c>
+      <c r="Z8">
+        <v>4</v>
+      </c>
+      <c r="AA8">
+        <v>1.7</v>
+      </c>
+      <c r="AB8">
         <v>2.1</v>
       </c>
-      <c r="S8">
+      <c r="AC8">
+        <v>2.77</v>
+      </c>
+      <c r="AD8">
         <v>1.37</v>
       </c>
-      <c r="T8">
-        <v>2.98</v>
-      </c>
-      <c r="U8">
-        <v>2.86</v>
-      </c>
-      <c r="V8">
-        <v>1.37</v>
-      </c>
-      <c r="W8">
-        <v>1.05</v>
-      </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
-      <c r="Y8">
+      <c r="AE8">
+        <v>1.11</v>
+      </c>
+      <c r="AF8">
+        <v>1.55</v>
+      </c>
+      <c r="AG8">
+        <v>2.25</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.26</v>
       </c>
-      <c r="Z8">
-        <v>3.43</v>
-      </c>
-      <c r="AA8">
-        <v>1.97</v>
-      </c>
-      <c r="AB8">
-        <v>1.79</v>
-      </c>
-      <c r="AC8">
-        <v>3.14</v>
-      </c>
-      <c r="AD8">
-        <v>1.27</v>
-      </c>
-      <c r="AE8">
-        <v>1.07</v>
-      </c>
-      <c r="AF8">
-        <v>1.7</v>
-      </c>
-      <c r="AG8">
-        <v>2</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.28</v>
-      </c>
       <c r="AK8">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="O9">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="P9">
-        <v>2.47</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
+        <v>3.13</v>
+      </c>
+      <c r="R9">
+        <v>1.98</v>
+      </c>
+      <c r="S9">
+        <v>1.45</v>
+      </c>
+      <c r="T9">
+        <v>2.42</v>
+      </c>
+      <c r="U9">
         <v>3.22</v>
       </c>
-      <c r="R9">
-        <v>2.17</v>
-      </c>
-      <c r="S9">
-        <v>1.3</v>
-      </c>
-      <c r="T9">
-        <v>3.2</v>
-      </c>
-      <c r="U9">
-        <v>2.45</v>
-      </c>
       <c r="V9">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
+        <v>1.04</v>
+      </c>
+      <c r="Y9">
+        <v>1.35</v>
+      </c>
+      <c r="Z9">
+        <v>2.74</v>
+      </c>
+      <c r="AA9">
+        <v>2.19</v>
+      </c>
+      <c r="AB9">
+        <v>1.61</v>
+      </c>
+      <c r="AC9">
+        <v>3.74</v>
+      </c>
+      <c r="AD9">
+        <v>1.19</v>
+      </c>
+      <c r="AE9">
         <v>1.03</v>
       </c>
-      <c r="Y9">
-        <v>1.17</v>
-      </c>
-      <c r="Z9">
-        <v>4</v>
-      </c>
-      <c r="AA9">
-        <v>1.7</v>
-      </c>
-      <c r="AB9">
-        <v>2.1</v>
-      </c>
-      <c r="AC9">
-        <v>2.77</v>
-      </c>
-      <c r="AD9">
-        <v>1.37</v>
-      </c>
-      <c r="AE9">
-        <v>1.11</v>
-      </c>
       <c r="AF9">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AG9">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.49</v>
+        <v>2.32</v>
       </c>
       <c r="O10">
-        <v>3.98</v>
+        <v>3.38</v>
       </c>
       <c r="P10">
-        <v>5.47</v>
+        <v>2.55</v>
       </c>
       <c r="Q10">
-        <v>1.99</v>
+        <v>2.93</v>
       </c>
       <c r="R10">
         <v>2.28</v>
       </c>
       <c r="S10">
+        <v>1.33</v>
+      </c>
+      <c r="T10">
+        <v>3.18</v>
+      </c>
+      <c r="U10">
+        <v>2.67</v>
+      </c>
+      <c r="V10">
+        <v>1.44</v>
+      </c>
+      <c r="W10">
+        <v>1.07</v>
+      </c>
+      <c r="X10">
+        <v>1.04</v>
+      </c>
+      <c r="Y10">
+        <v>1.2</v>
+      </c>
+      <c r="Z10">
+        <v>3.72</v>
+      </c>
+      <c r="AA10">
+        <v>1.74</v>
+      </c>
+      <c r="AB10">
+        <v>2.02</v>
+      </c>
+      <c r="AC10">
+        <v>2.99</v>
+      </c>
+      <c r="AD10">
         <v>1.32</v>
       </c>
-      <c r="T10">
-        <v>3.2</v>
-      </c>
-      <c r="U10">
-        <v>2.57</v>
-      </c>
-      <c r="V10">
-        <v>1.48</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.18</v>
-      </c>
-      <c r="Z10">
-        <v>4.01</v>
-      </c>
-      <c r="AA10">
-        <v>1.82</v>
-      </c>
-      <c r="AB10">
-        <v>1.94</v>
-      </c>
-      <c r="AC10">
-        <v>2.66</v>
-      </c>
-      <c r="AD10">
-        <v>1.41</v>
-      </c>
       <c r="AE10">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK10">
-        <v>2.21</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.32</v>
+        <v>1.49</v>
       </c>
       <c r="O11">
-        <v>3.38</v>
+        <v>3.98</v>
       </c>
       <c r="P11">
-        <v>2.55</v>
+        <v>5.47</v>
       </c>
       <c r="Q11">
-        <v>2.93</v>
+        <v>1.99</v>
       </c>
       <c r="R11">
         <v>2.28</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T11">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
+        <v>1.18</v>
+      </c>
+      <c r="Z11">
+        <v>4.01</v>
+      </c>
+      <c r="AA11">
+        <v>1.82</v>
+      </c>
+      <c r="AB11">
+        <v>1.94</v>
+      </c>
+      <c r="AC11">
+        <v>2.66</v>
+      </c>
+      <c r="AD11">
+        <v>1.41</v>
+      </c>
+      <c r="AE11">
+        <v>1.11</v>
+      </c>
+      <c r="AF11">
+        <v>1.71</v>
+      </c>
+      <c r="AG11">
+        <v>2</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
         <v>1.2</v>
       </c>
-      <c r="Z11">
-        <v>3.72</v>
-      </c>
-      <c r="AA11">
-        <v>1.74</v>
-      </c>
-      <c r="AB11">
-        <v>2.02</v>
-      </c>
-      <c r="AC11">
-        <v>2.99</v>
-      </c>
-      <c r="AD11">
-        <v>1.32</v>
-      </c>
-      <c r="AE11">
-        <v>1.08</v>
-      </c>
-      <c r="AF11">
-        <v>1.61</v>
-      </c>
-      <c r="AG11">
-        <v>2.12</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.44</v>
-      </c>
       <c r="AK11">
-        <v>1.5</v>
+        <v>2.21</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,68 +7477,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="O44">
-        <v>3.26</v>
+        <v>3.68</v>
       </c>
       <c r="P44">
-        <v>3.54</v>
+        <v>4.3</v>
       </c>
       <c r="Q44">
-        <v>2.69</v>
+        <v>2.28</v>
       </c>
       <c r="R44">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="S44">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T44">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="U44">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W44">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AA44">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AB44">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AC44">
-        <v>3.76</v>
+        <v>3.01</v>
       </c>
       <c r="AD44">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AE44">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF44">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AG44">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK44">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.09</v>
+        <v>1.48</v>
       </c>
       <c r="O45">
+        <v>4.6</v>
+      </c>
+      <c r="P45">
+        <v>5.36</v>
+      </c>
+      <c r="Q45">
+        <v>1.93</v>
+      </c>
+      <c r="R45">
+        <v>2.45</v>
+      </c>
+      <c r="S45">
+        <v>1.25</v>
+      </c>
+      <c r="T45">
         <v>3.54</v>
       </c>
-      <c r="P45">
-        <v>3.15</v>
-      </c>
-      <c r="Q45">
-        <v>2.75</v>
-      </c>
-      <c r="R45">
+      <c r="U45">
+        <v>2.24</v>
+      </c>
+      <c r="V45">
+        <v>1.57</v>
+      </c>
+      <c r="W45">
+        <v>1.11</v>
+      </c>
+      <c r="X45">
+        <v>1.01</v>
+      </c>
+      <c r="Y45">
+        <v>1.18</v>
+      </c>
+      <c r="Z45">
+        <v>4.25</v>
+      </c>
+      <c r="AA45">
+        <v>1.58</v>
+      </c>
+      <c r="AB45">
         <v>2.19</v>
       </c>
-      <c r="S45">
-        <v>1.26</v>
-      </c>
-      <c r="T45">
-        <v>3.4</v>
-      </c>
-      <c r="U45">
-        <v>2.32</v>
-      </c>
-      <c r="V45">
-        <v>1.49</v>
-      </c>
-      <c r="W45">
-        <v>1.1</v>
-      </c>
-      <c r="X45">
-        <v>1.02</v>
-      </c>
-      <c r="Y45">
-        <v>1.2</v>
-      </c>
-      <c r="Z45">
-        <v>4.33</v>
-      </c>
-      <c r="AA45">
-        <v>1.83</v>
-      </c>
-      <c r="AB45">
-        <v>2.03</v>
-      </c>
       <c r="AC45">
-        <v>2.77</v>
+        <v>2.36</v>
       </c>
       <c r="AD45">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE45">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF45">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG45">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK45">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G46">
@@ -7803,69 +7803,69 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="O46">
-        <v>3.62</v>
+        <v>3.26</v>
       </c>
       <c r="P46">
-        <v>2.88</v>
+        <v>3.54</v>
       </c>
       <c r="Q46">
-        <v>2.43</v>
+        <v>2.69</v>
       </c>
       <c r="R46">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="S46">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="T46">
-        <v>3.12</v>
+        <v>2.71</v>
       </c>
       <c r="U46">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="V46">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W46">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="Z46">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AA46">
+        <v>2.12</v>
+      </c>
+      <c r="AB46">
+        <v>1.61</v>
+      </c>
+      <c r="AC46">
+        <v>3.76</v>
+      </c>
+      <c r="AD46">
+        <v>1.19</v>
+      </c>
+      <c r="AE46">
+        <v>1.03</v>
+      </c>
+      <c r="AF46">
+        <v>1.87</v>
+      </c>
+      <c r="AG46">
         <v>1.83</v>
       </c>
-      <c r="AB46">
-        <v>1.93</v>
-      </c>
-      <c r="AC46">
-        <v>2.83</v>
-      </c>
-      <c r="AD46">
-        <v>1.33</v>
-      </c>
-      <c r="AE46">
-        <v>1.12</v>
-      </c>
-      <c r="AF46">
-        <v>1.64</v>
-      </c>
-      <c r="AG46">
-        <v>2.13</v>
-      </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.73</v>
+        <v>1.63</v>
       </c>
       <c r="O47">
-        <v>3.02</v>
+        <v>4.25</v>
       </c>
       <c r="P47">
-        <v>2.58</v>
+        <v>4.34</v>
       </c>
       <c r="Q47">
-        <v>3.18</v>
+        <v>2.2</v>
       </c>
       <c r="R47">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S47">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="T47">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U47">
-        <v>2.96</v>
+        <v>2.42</v>
       </c>
       <c r="V47">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z47">
-        <v>3.2</v>
+        <v>3.82</v>
       </c>
       <c r="AA47">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AB47">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AC47">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="AD47">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE47">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG47">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AK47">
-        <v>1.44</v>
+        <v>2.03</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.83</v>
+        <v>2.09</v>
       </c>
       <c r="O48">
-        <v>2.91</v>
+        <v>3.54</v>
       </c>
       <c r="P48">
-        <v>2.57</v>
+        <v>3.15</v>
       </c>
       <c r="Q48">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="R48">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S48">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="T48">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="U48">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="V48">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W48">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>4.07</v>
+        <v>4.33</v>
       </c>
       <c r="AA48">
+        <v>1.83</v>
+      </c>
+      <c r="AB48">
         <v>2.03</v>
       </c>
-      <c r="AB48">
-        <v>1.83</v>
-      </c>
       <c r="AC48">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="AD48">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE48">
         <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.74</v>
+        <v>2.73</v>
       </c>
       <c r="O49">
-        <v>3.68</v>
+        <v>3.02</v>
       </c>
       <c r="P49">
-        <v>4.3</v>
+        <v>2.58</v>
       </c>
       <c r="Q49">
-        <v>2.28</v>
+        <v>3.18</v>
       </c>
       <c r="R49">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="S49">
+        <v>1.38</v>
+      </c>
+      <c r="T49">
+        <v>2.75</v>
+      </c>
+      <c r="U49">
+        <v>2.96</v>
+      </c>
+      <c r="V49">
+        <v>1.4</v>
+      </c>
+      <c r="W49">
+        <v>1.06</v>
+      </c>
+      <c r="X49">
+        <v>1.03</v>
+      </c>
+      <c r="Y49">
         <v>1.3</v>
       </c>
-      <c r="T49">
-        <v>3.1</v>
-      </c>
-      <c r="U49">
-        <v>2.5</v>
-      </c>
-      <c r="V49">
+      <c r="Z49">
+        <v>3.2</v>
+      </c>
+      <c r="AA49">
+        <v>1.94</v>
+      </c>
+      <c r="AB49">
+        <v>1.8</v>
+      </c>
+      <c r="AC49">
+        <v>3.28</v>
+      </c>
+      <c r="AD49">
+        <v>1.25</v>
+      </c>
+      <c r="AE49">
+        <v>1.05</v>
+      </c>
+      <c r="AF49">
+        <v>1.73</v>
+      </c>
+      <c r="AG49">
+        <v>1.95</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.41</v>
+      </c>
+      <c r="AK49">
         <v>1.44</v>
-      </c>
-      <c r="W49">
-        <v>1.07</v>
-      </c>
-      <c r="X49">
-        <v>1</v>
-      </c>
-      <c r="Y49">
-        <v>1.22</v>
-      </c>
-      <c r="Z49">
-        <v>3.5</v>
-      </c>
-      <c r="AA49">
-        <v>1.91</v>
-      </c>
-      <c r="AB49">
-        <v>1.86</v>
-      </c>
-      <c r="AC49">
-        <v>3.01</v>
-      </c>
-      <c r="AD49">
-        <v>1.32</v>
-      </c>
-      <c r="AE49">
-        <v>1.1</v>
-      </c>
-      <c r="AF49">
-        <v>1.67</v>
-      </c>
-      <c r="AG49">
-        <v>2.05</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.23</v>
-      </c>
-      <c r="AK49">
-        <v>1.91</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O50">
-        <v>3.74</v>
+        <v>2.91</v>
       </c>
       <c r="P50">
-        <v>2.13</v>
+        <v>2.57</v>
       </c>
       <c r="Q50">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="R50">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="U50">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V50">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W50">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
         <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>4.2</v>
+        <v>4.07</v>
       </c>
       <c r="AA50">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="AB50">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AC50">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE50">
         <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AK50">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.48</v>
+        <v>2.19</v>
       </c>
       <c r="O51">
-        <v>4.6</v>
+        <v>3.62</v>
       </c>
       <c r="P51">
-        <v>5.36</v>
+        <v>2.88</v>
       </c>
       <c r="Q51">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="R51">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T51">
-        <v>3.54</v>
+        <v>3.12</v>
       </c>
       <c r="U51">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="V51">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="AC51">
-        <v>2.36</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
+        <v>1.64</v>
+      </c>
+      <c r="AG51">
+        <v>2.13</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.27</v>
+      </c>
+      <c r="AK51">
         <v>1.65</v>
-      </c>
-      <c r="AG51">
-        <v>2.02</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.16</v>
-      </c>
-      <c r="AK51">
-        <v>2.45</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,49 +8785,49 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.63</v>
+        <v>2.92</v>
       </c>
       <c r="O52">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="P52">
-        <v>4.34</v>
+        <v>2.13</v>
       </c>
       <c r="Q52">
+        <v>3.26</v>
+      </c>
+      <c r="R52">
         <v>2.2</v>
       </c>
-      <c r="R52">
-        <v>2.22</v>
-      </c>
       <c r="S52">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="V52">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB52">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AC52">
         <v>2.7</v>
@@ -8836,13 +8836,13 @@
         <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG52">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="AK52">
-        <v>2.03</v>
+        <v>1.33</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O114">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P114">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q114">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R114">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S114">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T114">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U114">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="V114">
         <v>1.4</v>
       </c>
       <c r="W114">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X114">
         <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z114">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="AA114">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AB114">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AC114">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AD114">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE114">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF114">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG114">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK114">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,80 +19054,80 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q115">
-        <v>2.75</v>
+        <v>3.48</v>
       </c>
       <c r="R115">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="S115">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T115">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="U115">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V115">
         <v>1.4</v>
       </c>
       <c r="W115">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X115">
         <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z115">
-        <v>3.86</v>
+        <v>3.2</v>
       </c>
       <c r="AA115">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AB115">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AC115">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AD115">
+        <v>1.31</v>
+      </c>
+      <c r="AE115">
+        <v>1.06</v>
+      </c>
+      <c r="AF115">
+        <v>1.69</v>
+      </c>
+      <c r="AG115">
+        <v>2.03</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ115">
+        <v>1.5</v>
+      </c>
+      <c r="AK115">
         <v>1.33</v>
-      </c>
-      <c r="AE115">
-        <v>1.09</v>
-      </c>
-      <c r="AF115">
-        <v>1.65</v>
-      </c>
-      <c r="AG115">
-        <v>2.16</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ115">
-        <v>1.25</v>
-      </c>
-      <c r="AK115">
-        <v>1.62</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,65 +19217,65 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="O116">
+        <v>3.5</v>
+      </c>
+      <c r="P116">
+        <v>2.04</v>
+      </c>
+      <c r="Q116">
+        <v>4.03</v>
+      </c>
+      <c r="R116">
+        <v>2.1</v>
+      </c>
+      <c r="S116">
+        <v>1.33</v>
+      </c>
+      <c r="T116">
         <v>3.2</v>
       </c>
-      <c r="P116">
-        <v>2.41</v>
-      </c>
-      <c r="Q116">
-        <v>3.3</v>
-      </c>
-      <c r="R116">
+      <c r="U116">
+        <v>2.78</v>
+      </c>
+      <c r="V116">
+        <v>1.41</v>
+      </c>
+      <c r="W116">
+        <v>1.1</v>
+      </c>
+      <c r="X116">
+        <v>1.01</v>
+      </c>
+      <c r="Y116">
+        <v>1.26</v>
+      </c>
+      <c r="Z116">
+        <v>3.42</v>
+      </c>
+      <c r="AA116">
+        <v>1.82</v>
+      </c>
+      <c r="AB116">
+        <v>1.85</v>
+      </c>
+      <c r="AC116">
+        <v>2.97</v>
+      </c>
+      <c r="AD116">
+        <v>1.3</v>
+      </c>
+      <c r="AE116">
+        <v>1.08</v>
+      </c>
+      <c r="AF116">
+        <v>1.68</v>
+      </c>
+      <c r="AG116">
         <v>2</v>
       </c>
-      <c r="S116">
-        <v>1.45</v>
-      </c>
-      <c r="T116">
-        <v>2.45</v>
-      </c>
-      <c r="U116">
-        <v>3.12</v>
-      </c>
-      <c r="V116">
-        <v>1.28</v>
-      </c>
-      <c r="W116">
-        <v>1.01</v>
-      </c>
-      <c r="X116">
-        <v>1.03</v>
-      </c>
-      <c r="Y116">
-        <v>1.38</v>
-      </c>
-      <c r="Z116">
-        <v>2.74</v>
-      </c>
-      <c r="AA116">
-        <v>2.25</v>
-      </c>
-      <c r="AB116">
-        <v>1.59</v>
-      </c>
-      <c r="AC116">
-        <v>3.96</v>
-      </c>
-      <c r="AD116">
-        <v>1.17</v>
-      </c>
-      <c r="AE116">
-        <v>1.02</v>
-      </c>
-      <c r="AF116">
-        <v>1.87</v>
-      </c>
-      <c r="AG116">
-        <v>1.82</v>
-      </c>
       <c r="AH116" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK116">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,16 +19380,16 @@
         </is>
       </c>
       <c r="N117">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="O117">
         <v>3.2</v>
       </c>
       <c r="P117">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="Q117">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="R117">
         <v>2</v>
@@ -19398,46 +19398,46 @@
         <v>1.45</v>
       </c>
       <c r="T117">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U117">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="V117">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W117">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y117">
         <v>1.38</v>
       </c>
       <c r="Z117">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="AA117">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB117">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AC117">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="AD117">
         <v>1.17</v>
       </c>
       <c r="AE117">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF117">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG117">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK117">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="O118">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P118">
-        <v>2.47</v>
+        <v>1.96</v>
       </c>
       <c r="Q118">
-        <v>3.48</v>
+        <v>4.64</v>
       </c>
       <c r="R118">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="S118">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T118">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="U118">
         <v>2.8</v>
       </c>
       <c r="V118">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W118">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z118">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="AA118">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AB118">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AC118">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="AD118">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE118">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF118">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AG118">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AK118">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,80 +19706,80 @@
         </is>
       </c>
       <c r="N119">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O119">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P119">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="Q119">
-        <v>4.03</v>
+        <v>3.48</v>
       </c>
       <c r="R119">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S119">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T119">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="U119">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="V119">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="W119">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X119">
         <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Z119">
-        <v>3.42</v>
+        <v>2.81</v>
       </c>
       <c r="AA119">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AB119">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AC119">
-        <v>2.97</v>
+        <v>4</v>
       </c>
       <c r="AD119">
+        <v>1.17</v>
+      </c>
+      <c r="AE119">
+        <v>1.01</v>
+      </c>
+      <c r="AF119">
+        <v>1.86</v>
+      </c>
+      <c r="AG119">
+        <v>1.8</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ119">
         <v>1.3</v>
       </c>
-      <c r="AE119">
-        <v>1.08</v>
-      </c>
-      <c r="AF119">
-        <v>1.68</v>
-      </c>
-      <c r="AG119">
-        <v>2</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>1.23</v>
-      </c>
       <c r="AK119">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>3.75</v>
+        <v>2.54</v>
       </c>
       <c r="O120">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P120">
-        <v>1.96</v>
+        <v>2.37</v>
       </c>
       <c r="Q120">
-        <v>4.64</v>
+        <v>3.1</v>
       </c>
       <c r="R120">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S120">
+        <v>1.37</v>
+      </c>
+      <c r="T120">
+        <v>3</v>
+      </c>
+      <c r="U120">
+        <v>2.68</v>
+      </c>
+      <c r="V120">
         <v>1.4</v>
       </c>
-      <c r="T120">
-        <v>2.82</v>
-      </c>
-      <c r="U120">
-        <v>2.8</v>
-      </c>
-      <c r="V120">
-        <v>1.36</v>
-      </c>
       <c r="W120">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X120">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z120">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="AA120">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="AB120">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AC120">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD120">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE120">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF120">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG120">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="AK120">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -21508,28 +21508,28 @@
         <v>3.19</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y130">
         <v>1.49</v>
@@ -21538,25 +21538,25 @@
         <v>2.45</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21997,34 +21997,34 @@
         <v>2.9</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U133">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V133">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W133">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X133">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y133">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z133">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA133">
         <v>1.78</v>
@@ -22033,19 +22033,19 @@
         <v>1.97</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22160,55 +22160,55 @@
         <v>3.24</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22323,55 +22323,55 @@
         <v>3.86</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22486,34 +22486,34 @@
         <v>3.6</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA136">
         <v>1.83</v>
@@ -22522,19 +22522,19 @@
         <v>1.93</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -23790,34 +23790,34 @@
         <v>2.18</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S144">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T144">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U144">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V144">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W144">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X144">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z144">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AA144">
         <v>1.83</v>
@@ -23826,19 +23826,19 @@
         <v>1.93</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD144">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE144">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF144">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG144">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK144">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24768,55 +24768,55 @@
         <v>4.59</v>
       </c>
       <c r="Q150">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R150">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S150">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T150">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U150">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V150">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W150">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X150">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y150">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z150">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA150">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB150">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC150">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD150">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE150">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF150">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG150">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK150">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24931,34 +24931,34 @@
         <v>2.09</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S151">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T151">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U151">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V151">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W151">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X151">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y151">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z151">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA151">
         <v>1.85</v>
@@ -24967,19 +24967,19 @@
         <v>1.9</v>
       </c>
       <c r="AC151">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD151">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE151">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF151">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG151">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK151">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25257,55 +25257,55 @@
         <v>2.96</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S153">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T153">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U153">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V153">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W153">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X153">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y153">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z153">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF153">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG153">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK153">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25420,55 +25420,55 @@
         <v>2.05</v>
       </c>
       <c r="Q154">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R154">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S154">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T154">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U154">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V154">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W154">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y154">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z154">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC154">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD154">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE154">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF154">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG154">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK154">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25583,55 +25583,55 @@
         <v>2.27</v>
       </c>
       <c r="Q155">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R155">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S155">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T155">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U155">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V155">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W155">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X155">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y155">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z155">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA155">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB155">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC155">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD155">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE155">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF155">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG155">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK155">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL155">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="O9">
-        <v>2.99</v>
+        <v>3.38</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q9">
-        <v>3.13</v>
+        <v>2.93</v>
       </c>
       <c r="R9">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="S9">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>2.42</v>
+        <v>3.18</v>
       </c>
       <c r="U9">
-        <v>3.22</v>
+        <v>2.67</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
         <v>1.07</v>
@@ -1809,31 +1809,31 @@
         <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>2.74</v>
+        <v>3.72</v>
       </c>
       <c r="AA9">
-        <v>2.19</v>
+        <v>1.74</v>
       </c>
       <c r="AB9">
+        <v>2.02</v>
+      </c>
+      <c r="AC9">
+        <v>2.99</v>
+      </c>
+      <c r="AD9">
+        <v>1.32</v>
+      </c>
+      <c r="AE9">
+        <v>1.08</v>
+      </c>
+      <c r="AF9">
         <v>1.61</v>
       </c>
-      <c r="AC9">
-        <v>3.74</v>
-      </c>
-      <c r="AD9">
-        <v>1.19</v>
-      </c>
-      <c r="AE9">
-        <v>1.03</v>
-      </c>
-      <c r="AF9">
-        <v>1.84</v>
-      </c>
       <c r="AG9">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK9">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.32</v>
+        <v>1.49</v>
       </c>
       <c r="O10">
-        <v>3.38</v>
+        <v>3.98</v>
       </c>
       <c r="P10">
-        <v>2.55</v>
+        <v>5.47</v>
       </c>
       <c r="Q10">
-        <v>2.93</v>
+        <v>1.99</v>
       </c>
       <c r="R10">
         <v>2.28</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
+        <v>1.18</v>
+      </c>
+      <c r="Z10">
+        <v>4.01</v>
+      </c>
+      <c r="AA10">
+        <v>1.82</v>
+      </c>
+      <c r="AB10">
+        <v>1.94</v>
+      </c>
+      <c r="AC10">
+        <v>2.66</v>
+      </c>
+      <c r="AD10">
+        <v>1.41</v>
+      </c>
+      <c r="AE10">
+        <v>1.11</v>
+      </c>
+      <c r="AF10">
+        <v>1.71</v>
+      </c>
+      <c r="AG10">
+        <v>2</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.2</v>
       </c>
-      <c r="Z10">
-        <v>3.72</v>
-      </c>
-      <c r="AA10">
-        <v>1.74</v>
-      </c>
-      <c r="AB10">
-        <v>2.02</v>
-      </c>
-      <c r="AC10">
-        <v>2.99</v>
-      </c>
-      <c r="AD10">
-        <v>1.32</v>
-      </c>
-      <c r="AE10">
-        <v>1.08</v>
-      </c>
-      <c r="AF10">
-        <v>1.61</v>
-      </c>
-      <c r="AG10">
-        <v>2.12</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.44</v>
-      </c>
       <c r="AK10">
-        <v>1.5</v>
+        <v>2.21</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="O11">
-        <v>3.98</v>
+        <v>2.99</v>
       </c>
       <c r="P11">
-        <v>5.47</v>
+        <v>3.1</v>
       </c>
       <c r="Q11">
-        <v>1.99</v>
+        <v>3.13</v>
       </c>
       <c r="R11">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="S11">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="U11">
-        <v>2.57</v>
+        <v>3.22</v>
       </c>
       <c r="V11">
+        <v>1.35</v>
+      </c>
+      <c r="W11">
+        <v>1.07</v>
+      </c>
+      <c r="X11">
+        <v>1.04</v>
+      </c>
+      <c r="Y11">
+        <v>1.35</v>
+      </c>
+      <c r="Z11">
+        <v>2.74</v>
+      </c>
+      <c r="AA11">
+        <v>2.19</v>
+      </c>
+      <c r="AB11">
+        <v>1.61</v>
+      </c>
+      <c r="AC11">
+        <v>3.74</v>
+      </c>
+      <c r="AD11">
+        <v>1.19</v>
+      </c>
+      <c r="AE11">
+        <v>1.03</v>
+      </c>
+      <c r="AF11">
+        <v>1.84</v>
+      </c>
+      <c r="AG11">
+        <v>1.82</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.29</v>
+      </c>
+      <c r="AK11">
         <v>1.48</v>
-      </c>
-      <c r="W11">
-        <v>1.11</v>
-      </c>
-      <c r="X11">
-        <v>1.03</v>
-      </c>
-      <c r="Y11">
-        <v>1.18</v>
-      </c>
-      <c r="Z11">
-        <v>4.01</v>
-      </c>
-      <c r="AA11">
-        <v>1.82</v>
-      </c>
-      <c r="AB11">
-        <v>1.94</v>
-      </c>
-      <c r="AC11">
-        <v>2.66</v>
-      </c>
-      <c r="AD11">
-        <v>1.41</v>
-      </c>
-      <c r="AE11">
-        <v>1.11</v>
-      </c>
-      <c r="AF11">
-        <v>1.71</v>
-      </c>
-      <c r="AG11">
-        <v>2</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.2</v>
-      </c>
-      <c r="AK11">
-        <v>2.21</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="O40">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>4.79</v>
+        <v>3.94</v>
       </c>
       <c r="Q40">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="U40">
         <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
         <v>1.13</v>
@@ -6862,31 +6862,31 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>4.18</v>
+        <v>3.9</v>
       </c>
       <c r="AA40">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB40">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC40">
         <v>2.56</v>
       </c>
       <c r="AD40">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE40">
         <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK40">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.74</v>
+        <v>3.62</v>
       </c>
       <c r="O41">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P41">
-        <v>3.94</v>
+        <v>1.88</v>
       </c>
       <c r="Q41">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="R41">
         <v>2.3</v>
       </c>
       <c r="S41">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U41">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V41">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W41">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="AA41">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB41">
         <v>2.06</v>
       </c>
       <c r="AC41">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD41">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG41">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
+        <v>1.22</v>
+      </c>
+      <c r="AK41">
         <v>1.19</v>
-      </c>
-      <c r="AK41">
-        <v>2</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,61 +7155,61 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.62</v>
+        <v>1.55</v>
       </c>
       <c r="O42">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="P42">
-        <v>1.88</v>
+        <v>4.79</v>
       </c>
       <c r="Q42">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
         <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="U42">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>3.82</v>
+        <v>4.18</v>
       </c>
       <c r="AA42">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC42">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD42">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG42">
         <v>2.1</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK42">
-        <v>1.19</v>
+        <v>2.14</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.09</v>
+        <v>2.73</v>
       </c>
       <c r="O48">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
       <c r="P48">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="Q48">
+        <v>3.18</v>
+      </c>
+      <c r="R48">
+        <v>2.18</v>
+      </c>
+      <c r="S48">
+        <v>1.38</v>
+      </c>
+      <c r="T48">
         <v>2.75</v>
       </c>
-      <c r="R48">
-        <v>2.19</v>
-      </c>
-      <c r="S48">
-        <v>1.26</v>
-      </c>
-      <c r="T48">
-        <v>3.4</v>
-      </c>
       <c r="U48">
-        <v>2.32</v>
+        <v>2.96</v>
       </c>
       <c r="V48">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z48">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AA48">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AB48">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AC48">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="AD48">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AK48">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.73</v>
+        <v>2.19</v>
       </c>
       <c r="O49">
-        <v>3.02</v>
+        <v>3.62</v>
       </c>
       <c r="P49">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="Q49">
-        <v>3.18</v>
+        <v>2.43</v>
       </c>
       <c r="R49">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="S49">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="U49">
-        <v>2.96</v>
+        <v>2.47</v>
       </c>
       <c r="V49">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC49">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD49">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG49">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AK49">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="O50">
-        <v>2.91</v>
+        <v>3.74</v>
       </c>
       <c r="P50">
-        <v>2.57</v>
+        <v>2.13</v>
       </c>
       <c r="Q50">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V50">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
         <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="AA50">
-        <v>2.03</v>
+        <v>1.69</v>
       </c>
       <c r="AB50">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AC50">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD50">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
         <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG50">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AK50">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,77 +8622,77 @@
         </is>
       </c>
       <c r="N51">
+        <v>2.09</v>
+      </c>
+      <c r="O51">
+        <v>3.54</v>
+      </c>
+      <c r="P51">
+        <v>3.15</v>
+      </c>
+      <c r="Q51">
+        <v>2.75</v>
+      </c>
+      <c r="R51">
         <v>2.19</v>
       </c>
-      <c r="O51">
-        <v>3.62</v>
-      </c>
-      <c r="P51">
-        <v>2.88</v>
-      </c>
-      <c r="Q51">
-        <v>2.43</v>
-      </c>
-      <c r="R51">
-        <v>2.21</v>
-      </c>
       <c r="S51">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T51">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U51">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA51">
         <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="AD51">
+        <v>1.43</v>
+      </c>
+      <c r="AE51">
+        <v>1.13</v>
+      </c>
+      <c r="AF51">
+        <v>1.55</v>
+      </c>
+      <c r="AG51">
+        <v>2.25</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.33</v>
-      </c>
-      <c r="AE51">
-        <v>1.12</v>
-      </c>
-      <c r="AF51">
-        <v>1.64</v>
-      </c>
-      <c r="AG51">
-        <v>2.13</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.27</v>
       </c>
       <c r="AK51">
         <v>1.65</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O52">
-        <v>3.74</v>
+        <v>2.91</v>
       </c>
       <c r="P52">
-        <v>2.13</v>
+        <v>2.57</v>
       </c>
       <c r="Q52">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="U52">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W52">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
         <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.2</v>
+        <v>4.07</v>
       </c>
       <c r="AA52">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="AB52">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AC52">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD52">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE52">
         <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AK52">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="O62">
-        <v>3.48</v>
+        <v>5</v>
       </c>
       <c r="P62">
-        <v>3.94</v>
+        <v>6.4</v>
       </c>
       <c r="Q62">
-        <v>2.39</v>
+        <v>1.74</v>
       </c>
       <c r="R62">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="S62">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="T62">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="U62">
-        <v>2.71</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="W62">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="X62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="Z62">
-        <v>3.05</v>
+        <v>5.85</v>
       </c>
       <c r="AA62">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>1.79</v>
+        <v>2.87</v>
       </c>
       <c r="AC62">
-        <v>3.44</v>
+        <v>2.02</v>
       </c>
       <c r="AD62">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="AE62">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AF62">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK62">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,80 +10578,80 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="O63">
-        <v>5</v>
+        <v>3.48</v>
       </c>
       <c r="P63">
-        <v>6.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q63">
-        <v>1.74</v>
+        <v>2.39</v>
       </c>
       <c r="R63">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="S63">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="T63">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="U63">
-        <v>1.95</v>
+        <v>2.71</v>
       </c>
       <c r="V63">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="W63">
+        <v>1.06</v>
+      </c>
+      <c r="X63">
+        <v>1.03</v>
+      </c>
+      <c r="Y63">
+        <v>1.26</v>
+      </c>
+      <c r="Z63">
+        <v>3.05</v>
+      </c>
+      <c r="AA63">
+        <v>2.01</v>
+      </c>
+      <c r="AB63">
+        <v>1.79</v>
+      </c>
+      <c r="AC63">
+        <v>3.44</v>
+      </c>
+      <c r="AD63">
+        <v>1.26</v>
+      </c>
+      <c r="AE63">
+        <v>1.06</v>
+      </c>
+      <c r="AF63">
+        <v>1.82</v>
+      </c>
+      <c r="AG63">
+        <v>1.88</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
         <v>1.19</v>
       </c>
-      <c r="X63">
-        <v>1.01</v>
-      </c>
-      <c r="Y63">
-        <v>1.07</v>
-      </c>
-      <c r="Z63">
-        <v>5.85</v>
-      </c>
-      <c r="AA63">
-        <v>1.4</v>
-      </c>
-      <c r="AB63">
-        <v>2.87</v>
-      </c>
-      <c r="AC63">
-        <v>2.02</v>
-      </c>
-      <c r="AD63">
-        <v>1.77</v>
-      </c>
-      <c r="AE63">
-        <v>1.33</v>
-      </c>
-      <c r="AF63">
-        <v>1.57</v>
-      </c>
-      <c r="AG63">
-        <v>2.26</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.13</v>
-      </c>
       <c r="AK63">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,65 +18891,65 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q114">
-        <v>2.75</v>
+        <v>4.03</v>
       </c>
       <c r="R114">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S114">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T114">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="U114">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="V114">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W114">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X114">
         <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z114">
-        <v>3.86</v>
+        <v>3.42</v>
       </c>
       <c r="AA114">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB114">
+        <v>1.85</v>
+      </c>
+      <c r="AC114">
+        <v>2.97</v>
+      </c>
+      <c r="AD114">
+        <v>1.3</v>
+      </c>
+      <c r="AE114">
+        <v>1.08</v>
+      </c>
+      <c r="AF114">
+        <v>1.68</v>
+      </c>
+      <c r="AG114">
         <v>2</v>
       </c>
-      <c r="AC114">
-        <v>2.83</v>
-      </c>
-      <c r="AD114">
-        <v>1.33</v>
-      </c>
-      <c r="AE114">
-        <v>1.09</v>
-      </c>
-      <c r="AF114">
-        <v>1.65</v>
-      </c>
-      <c r="AG114">
-        <v>2.16</v>
-      </c>
       <c r="AH114" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
+        <v>1.23</v>
+      </c>
+      <c r="AK114">
         <v>1.25</v>
-      </c>
-      <c r="AK114">
-        <v>1.62</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="O115">
         <v>3.2</v>
       </c>
       <c r="P115">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="Q115">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="R115">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S115">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="T115">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="U115">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="V115">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="W115">
+        <v>1.01</v>
+      </c>
+      <c r="X115">
         <v>1.03</v>
       </c>
-      <c r="X115">
-        <v>1.01</v>
-      </c>
       <c r="Y115">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Z115">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA115">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AB115">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AC115">
-        <v>3.14</v>
+        <v>3.96</v>
       </c>
       <c r="AD115">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AE115">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF115">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AG115">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AK115">
         <v>1.33</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,65 +19217,65 @@
         </is>
       </c>
       <c r="N116">
+        <v>3.75</v>
+      </c>
+      <c r="O116">
         <v>3.3</v>
       </c>
-      <c r="O116">
-        <v>3.5</v>
-      </c>
       <c r="P116">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="Q116">
-        <v>4.03</v>
+        <v>4.64</v>
       </c>
       <c r="R116">
         <v>2.1</v>
       </c>
       <c r="S116">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T116">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U116">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V116">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W116">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z116">
-        <v>3.42</v>
+        <v>3.21</v>
       </c>
       <c r="AA116">
+        <v>2.01</v>
+      </c>
+      <c r="AB116">
+        <v>1.74</v>
+      </c>
+      <c r="AC116">
+        <v>3.6</v>
+      </c>
+      <c r="AD116">
+        <v>1.23</v>
+      </c>
+      <c r="AE116">
+        <v>1.04</v>
+      </c>
+      <c r="AF116">
+        <v>1.83</v>
+      </c>
+      <c r="AG116">
         <v>1.82</v>
       </c>
-      <c r="AB116">
-        <v>1.85</v>
-      </c>
-      <c r="AC116">
-        <v>2.97</v>
-      </c>
-      <c r="AD116">
-        <v>1.3</v>
-      </c>
-      <c r="AE116">
-        <v>1.08</v>
-      </c>
-      <c r="AF116">
-        <v>1.68</v>
-      </c>
-      <c r="AG116">
-        <v>2</v>
-      </c>
       <c r="AH116" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.23</v>
+        <v>1.76</v>
       </c>
       <c r="AK116">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,16 +19380,16 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="O117">
         <v>3.2</v>
       </c>
       <c r="P117">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="Q117">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="R117">
         <v>2</v>
@@ -19398,46 +19398,46 @@
         <v>1.45</v>
       </c>
       <c r="T117">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U117">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="V117">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W117">
+        <v>1.05</v>
+      </c>
+      <c r="X117">
         <v>1.01</v>
-      </c>
-      <c r="X117">
-        <v>1.03</v>
       </c>
       <c r="Y117">
         <v>1.38</v>
       </c>
       <c r="Z117">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="AA117">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB117">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AC117">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AD117">
         <v>1.17</v>
       </c>
       <c r="AE117">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF117">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG117">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK117">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>3.75</v>
+        <v>2.54</v>
       </c>
       <c r="O118">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P118">
-        <v>1.96</v>
+        <v>2.37</v>
       </c>
       <c r="Q118">
-        <v>4.64</v>
+        <v>3.1</v>
       </c>
       <c r="R118">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S118">
+        <v>1.37</v>
+      </c>
+      <c r="T118">
+        <v>3</v>
+      </c>
+      <c r="U118">
+        <v>2.68</v>
+      </c>
+      <c r="V118">
         <v>1.4</v>
       </c>
-      <c r="T118">
-        <v>2.82</v>
-      </c>
-      <c r="U118">
-        <v>2.8</v>
-      </c>
-      <c r="V118">
-        <v>1.36</v>
-      </c>
       <c r="W118">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X118">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z118">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="AA118">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="AB118">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AC118">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD118">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE118">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF118">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG118">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="AK118">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O119">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P119">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q119">
-        <v>3.48</v>
+        <v>2.75</v>
       </c>
       <c r="R119">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S119">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="T119">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="U119">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="V119">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="W119">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X119">
         <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="Z119">
-        <v>2.81</v>
+        <v>3.86</v>
       </c>
       <c r="AA119">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AB119">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AC119">
-        <v>4</v>
+        <v>2.83</v>
       </c>
       <c r="AD119">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AE119">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF119">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AG119">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK119">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,34 +19869,34 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="O120">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P120">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
       <c r="Q120">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="R120">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="S120">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T120">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U120">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="V120">
         <v>1.4</v>
       </c>
       <c r="W120">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X120">
         <v>1.01</v>
@@ -19908,25 +19908,25 @@
         <v>3.2</v>
       </c>
       <c r="AA120">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AB120">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AC120">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD120">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE120">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF120">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG120">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
+        <v>1.5</v>
+      </c>
+      <c r="AK120">
         <v>1.33</v>
-      </c>
-      <c r="AK120">
-        <v>1.39</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
+        <v>1.73</v>
+      </c>
+      <c r="O134">
+        <v>3.72</v>
+      </c>
+      <c r="P134">
+        <v>3.86</v>
+      </c>
+      <c r="Q134">
+        <v>2.1</v>
+      </c>
+      <c r="R134">
+        <v>2.5</v>
+      </c>
+      <c r="S134">
+        <v>1.2</v>
+      </c>
+      <c r="T134">
+        <v>4</v>
+      </c>
+      <c r="U134">
+        <v>2.13</v>
+      </c>
+      <c r="V134">
+        <v>1.68</v>
+      </c>
+      <c r="W134">
+        <v>1.15</v>
+      </c>
+      <c r="X134">
+        <v>1.02</v>
+      </c>
+      <c r="Y134">
+        <v>1.1</v>
+      </c>
+      <c r="Z134">
+        <v>5.15</v>
+      </c>
+      <c r="AA134">
+        <v>1.44</v>
+      </c>
+      <c r="AB134">
+        <v>2.66</v>
+      </c>
+      <c r="AC134">
         <v>2.08</v>
       </c>
-      <c r="O134">
-        <v>3.16</v>
-      </c>
-      <c r="P134">
-        <v>3.24</v>
-      </c>
-      <c r="Q134">
-        <v>2.7</v>
-      </c>
-      <c r="R134">
-        <v>2.1</v>
-      </c>
-      <c r="S134">
-        <v>1.36</v>
-      </c>
-      <c r="T134">
-        <v>2.88</v>
-      </c>
-      <c r="U134">
-        <v>2.73</v>
-      </c>
-      <c r="V134">
-        <v>1.36</v>
-      </c>
-      <c r="W134">
-        <v>1.08</v>
-      </c>
-      <c r="X134">
-        <v>1</v>
-      </c>
-      <c r="Y134">
-        <v>1.28</v>
-      </c>
-      <c r="Z134">
-        <v>3.08</v>
-      </c>
-      <c r="AA134">
-        <v>2.05</v>
-      </c>
-      <c r="AB134">
-        <v>1.75</v>
-      </c>
-      <c r="AC134">
-        <v>3.47</v>
-      </c>
       <c r="AD134">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AE134">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AF134">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AG134">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AK134">
-        <v>1.56</v>
+        <v>1.99</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="O135">
-        <v>3.72</v>
+        <v>3.54</v>
       </c>
       <c r="P135">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="Q135">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="R135">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S135">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T135">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U135">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="V135">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="W135">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z135">
-        <v>5.15</v>
+        <v>3.58</v>
       </c>
       <c r="AA135">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AB135">
-        <v>2.66</v>
+        <v>1.93</v>
       </c>
       <c r="AC135">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="AD135">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="AE135">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AF135">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AG135">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK135">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="O136">
-        <v>3.54</v>
+        <v>3.16</v>
       </c>
       <c r="P136">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="Q136">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R136">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S136">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T136">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U136">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="V136">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W136">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X136">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y136">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z136">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="AA136">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB136">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC136">
-        <v>2.74</v>
+        <v>3.47</v>
       </c>
       <c r="AD136">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE136">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF136">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG136">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK136">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.12</v>
+        <v>3.09</v>
       </c>
       <c r="O153">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P153">
-        <v>2.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q153">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="R153">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S153">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T153">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U153">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="V153">
         <v>1.5</v>
       </c>
       <c r="W153">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X153">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y153">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z153">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="AA153">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB153">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AC153">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD153">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE153">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF153">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG153">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AK153">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="O154">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="P154">
+        <v>2.27</v>
+      </c>
+      <c r="Q154">
+        <v>3.86</v>
+      </c>
+      <c r="R154">
         <v>2.05</v>
       </c>
-      <c r="Q154">
-        <v>3.5</v>
-      </c>
-      <c r="R154">
-        <v>2.2</v>
-      </c>
       <c r="S154">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="T154">
-        <v>3.12</v>
+        <v>2.58</v>
       </c>
       <c r="U154">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V154">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W154">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X154">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y154">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z154">
-        <v>3.72</v>
+        <v>2.7</v>
       </c>
       <c r="AA154">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AB154">
-        <v>2.07</v>
+        <v>1.6</v>
       </c>
       <c r="AC154">
-        <v>2.7</v>
+        <v>3.86</v>
       </c>
       <c r="AD154">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AE154">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF154">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG154">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="AK154">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="O155">
-        <v>3.02</v>
+        <v>3.38</v>
       </c>
       <c r="P155">
-        <v>2.27</v>
+        <v>2.96</v>
       </c>
       <c r="Q155">
-        <v>3.86</v>
+        <v>2.72</v>
       </c>
       <c r="R155">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S155">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="T155">
-        <v>2.58</v>
+        <v>3.28</v>
       </c>
       <c r="U155">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="V155">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W155">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X155">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y155">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Z155">
-        <v>2.7</v>
+        <v>3.78</v>
       </c>
       <c r="AA155">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AB155">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AC155">
-        <v>3.86</v>
+        <v>2.74</v>
       </c>
       <c r="AD155">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AE155">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AF155">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AG155">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK155">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AL155">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.73</v>
+        <v>2.19</v>
       </c>
       <c r="O48">
-        <v>3.02</v>
+        <v>3.62</v>
       </c>
       <c r="P48">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="Q48">
-        <v>3.18</v>
+        <v>2.43</v>
       </c>
       <c r="R48">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T48">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="U48">
-        <v>2.96</v>
+        <v>2.47</v>
       </c>
       <c r="V48">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA48">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC48">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD48">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE48">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG48">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AK48">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="O49">
-        <v>3.62</v>
+        <v>2.91</v>
       </c>
       <c r="P49">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="Q49">
-        <v>2.43</v>
+        <v>3.24</v>
       </c>
       <c r="R49">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T49">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="U49">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W49">
         <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
         <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>3.5</v>
+        <v>4.07</v>
       </c>
       <c r="AA49">
+        <v>2.03</v>
+      </c>
+      <c r="AB49">
         <v>1.83</v>
       </c>
-      <c r="AB49">
-        <v>1.93</v>
-      </c>
       <c r="AC49">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AD49">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE49">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AK49">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
       <c r="O50">
-        <v>3.74</v>
+        <v>3.02</v>
       </c>
       <c r="P50">
-        <v>2.13</v>
+        <v>2.58</v>
       </c>
       <c r="Q50">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="R50">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S50">
+        <v>1.38</v>
+      </c>
+      <c r="T50">
+        <v>2.75</v>
+      </c>
+      <c r="U50">
+        <v>2.96</v>
+      </c>
+      <c r="V50">
+        <v>1.4</v>
+      </c>
+      <c r="W50">
+        <v>1.06</v>
+      </c>
+      <c r="X50">
+        <v>1.03</v>
+      </c>
+      <c r="Y50">
         <v>1.3</v>
       </c>
-      <c r="T50">
-        <v>3.3</v>
-      </c>
-      <c r="U50">
-        <v>2.45</v>
-      </c>
-      <c r="V50">
-        <v>1.51</v>
-      </c>
-      <c r="W50">
-        <v>1.09</v>
-      </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.22</v>
-      </c>
       <c r="Z50">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA50">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="AB50">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC50">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF50">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AK50">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="O52">
-        <v>2.91</v>
+        <v>3.74</v>
       </c>
       <c r="P52">
-        <v>2.57</v>
+        <v>2.13</v>
       </c>
       <c r="Q52">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="R52">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S52">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V52">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
         <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
-        <v>2.03</v>
+        <v>1.69</v>
       </c>
       <c r="AB52">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AC52">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD52">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE52">
         <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG52">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AK52">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC81">
         <v>0</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC82">
         <v>0</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="O103">
-        <v>4.45</v>
+        <v>5.25</v>
       </c>
       <c r="P103">
-        <v>4</v>
+        <v>7.65</v>
       </c>
       <c r="Q103">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="R103">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="S103">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T103">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="U103">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="V103">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="W103">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="X103">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z103">
-        <v>7.8</v>
+        <v>6.45</v>
       </c>
       <c r="AA103">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AB103">
-        <v>3.83</v>
+        <v>2.92</v>
       </c>
       <c r="AC103">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AD103">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AE103">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AF103">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AG103">
-        <v>3.42</v>
+        <v>2.26</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK103">
-        <v>2.07</v>
+        <v>3.4</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="O104">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="P104">
-        <v>7.65</v>
+        <v>5.26</v>
       </c>
       <c r="Q104">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="R104">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S104">
         <v>1.2</v>
       </c>
       <c r="T104">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="U104">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V104">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="W104">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X104">
         <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z104">
-        <v>6.45</v>
+        <v>6.15</v>
       </c>
       <c r="AA104">
+        <v>1.32</v>
+      </c>
+      <c r="AB104">
+        <v>3.1</v>
+      </c>
+      <c r="AC104">
+        <v>1.91</v>
+      </c>
+      <c r="AD104">
+        <v>1.82</v>
+      </c>
+      <c r="AE104">
         <v>1.31</v>
       </c>
-      <c r="AB104">
-        <v>2.92</v>
-      </c>
-      <c r="AC104">
-        <v>1.9</v>
-      </c>
-      <c r="AD104">
-        <v>1.83</v>
-      </c>
-      <c r="AE104">
-        <v>1.34</v>
-      </c>
       <c r="AF104">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG104">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AK104">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.41</v>
+        <v>2.53</v>
       </c>
       <c r="O105">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P105">
-        <v>5.26</v>
+        <v>2.55</v>
       </c>
       <c r="Q105">
-        <v>1.85</v>
+        <v>3.11</v>
       </c>
       <c r="R105">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="S105">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T105">
-        <v>4.8</v>
+        <v>3.26</v>
       </c>
       <c r="U105">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="V105">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="W105">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="Z105">
-        <v>6.15</v>
+        <v>4.05</v>
       </c>
       <c r="AA105">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="AB105">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC105">
-        <v>1.91</v>
+        <v>2.56</v>
       </c>
       <c r="AD105">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="AE105">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AF105">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG105">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>2.42</v>
+        <v>1.45</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="O106">
-        <v>3.78</v>
+        <v>4.45</v>
       </c>
       <c r="P106">
-        <v>3.07</v>
+        <v>4</v>
       </c>
       <c r="Q106">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="R106">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="S106">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T106">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="U106">
-        <v>2.21</v>
+        <v>1.73</v>
       </c>
       <c r="V106">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="W106">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y106">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="Z106">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="AA106">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AB106">
-        <v>2.35</v>
+        <v>3.83</v>
       </c>
       <c r="AC106">
-        <v>2.33</v>
+        <v>1.62</v>
       </c>
       <c r="AD106">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="AE106">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AF106">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AG106">
-        <v>2.38</v>
+        <v>3.42</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.53</v>
+        <v>1.9</v>
       </c>
       <c r="O107">
+        <v>3.78</v>
+      </c>
+      <c r="P107">
+        <v>3.07</v>
+      </c>
+      <c r="Q107">
+        <v>2.4</v>
+      </c>
+      <c r="R107">
+        <v>2.4</v>
+      </c>
+      <c r="S107">
+        <v>1.25</v>
+      </c>
+      <c r="T107">
         <v>3.6</v>
       </c>
-      <c r="P107">
-        <v>2.55</v>
-      </c>
-      <c r="Q107">
-        <v>3.11</v>
-      </c>
-      <c r="R107">
-        <v>2.36</v>
-      </c>
-      <c r="S107">
-        <v>1.29</v>
-      </c>
-      <c r="T107">
-        <v>3.26</v>
-      </c>
       <c r="U107">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="V107">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W107">
         <v>1.12</v>
       </c>
       <c r="X107">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z107">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="AA107">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AB107">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="AC107">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="AD107">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE107">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF107">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG107">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK107">
-        <v>1.45</v>
+        <v>1.81</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,65 +18891,65 @@
         </is>
       </c>
       <c r="N114">
+        <v>3.75</v>
+      </c>
+      <c r="O114">
         <v>3.3</v>
       </c>
-      <c r="O114">
-        <v>3.5</v>
-      </c>
       <c r="P114">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="Q114">
-        <v>4.03</v>
+        <v>4.64</v>
       </c>
       <c r="R114">
         <v>2.1</v>
       </c>
       <c r="S114">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T114">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U114">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V114">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W114">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z114">
-        <v>3.42</v>
+        <v>3.21</v>
       </c>
       <c r="AA114">
+        <v>2.01</v>
+      </c>
+      <c r="AB114">
+        <v>1.74</v>
+      </c>
+      <c r="AC114">
+        <v>3.6</v>
+      </c>
+      <c r="AD114">
+        <v>1.23</v>
+      </c>
+      <c r="AE114">
+        <v>1.04</v>
+      </c>
+      <c r="AF114">
+        <v>1.83</v>
+      </c>
+      <c r="AG114">
         <v>1.82</v>
       </c>
-      <c r="AB114">
-        <v>1.85</v>
-      </c>
-      <c r="AC114">
-        <v>2.97</v>
-      </c>
-      <c r="AD114">
-        <v>1.3</v>
-      </c>
-      <c r="AE114">
-        <v>1.08</v>
-      </c>
-      <c r="AF114">
-        <v>1.68</v>
-      </c>
-      <c r="AG114">
-        <v>2</v>
-      </c>
       <c r="AH114" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.23</v>
+        <v>1.76</v>
       </c>
       <c r="AK114">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,16 +19054,16 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="O115">
         <v>3.2</v>
       </c>
       <c r="P115">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="Q115">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="R115">
         <v>2</v>
@@ -19072,46 +19072,46 @@
         <v>1.45</v>
       </c>
       <c r="T115">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U115">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="V115">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W115">
+        <v>1.05</v>
+      </c>
+      <c r="X115">
         <v>1.01</v>
-      </c>
-      <c r="X115">
-        <v>1.03</v>
       </c>
       <c r="Y115">
         <v>1.38</v>
       </c>
       <c r="Z115">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="AA115">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB115">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AC115">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AD115">
         <v>1.17</v>
       </c>
       <c r="AE115">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF115">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG115">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK115">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>3.75</v>
+        <v>2.54</v>
       </c>
       <c r="O116">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P116">
-        <v>1.96</v>
+        <v>2.37</v>
       </c>
       <c r="Q116">
-        <v>4.64</v>
+        <v>3.1</v>
       </c>
       <c r="R116">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S116">
+        <v>1.37</v>
+      </c>
+      <c r="T116">
+        <v>3</v>
+      </c>
+      <c r="U116">
+        <v>2.68</v>
+      </c>
+      <c r="V116">
         <v>1.4</v>
       </c>
-      <c r="T116">
-        <v>2.82</v>
-      </c>
-      <c r="U116">
-        <v>2.8</v>
-      </c>
-      <c r="V116">
-        <v>1.36</v>
-      </c>
       <c r="W116">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X116">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z116">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="AA116">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="AB116">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AC116">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD116">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE116">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF116">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG116">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="AK116">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="O117">
         <v>3.2</v>
       </c>
       <c r="P117">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="Q117">
         <v>3.48</v>
       </c>
       <c r="R117">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S117">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="T117">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U117">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V117">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="W117">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X117">
         <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="Z117">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="AA117">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB117">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AC117">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="AD117">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AE117">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF117">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="AG117">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK117">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O118">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P118">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q118">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R118">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S118">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T118">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U118">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="V118">
         <v>1.4</v>
       </c>
       <c r="W118">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X118">
         <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z118">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="AA118">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AB118">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AC118">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AD118">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE118">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF118">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG118">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK118">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,65 +19706,65 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q119">
-        <v>2.75</v>
+        <v>4.03</v>
       </c>
       <c r="R119">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S119">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T119">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="U119">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="V119">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W119">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X119">
         <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z119">
-        <v>3.86</v>
+        <v>3.42</v>
       </c>
       <c r="AA119">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB119">
+        <v>1.85</v>
+      </c>
+      <c r="AC119">
+        <v>2.97</v>
+      </c>
+      <c r="AD119">
+        <v>1.3</v>
+      </c>
+      <c r="AE119">
+        <v>1.08</v>
+      </c>
+      <c r="AF119">
+        <v>1.68</v>
+      </c>
+      <c r="AG119">
         <v>2</v>
       </c>
-      <c r="AC119">
-        <v>2.83</v>
-      </c>
-      <c r="AD119">
-        <v>1.33</v>
-      </c>
-      <c r="AE119">
-        <v>1.09</v>
-      </c>
-      <c r="AF119">
-        <v>1.65</v>
-      </c>
-      <c r="AG119">
-        <v>2.16</v>
-      </c>
       <c r="AH119" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
+        <v>1.23</v>
+      </c>
+      <c r="AK119">
         <v>1.25</v>
-      </c>
-      <c r="AK119">
-        <v>1.62</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="O120">
         <v>3.2</v>
       </c>
       <c r="P120">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="Q120">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="R120">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S120">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="T120">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="U120">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="V120">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="W120">
+        <v>1.01</v>
+      </c>
+      <c r="X120">
         <v>1.03</v>
       </c>
-      <c r="X120">
-        <v>1.01</v>
-      </c>
       <c r="Y120">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Z120">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA120">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AB120">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AC120">
-        <v>3.14</v>
+        <v>3.96</v>
       </c>
       <c r="AD120">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AE120">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF120">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AG120">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AK120">
         <v>1.33</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="O142">
-        <v>4.09</v>
+        <v>4.01</v>
       </c>
       <c r="P142">
-        <v>2.44</v>
+        <v>3.23</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23500,10 +23500,10 @@
         <v>0</v>
       </c>
       <c r="AC142">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AD142">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="O143">
-        <v>4.01</v>
+        <v>4.09</v>
       </c>
       <c r="P143">
-        <v>3.23</v>
+        <v>2.44</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23663,10 +23663,10 @@
         <v>0</v>
       </c>
       <c r="AC143">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AD143">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE143">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="O154">
-        <v>3.02</v>
+        <v>3.38</v>
       </c>
       <c r="P154">
-        <v>2.27</v>
+        <v>2.96</v>
       </c>
       <c r="Q154">
-        <v>3.86</v>
+        <v>2.72</v>
       </c>
       <c r="R154">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S154">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="T154">
-        <v>2.58</v>
+        <v>3.28</v>
       </c>
       <c r="U154">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="V154">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W154">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X154">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Z154">
-        <v>2.7</v>
+        <v>3.78</v>
       </c>
       <c r="AA154">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AB154">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AC154">
-        <v>3.86</v>
+        <v>2.74</v>
       </c>
       <c r="AD154">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AE154">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AF154">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AG154">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK154">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="O155">
-        <v>3.38</v>
+        <v>3.02</v>
       </c>
       <c r="P155">
-        <v>2.96</v>
+        <v>2.27</v>
       </c>
       <c r="Q155">
-        <v>2.72</v>
+        <v>3.86</v>
       </c>
       <c r="R155">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S155">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="T155">
-        <v>3.28</v>
+        <v>2.58</v>
       </c>
       <c r="U155">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="V155">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W155">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X155">
+        <v>1.04</v>
+      </c>
+      <c r="Y155">
+        <v>1.36</v>
+      </c>
+      <c r="Z155">
+        <v>2.7</v>
+      </c>
+      <c r="AA155">
+        <v>2.15</v>
+      </c>
+      <c r="AB155">
+        <v>1.6</v>
+      </c>
+      <c r="AC155">
+        <v>3.86</v>
+      </c>
+      <c r="AD155">
+        <v>1.18</v>
+      </c>
+      <c r="AE155">
         <v>1.03</v>
       </c>
-      <c r="Y155">
-        <v>1.23</v>
-      </c>
-      <c r="Z155">
-        <v>3.78</v>
-      </c>
-      <c r="AA155">
-        <v>1.72</v>
-      </c>
-      <c r="AB155">
-        <v>1.98</v>
-      </c>
-      <c r="AC155">
-        <v>2.74</v>
-      </c>
-      <c r="AD155">
-        <v>1.35</v>
-      </c>
-      <c r="AE155">
-        <v>1.15</v>
-      </c>
       <c r="AF155">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AG155">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK155">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AL155">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,65 +1124,65 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="O5">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="P5">
-        <v>2.09</v>
+        <v>2.49</v>
       </c>
       <c r="Q5">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R5">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="U5">
-        <v>2.65</v>
+        <v>3.12</v>
       </c>
       <c r="V5">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W5">
         <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="Z5">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="AA5">
-        <v>1.99</v>
+        <v>2.29</v>
       </c>
       <c r="AB5">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AC5">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD5">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
+        <v>1.91</v>
+      </c>
+      <c r="AG5">
         <v>1.73</v>
       </c>
-      <c r="AG5">
-        <v>1.98</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK5">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
+        <v>3.3</v>
+      </c>
+      <c r="P6">
+        <v>2.32</v>
+      </c>
+      <c r="Q6">
+        <v>3.2</v>
+      </c>
+      <c r="R6">
+        <v>2.1</v>
+      </c>
+      <c r="S6">
+        <v>1.37</v>
+      </c>
+      <c r="T6">
         <v>2.98</v>
       </c>
-      <c r="P6">
-        <v>2.49</v>
-      </c>
-      <c r="Q6">
-        <v>3.3</v>
-      </c>
-      <c r="R6">
+      <c r="U6">
+        <v>2.86</v>
+      </c>
+      <c r="V6">
+        <v>1.37</v>
+      </c>
+      <c r="W6">
+        <v>1.05</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>1.26</v>
+      </c>
+      <c r="Z6">
+        <v>3.43</v>
+      </c>
+      <c r="AA6">
+        <v>1.97</v>
+      </c>
+      <c r="AB6">
+        <v>1.79</v>
+      </c>
+      <c r="AC6">
+        <v>3.14</v>
+      </c>
+      <c r="AD6">
+        <v>1.27</v>
+      </c>
+      <c r="AE6">
+        <v>1.07</v>
+      </c>
+      <c r="AF6">
+        <v>1.7</v>
+      </c>
+      <c r="AG6">
         <v>2</v>
-      </c>
-      <c r="S6">
-        <v>1.44</v>
-      </c>
-      <c r="T6">
-        <v>2.5</v>
-      </c>
-      <c r="U6">
-        <v>3.12</v>
-      </c>
-      <c r="V6">
-        <v>1.28</v>
-      </c>
-      <c r="W6">
-        <v>1.06</v>
-      </c>
-      <c r="X6">
-        <v>1.04</v>
-      </c>
-      <c r="Y6">
-        <v>1.4</v>
-      </c>
-      <c r="Z6">
-        <v>2.72</v>
-      </c>
-      <c r="AA6">
-        <v>2.29</v>
-      </c>
-      <c r="AB6">
-        <v>1.53</v>
-      </c>
-      <c r="AC6">
-        <v>4.33</v>
-      </c>
-      <c r="AD6">
-        <v>1.14</v>
-      </c>
-      <c r="AE6">
-        <v>1.01</v>
-      </c>
-      <c r="AF6">
-        <v>1.91</v>
-      </c>
-      <c r="AG6">
-        <v>1.73</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P7">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="Q7">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S7">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="U7">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>3.43</v>
+        <v>3.72</v>
       </c>
       <c r="AA7">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AB7">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="AC7">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="AD7">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AK7">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.38</v>
+        <v>1.49</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="P8">
-        <v>2.47</v>
+        <v>5.47</v>
       </c>
       <c r="Q8">
-        <v>3.22</v>
+        <v>1.99</v>
       </c>
       <c r="R8">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
         <v>3.2</v>
       </c>
       <c r="U8">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="V8">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
         <v>1.11</v>
@@ -1646,31 +1646,31 @@
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="AA8">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AB8">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AC8">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AD8">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE8">
         <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AG8">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.39</v>
+        <v>2.21</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="O9">
-        <v>3.38</v>
+        <v>2.99</v>
       </c>
       <c r="P9">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>2.93</v>
+        <v>3.13</v>
       </c>
       <c r="R9">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T9">
-        <v>3.18</v>
+        <v>2.42</v>
       </c>
       <c r="U9">
-        <v>2.67</v>
+        <v>3.22</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
         <v>1.07</v>
@@ -1809,31 +1809,31 @@
         <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="Z9">
-        <v>3.72</v>
+        <v>2.74</v>
       </c>
       <c r="AA9">
-        <v>1.74</v>
+        <v>2.19</v>
       </c>
       <c r="AB9">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="AC9">
-        <v>2.99</v>
+        <v>3.74</v>
       </c>
       <c r="AD9">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AE9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AG9">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.49</v>
+        <v>3.14</v>
       </c>
       <c r="O10">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="P10">
-        <v>5.47</v>
+        <v>2.09</v>
       </c>
       <c r="Q10">
+        <v>3.5</v>
+      </c>
+      <c r="R10">
+        <v>2.08</v>
+      </c>
+      <c r="S10">
+        <v>1.33</v>
+      </c>
+      <c r="T10">
+        <v>2.95</v>
+      </c>
+      <c r="U10">
+        <v>2.65</v>
+      </c>
+      <c r="V10">
+        <v>1.38</v>
+      </c>
+      <c r="W10">
+        <v>1.06</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1.26</v>
+      </c>
+      <c r="Z10">
+        <v>3.2</v>
+      </c>
+      <c r="AA10">
         <v>1.99</v>
       </c>
-      <c r="R10">
-        <v>2.28</v>
-      </c>
-      <c r="S10">
-        <v>1.32</v>
-      </c>
-      <c r="T10">
+      <c r="AB10">
+        <v>1.78</v>
+      </c>
+      <c r="AC10">
         <v>3.2</v>
       </c>
-      <c r="U10">
-        <v>2.57</v>
-      </c>
-      <c r="V10">
-        <v>1.48</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.18</v>
-      </c>
-      <c r="Z10">
-        <v>4.01</v>
-      </c>
-      <c r="AA10">
-        <v>1.82</v>
-      </c>
-      <c r="AB10">
-        <v>1.94</v>
-      </c>
-      <c r="AC10">
-        <v>2.66</v>
-      </c>
       <c r="AD10">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE10">
         <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="O11">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>3.1</v>
+        <v>2.47</v>
       </c>
       <c r="Q11">
-        <v>3.13</v>
+        <v>3.22</v>
       </c>
       <c r="R11">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="S11">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>3.22</v>
+        <v>2.45</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="AA11">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AB11">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AC11">
-        <v>3.74</v>
+        <v>2.77</v>
       </c>
       <c r="AD11">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AE11">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AG11">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,34 +4719,34 @@
         <v>2.86</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA27">
         <v>2</v>
@@ -4755,19 +4755,19 @@
         <v>1.68</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,34 +4882,34 @@
         <v>2.35</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA28">
         <v>2</v>
@@ -4918,19 +4918,19 @@
         <v>1.7</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,31 +5199,31 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="O30">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>3.41</v>
+        <v>3.21</v>
       </c>
       <c r="Q30">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="R30">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S30">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T30">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="U30">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="V30">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W30">
         <v>1.05</v>
@@ -5232,19 +5232,19 @@
         <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z30">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA30">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB30">
         <v>1.6</v>
       </c>
       <c r="AC30">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="AD30">
         <v>1.18</v>
@@ -5253,10 +5253,10 @@
         <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AG30">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,61 +5362,61 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.11</v>
+        <v>3.89</v>
       </c>
       <c r="O31">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="P31">
-        <v>3.21</v>
+        <v>1.84</v>
       </c>
       <c r="Q31">
-        <v>2.78</v>
+        <v>4.88</v>
       </c>
       <c r="R31">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="S31">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T31">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="U31">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="V31">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z31">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AA31">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB31">
         <v>1.6</v>
       </c>
       <c r="AC31">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="AD31">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE31">
         <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG31">
         <v>1.78</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK31">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,43 +5525,43 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.89</v>
+        <v>2.01</v>
       </c>
       <c r="O32">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="P32">
-        <v>1.84</v>
+        <v>3.41</v>
       </c>
       <c r="Q32">
-        <v>4.88</v>
+        <v>2.7</v>
       </c>
       <c r="R32">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="S32">
         <v>1.41</v>
       </c>
       <c r="T32">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="U32">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="V32">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W32">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z32">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AA32">
         <v>2.15</v>
@@ -5570,19 +5570,19 @@
         <v>1.6</v>
       </c>
       <c r="AC32">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AD32">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE32">
         <v>1.03</v>
       </c>
       <c r="AF32">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG32">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>1.16</v>
+        <v>1.64</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="O48">
-        <v>3.62</v>
+        <v>2.91</v>
       </c>
       <c r="P48">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="Q48">
-        <v>2.43</v>
+        <v>3.24</v>
       </c>
       <c r="R48">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S48">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T48">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="U48">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="V48">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W48">
         <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
         <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.5</v>
+        <v>4.07</v>
       </c>
       <c r="AA48">
+        <v>2.03</v>
+      </c>
+      <c r="AB48">
         <v>1.83</v>
       </c>
-      <c r="AB48">
-        <v>1.93</v>
-      </c>
       <c r="AC48">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AD48">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE48">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG48">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AK48">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.83</v>
+        <v>2.09</v>
       </c>
       <c r="O49">
-        <v>2.91</v>
+        <v>3.54</v>
       </c>
       <c r="P49">
-        <v>2.57</v>
+        <v>3.15</v>
       </c>
       <c r="Q49">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="R49">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S49">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="T49">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="U49">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="V49">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>4.07</v>
+        <v>4.33</v>
       </c>
       <c r="AA49">
+        <v>1.83</v>
+      </c>
+      <c r="AB49">
         <v>2.03</v>
       </c>
-      <c r="AB49">
-        <v>1.83</v>
-      </c>
       <c r="AC49">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="AD49">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE49">
         <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK49">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="O51">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P51">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="Q51">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="R51">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S51">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T51">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U51">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="V51">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
         <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC51">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG51">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
         <v>1.65</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13195,34 +13195,34 @@
         <v>4.58</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA79">
         <v>2.25</v>
@@ -13231,19 +13231,19 @@
         <v>1.57</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13521,34 +13521,34 @@
         <v>2.68</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA81">
         <v>1.98</v>
@@ -13557,19 +13557,19 @@
         <v>1.71</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,34 +13684,34 @@
         <v>5.13</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA82">
         <v>1.9</v>
@@ -13720,19 +13720,19 @@
         <v>1.78</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O83">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="P83">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="Q83">
         <v>2.9</v>
       </c>
       <c r="R83">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S83">
+        <v>1.44</v>
+      </c>
+      <c r="T83">
+        <v>2.45</v>
+      </c>
+      <c r="U83">
+        <v>3.12</v>
+      </c>
+      <c r="V83">
+        <v>1.28</v>
+      </c>
+      <c r="W83">
+        <v>1.02</v>
+      </c>
+      <c r="X83">
+        <v>1.03</v>
+      </c>
+      <c r="Y83">
         <v>1.36</v>
       </c>
-      <c r="T83">
-        <v>2.73</v>
-      </c>
-      <c r="U83">
-        <v>3</v>
-      </c>
-      <c r="V83">
-        <v>1.33</v>
-      </c>
-      <c r="W83">
-        <v>1.06</v>
-      </c>
-      <c r="X83">
-        <v>1.01</v>
-      </c>
-      <c r="Y83">
-        <v>1.3</v>
-      </c>
       <c r="Z83">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AA83">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB83">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC83">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="AD83">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE83">
         <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG83">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK83">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="O84">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="P84">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="Q84">
         <v>2.9</v>
       </c>
       <c r="R84">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S84">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T84">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="U84">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="V84">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W84">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X84">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z84">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AA84">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB84">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC84">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="AD84">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE84">
         <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG84">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -17922,55 +17922,55 @@
         <v>2.51</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18248,55 +18248,55 @@
         <v>3.89</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,65 +19543,65 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q118">
-        <v>2.75</v>
+        <v>4.03</v>
       </c>
       <c r="R118">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S118">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T118">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="U118">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="V118">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W118">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X118">
         <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z118">
-        <v>3.86</v>
+        <v>3.42</v>
       </c>
       <c r="AA118">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB118">
+        <v>1.85</v>
+      </c>
+      <c r="AC118">
+        <v>2.97</v>
+      </c>
+      <c r="AD118">
+        <v>1.3</v>
+      </c>
+      <c r="AE118">
+        <v>1.08</v>
+      </c>
+      <c r="AF118">
+        <v>1.68</v>
+      </c>
+      <c r="AG118">
         <v>2</v>
       </c>
-      <c r="AC118">
-        <v>2.83</v>
-      </c>
-      <c r="AD118">
-        <v>1.33</v>
-      </c>
-      <c r="AE118">
-        <v>1.09</v>
-      </c>
-      <c r="AF118">
-        <v>1.65</v>
-      </c>
-      <c r="AG118">
-        <v>2.16</v>
-      </c>
       <c r="AH118" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
+        <v>1.23</v>
+      </c>
+      <c r="AK118">
         <v>1.25</v>
-      </c>
-      <c r="AK118">
-        <v>1.62</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,80 +19706,80 @@
         </is>
       </c>
       <c r="N119">
+        <v>2.85</v>
+      </c>
+      <c r="O119">
+        <v>3.2</v>
+      </c>
+      <c r="P119">
+        <v>2.41</v>
+      </c>
+      <c r="Q119">
         <v>3.3</v>
       </c>
-      <c r="O119">
-        <v>3.5</v>
-      </c>
-      <c r="P119">
-        <v>2.04</v>
-      </c>
-      <c r="Q119">
-        <v>4.03</v>
-      </c>
       <c r="R119">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S119">
+        <v>1.45</v>
+      </c>
+      <c r="T119">
+        <v>2.45</v>
+      </c>
+      <c r="U119">
+        <v>3.12</v>
+      </c>
+      <c r="V119">
+        <v>1.28</v>
+      </c>
+      <c r="W119">
+        <v>1.01</v>
+      </c>
+      <c r="X119">
+        <v>1.03</v>
+      </c>
+      <c r="Y119">
+        <v>1.38</v>
+      </c>
+      <c r="Z119">
+        <v>2.74</v>
+      </c>
+      <c r="AA119">
+        <v>2.25</v>
+      </c>
+      <c r="AB119">
+        <v>1.59</v>
+      </c>
+      <c r="AC119">
+        <v>3.96</v>
+      </c>
+      <c r="AD119">
+        <v>1.17</v>
+      </c>
+      <c r="AE119">
+        <v>1.02</v>
+      </c>
+      <c r="AF119">
+        <v>1.87</v>
+      </c>
+      <c r="AG119">
+        <v>1.82</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ119">
+        <v>1.28</v>
+      </c>
+      <c r="AK119">
         <v>1.33</v>
-      </c>
-      <c r="T119">
-        <v>3.2</v>
-      </c>
-      <c r="U119">
-        <v>2.78</v>
-      </c>
-      <c r="V119">
-        <v>1.41</v>
-      </c>
-      <c r="W119">
-        <v>1.1</v>
-      </c>
-      <c r="X119">
-        <v>1.01</v>
-      </c>
-      <c r="Y119">
-        <v>1.26</v>
-      </c>
-      <c r="Z119">
-        <v>3.42</v>
-      </c>
-      <c r="AA119">
-        <v>1.82</v>
-      </c>
-      <c r="AB119">
-        <v>1.85</v>
-      </c>
-      <c r="AC119">
-        <v>2.97</v>
-      </c>
-      <c r="AD119">
-        <v>1.3</v>
-      </c>
-      <c r="AE119">
-        <v>1.08</v>
-      </c>
-      <c r="AF119">
-        <v>1.68</v>
-      </c>
-      <c r="AG119">
-        <v>2</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>1.23</v>
-      </c>
-      <c r="AK119">
-        <v>1.25</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O120">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P120">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q120">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="R120">
+        <v>2.2</v>
+      </c>
+      <c r="S120">
+        <v>1.34</v>
+      </c>
+      <c r="T120">
+        <v>2.86</v>
+      </c>
+      <c r="U120">
+        <v>2.62</v>
+      </c>
+      <c r="V120">
+        <v>1.4</v>
+      </c>
+      <c r="W120">
+        <v>1.08</v>
+      </c>
+      <c r="X120">
+        <v>1.01</v>
+      </c>
+      <c r="Y120">
+        <v>1.21</v>
+      </c>
+      <c r="Z120">
+        <v>3.86</v>
+      </c>
+      <c r="AA120">
+        <v>1.76</v>
+      </c>
+      <c r="AB120">
         <v>2</v>
       </c>
-      <c r="S120">
-        <v>1.45</v>
-      </c>
-      <c r="T120">
-        <v>2.45</v>
-      </c>
-      <c r="U120">
-        <v>3.12</v>
-      </c>
-      <c r="V120">
-        <v>1.28</v>
-      </c>
-      <c r="W120">
-        <v>1.01</v>
-      </c>
-      <c r="X120">
-        <v>1.03</v>
-      </c>
-      <c r="Y120">
-        <v>1.38</v>
-      </c>
-      <c r="Z120">
-        <v>2.74</v>
-      </c>
-      <c r="AA120">
-        <v>2.25</v>
-      </c>
-      <c r="AB120">
-        <v>1.59</v>
-      </c>
       <c r="AC120">
-        <v>3.96</v>
+        <v>2.83</v>
       </c>
       <c r="AD120">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AE120">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AF120">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AG120">
-        <v>1.82</v>
+        <v>2.16</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK120">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22842,10 +22842,10 @@
         <v>0</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC138">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.63</v>
+        <v>2.32</v>
       </c>
       <c r="O3">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="P3">
-        <v>4.87</v>
+        <v>2.55</v>
       </c>
       <c r="Q3">
-        <v>2.23</v>
+        <v>2.93</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S3">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.64</v>
+        <v>3.18</v>
       </c>
       <c r="U3">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>3.08</v>
+        <v>3.72</v>
       </c>
       <c r="AA3">
+        <v>1.74</v>
+      </c>
+      <c r="AB3">
         <v>2.02</v>
       </c>
-      <c r="AB3">
-        <v>1.77</v>
-      </c>
       <c r="AC3">
-        <v>3.48</v>
+        <v>2.99</v>
       </c>
       <c r="AD3">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG3">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK3">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="O4">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="P4">
-        <v>2.03</v>
+        <v>2.49</v>
       </c>
       <c r="Q4">
-        <v>3.99</v>
+        <v>3.3</v>
       </c>
       <c r="R4">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U4">
-        <v>2.51</v>
+        <v>3.12</v>
       </c>
       <c r="V4">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="Z4">
-        <v>3.42</v>
+        <v>2.72</v>
       </c>
       <c r="AA4">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="AB4">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="AC4">
-        <v>3.07</v>
+        <v>4.33</v>
       </c>
       <c r="AD4">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AE4">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AG4">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK4">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,65 +1124,65 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.62</v>
+        <v>1.49</v>
       </c>
       <c r="O5">
-        <v>2.98</v>
+        <v>3.98</v>
       </c>
       <c r="P5">
-        <v>2.49</v>
+        <v>5.47</v>
       </c>
       <c r="Q5">
-        <v>3.3</v>
+        <v>1.99</v>
       </c>
       <c r="R5">
+        <v>2.28</v>
+      </c>
+      <c r="S5">
+        <v>1.32</v>
+      </c>
+      <c r="T5">
+        <v>3.2</v>
+      </c>
+      <c r="U5">
+        <v>2.57</v>
+      </c>
+      <c r="V5">
+        <v>1.48</v>
+      </c>
+      <c r="W5">
+        <v>1.11</v>
+      </c>
+      <c r="X5">
+        <v>1.03</v>
+      </c>
+      <c r="Y5">
+        <v>1.18</v>
+      </c>
+      <c r="Z5">
+        <v>4.01</v>
+      </c>
+      <c r="AA5">
+        <v>1.82</v>
+      </c>
+      <c r="AB5">
+        <v>1.94</v>
+      </c>
+      <c r="AC5">
+        <v>2.66</v>
+      </c>
+      <c r="AD5">
+        <v>1.41</v>
+      </c>
+      <c r="AE5">
+        <v>1.11</v>
+      </c>
+      <c r="AF5">
+        <v>1.71</v>
+      </c>
+      <c r="AG5">
         <v>2</v>
       </c>
-      <c r="S5">
-        <v>1.44</v>
-      </c>
-      <c r="T5">
-        <v>2.5</v>
-      </c>
-      <c r="U5">
-        <v>3.12</v>
-      </c>
-      <c r="V5">
-        <v>1.28</v>
-      </c>
-      <c r="W5">
-        <v>1.06</v>
-      </c>
-      <c r="X5">
-        <v>1.04</v>
-      </c>
-      <c r="Y5">
-        <v>1.4</v>
-      </c>
-      <c r="Z5">
-        <v>2.72</v>
-      </c>
-      <c r="AA5">
-        <v>2.29</v>
-      </c>
-      <c r="AB5">
-        <v>1.53</v>
-      </c>
-      <c r="AC5">
-        <v>4.33</v>
-      </c>
-      <c r="AD5">
-        <v>1.14</v>
-      </c>
-      <c r="AE5">
-        <v>1.01</v>
-      </c>
-      <c r="AF5">
-        <v>1.91</v>
-      </c>
-      <c r="AG5">
-        <v>1.73</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>1.36</v>
+        <v>2.21</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="Q6">
+        <v>3.22</v>
+      </c>
+      <c r="R6">
+        <v>2.17</v>
+      </c>
+      <c r="S6">
+        <v>1.3</v>
+      </c>
+      <c r="T6">
         <v>3.2</v>
       </c>
-      <c r="R6">
+      <c r="U6">
+        <v>2.45</v>
+      </c>
+      <c r="V6">
+        <v>1.49</v>
+      </c>
+      <c r="W6">
+        <v>1.11</v>
+      </c>
+      <c r="X6">
+        <v>1.03</v>
+      </c>
+      <c r="Y6">
+        <v>1.17</v>
+      </c>
+      <c r="Z6">
+        <v>4</v>
+      </c>
+      <c r="AA6">
+        <v>1.7</v>
+      </c>
+      <c r="AB6">
         <v>2.1</v>
       </c>
-      <c r="S6">
+      <c r="AC6">
+        <v>2.77</v>
+      </c>
+      <c r="AD6">
         <v>1.37</v>
       </c>
-      <c r="T6">
-        <v>2.98</v>
-      </c>
-      <c r="U6">
-        <v>2.86</v>
-      </c>
-      <c r="V6">
-        <v>1.37</v>
-      </c>
-      <c r="W6">
-        <v>1.05</v>
-      </c>
-      <c r="X6">
-        <v>1.01</v>
-      </c>
-      <c r="Y6">
+      <c r="AE6">
+        <v>1.11</v>
+      </c>
+      <c r="AF6">
+        <v>1.55</v>
+      </c>
+      <c r="AG6">
+        <v>2.25</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.26</v>
       </c>
-      <c r="Z6">
-        <v>3.43</v>
-      </c>
-      <c r="AA6">
-        <v>1.97</v>
-      </c>
-      <c r="AB6">
-        <v>1.79</v>
-      </c>
-      <c r="AC6">
-        <v>3.14</v>
-      </c>
-      <c r="AD6">
-        <v>1.27</v>
-      </c>
-      <c r="AE6">
-        <v>1.07</v>
-      </c>
-      <c r="AF6">
-        <v>1.7</v>
-      </c>
-      <c r="AG6">
-        <v>2</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.28</v>
-      </c>
       <c r="AK6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,65 +1450,65 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.32</v>
+        <v>3.28</v>
       </c>
       <c r="O7">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="P7">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="Q7">
-        <v>2.93</v>
+        <v>3.99</v>
       </c>
       <c r="R7">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S7">
         <v>1.33</v>
       </c>
       <c r="T7">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U7">
-        <v>2.67</v>
+        <v>2.51</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>3.72</v>
+        <v>3.42</v>
       </c>
       <c r="AA7">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AB7">
+        <v>1.94</v>
+      </c>
+      <c r="AC7">
+        <v>3.07</v>
+      </c>
+      <c r="AD7">
+        <v>1.31</v>
+      </c>
+      <c r="AE7">
+        <v>1.09</v>
+      </c>
+      <c r="AF7">
+        <v>1.67</v>
+      </c>
+      <c r="AG7">
         <v>2.02</v>
       </c>
-      <c r="AC7">
-        <v>2.99</v>
-      </c>
-      <c r="AD7">
-        <v>1.32</v>
-      </c>
-      <c r="AE7">
-        <v>1.08</v>
-      </c>
-      <c r="AF7">
-        <v>1.61</v>
-      </c>
-      <c r="AG7">
-        <v>2.12</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.49</v>
+        <v>3.14</v>
       </c>
       <c r="O8">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="P8">
-        <v>5.47</v>
+        <v>2.09</v>
       </c>
       <c r="Q8">
+        <v>3.5</v>
+      </c>
+      <c r="R8">
+        <v>2.08</v>
+      </c>
+      <c r="S8">
+        <v>1.33</v>
+      </c>
+      <c r="T8">
+        <v>2.95</v>
+      </c>
+      <c r="U8">
+        <v>2.65</v>
+      </c>
+      <c r="V8">
+        <v>1.38</v>
+      </c>
+      <c r="W8">
+        <v>1.06</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1.26</v>
+      </c>
+      <c r="Z8">
+        <v>3.2</v>
+      </c>
+      <c r="AA8">
         <v>1.99</v>
       </c>
-      <c r="R8">
-        <v>2.28</v>
-      </c>
-      <c r="S8">
-        <v>1.32</v>
-      </c>
-      <c r="T8">
+      <c r="AB8">
+        <v>1.78</v>
+      </c>
+      <c r="AC8">
         <v>3.2</v>
       </c>
-      <c r="U8">
-        <v>2.57</v>
-      </c>
-      <c r="V8">
-        <v>1.48</v>
-      </c>
-      <c r="W8">
-        <v>1.11</v>
-      </c>
-      <c r="X8">
-        <v>1.03</v>
-      </c>
-      <c r="Y8">
-        <v>1.18</v>
-      </c>
-      <c r="Z8">
-        <v>4.01</v>
-      </c>
-      <c r="AA8">
-        <v>1.82</v>
-      </c>
-      <c r="AB8">
-        <v>1.94</v>
-      </c>
-      <c r="AC8">
-        <v>2.66</v>
-      </c>
       <c r="AD8">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE8">
         <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,31 +1939,31 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.14</v>
+        <v>1.63</v>
       </c>
       <c r="O10">
-        <v>3.24</v>
+        <v>3.48</v>
       </c>
       <c r="P10">
-        <v>2.09</v>
+        <v>4.87</v>
       </c>
       <c r="Q10">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="R10">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T10">
-        <v>2.95</v>
+        <v>2.64</v>
       </c>
       <c r="U10">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="V10">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
         <v>1.06</v>
@@ -1972,47 +1972,47 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z10">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA10">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AB10">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC10">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD10">
+        <v>1.22</v>
+      </c>
+      <c r="AE10">
+        <v>1.04</v>
+      </c>
+      <c r="AF10">
+        <v>1.85</v>
+      </c>
+      <c r="AG10">
+        <v>1.75</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.3</v>
       </c>
-      <c r="AE10">
-        <v>1.11</v>
-      </c>
-      <c r="AF10">
-        <v>1.73</v>
-      </c>
-      <c r="AG10">
-        <v>1.98</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.24</v>
-      </c>
       <c r="AK10">
-        <v>1.27</v>
+        <v>2.05</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="Q11">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="R11">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="V11">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z11">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="AA11">
+        <v>1.97</v>
+      </c>
+      <c r="AB11">
+        <v>1.79</v>
+      </c>
+      <c r="AC11">
+        <v>3.14</v>
+      </c>
+      <c r="AD11">
+        <v>1.27</v>
+      </c>
+      <c r="AE11">
+        <v>1.07</v>
+      </c>
+      <c r="AF11">
         <v>1.7</v>
       </c>
-      <c r="AB11">
-        <v>2.1</v>
-      </c>
-      <c r="AC11">
-        <v>2.77</v>
-      </c>
-      <c r="AD11">
-        <v>1.37</v>
-      </c>
-      <c r="AE11">
-        <v>1.11</v>
-      </c>
-      <c r="AF11">
-        <v>1.55</v>
-      </c>
       <c r="AG11">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK11">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.64</v>
+        <v>2.27</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="P26">
-        <v>5.2</v>
+        <v>2.86</v>
       </c>
       <c r="Q26">
-        <v>2.14</v>
+        <v>2.91</v>
       </c>
       <c r="R26">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="S26">
+        <v>1.4</v>
+      </c>
+      <c r="T26">
+        <v>2.75</v>
+      </c>
+      <c r="U26">
+        <v>2.73</v>
+      </c>
+      <c r="V26">
         <v>1.36</v>
       </c>
-      <c r="T26">
-        <v>2.64</v>
-      </c>
-      <c r="U26">
-        <v>2.8</v>
-      </c>
-      <c r="V26">
-        <v>1.34</v>
-      </c>
       <c r="W26">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA26">
         <v>2</v>
       </c>
       <c r="AB26">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC26">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD26">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AG26">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.27</v>
+        <v>1.64</v>
       </c>
       <c r="O27">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>2.86</v>
+        <v>5.2</v>
       </c>
       <c r="Q27">
-        <v>2.91</v>
+        <v>2.14</v>
       </c>
       <c r="R27">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="S27">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="U27">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA27">
         <v>2</v>
       </c>
       <c r="AB27">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC27">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD27">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="AG27">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK27">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.09</v>
+        <v>2.92</v>
       </c>
       <c r="O49">
-        <v>3.54</v>
+        <v>3.74</v>
       </c>
       <c r="P49">
-        <v>3.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q49">
-        <v>2.75</v>
+        <v>3.26</v>
       </c>
       <c r="R49">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S49">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="V49">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA49">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AB49">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AC49">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AD49">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE49">
         <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG49">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
+        <v>1.65</v>
+      </c>
+      <c r="AK49">
         <v>1.33</v>
-      </c>
-      <c r="AK49">
-        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,77 +8622,77 @@
         </is>
       </c>
       <c r="N51">
+        <v>2.09</v>
+      </c>
+      <c r="O51">
+        <v>3.54</v>
+      </c>
+      <c r="P51">
+        <v>3.15</v>
+      </c>
+      <c r="Q51">
+        <v>2.75</v>
+      </c>
+      <c r="R51">
         <v>2.19</v>
       </c>
-      <c r="O51">
-        <v>3.62</v>
-      </c>
-      <c r="P51">
-        <v>2.88</v>
-      </c>
-      <c r="Q51">
-        <v>2.43</v>
-      </c>
-      <c r="R51">
-        <v>2.21</v>
-      </c>
       <c r="S51">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T51">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U51">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA51">
         <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="AD51">
+        <v>1.43</v>
+      </c>
+      <c r="AE51">
+        <v>1.13</v>
+      </c>
+      <c r="AF51">
+        <v>1.55</v>
+      </c>
+      <c r="AG51">
+        <v>2.25</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.33</v>
-      </c>
-      <c r="AE51">
-        <v>1.12</v>
-      </c>
-      <c r="AF51">
-        <v>1.64</v>
-      </c>
-      <c r="AG51">
-        <v>2.13</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.27</v>
       </c>
       <c r="AK51">
         <v>1.65</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,34 +8785,34 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.92</v>
+        <v>2.19</v>
       </c>
       <c r="O52">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="P52">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="Q52">
-        <v>3.26</v>
+        <v>2.43</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U52">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
         <v>1.01</v>
@@ -8821,28 +8821,28 @@
         <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA52">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AB52">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AC52">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD52">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AG52">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
+        <v>1.27</v>
+      </c>
+      <c r="AK52">
         <v>1.65</v>
-      </c>
-      <c r="AK52">
-        <v>1.33</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="O62">
-        <v>5</v>
+        <v>3.48</v>
       </c>
       <c r="P62">
-        <v>6.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q62">
-        <v>1.74</v>
+        <v>2.39</v>
       </c>
       <c r="R62">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="S62">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="T62">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="U62">
-        <v>1.95</v>
+        <v>2.71</v>
       </c>
       <c r="V62">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="W62">
+        <v>1.06</v>
+      </c>
+      <c r="X62">
+        <v>1.03</v>
+      </c>
+      <c r="Y62">
+        <v>1.26</v>
+      </c>
+      <c r="Z62">
+        <v>3.05</v>
+      </c>
+      <c r="AA62">
+        <v>2.01</v>
+      </c>
+      <c r="AB62">
+        <v>1.79</v>
+      </c>
+      <c r="AC62">
+        <v>3.44</v>
+      </c>
+      <c r="AD62">
+        <v>1.26</v>
+      </c>
+      <c r="AE62">
+        <v>1.06</v>
+      </c>
+      <c r="AF62">
+        <v>1.82</v>
+      </c>
+      <c r="AG62">
+        <v>1.88</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.19</v>
       </c>
-      <c r="X62">
-        <v>1.01</v>
-      </c>
-      <c r="Y62">
-        <v>1.07</v>
-      </c>
-      <c r="Z62">
-        <v>5.85</v>
-      </c>
-      <c r="AA62">
-        <v>1.4</v>
-      </c>
-      <c r="AB62">
-        <v>2.87</v>
-      </c>
-      <c r="AC62">
-        <v>2.02</v>
-      </c>
-      <c r="AD62">
-        <v>1.77</v>
-      </c>
-      <c r="AE62">
-        <v>1.33</v>
-      </c>
-      <c r="AF62">
-        <v>1.57</v>
-      </c>
-      <c r="AG62">
-        <v>2.26</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.13</v>
-      </c>
       <c r="AK62">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="O63">
-        <v>3.48</v>
+        <v>5</v>
       </c>
       <c r="P63">
-        <v>3.94</v>
+        <v>6.4</v>
       </c>
       <c r="Q63">
-        <v>2.39</v>
+        <v>1.74</v>
       </c>
       <c r="R63">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="S63">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="T63">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="U63">
-        <v>2.71</v>
+        <v>1.95</v>
       </c>
       <c r="V63">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="W63">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="X63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="Z63">
-        <v>3.05</v>
+        <v>5.85</v>
       </c>
       <c r="AA63">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>1.79</v>
+        <v>2.87</v>
       </c>
       <c r="AC63">
-        <v>3.44</v>
+        <v>2.02</v>
       </c>
       <c r="AD63">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="AE63">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AF63">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AG63">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK63">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="O69">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P69">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q69">
-        <v>2.16</v>
+        <v>2.99</v>
       </c>
       <c r="R69">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S69">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T69">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U69">
-        <v>2.89</v>
+        <v>3.24</v>
       </c>
       <c r="V69">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W69">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X69">
+        <v>1.02</v>
+      </c>
+      <c r="Y69">
+        <v>1.36</v>
+      </c>
+      <c r="Z69">
+        <v>2.7</v>
+      </c>
+      <c r="AA69">
+        <v>2.2</v>
+      </c>
+      <c r="AB69">
+        <v>1.57</v>
+      </c>
+      <c r="AC69">
+        <v>4.2</v>
+      </c>
+      <c r="AD69">
+        <v>1.16</v>
+      </c>
+      <c r="AE69">
         <v>1.01</v>
       </c>
-      <c r="Y69">
-        <v>1.3</v>
-      </c>
-      <c r="Z69">
-        <v>2.97</v>
-      </c>
-      <c r="AA69">
-        <v>2.01</v>
-      </c>
-      <c r="AB69">
-        <v>1.69</v>
-      </c>
-      <c r="AC69">
-        <v>3.5</v>
-      </c>
-      <c r="AD69">
-        <v>1.22</v>
-      </c>
-      <c r="AE69">
-        <v>1.04</v>
-      </c>
       <c r="AF69">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG69">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AK69">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="O70">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P70">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q70">
-        <v>2.99</v>
+        <v>2.16</v>
       </c>
       <c r="R70">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S70">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T70">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="U70">
-        <v>3.24</v>
+        <v>2.89</v>
       </c>
       <c r="V70">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W70">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z70">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AA70">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AB70">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AC70">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD70">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE70">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF70">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG70">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AK70">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="O83">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="P83">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="Q83">
         <v>2.9</v>
       </c>
       <c r="R83">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S83">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T83">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="U83">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="V83">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W83">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z83">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AA83">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB83">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC83">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="AD83">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE83">
         <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG83">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O84">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="P84">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="Q84">
         <v>2.9</v>
       </c>
       <c r="R84">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S84">
+        <v>1.44</v>
+      </c>
+      <c r="T84">
+        <v>2.45</v>
+      </c>
+      <c r="U84">
+        <v>3.12</v>
+      </c>
+      <c r="V84">
+        <v>1.28</v>
+      </c>
+      <c r="W84">
+        <v>1.02</v>
+      </c>
+      <c r="X84">
+        <v>1.03</v>
+      </c>
+      <c r="Y84">
         <v>1.36</v>
       </c>
-      <c r="T84">
-        <v>2.73</v>
-      </c>
-      <c r="U84">
-        <v>3</v>
-      </c>
-      <c r="V84">
-        <v>1.33</v>
-      </c>
-      <c r="W84">
-        <v>1.06</v>
-      </c>
-      <c r="X84">
-        <v>1.01</v>
-      </c>
-      <c r="Y84">
-        <v>1.3</v>
-      </c>
       <c r="Z84">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AA84">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB84">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC84">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="AD84">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE84">
         <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG84">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK84">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="O96">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P96">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q96">
-        <v>2.98</v>
+        <v>3.92</v>
       </c>
       <c r="R96">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="S96">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T96">
-        <v>2.54</v>
+        <v>2.73</v>
       </c>
       <c r="U96">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="V96">
+        <v>1.35</v>
+      </c>
+      <c r="W96">
+        <v>1.05</v>
+      </c>
+      <c r="X96">
+        <v>1.01</v>
+      </c>
+      <c r="Y96">
         <v>1.3</v>
       </c>
-      <c r="W96">
-        <v>1.02</v>
-      </c>
-      <c r="X96">
-        <v>1.02</v>
-      </c>
-      <c r="Y96">
-        <v>1.33</v>
-      </c>
       <c r="Z96">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA96">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AB96">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AC96">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD96">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE96">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF96">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG96">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
+        <v>2.25</v>
+      </c>
+      <c r="O97">
         <v>3.25</v>
       </c>
-      <c r="O97">
-        <v>3.3</v>
-      </c>
       <c r="P97">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q97">
-        <v>3.92</v>
+        <v>2.98</v>
       </c>
       <c r="R97">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="S97">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T97">
-        <v>2.73</v>
+        <v>2.54</v>
       </c>
       <c r="U97">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="V97">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W97">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z97">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA97">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AB97">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AC97">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD97">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE97">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF97">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG97">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK97">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,34 +19380,34 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="O117">
+        <v>3.5</v>
+      </c>
+      <c r="P117">
+        <v>2.04</v>
+      </c>
+      <c r="Q117">
+        <v>4.03</v>
+      </c>
+      <c r="R117">
+        <v>2.1</v>
+      </c>
+      <c r="S117">
+        <v>1.33</v>
+      </c>
+      <c r="T117">
         <v>3.2</v>
       </c>
-      <c r="P117">
-        <v>2.47</v>
-      </c>
-      <c r="Q117">
-        <v>3.48</v>
-      </c>
-      <c r="R117">
-        <v>1.92</v>
-      </c>
-      <c r="S117">
-        <v>1.35</v>
-      </c>
-      <c r="T117">
-        <v>2.9</v>
-      </c>
       <c r="U117">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V117">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W117">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X117">
         <v>1.01</v>
@@ -19416,28 +19416,28 @@
         <v>1.26</v>
       </c>
       <c r="Z117">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA117">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AB117">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC117">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AD117">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE117">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF117">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AG117">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AK117">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,80 +19543,80 @@
         </is>
       </c>
       <c r="N118">
+        <v>2.85</v>
+      </c>
+      <c r="O118">
+        <v>3.2</v>
+      </c>
+      <c r="P118">
+        <v>2.41</v>
+      </c>
+      <c r="Q118">
         <v>3.3</v>
       </c>
-      <c r="O118">
-        <v>3.5</v>
-      </c>
-      <c r="P118">
-        <v>2.04</v>
-      </c>
-      <c r="Q118">
-        <v>4.03</v>
-      </c>
       <c r="R118">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S118">
+        <v>1.45</v>
+      </c>
+      <c r="T118">
+        <v>2.45</v>
+      </c>
+      <c r="U118">
+        <v>3.12</v>
+      </c>
+      <c r="V118">
+        <v>1.28</v>
+      </c>
+      <c r="W118">
+        <v>1.01</v>
+      </c>
+      <c r="X118">
+        <v>1.03</v>
+      </c>
+      <c r="Y118">
+        <v>1.38</v>
+      </c>
+      <c r="Z118">
+        <v>2.74</v>
+      </c>
+      <c r="AA118">
+        <v>2.25</v>
+      </c>
+      <c r="AB118">
+        <v>1.59</v>
+      </c>
+      <c r="AC118">
+        <v>3.96</v>
+      </c>
+      <c r="AD118">
+        <v>1.17</v>
+      </c>
+      <c r="AE118">
+        <v>1.02</v>
+      </c>
+      <c r="AF118">
+        <v>1.87</v>
+      </c>
+      <c r="AG118">
+        <v>1.82</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ118">
+        <v>1.28</v>
+      </c>
+      <c r="AK118">
         <v>1.33</v>
-      </c>
-      <c r="T118">
-        <v>3.2</v>
-      </c>
-      <c r="U118">
-        <v>2.78</v>
-      </c>
-      <c r="V118">
-        <v>1.41</v>
-      </c>
-      <c r="W118">
-        <v>1.1</v>
-      </c>
-      <c r="X118">
-        <v>1.01</v>
-      </c>
-      <c r="Y118">
-        <v>1.26</v>
-      </c>
-      <c r="Z118">
-        <v>3.42</v>
-      </c>
-      <c r="AA118">
-        <v>1.82</v>
-      </c>
-      <c r="AB118">
-        <v>1.85</v>
-      </c>
-      <c r="AC118">
-        <v>2.97</v>
-      </c>
-      <c r="AD118">
-        <v>1.3</v>
-      </c>
-      <c r="AE118">
-        <v>1.08</v>
-      </c>
-      <c r="AF118">
-        <v>1.68</v>
-      </c>
-      <c r="AG118">
-        <v>2</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>1.23</v>
-      </c>
-      <c r="AK118">
-        <v>1.25</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O119">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P119">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q119">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="R119">
+        <v>2.2</v>
+      </c>
+      <c r="S119">
+        <v>1.34</v>
+      </c>
+      <c r="T119">
+        <v>2.86</v>
+      </c>
+      <c r="U119">
+        <v>2.62</v>
+      </c>
+      <c r="V119">
+        <v>1.4</v>
+      </c>
+      <c r="W119">
+        <v>1.08</v>
+      </c>
+      <c r="X119">
+        <v>1.01</v>
+      </c>
+      <c r="Y119">
+        <v>1.21</v>
+      </c>
+      <c r="Z119">
+        <v>3.86</v>
+      </c>
+      <c r="AA119">
+        <v>1.76</v>
+      </c>
+      <c r="AB119">
         <v>2</v>
       </c>
-      <c r="S119">
-        <v>1.45</v>
-      </c>
-      <c r="T119">
-        <v>2.45</v>
-      </c>
-      <c r="U119">
-        <v>3.12</v>
-      </c>
-      <c r="V119">
-        <v>1.28</v>
-      </c>
-      <c r="W119">
-        <v>1.01</v>
-      </c>
-      <c r="X119">
-        <v>1.03</v>
-      </c>
-      <c r="Y119">
-        <v>1.38</v>
-      </c>
-      <c r="Z119">
-        <v>2.74</v>
-      </c>
-      <c r="AA119">
-        <v>2.25</v>
-      </c>
-      <c r="AB119">
-        <v>1.59</v>
-      </c>
       <c r="AC119">
-        <v>3.96</v>
+        <v>2.83</v>
       </c>
       <c r="AD119">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AE119">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AF119">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AG119">
-        <v>1.82</v>
+        <v>2.16</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK119">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,80 +19869,80 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q120">
-        <v>2.75</v>
+        <v>3.48</v>
       </c>
       <c r="R120">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="S120">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T120">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="U120">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V120">
         <v>1.4</v>
       </c>
       <c r="W120">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X120">
         <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z120">
-        <v>3.86</v>
+        <v>3.2</v>
       </c>
       <c r="AA120">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AB120">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AC120">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AD120">
+        <v>1.31</v>
+      </c>
+      <c r="AE120">
+        <v>1.06</v>
+      </c>
+      <c r="AF120">
+        <v>1.69</v>
+      </c>
+      <c r="AG120">
+        <v>2.03</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ120">
+        <v>1.5</v>
+      </c>
+      <c r="AK120">
         <v>1.33</v>
-      </c>
-      <c r="AE120">
-        <v>1.09</v>
-      </c>
-      <c r="AF120">
-        <v>1.65</v>
-      </c>
-      <c r="AG120">
-        <v>2.16</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>1.25</v>
-      </c>
-      <c r="AK120">
-        <v>1.62</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -21212,10 +21212,10 @@
         <v>0</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC128">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.26</v>
+        <v>2.26</v>
       </c>
       <c r="O156">
-        <v>6.55</v>
+        <v>3.77</v>
       </c>
       <c r="P156">
-        <v>11.4</v>
+        <v>3.09</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25776,16 +25776,16 @@
         <v>0</v>
       </c>
       <c r="AA156">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB156">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC156">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD156">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="O157">
-        <v>3.77</v>
+        <v>4.07</v>
       </c>
       <c r="P157">
-        <v>3.09</v>
+        <v>3.57</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -25939,16 +25939,16 @@
         <v>0</v>
       </c>
       <c r="AA157">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB157">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC157">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD157">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.98</v>
+        <v>1.26</v>
       </c>
       <c r="O158">
-        <v>4.07</v>
+        <v>6.55</v>
       </c>
       <c r="P158">
-        <v>3.57</v>
+        <v>11.4</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26108,10 +26108,10 @@
         <v>0</v>
       </c>
       <c r="AC158">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD158">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AE158">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="O3">
-        <v>3.38</v>
+        <v>2.98</v>
       </c>
       <c r="P3">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="Q3">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="R3">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
-        <v>3.18</v>
+        <v>2.5</v>
       </c>
       <c r="U3">
-        <v>2.67</v>
+        <v>3.12</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
         <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="Z3">
-        <v>3.72</v>
+        <v>2.72</v>
       </c>
       <c r="AA3">
-        <v>1.74</v>
+        <v>2.29</v>
       </c>
       <c r="AB3">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="AC3">
-        <v>2.99</v>
+        <v>4.33</v>
       </c>
       <c r="AD3">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AE3">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AG3">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="O4">
-        <v>2.98</v>
+        <v>3.24</v>
       </c>
       <c r="P4">
-        <v>2.49</v>
+        <v>2.09</v>
       </c>
       <c r="Q4">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S4">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="U4">
-        <v>3.12</v>
+        <v>2.65</v>
       </c>
       <c r="V4">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W4">
         <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="Z4">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="AA4">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="AB4">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AC4">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AD4">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.49</v>
+        <v>3.28</v>
       </c>
       <c r="O5">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="P5">
-        <v>5.47</v>
+        <v>2.03</v>
       </c>
       <c r="Q5">
-        <v>1.99</v>
+        <v>3.99</v>
       </c>
       <c r="R5">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U5">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="V5">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z5">
-        <v>4.01</v>
+        <v>3.42</v>
       </c>
       <c r="AA5">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AB5">
         <v>1.94</v>
       </c>
       <c r="AC5">
-        <v>2.66</v>
+        <v>3.07</v>
       </c>
       <c r="AD5">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF5">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,31 +1287,31 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.38</v>
+        <v>1.49</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="P6">
-        <v>2.47</v>
+        <v>5.47</v>
       </c>
       <c r="Q6">
-        <v>3.22</v>
+        <v>1.99</v>
       </c>
       <c r="R6">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T6">
         <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="V6">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
         <v>1.11</v>
@@ -1320,31 +1320,31 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="AA6">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AB6">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AC6">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AD6">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE6">
         <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AG6">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>1.39</v>
+        <v>2.21</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.28</v>
+        <v>2.23</v>
       </c>
       <c r="O7">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="P7">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="Q7">
-        <v>3.99</v>
+        <v>3.13</v>
       </c>
       <c r="R7">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="U7">
-        <v>2.51</v>
+        <v>3.22</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="Z7">
-        <v>3.42</v>
+        <v>2.74</v>
       </c>
       <c r="AA7">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AB7">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="AC7">
-        <v>3.07</v>
+        <v>3.74</v>
       </c>
       <c r="AD7">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AE7">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AG7">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.14</v>
+        <v>1.63</v>
       </c>
       <c r="O8">
-        <v>3.24</v>
+        <v>3.48</v>
       </c>
       <c r="P8">
-        <v>2.09</v>
+        <v>4.87</v>
       </c>
       <c r="Q8">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="R8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T8">
-        <v>2.95</v>
+        <v>2.64</v>
       </c>
       <c r="U8">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
         <v>1.06</v>
@@ -1646,47 +1646,47 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z8">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA8">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AB8">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC8">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD8">
+        <v>1.22</v>
+      </c>
+      <c r="AE8">
+        <v>1.04</v>
+      </c>
+      <c r="AF8">
+        <v>1.85</v>
+      </c>
+      <c r="AG8">
+        <v>1.75</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.3</v>
       </c>
-      <c r="AE8">
-        <v>1.11</v>
-      </c>
-      <c r="AF8">
-        <v>1.73</v>
-      </c>
-      <c r="AG8">
-        <v>1.98</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.24</v>
-      </c>
       <c r="AK8">
-        <v>1.27</v>
+        <v>2.05</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="O9">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q9">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="R9">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T9">
-        <v>2.42</v>
+        <v>2.98</v>
       </c>
       <c r="U9">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
+        <v>1.05</v>
+      </c>
+      <c r="X9">
+        <v>1.01</v>
+      </c>
+      <c r="Y9">
+        <v>1.26</v>
+      </c>
+      <c r="Z9">
+        <v>3.43</v>
+      </c>
+      <c r="AA9">
+        <v>1.97</v>
+      </c>
+      <c r="AB9">
+        <v>1.79</v>
+      </c>
+      <c r="AC9">
+        <v>3.14</v>
+      </c>
+      <c r="AD9">
+        <v>1.27</v>
+      </c>
+      <c r="AE9">
         <v>1.07</v>
       </c>
-      <c r="X9">
-        <v>1.04</v>
-      </c>
-      <c r="Y9">
-        <v>1.35</v>
-      </c>
-      <c r="Z9">
-        <v>2.74</v>
-      </c>
-      <c r="AA9">
-        <v>2.19</v>
-      </c>
-      <c r="AB9">
-        <v>1.61</v>
-      </c>
-      <c r="AC9">
-        <v>3.74</v>
-      </c>
-      <c r="AD9">
-        <v>1.19</v>
-      </c>
-      <c r="AE9">
-        <v>1.03</v>
-      </c>
       <c r="AF9">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG9">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.63</v>
+        <v>2.32</v>
       </c>
       <c r="O10">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="P10">
-        <v>4.87</v>
+        <v>2.55</v>
       </c>
       <c r="Q10">
-        <v>2.23</v>
+        <v>2.93</v>
       </c>
       <c r="R10">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S10">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.64</v>
+        <v>3.18</v>
       </c>
       <c r="U10">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="V10">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>3.08</v>
+        <v>3.72</v>
       </c>
       <c r="AA10">
+        <v>1.74</v>
+      </c>
+      <c r="AB10">
         <v>2.02</v>
       </c>
-      <c r="AB10">
-        <v>1.77</v>
-      </c>
       <c r="AC10">
-        <v>3.48</v>
+        <v>2.99</v>
       </c>
       <c r="AD10">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG10">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK10">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="Q11">
+        <v>3.22</v>
+      </c>
+      <c r="R11">
+        <v>2.17</v>
+      </c>
+      <c r="S11">
+        <v>1.3</v>
+      </c>
+      <c r="T11">
         <v>3.2</v>
       </c>
-      <c r="R11">
+      <c r="U11">
+        <v>2.45</v>
+      </c>
+      <c r="V11">
+        <v>1.49</v>
+      </c>
+      <c r="W11">
+        <v>1.11</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
+        <v>1.17</v>
+      </c>
+      <c r="Z11">
+        <v>4</v>
+      </c>
+      <c r="AA11">
+        <v>1.7</v>
+      </c>
+      <c r="AB11">
         <v>2.1</v>
       </c>
-      <c r="S11">
+      <c r="AC11">
+        <v>2.77</v>
+      </c>
+      <c r="AD11">
         <v>1.37</v>
       </c>
-      <c r="T11">
-        <v>2.98</v>
-      </c>
-      <c r="U11">
-        <v>2.86</v>
-      </c>
-      <c r="V11">
-        <v>1.37</v>
-      </c>
-      <c r="W11">
-        <v>1.05</v>
-      </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
-      <c r="Y11">
+      <c r="AE11">
+        <v>1.11</v>
+      </c>
+      <c r="AF11">
+        <v>1.55</v>
+      </c>
+      <c r="AG11">
+        <v>2.25</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
         <v>1.26</v>
       </c>
-      <c r="Z11">
-        <v>3.43</v>
-      </c>
-      <c r="AA11">
-        <v>1.97</v>
-      </c>
-      <c r="AB11">
-        <v>1.79</v>
-      </c>
-      <c r="AC11">
-        <v>3.14</v>
-      </c>
-      <c r="AD11">
-        <v>1.27</v>
-      </c>
-      <c r="AE11">
-        <v>1.07</v>
-      </c>
-      <c r="AF11">
-        <v>1.7</v>
-      </c>
-      <c r="AG11">
-        <v>2</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.28</v>
-      </c>
       <c r="AK11">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,34 +8296,34 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.92</v>
+        <v>2.19</v>
       </c>
       <c r="O49">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="P49">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="Q49">
-        <v>3.26</v>
+        <v>2.43</v>
       </c>
       <c r="R49">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U49">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V49">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
         <v>1.01</v>
@@ -8332,28 +8332,28 @@
         <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AC49">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD49">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AG49">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
+        <v>1.27</v>
+      </c>
+      <c r="AK49">
         <v>1.65</v>
-      </c>
-      <c r="AK49">
-        <v>1.33</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="O50">
-        <v>3.02</v>
+        <v>3.74</v>
       </c>
       <c r="P50">
-        <v>2.58</v>
+        <v>2.13</v>
       </c>
       <c r="Q50">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="R50">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.96</v>
+        <v>2.45</v>
       </c>
       <c r="V50">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA50">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="AB50">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC50">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="AD50">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG50">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.09</v>
+        <v>2.73</v>
       </c>
       <c r="O51">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
       <c r="P51">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="Q51">
+        <v>3.18</v>
+      </c>
+      <c r="R51">
+        <v>2.18</v>
+      </c>
+      <c r="S51">
+        <v>1.38</v>
+      </c>
+      <c r="T51">
         <v>2.75</v>
       </c>
-      <c r="R51">
-        <v>2.19</v>
-      </c>
-      <c r="S51">
-        <v>1.26</v>
-      </c>
-      <c r="T51">
-        <v>3.4</v>
-      </c>
       <c r="U51">
-        <v>2.32</v>
+        <v>2.96</v>
       </c>
       <c r="V51">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AA51">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AB51">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AC51">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="AD51">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF51">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG51">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AK51">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,77 +8785,77 @@
         </is>
       </c>
       <c r="N52">
+        <v>2.09</v>
+      </c>
+      <c r="O52">
+        <v>3.54</v>
+      </c>
+      <c r="P52">
+        <v>3.15</v>
+      </c>
+      <c r="Q52">
+        <v>2.75</v>
+      </c>
+      <c r="R52">
         <v>2.19</v>
       </c>
-      <c r="O52">
-        <v>3.62</v>
-      </c>
-      <c r="P52">
-        <v>2.88</v>
-      </c>
-      <c r="Q52">
-        <v>2.43</v>
-      </c>
-      <c r="R52">
-        <v>2.21</v>
-      </c>
       <c r="S52">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T52">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U52">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z52">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA52">
         <v>1.83</v>
       </c>
       <c r="AB52">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AC52">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="AD52">
+        <v>1.43</v>
+      </c>
+      <c r="AE52">
+        <v>1.13</v>
+      </c>
+      <c r="AF52">
+        <v>1.55</v>
+      </c>
+      <c r="AG52">
+        <v>2.25</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.33</v>
-      </c>
-      <c r="AE52">
-        <v>1.12</v>
-      </c>
-      <c r="AF52">
-        <v>1.64</v>
-      </c>
-      <c r="AG52">
-        <v>2.13</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.27</v>
       </c>
       <c r="AK52">
         <v>1.65</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="O62">
-        <v>3.48</v>
+        <v>5</v>
       </c>
       <c r="P62">
-        <v>3.94</v>
+        <v>6.4</v>
       </c>
       <c r="Q62">
-        <v>2.39</v>
+        <v>1.74</v>
       </c>
       <c r="R62">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="S62">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="T62">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="U62">
-        <v>2.71</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="W62">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="X62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="Z62">
-        <v>3.05</v>
+        <v>5.85</v>
       </c>
       <c r="AA62">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>1.79</v>
+        <v>2.87</v>
       </c>
       <c r="AC62">
-        <v>3.44</v>
+        <v>2.02</v>
       </c>
       <c r="AD62">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="AE62">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AF62">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK62">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,80 +10578,80 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="O63">
-        <v>5</v>
+        <v>3.48</v>
       </c>
       <c r="P63">
-        <v>6.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q63">
-        <v>1.74</v>
+        <v>2.39</v>
       </c>
       <c r="R63">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="S63">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="T63">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="U63">
-        <v>1.95</v>
+        <v>2.71</v>
       </c>
       <c r="V63">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="W63">
+        <v>1.06</v>
+      </c>
+      <c r="X63">
+        <v>1.03</v>
+      </c>
+      <c r="Y63">
+        <v>1.26</v>
+      </c>
+      <c r="Z63">
+        <v>3.05</v>
+      </c>
+      <c r="AA63">
+        <v>2.01</v>
+      </c>
+      <c r="AB63">
+        <v>1.79</v>
+      </c>
+      <c r="AC63">
+        <v>3.44</v>
+      </c>
+      <c r="AD63">
+        <v>1.26</v>
+      </c>
+      <c r="AE63">
+        <v>1.06</v>
+      </c>
+      <c r="AF63">
+        <v>1.82</v>
+      </c>
+      <c r="AG63">
+        <v>1.88</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
         <v>1.19</v>
       </c>
-      <c r="X63">
-        <v>1.01</v>
-      </c>
-      <c r="Y63">
-        <v>1.07</v>
-      </c>
-      <c r="Z63">
-        <v>5.85</v>
-      </c>
-      <c r="AA63">
-        <v>1.4</v>
-      </c>
-      <c r="AB63">
-        <v>2.87</v>
-      </c>
-      <c r="AC63">
-        <v>2.02</v>
-      </c>
-      <c r="AD63">
-        <v>1.77</v>
-      </c>
-      <c r="AE63">
-        <v>1.33</v>
-      </c>
-      <c r="AF63">
-        <v>1.57</v>
-      </c>
-      <c r="AG63">
-        <v>2.26</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.13</v>
-      </c>
       <c r="AK63">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.98</v>
+        <v>1.26</v>
       </c>
       <c r="O157">
-        <v>4.07</v>
+        <v>6.55</v>
       </c>
       <c r="P157">
-        <v>3.57</v>
+        <v>11.4</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -25945,10 +25945,10 @@
         <v>0</v>
       </c>
       <c r="AC157">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD157">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AE157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.26</v>
+        <v>1.98</v>
       </c>
       <c r="O158">
-        <v>6.55</v>
+        <v>4.07</v>
       </c>
       <c r="P158">
-        <v>11.4</v>
+        <v>3.57</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26108,10 +26108,10 @@
         <v>0</v>
       </c>
       <c r="AC158">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AD158">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AE158">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G4">
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="O4">
         <v>3.24</v>
       </c>
       <c r="P4">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="Q4">
-        <v>3.5</v>
+        <v>3.99</v>
       </c>
       <c r="R4">
         <v>2.08</v>
@@ -979,59 +979,59 @@
         <v>1.33</v>
       </c>
       <c r="T4">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U4">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="V4">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z4">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA4">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AB4">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC4">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="AD4">
+        <v>1.31</v>
+      </c>
+      <c r="AE4">
+        <v>1.09</v>
+      </c>
+      <c r="AF4">
+        <v>1.67</v>
+      </c>
+      <c r="AG4">
+        <v>2.02</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.3</v>
-      </c>
-      <c r="AE4">
-        <v>1.11</v>
-      </c>
-      <c r="AF4">
-        <v>1.73</v>
-      </c>
-      <c r="AG4">
-        <v>1.98</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.24</v>
       </c>
       <c r="AK4">
         <v>1.27</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.28</v>
+        <v>1.63</v>
       </c>
       <c r="O5">
-        <v>3.24</v>
+        <v>3.48</v>
       </c>
       <c r="P5">
-        <v>2.03</v>
+        <v>4.87</v>
       </c>
       <c r="Q5">
-        <v>3.99</v>
+        <v>2.23</v>
       </c>
       <c r="R5">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T5">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="U5">
-        <v>2.51</v>
+        <v>2.89</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z5">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AA5">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB5">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AC5">
-        <v>3.07</v>
+        <v>3.48</v>
       </c>
       <c r="AD5">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AE5">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG5">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>1.27</v>
+        <v>2.05</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="O6">
-        <v>3.98</v>
+        <v>2.99</v>
       </c>
       <c r="P6">
-        <v>5.47</v>
+        <v>3.1</v>
       </c>
       <c r="Q6">
-        <v>1.99</v>
+        <v>3.13</v>
       </c>
       <c r="R6">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="S6">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="T6">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="U6">
-        <v>2.57</v>
+        <v>3.22</v>
       </c>
       <c r="V6">
+        <v>1.35</v>
+      </c>
+      <c r="W6">
+        <v>1.07</v>
+      </c>
+      <c r="X6">
+        <v>1.04</v>
+      </c>
+      <c r="Y6">
+        <v>1.35</v>
+      </c>
+      <c r="Z6">
+        <v>2.74</v>
+      </c>
+      <c r="AA6">
+        <v>2.19</v>
+      </c>
+      <c r="AB6">
+        <v>1.61</v>
+      </c>
+      <c r="AC6">
+        <v>3.74</v>
+      </c>
+      <c r="AD6">
+        <v>1.19</v>
+      </c>
+      <c r="AE6">
+        <v>1.03</v>
+      </c>
+      <c r="AF6">
+        <v>1.84</v>
+      </c>
+      <c r="AG6">
+        <v>1.82</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.29</v>
+      </c>
+      <c r="AK6">
         <v>1.48</v>
-      </c>
-      <c r="W6">
-        <v>1.11</v>
-      </c>
-      <c r="X6">
-        <v>1.03</v>
-      </c>
-      <c r="Y6">
-        <v>1.18</v>
-      </c>
-      <c r="Z6">
-        <v>4.01</v>
-      </c>
-      <c r="AA6">
-        <v>1.82</v>
-      </c>
-      <c r="AB6">
-        <v>1.94</v>
-      </c>
-      <c r="AC6">
-        <v>2.66</v>
-      </c>
-      <c r="AD6">
-        <v>1.41</v>
-      </c>
-      <c r="AE6">
-        <v>1.11</v>
-      </c>
-      <c r="AF6">
-        <v>1.71</v>
-      </c>
-      <c r="AG6">
-        <v>2</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.2</v>
-      </c>
-      <c r="AK6">
-        <v>2.21</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="O7">
-        <v>2.99</v>
+        <v>3.38</v>
       </c>
       <c r="P7">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q7">
-        <v>3.13</v>
+        <v>2.93</v>
       </c>
       <c r="R7">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="S7">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.42</v>
+        <v>3.18</v>
       </c>
       <c r="U7">
-        <v>3.22</v>
+        <v>2.67</v>
       </c>
       <c r="V7">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>1.07</v>
@@ -1483,31 +1483,31 @@
         <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>2.74</v>
+        <v>3.72</v>
       </c>
       <c r="AA7">
-        <v>2.19</v>
+        <v>1.74</v>
       </c>
       <c r="AB7">
+        <v>2.02</v>
+      </c>
+      <c r="AC7">
+        <v>2.99</v>
+      </c>
+      <c r="AD7">
+        <v>1.32</v>
+      </c>
+      <c r="AE7">
+        <v>1.08</v>
+      </c>
+      <c r="AF7">
         <v>1.61</v>
       </c>
-      <c r="AC7">
-        <v>3.74</v>
-      </c>
-      <c r="AD7">
-        <v>1.19</v>
-      </c>
-      <c r="AE7">
-        <v>1.03</v>
-      </c>
-      <c r="AF7">
-        <v>1.84</v>
-      </c>
       <c r="AG7">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK7">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="O8">
-        <v>3.48</v>
+        <v>3.98</v>
       </c>
       <c r="P8">
-        <v>4.87</v>
+        <v>5.47</v>
       </c>
       <c r="Q8">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="AA8">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AB8">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AC8">
-        <v>3.48</v>
+        <v>2.66</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AE8">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG8">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P9">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="Q9">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S9">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="U9">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="V9">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9">
         <v>1.26</v>
       </c>
       <c r="Z9">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="AA9">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB9">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC9">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD9">
+        <v>1.3</v>
+      </c>
+      <c r="AE9">
+        <v>1.11</v>
+      </c>
+      <c r="AF9">
+        <v>1.73</v>
+      </c>
+      <c r="AG9">
+        <v>1.98</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.24</v>
+      </c>
+      <c r="AK9">
         <v>1.27</v>
-      </c>
-      <c r="AE9">
-        <v>1.07</v>
-      </c>
-      <c r="AF9">
-        <v>1.7</v>
-      </c>
-      <c r="AG9">
-        <v>2</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.28</v>
-      </c>
-      <c r="AK9">
-        <v>1.38</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
+        <v>2.6</v>
+      </c>
+      <c r="O10">
+        <v>3.3</v>
+      </c>
+      <c r="P10">
         <v>2.32</v>
       </c>
-      <c r="O10">
-        <v>3.38</v>
-      </c>
-      <c r="P10">
-        <v>2.55</v>
-      </c>
       <c r="Q10">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="R10">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="U10">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
+        <v>1.05</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>1.26</v>
+      </c>
+      <c r="Z10">
+        <v>3.43</v>
+      </c>
+      <c r="AA10">
+        <v>1.97</v>
+      </c>
+      <c r="AB10">
+        <v>1.79</v>
+      </c>
+      <c r="AC10">
+        <v>3.14</v>
+      </c>
+      <c r="AD10">
+        <v>1.27</v>
+      </c>
+      <c r="AE10">
         <v>1.07</v>
       </c>
-      <c r="X10">
-        <v>1.04</v>
-      </c>
-      <c r="Y10">
-        <v>1.2</v>
-      </c>
-      <c r="Z10">
-        <v>3.72</v>
-      </c>
-      <c r="AA10">
-        <v>1.74</v>
-      </c>
-      <c r="AB10">
-        <v>2.02</v>
-      </c>
-      <c r="AC10">
-        <v>2.99</v>
-      </c>
-      <c r="AD10">
-        <v>1.32</v>
-      </c>
-      <c r="AE10">
-        <v>1.08</v>
-      </c>
       <c r="AF10">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG10">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="O48">
-        <v>2.91</v>
+        <v>3.62</v>
       </c>
       <c r="P48">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="Q48">
-        <v>3.24</v>
+        <v>2.43</v>
       </c>
       <c r="R48">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S48">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T48">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="U48">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="V48">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
         <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
         <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>4.07</v>
+        <v>3.5</v>
       </c>
       <c r="AA48">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC48">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD48">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG48">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK48">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.19</v>
+        <v>2.73</v>
       </c>
       <c r="O49">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="P49">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="Q49">
-        <v>2.43</v>
+        <v>3.18</v>
       </c>
       <c r="R49">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S49">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T49">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U49">
-        <v>2.47</v>
+        <v>2.96</v>
       </c>
       <c r="V49">
+        <v>1.4</v>
+      </c>
+      <c r="W49">
+        <v>1.06</v>
+      </c>
+      <c r="X49">
+        <v>1.03</v>
+      </c>
+      <c r="Y49">
+        <v>1.3</v>
+      </c>
+      <c r="Z49">
+        <v>3.2</v>
+      </c>
+      <c r="AA49">
+        <v>1.94</v>
+      </c>
+      <c r="AB49">
+        <v>1.8</v>
+      </c>
+      <c r="AC49">
+        <v>3.28</v>
+      </c>
+      <c r="AD49">
+        <v>1.25</v>
+      </c>
+      <c r="AE49">
+        <v>1.05</v>
+      </c>
+      <c r="AF49">
+        <v>1.73</v>
+      </c>
+      <c r="AG49">
+        <v>1.95</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.41</v>
+      </c>
+      <c r="AK49">
         <v>1.44</v>
-      </c>
-      <c r="W49">
-        <v>1.07</v>
-      </c>
-      <c r="X49">
-        <v>1.01</v>
-      </c>
-      <c r="Y49">
-        <v>1.22</v>
-      </c>
-      <c r="Z49">
-        <v>3.5</v>
-      </c>
-      <c r="AA49">
-        <v>1.83</v>
-      </c>
-      <c r="AB49">
-        <v>1.93</v>
-      </c>
-      <c r="AC49">
-        <v>2.83</v>
-      </c>
-      <c r="AD49">
-        <v>1.33</v>
-      </c>
-      <c r="AE49">
-        <v>1.12</v>
-      </c>
-      <c r="AF49">
-        <v>1.64</v>
-      </c>
-      <c r="AG49">
-        <v>2.13</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.27</v>
-      </c>
-      <c r="AK49">
-        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.73</v>
+        <v>2.09</v>
       </c>
       <c r="O51">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="P51">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="Q51">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="R51">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S51">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="T51">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U51">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="V51">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA51">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AC51">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AD51">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AE51">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF51">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG51">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK51">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.09</v>
+        <v>2.83</v>
       </c>
       <c r="O52">
-        <v>3.54</v>
+        <v>2.91</v>
       </c>
       <c r="P52">
-        <v>3.15</v>
+        <v>2.57</v>
       </c>
       <c r="Q52">
+        <v>3.24</v>
+      </c>
+      <c r="R52">
+        <v>2.25</v>
+      </c>
+      <c r="S52">
+        <v>1.37</v>
+      </c>
+      <c r="T52">
+        <v>2.7</v>
+      </c>
+      <c r="U52">
         <v>2.75</v>
       </c>
-      <c r="R52">
-        <v>2.19</v>
-      </c>
-      <c r="S52">
-        <v>1.26</v>
-      </c>
-      <c r="T52">
-        <v>3.4</v>
-      </c>
-      <c r="U52">
-        <v>2.32</v>
-      </c>
       <c r="V52">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.33</v>
+        <v>4.07</v>
       </c>
       <c r="AA52">
+        <v>2.03</v>
+      </c>
+      <c r="AB52">
         <v>1.83</v>
       </c>
-      <c r="AB52">
-        <v>2.03</v>
-      </c>
       <c r="AC52">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="AD52">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE52">
         <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK52">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O83">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="P83">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="Q83">
         <v>2.9</v>
       </c>
       <c r="R83">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S83">
+        <v>1.44</v>
+      </c>
+      <c r="T83">
+        <v>2.45</v>
+      </c>
+      <c r="U83">
+        <v>3.12</v>
+      </c>
+      <c r="V83">
+        <v>1.28</v>
+      </c>
+      <c r="W83">
+        <v>1.02</v>
+      </c>
+      <c r="X83">
+        <v>1.03</v>
+      </c>
+      <c r="Y83">
         <v>1.36</v>
       </c>
-      <c r="T83">
-        <v>2.73</v>
-      </c>
-      <c r="U83">
-        <v>3</v>
-      </c>
-      <c r="V83">
-        <v>1.33</v>
-      </c>
-      <c r="W83">
-        <v>1.06</v>
-      </c>
-      <c r="X83">
-        <v>1.01</v>
-      </c>
-      <c r="Y83">
-        <v>1.3</v>
-      </c>
       <c r="Z83">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AA83">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB83">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC83">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="AD83">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE83">
         <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG83">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK83">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="O84">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="P84">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="Q84">
         <v>2.9</v>
       </c>
       <c r="R84">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S84">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T84">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="U84">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="V84">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W84">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X84">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z84">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AA84">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB84">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC84">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="AD84">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE84">
         <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG84">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q94">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="O6">
-        <v>2.99</v>
+        <v>3.98</v>
       </c>
       <c r="P6">
-        <v>3.1</v>
+        <v>5.47</v>
       </c>
       <c r="Q6">
-        <v>3.13</v>
+        <v>1.99</v>
       </c>
       <c r="R6">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="S6">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="T6">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>3.22</v>
+        <v>2.57</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>2.74</v>
+        <v>4.01</v>
       </c>
       <c r="AA6">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="AB6">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AC6">
-        <v>3.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD6">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AG6">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>1.48</v>
+        <v>2.21</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O7">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="Q7">
-        <v>2.93</v>
+        <v>3.22</v>
       </c>
       <c r="R7">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U7">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AA7">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB7">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="AD7">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE7">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG7">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK7">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.49</v>
+        <v>3.14</v>
       </c>
       <c r="O8">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="P8">
-        <v>5.47</v>
+        <v>2.09</v>
       </c>
       <c r="Q8">
+        <v>3.5</v>
+      </c>
+      <c r="R8">
+        <v>2.08</v>
+      </c>
+      <c r="S8">
+        <v>1.33</v>
+      </c>
+      <c r="T8">
+        <v>2.95</v>
+      </c>
+      <c r="U8">
+        <v>2.65</v>
+      </c>
+      <c r="V8">
+        <v>1.38</v>
+      </c>
+      <c r="W8">
+        <v>1.06</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1.26</v>
+      </c>
+      <c r="Z8">
+        <v>3.2</v>
+      </c>
+      <c r="AA8">
         <v>1.99</v>
       </c>
-      <c r="R8">
-        <v>2.28</v>
-      </c>
-      <c r="S8">
-        <v>1.32</v>
-      </c>
-      <c r="T8">
+      <c r="AB8">
+        <v>1.78</v>
+      </c>
+      <c r="AC8">
         <v>3.2</v>
       </c>
-      <c r="U8">
-        <v>2.57</v>
-      </c>
-      <c r="V8">
-        <v>1.48</v>
-      </c>
-      <c r="W8">
-        <v>1.11</v>
-      </c>
-      <c r="X8">
-        <v>1.03</v>
-      </c>
-      <c r="Y8">
-        <v>1.18</v>
-      </c>
-      <c r="Z8">
-        <v>4.01</v>
-      </c>
-      <c r="AA8">
-        <v>1.82</v>
-      </c>
-      <c r="AB8">
-        <v>1.94</v>
-      </c>
-      <c r="AC8">
-        <v>2.66</v>
-      </c>
       <c r="AD8">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE8">
         <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.14</v>
+        <v>2.23</v>
       </c>
       <c r="O9">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="P9">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="R9">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T9">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="U9">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z9">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA9">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="AB9">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AC9">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD9">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG9">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P11">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="Q11">
-        <v>3.22</v>
+        <v>2.93</v>
       </c>
       <c r="R11">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="V11">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="AA11">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB11">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC11">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="AD11">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE11">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AG11">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AK11">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.19</v>
+        <v>2.73</v>
       </c>
       <c r="O48">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="P48">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="Q48">
-        <v>2.43</v>
+        <v>3.18</v>
       </c>
       <c r="R48">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S48">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T48">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U48">
-        <v>2.47</v>
+        <v>2.96</v>
       </c>
       <c r="V48">
+        <v>1.4</v>
+      </c>
+      <c r="W48">
+        <v>1.06</v>
+      </c>
+      <c r="X48">
+        <v>1.03</v>
+      </c>
+      <c r="Y48">
+        <v>1.3</v>
+      </c>
+      <c r="Z48">
+        <v>3.2</v>
+      </c>
+      <c r="AA48">
+        <v>1.94</v>
+      </c>
+      <c r="AB48">
+        <v>1.8</v>
+      </c>
+      <c r="AC48">
+        <v>3.28</v>
+      </c>
+      <c r="AD48">
+        <v>1.25</v>
+      </c>
+      <c r="AE48">
+        <v>1.05</v>
+      </c>
+      <c r="AF48">
+        <v>1.73</v>
+      </c>
+      <c r="AG48">
+        <v>1.95</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.41</v>
+      </c>
+      <c r="AK48">
         <v>1.44</v>
-      </c>
-      <c r="W48">
-        <v>1.07</v>
-      </c>
-      <c r="X48">
-        <v>1.01</v>
-      </c>
-      <c r="Y48">
-        <v>1.22</v>
-      </c>
-      <c r="Z48">
-        <v>3.5</v>
-      </c>
-      <c r="AA48">
-        <v>1.83</v>
-      </c>
-      <c r="AB48">
-        <v>1.93</v>
-      </c>
-      <c r="AC48">
-        <v>2.83</v>
-      </c>
-      <c r="AD48">
-        <v>1.33</v>
-      </c>
-      <c r="AE48">
-        <v>1.12</v>
-      </c>
-      <c r="AF48">
-        <v>1.64</v>
-      </c>
-      <c r="AG48">
-        <v>2.13</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.27</v>
-      </c>
-      <c r="AK48">
-        <v>1.65</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="O49">
-        <v>3.02</v>
+        <v>3.74</v>
       </c>
       <c r="P49">
-        <v>2.58</v>
+        <v>2.13</v>
       </c>
       <c r="Q49">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="R49">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S49">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>2.96</v>
+        <v>2.45</v>
       </c>
       <c r="V49">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA49">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="AB49">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC49">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="AD49">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG49">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AK49">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.92</v>
+        <v>2.09</v>
       </c>
       <c r="O50">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="P50">
-        <v>2.13</v>
+        <v>3.15</v>
       </c>
       <c r="Q50">
-        <v>3.26</v>
+        <v>2.75</v>
       </c>
       <c r="R50">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="V50">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W50">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA50">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AB50">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AC50">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE50">
         <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
+        <v>1.33</v>
+      </c>
+      <c r="AK50">
         <v>1.65</v>
-      </c>
-      <c r="AK50">
-        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.09</v>
+        <v>2.83</v>
       </c>
       <c r="O51">
-        <v>3.54</v>
+        <v>2.91</v>
       </c>
       <c r="P51">
-        <v>3.15</v>
+        <v>2.57</v>
       </c>
       <c r="Q51">
+        <v>3.24</v>
+      </c>
+      <c r="R51">
+        <v>2.25</v>
+      </c>
+      <c r="S51">
+        <v>1.37</v>
+      </c>
+      <c r="T51">
+        <v>2.7</v>
+      </c>
+      <c r="U51">
         <v>2.75</v>
       </c>
-      <c r="R51">
-        <v>2.19</v>
-      </c>
-      <c r="S51">
-        <v>1.26</v>
-      </c>
-      <c r="T51">
-        <v>3.4</v>
-      </c>
-      <c r="U51">
-        <v>2.32</v>
-      </c>
       <c r="V51">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.33</v>
+        <v>4.07</v>
       </c>
       <c r="AA51">
+        <v>2.03</v>
+      </c>
+      <c r="AB51">
         <v>1.83</v>
       </c>
-      <c r="AB51">
-        <v>2.03</v>
-      </c>
       <c r="AC51">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="AD51">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE51">
         <v>1.13</v>
       </c>
       <c r="AF51">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK51">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="O52">
-        <v>2.91</v>
+        <v>3.62</v>
       </c>
       <c r="P52">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="Q52">
-        <v>3.24</v>
+        <v>2.43</v>
       </c>
       <c r="R52">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S52">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T52">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="U52">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="V52">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
         <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
         <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.07</v>
+        <v>3.5</v>
       </c>
       <c r="AA52">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AB52">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC52">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD52">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG52">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK52">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,25 +13512,25 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.32</v>
+        <v>1.59</v>
       </c>
       <c r="O81">
-        <v>3.14</v>
+        <v>3.52</v>
       </c>
       <c r="P81">
-        <v>2.68</v>
+        <v>5.13</v>
       </c>
       <c r="Q81">
-        <v>3</v>
+        <v>1.98</v>
       </c>
       <c r="R81">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S81">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T81">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="U81">
         <v>2.89</v>
@@ -13539,37 +13539,37 @@
         <v>1.32</v>
       </c>
       <c r="W81">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X81">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z81">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA81">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB81">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AC81">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD81">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE81">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF81">
-        <v>1.76</v>
+        <v>2.13</v>
       </c>
       <c r="AG81">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK81">
-        <v>1.46</v>
+        <v>2.46</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,25 +13675,25 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.59</v>
+        <v>2.32</v>
       </c>
       <c r="O82">
-        <v>3.52</v>
+        <v>3.14</v>
       </c>
       <c r="P82">
-        <v>5.13</v>
+        <v>2.68</v>
       </c>
       <c r="Q82">
-        <v>1.98</v>
+        <v>3</v>
       </c>
       <c r="R82">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="S82">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T82">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="U82">
         <v>2.89</v>
@@ -13702,37 +13702,37 @@
         <v>1.32</v>
       </c>
       <c r="W82">
+        <v>1.06</v>
+      </c>
+      <c r="X82">
+        <v>1</v>
+      </c>
+      <c r="Y82">
+        <v>1.28</v>
+      </c>
+      <c r="Z82">
+        <v>3.05</v>
+      </c>
+      <c r="AA82">
+        <v>1.98</v>
+      </c>
+      <c r="AB82">
+        <v>1.71</v>
+      </c>
+      <c r="AC82">
+        <v>3.5</v>
+      </c>
+      <c r="AD82">
+        <v>1.22</v>
+      </c>
+      <c r="AE82">
         <v>1.03</v>
       </c>
-      <c r="X82">
-        <v>1.01</v>
-      </c>
-      <c r="Y82">
-        <v>1.29</v>
-      </c>
-      <c r="Z82">
-        <v>3.04</v>
-      </c>
-      <c r="AA82">
-        <v>1.9</v>
-      </c>
-      <c r="AB82">
-        <v>1.78</v>
-      </c>
-      <c r="AC82">
-        <v>3.42</v>
-      </c>
-      <c r="AD82">
-        <v>1.23</v>
-      </c>
-      <c r="AE82">
-        <v>1.04</v>
-      </c>
       <c r="AF82">
-        <v>2.13</v>
+        <v>1.76</v>
       </c>
       <c r="AG82">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>2.46</v>
+        <v>1.46</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="O83">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="P83">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="Q83">
         <v>2.9</v>
       </c>
       <c r="R83">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S83">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T83">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="U83">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="V83">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W83">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z83">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AA83">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB83">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC83">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="AD83">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE83">
         <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG83">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O84">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="P84">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="Q84">
         <v>2.9</v>
       </c>
       <c r="R84">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S84">
+        <v>1.44</v>
+      </c>
+      <c r="T84">
+        <v>2.45</v>
+      </c>
+      <c r="U84">
+        <v>3.12</v>
+      </c>
+      <c r="V84">
+        <v>1.28</v>
+      </c>
+      <c r="W84">
+        <v>1.02</v>
+      </c>
+      <c r="X84">
+        <v>1.03</v>
+      </c>
+      <c r="Y84">
         <v>1.36</v>
       </c>
-      <c r="T84">
-        <v>2.73</v>
-      </c>
-      <c r="U84">
-        <v>3</v>
-      </c>
-      <c r="V84">
-        <v>1.33</v>
-      </c>
-      <c r="W84">
-        <v>1.06</v>
-      </c>
-      <c r="X84">
-        <v>1.01</v>
-      </c>
-      <c r="Y84">
-        <v>1.3</v>
-      </c>
       <c r="Z84">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AA84">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB84">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC84">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="AD84">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE84">
         <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG84">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK84">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="R90">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T90">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="U90">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="V90">
+        <v>1.4</v>
+      </c>
+      <c r="W90">
+        <v>1.06</v>
+      </c>
+      <c r="X90">
+        <v>1.03</v>
+      </c>
+      <c r="Y90">
         <v>1.3</v>
       </c>
-      <c r="W90">
-        <v>1.02</v>
-      </c>
-      <c r="X90">
-        <v>1.04</v>
-      </c>
-      <c r="Y90">
-        <v>1.36</v>
-      </c>
       <c r="Z90">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AA90">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB90">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC90">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD90">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE90">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG90">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK90">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q91">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="R91">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S91">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T91">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="U91">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="V91">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X91">
+        <v>1.04</v>
+      </c>
+      <c r="Y91">
+        <v>1.36</v>
+      </c>
+      <c r="Z91">
+        <v>2.7</v>
+      </c>
+      <c r="AA91">
+        <v>2.25</v>
+      </c>
+      <c r="AB91">
+        <v>1.57</v>
+      </c>
+      <c r="AC91">
+        <v>3.9</v>
+      </c>
+      <c r="AD91">
+        <v>1.17</v>
+      </c>
+      <c r="AE91">
         <v>1.03</v>
       </c>
-      <c r="Y91">
-        <v>1.3</v>
-      </c>
-      <c r="Z91">
-        <v>3.25</v>
-      </c>
-      <c r="AA91">
-        <v>2.1</v>
-      </c>
-      <c r="AB91">
-        <v>1.7</v>
-      </c>
-      <c r="AC91">
-        <v>3.6</v>
-      </c>
-      <c r="AD91">
-        <v>1.25</v>
-      </c>
-      <c r="AE91">
-        <v>1.06</v>
-      </c>
       <c r="AF91">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AG91">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK91">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="O106">
-        <v>4.45</v>
+        <v>3.78</v>
       </c>
       <c r="P106">
-        <v>4</v>
+        <v>3.07</v>
       </c>
       <c r="Q106">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="R106">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="S106">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="U106">
-        <v>1.73</v>
+        <v>2.21</v>
       </c>
       <c r="V106">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="W106">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="X106">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="Z106">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="AA106">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AB106">
-        <v>3.83</v>
+        <v>2.35</v>
       </c>
       <c r="AC106">
-        <v>1.62</v>
+        <v>2.33</v>
       </c>
       <c r="AD106">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="AE106">
+        <v>1.16</v>
+      </c>
+      <c r="AF106">
         <v>1.5</v>
       </c>
-      <c r="AF106">
-        <v>1.3</v>
-      </c>
       <c r="AG106">
-        <v>3.42</v>
+        <v>2.38</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="O107">
-        <v>3.78</v>
+        <v>4.45</v>
       </c>
       <c r="P107">
-        <v>3.07</v>
+        <v>4</v>
       </c>
       <c r="Q107">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="R107">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="S107">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T107">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="U107">
-        <v>2.21</v>
+        <v>1.73</v>
       </c>
       <c r="V107">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="W107">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y107">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="Z107">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="AA107">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AB107">
-        <v>2.35</v>
+        <v>3.83</v>
       </c>
       <c r="AC107">
-        <v>2.33</v>
+        <v>1.62</v>
       </c>
       <c r="AD107">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="AE107">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AF107">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AG107">
-        <v>2.38</v>
+        <v>3.42</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.22</v>
       </c>
       <c r="AK107">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q132">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="O5">
-        <v>3.48</v>
+        <v>3.98</v>
       </c>
       <c r="P5">
-        <v>4.87</v>
+        <v>5.47</v>
       </c>
       <c r="Q5">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="R5">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S5">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T5">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="V5">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z5">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="AA5">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AB5">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AC5">
-        <v>3.48</v>
+        <v>2.66</v>
       </c>
       <c r="AD5">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AE5">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG5">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,61 +1287,61 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.49</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>5.47</v>
+        <v>2.32</v>
       </c>
       <c r="Q6">
-        <v>1.99</v>
+        <v>3.2</v>
       </c>
       <c r="R6">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T6">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="U6">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="V6">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>4.01</v>
+        <v>3.43</v>
       </c>
       <c r="AA6">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AB6">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC6">
-        <v>2.66</v>
+        <v>3.14</v>
       </c>
       <c r="AD6">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AE6">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
         <v>2</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>2.21</v>
+        <v>1.38</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="P7">
-        <v>2.47</v>
+        <v>2.09</v>
       </c>
       <c r="Q7">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="R7">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="S7">
+        <v>1.33</v>
+      </c>
+      <c r="T7">
+        <v>2.95</v>
+      </c>
+      <c r="U7">
+        <v>2.65</v>
+      </c>
+      <c r="V7">
+        <v>1.38</v>
+      </c>
+      <c r="W7">
+        <v>1.06</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1.26</v>
+      </c>
+      <c r="Z7">
+        <v>3.2</v>
+      </c>
+      <c r="AA7">
+        <v>1.99</v>
+      </c>
+      <c r="AB7">
+        <v>1.78</v>
+      </c>
+      <c r="AC7">
+        <v>3.2</v>
+      </c>
+      <c r="AD7">
         <v>1.3</v>
-      </c>
-      <c r="T7">
-        <v>3.2</v>
-      </c>
-      <c r="U7">
-        <v>2.45</v>
-      </c>
-      <c r="V7">
-        <v>1.49</v>
-      </c>
-      <c r="W7">
-        <v>1.11</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.17</v>
-      </c>
-      <c r="Z7">
-        <v>4</v>
-      </c>
-      <c r="AA7">
-        <v>1.7</v>
-      </c>
-      <c r="AB7">
-        <v>2.1</v>
-      </c>
-      <c r="AC7">
-        <v>2.77</v>
-      </c>
-      <c r="AD7">
-        <v>1.37</v>
       </c>
       <c r="AE7">
         <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.14</v>
+        <v>2.23</v>
       </c>
       <c r="O8">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="P8">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="R8">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T8">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="U8">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z8">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA8">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="AB8">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AC8">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD8">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE8">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG8">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
+        <v>1.63</v>
+      </c>
+      <c r="O9">
+        <v>3.48</v>
+      </c>
+      <c r="P9">
+        <v>4.87</v>
+      </c>
+      <c r="Q9">
         <v>2.23</v>
       </c>
-      <c r="O9">
-        <v>2.99</v>
-      </c>
-      <c r="P9">
-        <v>3.1</v>
-      </c>
-      <c r="Q9">
-        <v>3.13</v>
-      </c>
       <c r="R9">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="T9">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="U9">
-        <v>3.22</v>
+        <v>2.89</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1.28</v>
+      </c>
+      <c r="Z9">
+        <v>3.08</v>
+      </c>
+      <c r="AA9">
+        <v>2.02</v>
+      </c>
+      <c r="AB9">
+        <v>1.77</v>
+      </c>
+      <c r="AC9">
+        <v>3.48</v>
+      </c>
+      <c r="AD9">
+        <v>1.22</v>
+      </c>
+      <c r="AE9">
         <v>1.04</v>
       </c>
-      <c r="Y9">
-        <v>1.35</v>
-      </c>
-      <c r="Z9">
-        <v>2.74</v>
-      </c>
-      <c r="AA9">
-        <v>2.19</v>
-      </c>
-      <c r="AB9">
-        <v>1.61</v>
-      </c>
-      <c r="AC9">
-        <v>3.74</v>
-      </c>
-      <c r="AD9">
-        <v>1.19</v>
-      </c>
-      <c r="AE9">
-        <v>1.03</v>
-      </c>
       <c r="AF9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P10">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="Q10">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="R10">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="U10">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>3.43</v>
+        <v>3.72</v>
       </c>
       <c r="AA10">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AB10">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="AC10">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="AD10">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AK10">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O11">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="Q11">
-        <v>2.93</v>
+        <v>3.22</v>
       </c>
       <c r="R11">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AA11">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB11">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC11">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="AD11">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE11">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG11">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,61 +6992,61 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.62</v>
+        <v>1.55</v>
       </c>
       <c r="O41">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="P41">
-        <v>1.88</v>
+        <v>4.79</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S41">
         <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="U41">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>3.82</v>
+        <v>4.18</v>
       </c>
       <c r="AA41">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC41">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD41">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
         <v>2.1</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK41">
-        <v>1.19</v>
+        <v>2.14</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,61 +7155,61 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.55</v>
+        <v>3.62</v>
       </c>
       <c r="O42">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="P42">
-        <v>4.79</v>
+        <v>1.88</v>
       </c>
       <c r="Q42">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="R42">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
         <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V42">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z42">
-        <v>4.18</v>
+        <v>3.82</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB42">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC42">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD42">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG42">
         <v>2.1</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>2.14</v>
+        <v>1.19</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="O48">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="P48">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="Q48">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="R48">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T48">
+        <v>2.7</v>
+      </c>
+      <c r="U48">
         <v>2.75</v>
       </c>
-      <c r="U48">
-        <v>2.96</v>
-      </c>
       <c r="V48">
+        <v>1.43</v>
+      </c>
+      <c r="W48">
+        <v>1.07</v>
+      </c>
+      <c r="X48">
+        <v>1.02</v>
+      </c>
+      <c r="Y48">
+        <v>1.22</v>
+      </c>
+      <c r="Z48">
+        <v>4.07</v>
+      </c>
+      <c r="AA48">
+        <v>2.03</v>
+      </c>
+      <c r="AB48">
+        <v>1.83</v>
+      </c>
+      <c r="AC48">
+        <v>2.74</v>
+      </c>
+      <c r="AD48">
+        <v>1.35</v>
+      </c>
+      <c r="AE48">
+        <v>1.13</v>
+      </c>
+      <c r="AF48">
+        <v>1.6</v>
+      </c>
+      <c r="AG48">
+        <v>2.19</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
         <v>1.4</v>
       </c>
-      <c r="W48">
-        <v>1.06</v>
-      </c>
-      <c r="X48">
-        <v>1.03</v>
-      </c>
-      <c r="Y48">
-        <v>1.3</v>
-      </c>
-      <c r="Z48">
-        <v>3.2</v>
-      </c>
-      <c r="AA48">
-        <v>1.94</v>
-      </c>
-      <c r="AB48">
-        <v>1.8</v>
-      </c>
-      <c r="AC48">
-        <v>3.28</v>
-      </c>
-      <c r="AD48">
-        <v>1.25</v>
-      </c>
-      <c r="AE48">
-        <v>1.05</v>
-      </c>
-      <c r="AF48">
-        <v>1.73</v>
-      </c>
-      <c r="AG48">
-        <v>1.95</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.41</v>
-      </c>
       <c r="AK48">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,34 +8296,34 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.92</v>
+        <v>2.19</v>
       </c>
       <c r="O49">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="P49">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="Q49">
-        <v>3.26</v>
+        <v>2.43</v>
       </c>
       <c r="R49">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U49">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V49">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
         <v>1.01</v>
@@ -8332,28 +8332,28 @@
         <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AC49">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD49">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AG49">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
+        <v>1.27</v>
+      </c>
+      <c r="AK49">
         <v>1.65</v>
-      </c>
-      <c r="AK49">
-        <v>1.33</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="O51">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="P51">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="Q51">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S51">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T51">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U51">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="V51">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>4.07</v>
+        <v>3.2</v>
       </c>
       <c r="AA51">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AB51">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC51">
-        <v>2.74</v>
+        <v>3.28</v>
       </c>
       <c r="AD51">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG51">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AK51">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,34 +8785,34 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.19</v>
+        <v>2.92</v>
       </c>
       <c r="O52">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="P52">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="Q52">
-        <v>2.43</v>
+        <v>3.26</v>
       </c>
       <c r="R52">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S52">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X52">
         <v>1.01</v>
@@ -8821,44 +8821,44 @@
         <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AB52">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AC52">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD52">
+        <v>1.36</v>
+      </c>
+      <c r="AE52">
+        <v>1.13</v>
+      </c>
+      <c r="AF52">
+        <v>1.58</v>
+      </c>
+      <c r="AG52">
+        <v>2.3</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>1.65</v>
+      </c>
+      <c r="AK52">
         <v>1.33</v>
-      </c>
-      <c r="AE52">
-        <v>1.12</v>
-      </c>
-      <c r="AF52">
-        <v>1.64</v>
-      </c>
-      <c r="AG52">
-        <v>2.13</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.27</v>
-      </c>
-      <c r="AK52">
-        <v>1.65</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="O62">
-        <v>5</v>
+        <v>3.48</v>
       </c>
       <c r="P62">
-        <v>6.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q62">
-        <v>1.74</v>
+        <v>2.39</v>
       </c>
       <c r="R62">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="S62">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="T62">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="U62">
-        <v>1.95</v>
+        <v>2.71</v>
       </c>
       <c r="V62">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="W62">
+        <v>1.06</v>
+      </c>
+      <c r="X62">
+        <v>1.03</v>
+      </c>
+      <c r="Y62">
+        <v>1.26</v>
+      </c>
+      <c r="Z62">
+        <v>3.05</v>
+      </c>
+      <c r="AA62">
+        <v>2.01</v>
+      </c>
+      <c r="AB62">
+        <v>1.79</v>
+      </c>
+      <c r="AC62">
+        <v>3.44</v>
+      </c>
+      <c r="AD62">
+        <v>1.26</v>
+      </c>
+      <c r="AE62">
+        <v>1.06</v>
+      </c>
+      <c r="AF62">
+        <v>1.82</v>
+      </c>
+      <c r="AG62">
+        <v>1.88</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.19</v>
       </c>
-      <c r="X62">
-        <v>1.01</v>
-      </c>
-      <c r="Y62">
-        <v>1.07</v>
-      </c>
-      <c r="Z62">
-        <v>5.85</v>
-      </c>
-      <c r="AA62">
-        <v>1.4</v>
-      </c>
-      <c r="AB62">
-        <v>2.87</v>
-      </c>
-      <c r="AC62">
-        <v>2.02</v>
-      </c>
-      <c r="AD62">
-        <v>1.77</v>
-      </c>
-      <c r="AE62">
-        <v>1.33</v>
-      </c>
-      <c r="AF62">
-        <v>1.57</v>
-      </c>
-      <c r="AG62">
-        <v>2.26</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.13</v>
-      </c>
       <c r="AK62">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="O63">
-        <v>3.48</v>
+        <v>5</v>
       </c>
       <c r="P63">
-        <v>3.94</v>
+        <v>6.4</v>
       </c>
       <c r="Q63">
-        <v>2.39</v>
+        <v>1.74</v>
       </c>
       <c r="R63">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="S63">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="T63">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="U63">
-        <v>2.71</v>
+        <v>1.95</v>
       </c>
       <c r="V63">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="W63">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="X63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="Z63">
-        <v>3.05</v>
+        <v>5.85</v>
       </c>
       <c r="AA63">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>1.79</v>
+        <v>2.87</v>
       </c>
       <c r="AC63">
-        <v>3.44</v>
+        <v>2.02</v>
       </c>
       <c r="AD63">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="AE63">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AF63">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AG63">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK63">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="O69">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P69">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q69">
-        <v>2.99</v>
+        <v>2.16</v>
       </c>
       <c r="R69">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S69">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T69">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="U69">
-        <v>3.24</v>
+        <v>2.89</v>
       </c>
       <c r="V69">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W69">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z69">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AA69">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AB69">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AC69">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD69">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF69">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG69">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AK69">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="O70">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P70">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q70">
-        <v>2.16</v>
+        <v>2.99</v>
       </c>
       <c r="R70">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S70">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T70">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U70">
-        <v>2.89</v>
+        <v>3.24</v>
       </c>
       <c r="V70">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W70">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X70">
+        <v>1.02</v>
+      </c>
+      <c r="Y70">
+        <v>1.36</v>
+      </c>
+      <c r="Z70">
+        <v>2.7</v>
+      </c>
+      <c r="AA70">
+        <v>2.2</v>
+      </c>
+      <c r="AB70">
+        <v>1.57</v>
+      </c>
+      <c r="AC70">
+        <v>4.2</v>
+      </c>
+      <c r="AD70">
+        <v>1.16</v>
+      </c>
+      <c r="AE70">
         <v>1.01</v>
       </c>
-      <c r="Y70">
-        <v>1.3</v>
-      </c>
-      <c r="Z70">
-        <v>2.97</v>
-      </c>
-      <c r="AA70">
-        <v>2.01</v>
-      </c>
-      <c r="AB70">
-        <v>1.69</v>
-      </c>
-      <c r="AC70">
-        <v>3.5</v>
-      </c>
-      <c r="AD70">
-        <v>1.22</v>
-      </c>
-      <c r="AE70">
-        <v>1.04</v>
-      </c>
       <c r="AF70">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG70">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AK70">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -13032,55 +13032,55 @@
         <v>2.42</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL78">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.49</v>
+        <v>3.14</v>
       </c>
       <c r="O5">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="P5">
-        <v>5.47</v>
+        <v>2.09</v>
       </c>
       <c r="Q5">
+        <v>3.5</v>
+      </c>
+      <c r="R5">
+        <v>2.08</v>
+      </c>
+      <c r="S5">
+        <v>1.33</v>
+      </c>
+      <c r="T5">
+        <v>2.95</v>
+      </c>
+      <c r="U5">
+        <v>2.65</v>
+      </c>
+      <c r="V5">
+        <v>1.38</v>
+      </c>
+      <c r="W5">
+        <v>1.06</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>1.26</v>
+      </c>
+      <c r="Z5">
+        <v>3.2</v>
+      </c>
+      <c r="AA5">
         <v>1.99</v>
       </c>
-      <c r="R5">
-        <v>2.28</v>
-      </c>
-      <c r="S5">
-        <v>1.32</v>
-      </c>
-      <c r="T5">
+      <c r="AB5">
+        <v>1.78</v>
+      </c>
+      <c r="AC5">
         <v>3.2</v>
       </c>
-      <c r="U5">
-        <v>2.57</v>
-      </c>
-      <c r="V5">
-        <v>1.48</v>
-      </c>
-      <c r="W5">
-        <v>1.11</v>
-      </c>
-      <c r="X5">
-        <v>1.03</v>
-      </c>
-      <c r="Y5">
-        <v>1.18</v>
-      </c>
-      <c r="Z5">
-        <v>4.01</v>
-      </c>
-      <c r="AA5">
-        <v>1.82</v>
-      </c>
-      <c r="AB5">
-        <v>1.94</v>
-      </c>
-      <c r="AC5">
-        <v>2.66</v>
-      </c>
       <c r="AD5">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
         <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK5">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.14</v>
+        <v>1.49</v>
       </c>
       <c r="O7">
-        <v>3.24</v>
+        <v>3.98</v>
       </c>
       <c r="P7">
-        <v>2.09</v>
+        <v>5.47</v>
       </c>
       <c r="Q7">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="R7">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U7">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>3.2</v>
+        <v>4.01</v>
       </c>
       <c r="AA7">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AB7">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
         <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>1.27</v>
+        <v>2.21</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="O8">
-        <v>2.99</v>
+        <v>3.38</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q8">
-        <v>3.13</v>
+        <v>2.93</v>
       </c>
       <c r="R8">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>2.42</v>
+        <v>3.18</v>
       </c>
       <c r="U8">
-        <v>3.22</v>
+        <v>2.67</v>
       </c>
       <c r="V8">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
         <v>1.07</v>
@@ -1646,31 +1646,31 @@
         <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>2.74</v>
+        <v>3.72</v>
       </c>
       <c r="AA8">
-        <v>2.19</v>
+        <v>1.74</v>
       </c>
       <c r="AB8">
+        <v>2.02</v>
+      </c>
+      <c r="AC8">
+        <v>2.99</v>
+      </c>
+      <c r="AD8">
+        <v>1.32</v>
+      </c>
+      <c r="AE8">
+        <v>1.08</v>
+      </c>
+      <c r="AF8">
         <v>1.61</v>
       </c>
-      <c r="AC8">
-        <v>3.74</v>
-      </c>
-      <c r="AD8">
-        <v>1.19</v>
-      </c>
-      <c r="AE8">
-        <v>1.03</v>
-      </c>
-      <c r="AF8">
-        <v>1.84</v>
-      </c>
       <c r="AG8">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK8">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.63</v>
+        <v>2.23</v>
       </c>
       <c r="O9">
-        <v>3.48</v>
+        <v>2.99</v>
       </c>
       <c r="P9">
-        <v>4.87</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>2.23</v>
+        <v>3.13</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S9">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="T9">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="U9">
-        <v>2.89</v>
+        <v>3.22</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z9">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="AA9">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="AB9">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AC9">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="AD9">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG9">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.32</v>
+        <v>1.63</v>
       </c>
       <c r="O10">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="P10">
-        <v>2.55</v>
+        <v>4.87</v>
       </c>
       <c r="Q10">
-        <v>2.93</v>
+        <v>2.23</v>
       </c>
       <c r="R10">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T10">
-        <v>3.18</v>
+        <v>2.64</v>
       </c>
       <c r="U10">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1.28</v>
+      </c>
+      <c r="Z10">
+        <v>3.08</v>
+      </c>
+      <c r="AA10">
+        <v>2.02</v>
+      </c>
+      <c r="AB10">
+        <v>1.77</v>
+      </c>
+      <c r="AC10">
+        <v>3.48</v>
+      </c>
+      <c r="AD10">
+        <v>1.22</v>
+      </c>
+      <c r="AE10">
         <v>1.04</v>
       </c>
-      <c r="Y10">
-        <v>1.2</v>
-      </c>
-      <c r="Z10">
-        <v>3.72</v>
-      </c>
-      <c r="AA10">
-        <v>1.74</v>
-      </c>
-      <c r="AB10">
-        <v>2.02</v>
-      </c>
-      <c r="AC10">
-        <v>2.99</v>
-      </c>
-      <c r="AD10">
-        <v>1.32</v>
-      </c>
-      <c r="AE10">
-        <v>1.08</v>
-      </c>
       <c r="AF10">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,61 +6992,61 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.55</v>
+        <v>3.62</v>
       </c>
       <c r="O41">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="P41">
-        <v>4.79</v>
+        <v>1.88</v>
       </c>
       <c r="Q41">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="R41">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
         <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="U41">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V41">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W41">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
-        <v>4.18</v>
+        <v>3.82</v>
       </c>
       <c r="AA41">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB41">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC41">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD41">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG41">
         <v>2.1</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>2.14</v>
+        <v>1.19</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,61 +7155,61 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.62</v>
+        <v>1.55</v>
       </c>
       <c r="O42">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="P42">
-        <v>1.88</v>
+        <v>4.79</v>
       </c>
       <c r="Q42">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
         <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="U42">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>3.82</v>
+        <v>4.18</v>
       </c>
       <c r="AA42">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC42">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD42">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG42">
         <v>2.1</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK42">
-        <v>1.19</v>
+        <v>2.14</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="O48">
-        <v>2.91</v>
+        <v>3.62</v>
       </c>
       <c r="P48">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="Q48">
-        <v>3.24</v>
+        <v>2.43</v>
       </c>
       <c r="R48">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S48">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T48">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="U48">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="V48">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
         <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
         <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>4.07</v>
+        <v>3.5</v>
       </c>
       <c r="AA48">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC48">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD48">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG48">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK48">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,77 +8296,77 @@
         </is>
       </c>
       <c r="N49">
+        <v>2.09</v>
+      </c>
+      <c r="O49">
+        <v>3.54</v>
+      </c>
+      <c r="P49">
+        <v>3.15</v>
+      </c>
+      <c r="Q49">
+        <v>2.75</v>
+      </c>
+      <c r="R49">
         <v>2.19</v>
       </c>
-      <c r="O49">
-        <v>3.62</v>
-      </c>
-      <c r="P49">
-        <v>2.88</v>
-      </c>
-      <c r="Q49">
-        <v>2.43</v>
-      </c>
-      <c r="R49">
-        <v>2.21</v>
-      </c>
       <c r="S49">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T49">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U49">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA49">
         <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AC49">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="AD49">
+        <v>1.43</v>
+      </c>
+      <c r="AE49">
+        <v>1.13</v>
+      </c>
+      <c r="AF49">
+        <v>1.55</v>
+      </c>
+      <c r="AG49">
+        <v>2.25</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
         <v>1.33</v>
-      </c>
-      <c r="AE49">
-        <v>1.12</v>
-      </c>
-      <c r="AF49">
-        <v>1.64</v>
-      </c>
-      <c r="AG49">
-        <v>2.13</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.27</v>
       </c>
       <c r="AK49">
         <v>1.65</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.09</v>
+        <v>2.73</v>
       </c>
       <c r="O50">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
       <c r="P50">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="Q50">
+        <v>3.18</v>
+      </c>
+      <c r="R50">
+        <v>2.18</v>
+      </c>
+      <c r="S50">
+        <v>1.38</v>
+      </c>
+      <c r="T50">
         <v>2.75</v>
       </c>
-      <c r="R50">
-        <v>2.19</v>
-      </c>
-      <c r="S50">
-        <v>1.26</v>
-      </c>
-      <c r="T50">
-        <v>3.4</v>
-      </c>
       <c r="U50">
-        <v>2.32</v>
+        <v>2.96</v>
       </c>
       <c r="V50">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z50">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AA50">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AB50">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AC50">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="AD50">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF50">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG50">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AK50">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="O51">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="P51">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="Q51">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="R51">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T51">
+        <v>2.7</v>
+      </c>
+      <c r="U51">
         <v>2.75</v>
       </c>
-      <c r="U51">
-        <v>2.96</v>
-      </c>
       <c r="V51">
+        <v>1.43</v>
+      </c>
+      <c r="W51">
+        <v>1.07</v>
+      </c>
+      <c r="X51">
+        <v>1.02</v>
+      </c>
+      <c r="Y51">
+        <v>1.22</v>
+      </c>
+      <c r="Z51">
+        <v>4.07</v>
+      </c>
+      <c r="AA51">
+        <v>2.03</v>
+      </c>
+      <c r="AB51">
+        <v>1.83</v>
+      </c>
+      <c r="AC51">
+        <v>2.74</v>
+      </c>
+      <c r="AD51">
+        <v>1.35</v>
+      </c>
+      <c r="AE51">
+        <v>1.13</v>
+      </c>
+      <c r="AF51">
+        <v>1.6</v>
+      </c>
+      <c r="AG51">
+        <v>2.19</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.4</v>
       </c>
-      <c r="W51">
-        <v>1.06</v>
-      </c>
-      <c r="X51">
-        <v>1.03</v>
-      </c>
-      <c r="Y51">
-        <v>1.3</v>
-      </c>
-      <c r="Z51">
-        <v>3.2</v>
-      </c>
-      <c r="AA51">
-        <v>1.94</v>
-      </c>
-      <c r="AB51">
-        <v>1.8</v>
-      </c>
-      <c r="AC51">
-        <v>3.28</v>
-      </c>
-      <c r="AD51">
-        <v>1.25</v>
-      </c>
-      <c r="AE51">
-        <v>1.05</v>
-      </c>
-      <c r="AF51">
-        <v>1.73</v>
-      </c>
-      <c r="AG51">
-        <v>1.95</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.41</v>
-      </c>
       <c r="AK51">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="O69">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P69">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q69">
-        <v>2.16</v>
+        <v>2.99</v>
       </c>
       <c r="R69">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S69">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T69">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U69">
-        <v>2.89</v>
+        <v>3.24</v>
       </c>
       <c r="V69">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W69">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X69">
+        <v>1.02</v>
+      </c>
+      <c r="Y69">
+        <v>1.36</v>
+      </c>
+      <c r="Z69">
+        <v>2.7</v>
+      </c>
+      <c r="AA69">
+        <v>2.2</v>
+      </c>
+      <c r="AB69">
+        <v>1.57</v>
+      </c>
+      <c r="AC69">
+        <v>4.2</v>
+      </c>
+      <c r="AD69">
+        <v>1.16</v>
+      </c>
+      <c r="AE69">
         <v>1.01</v>
       </c>
-      <c r="Y69">
-        <v>1.3</v>
-      </c>
-      <c r="Z69">
-        <v>2.97</v>
-      </c>
-      <c r="AA69">
-        <v>2.01</v>
-      </c>
-      <c r="AB69">
-        <v>1.69</v>
-      </c>
-      <c r="AC69">
-        <v>3.5</v>
-      </c>
-      <c r="AD69">
-        <v>1.22</v>
-      </c>
-      <c r="AE69">
-        <v>1.04</v>
-      </c>
       <c r="AF69">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG69">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AK69">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="O70">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P70">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q70">
-        <v>2.99</v>
+        <v>2.16</v>
       </c>
       <c r="R70">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S70">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T70">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="U70">
-        <v>3.24</v>
+        <v>2.89</v>
       </c>
       <c r="V70">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W70">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z70">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AA70">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AB70">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AC70">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD70">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE70">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF70">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG70">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AK70">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O83">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="P83">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="Q83">
         <v>2.9</v>
       </c>
       <c r="R83">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S83">
+        <v>1.44</v>
+      </c>
+      <c r="T83">
+        <v>2.45</v>
+      </c>
+      <c r="U83">
+        <v>3.12</v>
+      </c>
+      <c r="V83">
+        <v>1.28</v>
+      </c>
+      <c r="W83">
+        <v>1.02</v>
+      </c>
+      <c r="X83">
+        <v>1.03</v>
+      </c>
+      <c r="Y83">
         <v>1.36</v>
       </c>
-      <c r="T83">
-        <v>2.73</v>
-      </c>
-      <c r="U83">
-        <v>3</v>
-      </c>
-      <c r="V83">
-        <v>1.33</v>
-      </c>
-      <c r="W83">
-        <v>1.06</v>
-      </c>
-      <c r="X83">
-        <v>1.01</v>
-      </c>
-      <c r="Y83">
-        <v>1.3</v>
-      </c>
       <c r="Z83">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AA83">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB83">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC83">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="AD83">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE83">
         <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG83">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK83">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="O84">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="P84">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="Q84">
         <v>2.9</v>
       </c>
       <c r="R84">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S84">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T84">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="U84">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="V84">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W84">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X84">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z84">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AA84">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB84">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC84">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="AD84">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE84">
         <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG84">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL84">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.14</v>
+        <v>1.49</v>
       </c>
       <c r="O5">
-        <v>3.24</v>
+        <v>3.98</v>
       </c>
       <c r="P5">
-        <v>2.09</v>
+        <v>5.47</v>
       </c>
       <c r="Q5">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="R5">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T5">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="V5">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z5">
-        <v>3.2</v>
+        <v>4.01</v>
       </c>
       <c r="AA5">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AB5">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC5">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD5">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE5">
         <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG5">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>1.27</v>
+        <v>2.21</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P6">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="Q6">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="R6">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S6">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="U6">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="V6">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>3.43</v>
+        <v>3.72</v>
       </c>
       <c r="AA6">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AB6">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="AC6">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="AD6">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AK6">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.49</v>
+        <v>3.14</v>
       </c>
       <c r="O7">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="P7">
-        <v>5.47</v>
+        <v>2.09</v>
       </c>
       <c r="Q7">
+        <v>3.5</v>
+      </c>
+      <c r="R7">
+        <v>2.08</v>
+      </c>
+      <c r="S7">
+        <v>1.33</v>
+      </c>
+      <c r="T7">
+        <v>2.95</v>
+      </c>
+      <c r="U7">
+        <v>2.65</v>
+      </c>
+      <c r="V7">
+        <v>1.38</v>
+      </c>
+      <c r="W7">
+        <v>1.06</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1.26</v>
+      </c>
+      <c r="Z7">
+        <v>3.2</v>
+      </c>
+      <c r="AA7">
         <v>1.99</v>
       </c>
-      <c r="R7">
-        <v>2.28</v>
-      </c>
-      <c r="S7">
-        <v>1.32</v>
-      </c>
-      <c r="T7">
+      <c r="AB7">
+        <v>1.78</v>
+      </c>
+      <c r="AC7">
         <v>3.2</v>
       </c>
-      <c r="U7">
-        <v>2.57</v>
-      </c>
-      <c r="V7">
-        <v>1.48</v>
-      </c>
-      <c r="W7">
-        <v>1.11</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.18</v>
-      </c>
-      <c r="Z7">
-        <v>4.01</v>
-      </c>
-      <c r="AA7">
-        <v>1.82</v>
-      </c>
-      <c r="AB7">
-        <v>1.94</v>
-      </c>
-      <c r="AC7">
-        <v>2.66</v>
-      </c>
       <c r="AD7">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
         <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="O8">
-        <v>3.38</v>
+        <v>2.99</v>
       </c>
       <c r="P8">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>2.93</v>
+        <v>3.13</v>
       </c>
       <c r="R8">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T8">
-        <v>3.18</v>
+        <v>2.42</v>
       </c>
       <c r="U8">
-        <v>2.67</v>
+        <v>3.22</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W8">
         <v>1.07</v>
@@ -1646,31 +1646,31 @@
         <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="Z8">
-        <v>3.72</v>
+        <v>2.74</v>
       </c>
       <c r="AA8">
-        <v>1.74</v>
+        <v>2.19</v>
       </c>
       <c r="AB8">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="AC8">
-        <v>2.99</v>
+        <v>3.74</v>
       </c>
       <c r="AD8">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AE8">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AG8">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
+        <v>1.63</v>
+      </c>
+      <c r="O9">
+        <v>3.48</v>
+      </c>
+      <c r="P9">
+        <v>4.87</v>
+      </c>
+      <c r="Q9">
         <v>2.23</v>
       </c>
-      <c r="O9">
-        <v>2.99</v>
-      </c>
-      <c r="P9">
-        <v>3.1</v>
-      </c>
-      <c r="Q9">
-        <v>3.13</v>
-      </c>
       <c r="R9">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="T9">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="U9">
-        <v>3.22</v>
+        <v>2.89</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1.28</v>
+      </c>
+      <c r="Z9">
+        <v>3.08</v>
+      </c>
+      <c r="AA9">
+        <v>2.02</v>
+      </c>
+      <c r="AB9">
+        <v>1.77</v>
+      </c>
+      <c r="AC9">
+        <v>3.48</v>
+      </c>
+      <c r="AD9">
+        <v>1.22</v>
+      </c>
+      <c r="AE9">
         <v>1.04</v>
       </c>
-      <c r="Y9">
-        <v>1.35</v>
-      </c>
-      <c r="Z9">
-        <v>2.74</v>
-      </c>
-      <c r="AA9">
-        <v>2.19</v>
-      </c>
-      <c r="AB9">
-        <v>1.61</v>
-      </c>
-      <c r="AC9">
-        <v>3.74</v>
-      </c>
-      <c r="AD9">
-        <v>1.19</v>
-      </c>
-      <c r="AE9">
-        <v>1.03</v>
-      </c>
       <c r="AF9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
       <c r="O10">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>4.87</v>
+        <v>2.32</v>
       </c>
       <c r="Q10">
-        <v>2.23</v>
+        <v>3.2</v>
       </c>
       <c r="R10">
         <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="U10">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="V10">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
+        <v>1.26</v>
+      </c>
+      <c r="Z10">
+        <v>3.43</v>
+      </c>
+      <c r="AA10">
+        <v>1.97</v>
+      </c>
+      <c r="AB10">
+        <v>1.79</v>
+      </c>
+      <c r="AC10">
+        <v>3.14</v>
+      </c>
+      <c r="AD10">
+        <v>1.27</v>
+      </c>
+      <c r="AE10">
+        <v>1.07</v>
+      </c>
+      <c r="AF10">
+        <v>1.7</v>
+      </c>
+      <c r="AG10">
+        <v>2</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.28</v>
       </c>
-      <c r="Z10">
-        <v>3.08</v>
-      </c>
-      <c r="AA10">
-        <v>2.02</v>
-      </c>
-      <c r="AB10">
-        <v>1.77</v>
-      </c>
-      <c r="AC10">
-        <v>3.48</v>
-      </c>
-      <c r="AD10">
-        <v>1.22</v>
-      </c>
-      <c r="AE10">
-        <v>1.04</v>
-      </c>
-      <c r="AF10">
-        <v>1.85</v>
-      </c>
-      <c r="AG10">
-        <v>1.75</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.3</v>
-      </c>
       <c r="AK10">
-        <v>2.05</v>
+        <v>1.38</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.19</v>
+        <v>2.73</v>
       </c>
       <c r="O48">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="P48">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="Q48">
-        <v>2.43</v>
+        <v>3.18</v>
       </c>
       <c r="R48">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S48">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T48">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U48">
-        <v>2.47</v>
+        <v>2.96</v>
       </c>
       <c r="V48">
+        <v>1.4</v>
+      </c>
+      <c r="W48">
+        <v>1.06</v>
+      </c>
+      <c r="X48">
+        <v>1.03</v>
+      </c>
+      <c r="Y48">
+        <v>1.3</v>
+      </c>
+      <c r="Z48">
+        <v>3.2</v>
+      </c>
+      <c r="AA48">
+        <v>1.94</v>
+      </c>
+      <c r="AB48">
+        <v>1.8</v>
+      </c>
+      <c r="AC48">
+        <v>3.28</v>
+      </c>
+      <c r="AD48">
+        <v>1.25</v>
+      </c>
+      <c r="AE48">
+        <v>1.05</v>
+      </c>
+      <c r="AF48">
+        <v>1.73</v>
+      </c>
+      <c r="AG48">
+        <v>1.95</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.41</v>
+      </c>
+      <c r="AK48">
         <v>1.44</v>
-      </c>
-      <c r="W48">
-        <v>1.07</v>
-      </c>
-      <c r="X48">
-        <v>1.01</v>
-      </c>
-      <c r="Y48">
-        <v>1.22</v>
-      </c>
-      <c r="Z48">
-        <v>3.5</v>
-      </c>
-      <c r="AA48">
-        <v>1.83</v>
-      </c>
-      <c r="AB48">
-        <v>1.93</v>
-      </c>
-      <c r="AC48">
-        <v>2.83</v>
-      </c>
-      <c r="AD48">
-        <v>1.33</v>
-      </c>
-      <c r="AE48">
-        <v>1.12</v>
-      </c>
-      <c r="AF48">
-        <v>1.64</v>
-      </c>
-      <c r="AG48">
-        <v>2.13</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.27</v>
-      </c>
-      <c r="AK48">
-        <v>1.65</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="O50">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="P50">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="Q50">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="R50">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T50">
+        <v>2.7</v>
+      </c>
+      <c r="U50">
         <v>2.75</v>
       </c>
-      <c r="U50">
-        <v>2.96</v>
-      </c>
       <c r="V50">
+        <v>1.43</v>
+      </c>
+      <c r="W50">
+        <v>1.07</v>
+      </c>
+      <c r="X50">
+        <v>1.02</v>
+      </c>
+      <c r="Y50">
+        <v>1.22</v>
+      </c>
+      <c r="Z50">
+        <v>4.07</v>
+      </c>
+      <c r="AA50">
+        <v>2.03</v>
+      </c>
+      <c r="AB50">
+        <v>1.83</v>
+      </c>
+      <c r="AC50">
+        <v>2.74</v>
+      </c>
+      <c r="AD50">
+        <v>1.35</v>
+      </c>
+      <c r="AE50">
+        <v>1.13</v>
+      </c>
+      <c r="AF50">
+        <v>1.6</v>
+      </c>
+      <c r="AG50">
+        <v>2.19</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.4</v>
       </c>
-      <c r="W50">
-        <v>1.06</v>
-      </c>
-      <c r="X50">
-        <v>1.03</v>
-      </c>
-      <c r="Y50">
-        <v>1.3</v>
-      </c>
-      <c r="Z50">
-        <v>3.2</v>
-      </c>
-      <c r="AA50">
-        <v>1.94</v>
-      </c>
-      <c r="AB50">
-        <v>1.8</v>
-      </c>
-      <c r="AC50">
-        <v>3.28</v>
-      </c>
-      <c r="AD50">
-        <v>1.25</v>
-      </c>
-      <c r="AE50">
-        <v>1.05</v>
-      </c>
-      <c r="AF50">
-        <v>1.73</v>
-      </c>
-      <c r="AG50">
-        <v>1.95</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.41</v>
-      </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="O51">
-        <v>2.91</v>
+        <v>3.62</v>
       </c>
       <c r="P51">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="Q51">
-        <v>3.24</v>
+        <v>2.43</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S51">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T51">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="U51">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="V51">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
         <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.07</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC51">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG51">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="O69">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P69">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q69">
-        <v>2.99</v>
+        <v>2.16</v>
       </c>
       <c r="R69">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S69">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T69">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="U69">
-        <v>3.24</v>
+        <v>2.89</v>
       </c>
       <c r="V69">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W69">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z69">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AA69">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AB69">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AC69">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD69">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF69">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG69">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AK69">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="O70">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P70">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q70">
-        <v>2.16</v>
+        <v>2.99</v>
       </c>
       <c r="R70">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S70">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T70">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U70">
-        <v>2.89</v>
+        <v>3.24</v>
       </c>
       <c r="V70">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W70">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X70">
+        <v>1.02</v>
+      </c>
+      <c r="Y70">
+        <v>1.36</v>
+      </c>
+      <c r="Z70">
+        <v>2.7</v>
+      </c>
+      <c r="AA70">
+        <v>2.2</v>
+      </c>
+      <c r="AB70">
+        <v>1.57</v>
+      </c>
+      <c r="AC70">
+        <v>4.2</v>
+      </c>
+      <c r="AD70">
+        <v>1.16</v>
+      </c>
+      <c r="AE70">
         <v>1.01</v>
       </c>
-      <c r="Y70">
-        <v>1.3</v>
-      </c>
-      <c r="Z70">
-        <v>2.97</v>
-      </c>
-      <c r="AA70">
-        <v>2.01</v>
-      </c>
-      <c r="AB70">
-        <v>1.69</v>
-      </c>
-      <c r="AC70">
-        <v>3.5</v>
-      </c>
-      <c r="AD70">
-        <v>1.22</v>
-      </c>
-      <c r="AE70">
-        <v>1.04</v>
-      </c>
       <c r="AF70">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG70">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AK70">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q90">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S90">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T90">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="U90">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="V90">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W90">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X90">
+        <v>1.04</v>
+      </c>
+      <c r="Y90">
+        <v>1.36</v>
+      </c>
+      <c r="Z90">
+        <v>2.7</v>
+      </c>
+      <c r="AA90">
+        <v>2.25</v>
+      </c>
+      <c r="AB90">
+        <v>1.57</v>
+      </c>
+      <c r="AC90">
+        <v>3.9</v>
+      </c>
+      <c r="AD90">
+        <v>1.17</v>
+      </c>
+      <c r="AE90">
         <v>1.03</v>
       </c>
-      <c r="Y90">
-        <v>1.3</v>
-      </c>
-      <c r="Z90">
-        <v>3.25</v>
-      </c>
-      <c r="AA90">
-        <v>2.1</v>
-      </c>
-      <c r="AB90">
-        <v>1.7</v>
-      </c>
-      <c r="AC90">
-        <v>3.6</v>
-      </c>
-      <c r="AD90">
-        <v>1.25</v>
-      </c>
-      <c r="AE90">
-        <v>1.06</v>
-      </c>
       <c r="AF90">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AG90">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK90">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="R91">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T91">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="U91">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="V91">
+        <v>1.4</v>
+      </c>
+      <c r="W91">
+        <v>1.06</v>
+      </c>
+      <c r="X91">
+        <v>1.03</v>
+      </c>
+      <c r="Y91">
         <v>1.3</v>
       </c>
-      <c r="W91">
-        <v>1.02</v>
-      </c>
-      <c r="X91">
-        <v>1.04</v>
-      </c>
-      <c r="Y91">
-        <v>1.36</v>
-      </c>
       <c r="Z91">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB91">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC91">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD91">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE91">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG91">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK91">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15670,10 +15670,10 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC94">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.49</v>
+        <v>2.32</v>
       </c>
       <c r="O5">
-        <v>3.98</v>
+        <v>3.38</v>
       </c>
       <c r="P5">
-        <v>5.47</v>
+        <v>2.55</v>
       </c>
       <c r="Q5">
-        <v>1.99</v>
+        <v>2.93</v>
       </c>
       <c r="R5">
         <v>2.28</v>
       </c>
       <c r="S5">
+        <v>1.33</v>
+      </c>
+      <c r="T5">
+        <v>3.18</v>
+      </c>
+      <c r="U5">
+        <v>2.67</v>
+      </c>
+      <c r="V5">
+        <v>1.44</v>
+      </c>
+      <c r="W5">
+        <v>1.07</v>
+      </c>
+      <c r="X5">
+        <v>1.04</v>
+      </c>
+      <c r="Y5">
+        <v>1.2</v>
+      </c>
+      <c r="Z5">
+        <v>3.72</v>
+      </c>
+      <c r="AA5">
+        <v>1.74</v>
+      </c>
+      <c r="AB5">
+        <v>2.02</v>
+      </c>
+      <c r="AC5">
+        <v>2.99</v>
+      </c>
+      <c r="AD5">
         <v>1.32</v>
       </c>
-      <c r="T5">
-        <v>3.2</v>
-      </c>
-      <c r="U5">
-        <v>2.57</v>
-      </c>
-      <c r="V5">
-        <v>1.48</v>
-      </c>
-      <c r="W5">
-        <v>1.11</v>
-      </c>
-      <c r="X5">
-        <v>1.03</v>
-      </c>
-      <c r="Y5">
-        <v>1.18</v>
-      </c>
-      <c r="Z5">
-        <v>4.01</v>
-      </c>
-      <c r="AA5">
-        <v>1.82</v>
-      </c>
-      <c r="AB5">
-        <v>1.94</v>
-      </c>
-      <c r="AC5">
-        <v>2.66</v>
-      </c>
-      <c r="AD5">
-        <v>1.41</v>
-      </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK5">
-        <v>2.21</v>
+        <v>1.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.32</v>
+        <v>3.14</v>
       </c>
       <c r="O6">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="P6">
-        <v>2.55</v>
+        <v>2.09</v>
       </c>
       <c r="Q6">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="R6">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S6">
         <v>1.33</v>
       </c>
       <c r="T6">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="U6">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="AB6">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="AC6">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AG6">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK6">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.14</v>
+        <v>1.49</v>
       </c>
       <c r="O7">
-        <v>3.24</v>
+        <v>3.98</v>
       </c>
       <c r="P7">
-        <v>2.09</v>
+        <v>5.47</v>
       </c>
       <c r="Q7">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="R7">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U7">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>3.2</v>
+        <v>4.01</v>
       </c>
       <c r="AA7">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AB7">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
         <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>1.27</v>
+        <v>2.21</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>3.44</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
         <v>0</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X35">
         <v>0</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,61 +6992,61 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.62</v>
+        <v>1.55</v>
       </c>
       <c r="O41">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="P41">
-        <v>1.88</v>
+        <v>4.79</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S41">
         <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="U41">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>3.82</v>
+        <v>4.18</v>
       </c>
       <c r="AA41">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC41">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD41">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
         <v>2.1</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK41">
-        <v>1.19</v>
+        <v>2.14</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,61 +7155,61 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.55</v>
+        <v>3.62</v>
       </c>
       <c r="O42">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="P42">
-        <v>4.79</v>
+        <v>1.88</v>
       </c>
       <c r="Q42">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="R42">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
         <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V42">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z42">
-        <v>4.18</v>
+        <v>3.82</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB42">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC42">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD42">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG42">
         <v>2.1</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>2.14</v>
+        <v>1.19</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="O49">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P49">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="Q49">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="R49">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S49">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U49">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="V49">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
         <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC49">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="AD49">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG49">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK49">
         <v>1.65</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,77 +8622,77 @@
         </is>
       </c>
       <c r="N51">
+        <v>2.09</v>
+      </c>
+      <c r="O51">
+        <v>3.54</v>
+      </c>
+      <c r="P51">
+        <v>3.15</v>
+      </c>
+      <c r="Q51">
+        <v>2.75</v>
+      </c>
+      <c r="R51">
         <v>2.19</v>
       </c>
-      <c r="O51">
-        <v>3.62</v>
-      </c>
-      <c r="P51">
-        <v>2.88</v>
-      </c>
-      <c r="Q51">
-        <v>2.43</v>
-      </c>
-      <c r="R51">
-        <v>2.21</v>
-      </c>
       <c r="S51">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T51">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U51">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA51">
         <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="AD51">
+        <v>1.43</v>
+      </c>
+      <c r="AE51">
+        <v>1.13</v>
+      </c>
+      <c r="AF51">
+        <v>1.55</v>
+      </c>
+      <c r="AG51">
+        <v>2.25</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.33</v>
-      </c>
-      <c r="AE51">
-        <v>1.12</v>
-      </c>
-      <c r="AF51">
-        <v>1.64</v>
-      </c>
-      <c r="AG51">
-        <v>2.13</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.27</v>
       </c>
       <c r="AK51">
         <v>1.65</v>
@@ -8957,55 +8957,55 @@
         <v>0</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X53">
         <v>0</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="O62">
-        <v>3.48</v>
+        <v>5</v>
       </c>
       <c r="P62">
-        <v>3.94</v>
+        <v>6.4</v>
       </c>
       <c r="Q62">
-        <v>2.39</v>
+        <v>1.74</v>
       </c>
       <c r="R62">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="S62">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="T62">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="U62">
-        <v>2.71</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="W62">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="X62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="Z62">
-        <v>3.05</v>
+        <v>5.85</v>
       </c>
       <c r="AA62">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>1.79</v>
+        <v>2.87</v>
       </c>
       <c r="AC62">
-        <v>3.44</v>
+        <v>2.02</v>
       </c>
       <c r="AD62">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="AE62">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AF62">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK62">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,80 +10578,80 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="O63">
-        <v>5</v>
+        <v>3.48</v>
       </c>
       <c r="P63">
-        <v>6.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q63">
-        <v>1.74</v>
+        <v>2.39</v>
       </c>
       <c r="R63">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="S63">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="T63">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="U63">
-        <v>1.95</v>
+        <v>2.71</v>
       </c>
       <c r="V63">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="W63">
+        <v>1.06</v>
+      </c>
+      <c r="X63">
+        <v>1.03</v>
+      </c>
+      <c r="Y63">
+        <v>1.26</v>
+      </c>
+      <c r="Z63">
+        <v>3.05</v>
+      </c>
+      <c r="AA63">
+        <v>2.01</v>
+      </c>
+      <c r="AB63">
+        <v>1.79</v>
+      </c>
+      <c r="AC63">
+        <v>3.44</v>
+      </c>
+      <c r="AD63">
+        <v>1.26</v>
+      </c>
+      <c r="AE63">
+        <v>1.06</v>
+      </c>
+      <c r="AF63">
+        <v>1.82</v>
+      </c>
+      <c r="AG63">
+        <v>1.88</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
         <v>1.19</v>
       </c>
-      <c r="X63">
-        <v>1.01</v>
-      </c>
-      <c r="Y63">
-        <v>1.07</v>
-      </c>
-      <c r="Z63">
-        <v>5.85</v>
-      </c>
-      <c r="AA63">
-        <v>1.4</v>
-      </c>
-      <c r="AB63">
-        <v>2.87</v>
-      </c>
-      <c r="AC63">
-        <v>2.02</v>
-      </c>
-      <c r="AD63">
-        <v>1.77</v>
-      </c>
-      <c r="AE63">
-        <v>1.33</v>
-      </c>
-      <c r="AF63">
-        <v>1.57</v>
-      </c>
-      <c r="AG63">
-        <v>2.26</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.13</v>
-      </c>
       <c r="AK63">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11239,55 +11239,55 @@
         <v>2.48</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE67">
         <v>0</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="R90">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T90">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="U90">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="V90">
+        <v>1.4</v>
+      </c>
+      <c r="W90">
+        <v>1.06</v>
+      </c>
+      <c r="X90">
+        <v>1.03</v>
+      </c>
+      <c r="Y90">
         <v>1.3</v>
       </c>
-      <c r="W90">
-        <v>1.02</v>
-      </c>
-      <c r="X90">
-        <v>1.04</v>
-      </c>
-      <c r="Y90">
-        <v>1.36</v>
-      </c>
       <c r="Z90">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AA90">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB90">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC90">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD90">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE90">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG90">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK90">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q91">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="R91">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S91">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T91">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="U91">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="V91">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X91">
+        <v>1.04</v>
+      </c>
+      <c r="Y91">
+        <v>1.36</v>
+      </c>
+      <c r="Z91">
+        <v>2.7</v>
+      </c>
+      <c r="AA91">
+        <v>2.25</v>
+      </c>
+      <c r="AB91">
+        <v>1.57</v>
+      </c>
+      <c r="AC91">
+        <v>3.9</v>
+      </c>
+      <c r="AD91">
+        <v>1.17</v>
+      </c>
+      <c r="AE91">
         <v>1.03</v>
       </c>
-      <c r="Y91">
-        <v>1.3</v>
-      </c>
-      <c r="Z91">
-        <v>3.25</v>
-      </c>
-      <c r="AA91">
-        <v>2.1</v>
-      </c>
-      <c r="AB91">
-        <v>1.7</v>
-      </c>
-      <c r="AC91">
-        <v>3.6</v>
-      </c>
-      <c r="AD91">
-        <v>1.25</v>
-      </c>
-      <c r="AE91">
-        <v>1.06</v>
-      </c>
       <c r="AF91">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AG91">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK91">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC99">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.14</v>
+        <v>2.23</v>
       </c>
       <c r="O6">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="P6">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q6">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T6">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="U6">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z6">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA6">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="AB6">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AC6">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE6">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG6">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.49</v>
+        <v>2.38</v>
       </c>
       <c r="O7">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>5.47</v>
+        <v>2.47</v>
       </c>
       <c r="Q7">
-        <v>1.99</v>
+        <v>3.22</v>
       </c>
       <c r="R7">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S7">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
         <v>3.2</v>
       </c>
       <c r="U7">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="V7">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W7">
         <v>1.11</v>
@@ -1483,31 +1483,31 @@
         <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="AA7">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AB7">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AD7">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE7">
         <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK7">
-        <v>2.21</v>
+        <v>1.39</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,65 +1613,65 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.23</v>
+        <v>3.14</v>
       </c>
       <c r="O8">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q8">
-        <v>3.13</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
+        <v>2.08</v>
+      </c>
+      <c r="S8">
+        <v>1.33</v>
+      </c>
+      <c r="T8">
+        <v>2.95</v>
+      </c>
+      <c r="U8">
+        <v>2.65</v>
+      </c>
+      <c r="V8">
+        <v>1.38</v>
+      </c>
+      <c r="W8">
+        <v>1.06</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1.26</v>
+      </c>
+      <c r="Z8">
+        <v>3.2</v>
+      </c>
+      <c r="AA8">
+        <v>1.99</v>
+      </c>
+      <c r="AB8">
+        <v>1.78</v>
+      </c>
+      <c r="AC8">
+        <v>3.2</v>
+      </c>
+      <c r="AD8">
+        <v>1.3</v>
+      </c>
+      <c r="AE8">
+        <v>1.11</v>
+      </c>
+      <c r="AF8">
+        <v>1.73</v>
+      </c>
+      <c r="AG8">
         <v>1.98</v>
       </c>
-      <c r="S8">
-        <v>1.45</v>
-      </c>
-      <c r="T8">
-        <v>2.42</v>
-      </c>
-      <c r="U8">
-        <v>3.22</v>
-      </c>
-      <c r="V8">
-        <v>1.35</v>
-      </c>
-      <c r="W8">
-        <v>1.07</v>
-      </c>
-      <c r="X8">
-        <v>1.04</v>
-      </c>
-      <c r="Y8">
-        <v>1.35</v>
-      </c>
-      <c r="Z8">
-        <v>2.74</v>
-      </c>
-      <c r="AA8">
-        <v>2.19</v>
-      </c>
-      <c r="AB8">
-        <v>1.61</v>
-      </c>
-      <c r="AC8">
-        <v>3.74</v>
-      </c>
-      <c r="AD8">
-        <v>1.19</v>
-      </c>
-      <c r="AE8">
-        <v>1.03</v>
-      </c>
-      <c r="AF8">
-        <v>1.84</v>
-      </c>
-      <c r="AG8">
-        <v>1.82</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="O9">
-        <v>3.48</v>
+        <v>3.98</v>
       </c>
       <c r="P9">
-        <v>4.87</v>
+        <v>5.47</v>
       </c>
       <c r="Q9">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S9">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T9">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="U9">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="AA9">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AB9">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AC9">
-        <v>3.48</v>
+        <v>2.66</v>
       </c>
       <c r="AD9">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG9">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P10">
-        <v>2.32</v>
+        <v>4.87</v>
       </c>
       <c r="Q10">
-        <v>3.2</v>
+        <v>2.23</v>
       </c>
       <c r="R10">
         <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T10">
-        <v>2.98</v>
+        <v>2.64</v>
       </c>
       <c r="U10">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z10">
-        <v>3.43</v>
+        <v>3.08</v>
       </c>
       <c r="AA10">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AB10">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AC10">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="AD10">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="Q11">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="R11">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="V11">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z11">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="AA11">
+        <v>1.97</v>
+      </c>
+      <c r="AB11">
+        <v>1.79</v>
+      </c>
+      <c r="AC11">
+        <v>3.14</v>
+      </c>
+      <c r="AD11">
+        <v>1.27</v>
+      </c>
+      <c r="AE11">
+        <v>1.07</v>
+      </c>
+      <c r="AF11">
         <v>1.7</v>
       </c>
-      <c r="AB11">
-        <v>2.1</v>
-      </c>
-      <c r="AC11">
-        <v>2.77</v>
-      </c>
-      <c r="AD11">
-        <v>1.37</v>
-      </c>
-      <c r="AE11">
-        <v>1.11</v>
-      </c>
-      <c r="AF11">
-        <v>1.55</v>
-      </c>
       <c r="AG11">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK11">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,61 +6992,61 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.55</v>
+        <v>3.62</v>
       </c>
       <c r="O41">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="P41">
-        <v>4.79</v>
+        <v>1.88</v>
       </c>
       <c r="Q41">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="R41">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
         <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="U41">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V41">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W41">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
-        <v>4.18</v>
+        <v>3.82</v>
       </c>
       <c r="AA41">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB41">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC41">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD41">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG41">
         <v>2.1</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>2.14</v>
+        <v>1.19</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,61 +7155,61 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.62</v>
+        <v>1.55</v>
       </c>
       <c r="O42">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="P42">
-        <v>1.88</v>
+        <v>4.79</v>
       </c>
       <c r="Q42">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
         <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="U42">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>3.82</v>
+        <v>4.18</v>
       </c>
       <c r="AA42">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC42">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD42">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG42">
         <v>2.1</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK42">
-        <v>1.19</v>
+        <v>2.14</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="O49">
-        <v>3.62</v>
+        <v>2.91</v>
       </c>
       <c r="P49">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="Q49">
-        <v>2.43</v>
+        <v>3.24</v>
       </c>
       <c r="R49">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T49">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="U49">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W49">
         <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
         <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>3.5</v>
+        <v>4.07</v>
       </c>
       <c r="AA49">
+        <v>2.03</v>
+      </c>
+      <c r="AB49">
         <v>1.83</v>
       </c>
-      <c r="AB49">
-        <v>1.93</v>
-      </c>
       <c r="AC49">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AD49">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE49">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AK49">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.83</v>
+        <v>2.09</v>
       </c>
       <c r="O50">
-        <v>2.91</v>
+        <v>3.54</v>
       </c>
       <c r="P50">
-        <v>2.57</v>
+        <v>3.15</v>
       </c>
       <c r="Q50">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S50">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="T50">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="V50">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>4.07</v>
+        <v>4.33</v>
       </c>
       <c r="AA50">
+        <v>1.83</v>
+      </c>
+      <c r="AB50">
         <v>2.03</v>
       </c>
-      <c r="AB50">
-        <v>1.83</v>
-      </c>
       <c r="AC50">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="AD50">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE50">
         <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG50">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK50">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="O51">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P51">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="Q51">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="R51">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S51">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T51">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U51">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="V51">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
         <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC51">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG51">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
         <v>1.65</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q86">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S86">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T86">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="U86">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="V86">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W86">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y86">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z86">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA86">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB86">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC86">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD86">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE86">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG86">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK86">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AL86">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q6">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="R6">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T6">
-        <v>2.42</v>
+        <v>2.98</v>
       </c>
       <c r="U6">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W6">
+        <v>1.05</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>1.26</v>
+      </c>
+      <c r="Z6">
+        <v>3.43</v>
+      </c>
+      <c r="AA6">
+        <v>1.97</v>
+      </c>
+      <c r="AB6">
+        <v>1.79</v>
+      </c>
+      <c r="AC6">
+        <v>3.14</v>
+      </c>
+      <c r="AD6">
+        <v>1.27</v>
+      </c>
+      <c r="AE6">
         <v>1.07</v>
       </c>
-      <c r="X6">
-        <v>1.04</v>
-      </c>
-      <c r="Y6">
-        <v>1.35</v>
-      </c>
-      <c r="Z6">
-        <v>2.74</v>
-      </c>
-      <c r="AA6">
-        <v>2.19</v>
-      </c>
-      <c r="AB6">
-        <v>1.61</v>
-      </c>
-      <c r="AC6">
-        <v>3.74</v>
-      </c>
-      <c r="AD6">
-        <v>1.19</v>
-      </c>
-      <c r="AE6">
-        <v>1.03</v>
-      </c>
       <c r="AF6">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="P7">
-        <v>2.47</v>
+        <v>2.09</v>
       </c>
       <c r="Q7">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="R7">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="S7">
+        <v>1.33</v>
+      </c>
+      <c r="T7">
+        <v>2.95</v>
+      </c>
+      <c r="U7">
+        <v>2.65</v>
+      </c>
+      <c r="V7">
+        <v>1.38</v>
+      </c>
+      <c r="W7">
+        <v>1.06</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1.26</v>
+      </c>
+      <c r="Z7">
+        <v>3.2</v>
+      </c>
+      <c r="AA7">
+        <v>1.99</v>
+      </c>
+      <c r="AB7">
+        <v>1.78</v>
+      </c>
+      <c r="AC7">
+        <v>3.2</v>
+      </c>
+      <c r="AD7">
         <v>1.3</v>
-      </c>
-      <c r="T7">
-        <v>3.2</v>
-      </c>
-      <c r="U7">
-        <v>2.45</v>
-      </c>
-      <c r="V7">
-        <v>1.49</v>
-      </c>
-      <c r="W7">
-        <v>1.11</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.17</v>
-      </c>
-      <c r="Z7">
-        <v>4</v>
-      </c>
-      <c r="AA7">
-        <v>1.7</v>
-      </c>
-      <c r="AB7">
-        <v>2.1</v>
-      </c>
-      <c r="AC7">
-        <v>2.77</v>
-      </c>
-      <c r="AD7">
-        <v>1.37</v>
       </c>
       <c r="AE7">
         <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.14</v>
+        <v>1.49</v>
       </c>
       <c r="O8">
-        <v>3.24</v>
+        <v>3.98</v>
       </c>
       <c r="P8">
-        <v>2.09</v>
+        <v>5.47</v>
       </c>
       <c r="Q8">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="R8">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>3.2</v>
+        <v>4.01</v>
       </c>
       <c r="AA8">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AB8">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC8">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD8">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE8">
         <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG8">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.27</v>
+        <v>2.21</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="O9">
-        <v>3.98</v>
+        <v>2.99</v>
       </c>
       <c r="P9">
-        <v>5.47</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>1.99</v>
+        <v>3.13</v>
       </c>
       <c r="R9">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="S9">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="T9">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="U9">
-        <v>2.57</v>
+        <v>3.22</v>
       </c>
       <c r="V9">
+        <v>1.35</v>
+      </c>
+      <c r="W9">
+        <v>1.07</v>
+      </c>
+      <c r="X9">
+        <v>1.04</v>
+      </c>
+      <c r="Y9">
+        <v>1.35</v>
+      </c>
+      <c r="Z9">
+        <v>2.74</v>
+      </c>
+      <c r="AA9">
+        <v>2.19</v>
+      </c>
+      <c r="AB9">
+        <v>1.61</v>
+      </c>
+      <c r="AC9">
+        <v>3.74</v>
+      </c>
+      <c r="AD9">
+        <v>1.19</v>
+      </c>
+      <c r="AE9">
+        <v>1.03</v>
+      </c>
+      <c r="AF9">
+        <v>1.84</v>
+      </c>
+      <c r="AG9">
+        <v>1.82</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.29</v>
+      </c>
+      <c r="AK9">
         <v>1.48</v>
-      </c>
-      <c r="W9">
-        <v>1.11</v>
-      </c>
-      <c r="X9">
-        <v>1.03</v>
-      </c>
-      <c r="Y9">
-        <v>1.18</v>
-      </c>
-      <c r="Z9">
-        <v>4.01</v>
-      </c>
-      <c r="AA9">
-        <v>1.82</v>
-      </c>
-      <c r="AB9">
-        <v>1.94</v>
-      </c>
-      <c r="AC9">
-        <v>2.66</v>
-      </c>
-      <c r="AD9">
-        <v>1.41</v>
-      </c>
-      <c r="AE9">
-        <v>1.11</v>
-      </c>
-      <c r="AF9">
-        <v>1.71</v>
-      </c>
-      <c r="AG9">
-        <v>2</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.2</v>
-      </c>
-      <c r="AK9">
-        <v>2.21</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="Q11">
+        <v>3.22</v>
+      </c>
+      <c r="R11">
+        <v>2.17</v>
+      </c>
+      <c r="S11">
+        <v>1.3</v>
+      </c>
+      <c r="T11">
         <v>3.2</v>
       </c>
-      <c r="R11">
+      <c r="U11">
+        <v>2.45</v>
+      </c>
+      <c r="V11">
+        <v>1.49</v>
+      </c>
+      <c r="W11">
+        <v>1.11</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
+        <v>1.17</v>
+      </c>
+      <c r="Z11">
+        <v>4</v>
+      </c>
+      <c r="AA11">
+        <v>1.7</v>
+      </c>
+      <c r="AB11">
         <v>2.1</v>
       </c>
-      <c r="S11">
+      <c r="AC11">
+        <v>2.77</v>
+      </c>
+      <c r="AD11">
         <v>1.37</v>
       </c>
-      <c r="T11">
-        <v>2.98</v>
-      </c>
-      <c r="U11">
-        <v>2.86</v>
-      </c>
-      <c r="V11">
-        <v>1.37</v>
-      </c>
-      <c r="W11">
-        <v>1.05</v>
-      </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
-      <c r="Y11">
+      <c r="AE11">
+        <v>1.11</v>
+      </c>
+      <c r="AF11">
+        <v>1.55</v>
+      </c>
+      <c r="AG11">
+        <v>2.25</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
         <v>1.26</v>
       </c>
-      <c r="Z11">
-        <v>3.43</v>
-      </c>
-      <c r="AA11">
-        <v>1.97</v>
-      </c>
-      <c r="AB11">
-        <v>1.79</v>
-      </c>
-      <c r="AC11">
-        <v>3.14</v>
-      </c>
-      <c r="AD11">
-        <v>1.27</v>
-      </c>
-      <c r="AE11">
-        <v>1.07</v>
-      </c>
-      <c r="AF11">
-        <v>1.7</v>
-      </c>
-      <c r="AG11">
-        <v>2</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.28</v>
-      </c>
       <c r="AK11">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="O48">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="P48">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="Q48">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="R48">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T48">
+        <v>2.7</v>
+      </c>
+      <c r="U48">
         <v>2.75</v>
       </c>
-      <c r="U48">
-        <v>2.96</v>
-      </c>
       <c r="V48">
+        <v>1.43</v>
+      </c>
+      <c r="W48">
+        <v>1.07</v>
+      </c>
+      <c r="X48">
+        <v>1.02</v>
+      </c>
+      <c r="Y48">
+        <v>1.22</v>
+      </c>
+      <c r="Z48">
+        <v>4.07</v>
+      </c>
+      <c r="AA48">
+        <v>2.03</v>
+      </c>
+      <c r="AB48">
+        <v>1.83</v>
+      </c>
+      <c r="AC48">
+        <v>2.74</v>
+      </c>
+      <c r="AD48">
+        <v>1.35</v>
+      </c>
+      <c r="AE48">
+        <v>1.13</v>
+      </c>
+      <c r="AF48">
+        <v>1.6</v>
+      </c>
+      <c r="AG48">
+        <v>2.19</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
         <v>1.4</v>
       </c>
-      <c r="W48">
-        <v>1.06</v>
-      </c>
-      <c r="X48">
-        <v>1.03</v>
-      </c>
-      <c r="Y48">
-        <v>1.3</v>
-      </c>
-      <c r="Z48">
-        <v>3.2</v>
-      </c>
-      <c r="AA48">
-        <v>1.94</v>
-      </c>
-      <c r="AB48">
-        <v>1.8</v>
-      </c>
-      <c r="AC48">
-        <v>3.28</v>
-      </c>
-      <c r="AD48">
-        <v>1.25</v>
-      </c>
-      <c r="AE48">
-        <v>1.05</v>
-      </c>
-      <c r="AF48">
-        <v>1.73</v>
-      </c>
-      <c r="AG48">
-        <v>1.95</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.41</v>
-      </c>
       <c r="AK48">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.83</v>
+        <v>2.09</v>
       </c>
       <c r="O49">
-        <v>2.91</v>
+        <v>3.54</v>
       </c>
       <c r="P49">
-        <v>2.57</v>
+        <v>3.15</v>
       </c>
       <c r="Q49">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="R49">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S49">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="T49">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="U49">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="V49">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>4.07</v>
+        <v>4.33</v>
       </c>
       <c r="AA49">
+        <v>1.83</v>
+      </c>
+      <c r="AB49">
         <v>2.03</v>
       </c>
-      <c r="AB49">
-        <v>1.83</v>
-      </c>
       <c r="AC49">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="AD49">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE49">
         <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK49">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="O50">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P50">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="Q50">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="R50">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S50">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T50">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U50">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="V50">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
         <v>1.83</v>
       </c>
       <c r="AB50">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC50">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="AD50">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE50">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG50">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK50">
         <v>1.65</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,34 +8622,34 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.19</v>
+        <v>2.92</v>
       </c>
       <c r="O51">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="P51">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="Q51">
-        <v>2.43</v>
+        <v>3.26</v>
       </c>
       <c r="R51">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X51">
         <v>1.01</v>
@@ -8658,44 +8658,44 @@
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA51">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AB51">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD51">
+        <v>1.36</v>
+      </c>
+      <c r="AE51">
+        <v>1.13</v>
+      </c>
+      <c r="AF51">
+        <v>1.58</v>
+      </c>
+      <c r="AG51">
+        <v>2.3</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.65</v>
+      </c>
+      <c r="AK51">
         <v>1.33</v>
-      </c>
-      <c r="AE51">
-        <v>1.12</v>
-      </c>
-      <c r="AF51">
-        <v>1.64</v>
-      </c>
-      <c r="AG51">
-        <v>2.13</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.27</v>
-      </c>
-      <c r="AK51">
-        <v>1.65</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
       <c r="O52">
-        <v>3.74</v>
+        <v>3.02</v>
       </c>
       <c r="P52">
-        <v>2.13</v>
+        <v>2.58</v>
       </c>
       <c r="Q52">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S52">
+        <v>1.38</v>
+      </c>
+      <c r="T52">
+        <v>2.75</v>
+      </c>
+      <c r="U52">
+        <v>2.96</v>
+      </c>
+      <c r="V52">
+        <v>1.4</v>
+      </c>
+      <c r="W52">
+        <v>1.06</v>
+      </c>
+      <c r="X52">
+        <v>1.03</v>
+      </c>
+      <c r="Y52">
         <v>1.3</v>
       </c>
-      <c r="T52">
-        <v>3.3</v>
-      </c>
-      <c r="U52">
-        <v>2.45</v>
-      </c>
-      <c r="V52">
-        <v>1.51</v>
-      </c>
-      <c r="W52">
-        <v>1.09</v>
-      </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.22</v>
-      </c>
       <c r="Z52">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA52">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="AB52">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC52">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD52">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF52">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AG52">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AK52">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="O69">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P69">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q69">
-        <v>2.16</v>
+        <v>2.99</v>
       </c>
       <c r="R69">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S69">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T69">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U69">
-        <v>2.89</v>
+        <v>3.24</v>
       </c>
       <c r="V69">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W69">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X69">
+        <v>1.02</v>
+      </c>
+      <c r="Y69">
+        <v>1.36</v>
+      </c>
+      <c r="Z69">
+        <v>2.7</v>
+      </c>
+      <c r="AA69">
+        <v>2.2</v>
+      </c>
+      <c r="AB69">
+        <v>1.57</v>
+      </c>
+      <c r="AC69">
+        <v>4.2</v>
+      </c>
+      <c r="AD69">
+        <v>1.16</v>
+      </c>
+      <c r="AE69">
         <v>1.01</v>
       </c>
-      <c r="Y69">
-        <v>1.3</v>
-      </c>
-      <c r="Z69">
-        <v>2.97</v>
-      </c>
-      <c r="AA69">
-        <v>2.01</v>
-      </c>
-      <c r="AB69">
-        <v>1.69</v>
-      </c>
-      <c r="AC69">
-        <v>3.5</v>
-      </c>
-      <c r="AD69">
-        <v>1.22</v>
-      </c>
-      <c r="AE69">
-        <v>1.04</v>
-      </c>
       <c r="AF69">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG69">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AK69">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="O70">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P70">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q70">
-        <v>2.99</v>
+        <v>2.16</v>
       </c>
       <c r="R70">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S70">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T70">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="U70">
-        <v>3.24</v>
+        <v>2.89</v>
       </c>
       <c r="V70">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W70">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z70">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AA70">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AB70">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AC70">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD70">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE70">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF70">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG70">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AK70">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q90">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S90">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T90">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="U90">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="V90">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W90">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X90">
+        <v>1.04</v>
+      </c>
+      <c r="Y90">
+        <v>1.36</v>
+      </c>
+      <c r="Z90">
+        <v>2.7</v>
+      </c>
+      <c r="AA90">
+        <v>2.25</v>
+      </c>
+      <c r="AB90">
+        <v>1.57</v>
+      </c>
+      <c r="AC90">
+        <v>3.9</v>
+      </c>
+      <c r="AD90">
+        <v>1.17</v>
+      </c>
+      <c r="AE90">
         <v>1.03</v>
       </c>
-      <c r="Y90">
-        <v>1.3</v>
-      </c>
-      <c r="Z90">
-        <v>3.25</v>
-      </c>
-      <c r="AA90">
-        <v>2.1</v>
-      </c>
-      <c r="AB90">
-        <v>1.7</v>
-      </c>
-      <c r="AC90">
-        <v>3.6</v>
-      </c>
-      <c r="AD90">
-        <v>1.25</v>
-      </c>
-      <c r="AE90">
-        <v>1.06</v>
-      </c>
       <c r="AF90">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AG90">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK90">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="R91">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T91">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="U91">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="V91">
+        <v>1.4</v>
+      </c>
+      <c r="W91">
+        <v>1.06</v>
+      </c>
+      <c r="X91">
+        <v>1.03</v>
+      </c>
+      <c r="Y91">
         <v>1.3</v>
       </c>
-      <c r="W91">
-        <v>1.02</v>
-      </c>
-      <c r="X91">
-        <v>1.04</v>
-      </c>
-      <c r="Y91">
-        <v>1.36</v>
-      </c>
       <c r="Z91">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB91">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC91">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD91">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE91">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG91">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK91">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AL91">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P6">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="Q6">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R6">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S6">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="U6">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="V6">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
         <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB6">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC6">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
+        <v>1.3</v>
+      </c>
+      <c r="AE6">
+        <v>1.11</v>
+      </c>
+      <c r="AF6">
+        <v>1.73</v>
+      </c>
+      <c r="AG6">
+        <v>1.98</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.24</v>
+      </c>
+      <c r="AK6">
         <v>1.27</v>
-      </c>
-      <c r="AE6">
-        <v>1.07</v>
-      </c>
-      <c r="AF6">
-        <v>1.7</v>
-      </c>
-      <c r="AG6">
-        <v>2</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.28</v>
-      </c>
-      <c r="AK6">
-        <v>1.38</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.14</v>
+        <v>2.23</v>
       </c>
       <c r="O7">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="P7">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q7">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="R7">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T7">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="U7">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z7">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA7">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="AB7">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AC7">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE7">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG7">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="O8">
-        <v>3.98</v>
+        <v>3.48</v>
       </c>
       <c r="P8">
-        <v>5.47</v>
+        <v>4.87</v>
       </c>
       <c r="Q8">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="R8">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T8">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="U8">
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="V8">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z8">
-        <v>4.01</v>
+        <v>3.08</v>
       </c>
       <c r="AA8">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AB8">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AC8">
-        <v>2.66</v>
+        <v>3.48</v>
       </c>
       <c r="AD8">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AE8">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF8">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="O9">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q9">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="R9">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T9">
-        <v>2.42</v>
+        <v>2.98</v>
       </c>
       <c r="U9">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
+        <v>1.05</v>
+      </c>
+      <c r="X9">
+        <v>1.01</v>
+      </c>
+      <c r="Y9">
+        <v>1.26</v>
+      </c>
+      <c r="Z9">
+        <v>3.43</v>
+      </c>
+      <c r="AA9">
+        <v>1.97</v>
+      </c>
+      <c r="AB9">
+        <v>1.79</v>
+      </c>
+      <c r="AC9">
+        <v>3.14</v>
+      </c>
+      <c r="AD9">
+        <v>1.27</v>
+      </c>
+      <c r="AE9">
         <v>1.07</v>
       </c>
-      <c r="X9">
-        <v>1.04</v>
-      </c>
-      <c r="Y9">
-        <v>1.35</v>
-      </c>
-      <c r="Z9">
-        <v>2.74</v>
-      </c>
-      <c r="AA9">
-        <v>2.19</v>
-      </c>
-      <c r="AB9">
-        <v>1.61</v>
-      </c>
-      <c r="AC9">
-        <v>3.74</v>
-      </c>
-      <c r="AD9">
-        <v>1.19</v>
-      </c>
-      <c r="AE9">
-        <v>1.03</v>
-      </c>
       <c r="AF9">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG9">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="O10">
-        <v>3.48</v>
+        <v>3.98</v>
       </c>
       <c r="P10">
-        <v>4.87</v>
+        <v>5.47</v>
       </c>
       <c r="Q10">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="R10">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S10">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="V10">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="AA10">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AB10">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AC10">
-        <v>3.48</v>
+        <v>2.66</v>
       </c>
       <c r="AD10">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AE10">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG10">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,61 +6992,61 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.62</v>
+        <v>1.55</v>
       </c>
       <c r="O41">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="P41">
-        <v>1.88</v>
+        <v>4.79</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S41">
         <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="U41">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>3.82</v>
+        <v>4.18</v>
       </c>
       <c r="AA41">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC41">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD41">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
         <v>2.1</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK41">
-        <v>1.19</v>
+        <v>2.14</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,61 +7155,61 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.55</v>
+        <v>3.62</v>
       </c>
       <c r="O42">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="P42">
-        <v>4.79</v>
+        <v>1.88</v>
       </c>
       <c r="Q42">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="R42">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
         <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V42">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z42">
-        <v>4.18</v>
+        <v>3.82</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB42">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC42">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD42">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG42">
         <v>2.1</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>2.14</v>
+        <v>1.19</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="O49">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P49">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="Q49">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="R49">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S49">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U49">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="V49">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
         <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC49">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="AD49">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG49">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK49">
         <v>1.65</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.19</v>
+        <v>2.73</v>
       </c>
       <c r="O50">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="P50">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="Q50">
-        <v>2.43</v>
+        <v>3.18</v>
       </c>
       <c r="R50">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S50">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T50">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U50">
-        <v>2.47</v>
+        <v>2.96</v>
       </c>
       <c r="V50">
+        <v>1.4</v>
+      </c>
+      <c r="W50">
+        <v>1.06</v>
+      </c>
+      <c r="X50">
+        <v>1.03</v>
+      </c>
+      <c r="Y50">
+        <v>1.3</v>
+      </c>
+      <c r="Z50">
+        <v>3.2</v>
+      </c>
+      <c r="AA50">
+        <v>1.94</v>
+      </c>
+      <c r="AB50">
+        <v>1.8</v>
+      </c>
+      <c r="AC50">
+        <v>3.28</v>
+      </c>
+      <c r="AD50">
+        <v>1.25</v>
+      </c>
+      <c r="AE50">
+        <v>1.05</v>
+      </c>
+      <c r="AF50">
+        <v>1.73</v>
+      </c>
+      <c r="AG50">
+        <v>1.95</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.41</v>
+      </c>
+      <c r="AK50">
         <v>1.44</v>
-      </c>
-      <c r="W50">
-        <v>1.07</v>
-      </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.22</v>
-      </c>
-      <c r="Z50">
-        <v>3.5</v>
-      </c>
-      <c r="AA50">
-        <v>1.83</v>
-      </c>
-      <c r="AB50">
-        <v>1.93</v>
-      </c>
-      <c r="AC50">
-        <v>2.83</v>
-      </c>
-      <c r="AD50">
-        <v>1.33</v>
-      </c>
-      <c r="AE50">
-        <v>1.12</v>
-      </c>
-      <c r="AF50">
-        <v>1.64</v>
-      </c>
-      <c r="AG50">
-        <v>2.13</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.27</v>
-      </c>
-      <c r="AK50">
-        <v>1.65</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.73</v>
+        <v>2.09</v>
       </c>
       <c r="O52">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="P52">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="Q52">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="R52">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S52">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="T52">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U52">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="V52">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z52">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA52">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB52">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AC52">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AD52">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AE52">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG52">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK52">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="O62">
-        <v>5</v>
+        <v>3.48</v>
       </c>
       <c r="P62">
-        <v>6.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q62">
-        <v>1.74</v>
+        <v>2.39</v>
       </c>
       <c r="R62">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="S62">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="T62">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="U62">
-        <v>1.95</v>
+        <v>2.71</v>
       </c>
       <c r="V62">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="W62">
+        <v>1.06</v>
+      </c>
+      <c r="X62">
+        <v>1.03</v>
+      </c>
+      <c r="Y62">
+        <v>1.26</v>
+      </c>
+      <c r="Z62">
+        <v>3.05</v>
+      </c>
+      <c r="AA62">
+        <v>2.01</v>
+      </c>
+      <c r="AB62">
+        <v>1.79</v>
+      </c>
+      <c r="AC62">
+        <v>3.44</v>
+      </c>
+      <c r="AD62">
+        <v>1.26</v>
+      </c>
+      <c r="AE62">
+        <v>1.06</v>
+      </c>
+      <c r="AF62">
+        <v>1.82</v>
+      </c>
+      <c r="AG62">
+        <v>1.88</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.19</v>
       </c>
-      <c r="X62">
-        <v>1.01</v>
-      </c>
-      <c r="Y62">
-        <v>1.07</v>
-      </c>
-      <c r="Z62">
-        <v>5.85</v>
-      </c>
-      <c r="AA62">
-        <v>1.4</v>
-      </c>
-      <c r="AB62">
-        <v>2.87</v>
-      </c>
-      <c r="AC62">
-        <v>2.02</v>
-      </c>
-      <c r="AD62">
-        <v>1.77</v>
-      </c>
-      <c r="AE62">
-        <v>1.33</v>
-      </c>
-      <c r="AF62">
-        <v>1.57</v>
-      </c>
-      <c r="AG62">
-        <v>2.26</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.13</v>
-      </c>
       <c r="AK62">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="O63">
-        <v>3.48</v>
+        <v>5</v>
       </c>
       <c r="P63">
-        <v>3.94</v>
+        <v>6.4</v>
       </c>
       <c r="Q63">
-        <v>2.39</v>
+        <v>1.74</v>
       </c>
       <c r="R63">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="S63">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="T63">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="U63">
-        <v>2.71</v>
+        <v>1.95</v>
       </c>
       <c r="V63">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="W63">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="X63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="Z63">
-        <v>3.05</v>
+        <v>5.85</v>
       </c>
       <c r="AA63">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>1.79</v>
+        <v>2.87</v>
       </c>
       <c r="AC63">
-        <v>3.44</v>
+        <v>2.02</v>
       </c>
       <c r="AD63">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="AE63">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AF63">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AG63">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK63">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>2.32</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL86">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,31 +1287,31 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.14</v>
+        <v>1.63</v>
       </c>
       <c r="O6">
-        <v>3.24</v>
+        <v>3.48</v>
       </c>
       <c r="P6">
-        <v>2.09</v>
+        <v>4.87</v>
       </c>
       <c r="Q6">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T6">
-        <v>2.95</v>
+        <v>2.64</v>
       </c>
       <c r="U6">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
         <v>1.06</v>
@@ -1320,47 +1320,47 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z6">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA6">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AB6">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC6">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD6">
+        <v>1.22</v>
+      </c>
+      <c r="AE6">
+        <v>1.04</v>
+      </c>
+      <c r="AF6">
+        <v>1.85</v>
+      </c>
+      <c r="AG6">
+        <v>1.75</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.3</v>
       </c>
-      <c r="AE6">
-        <v>1.11</v>
-      </c>
-      <c r="AF6">
-        <v>1.73</v>
-      </c>
-      <c r="AG6">
-        <v>1.98</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.24</v>
-      </c>
       <c r="AK6">
-        <v>1.27</v>
+        <v>2.05</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,65 +1450,65 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.23</v>
+        <v>3.14</v>
       </c>
       <c r="O7">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="P7">
-        <v>3.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q7">
-        <v>3.13</v>
+        <v>3.5</v>
       </c>
       <c r="R7">
+        <v>2.08</v>
+      </c>
+      <c r="S7">
+        <v>1.33</v>
+      </c>
+      <c r="T7">
+        <v>2.95</v>
+      </c>
+      <c r="U7">
+        <v>2.65</v>
+      </c>
+      <c r="V7">
+        <v>1.38</v>
+      </c>
+      <c r="W7">
+        <v>1.06</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1.26</v>
+      </c>
+      <c r="Z7">
+        <v>3.2</v>
+      </c>
+      <c r="AA7">
+        <v>1.99</v>
+      </c>
+      <c r="AB7">
+        <v>1.78</v>
+      </c>
+      <c r="AC7">
+        <v>3.2</v>
+      </c>
+      <c r="AD7">
+        <v>1.3</v>
+      </c>
+      <c r="AE7">
+        <v>1.11</v>
+      </c>
+      <c r="AF7">
+        <v>1.73</v>
+      </c>
+      <c r="AG7">
         <v>1.98</v>
       </c>
-      <c r="S7">
-        <v>1.45</v>
-      </c>
-      <c r="T7">
-        <v>2.42</v>
-      </c>
-      <c r="U7">
-        <v>3.22</v>
-      </c>
-      <c r="V7">
-        <v>1.35</v>
-      </c>
-      <c r="W7">
-        <v>1.07</v>
-      </c>
-      <c r="X7">
-        <v>1.04</v>
-      </c>
-      <c r="Y7">
-        <v>1.35</v>
-      </c>
-      <c r="Z7">
-        <v>2.74</v>
-      </c>
-      <c r="AA7">
-        <v>2.19</v>
-      </c>
-      <c r="AB7">
-        <v>1.61</v>
-      </c>
-      <c r="AC7">
-        <v>3.74</v>
-      </c>
-      <c r="AD7">
-        <v>1.19</v>
-      </c>
-      <c r="AE7">
-        <v>1.03</v>
-      </c>
-      <c r="AF7">
-        <v>1.84</v>
-      </c>
-      <c r="AG7">
-        <v>1.82</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="O8">
-        <v>3.48</v>
+        <v>3.98</v>
       </c>
       <c r="P8">
-        <v>4.87</v>
+        <v>5.47</v>
       </c>
       <c r="Q8">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="AA8">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AB8">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AC8">
-        <v>3.48</v>
+        <v>2.66</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AE8">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG8">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="Q9">
+        <v>3.22</v>
+      </c>
+      <c r="R9">
+        <v>2.17</v>
+      </c>
+      <c r="S9">
+        <v>1.3</v>
+      </c>
+      <c r="T9">
         <v>3.2</v>
       </c>
-      <c r="R9">
+      <c r="U9">
+        <v>2.45</v>
+      </c>
+      <c r="V9">
+        <v>1.49</v>
+      </c>
+      <c r="W9">
+        <v>1.11</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
+        <v>1.17</v>
+      </c>
+      <c r="Z9">
+        <v>4</v>
+      </c>
+      <c r="AA9">
+        <v>1.7</v>
+      </c>
+      <c r="AB9">
         <v>2.1</v>
       </c>
-      <c r="S9">
+      <c r="AC9">
+        <v>2.77</v>
+      </c>
+      <c r="AD9">
         <v>1.37</v>
       </c>
-      <c r="T9">
-        <v>2.98</v>
-      </c>
-      <c r="U9">
-        <v>2.86</v>
-      </c>
-      <c r="V9">
-        <v>1.37</v>
-      </c>
-      <c r="W9">
-        <v>1.05</v>
-      </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
-      <c r="Y9">
+      <c r="AE9">
+        <v>1.11</v>
+      </c>
+      <c r="AF9">
+        <v>1.55</v>
+      </c>
+      <c r="AG9">
+        <v>2.25</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.26</v>
       </c>
-      <c r="Z9">
-        <v>3.43</v>
-      </c>
-      <c r="AA9">
-        <v>1.97</v>
-      </c>
-      <c r="AB9">
-        <v>1.79</v>
-      </c>
-      <c r="AC9">
-        <v>3.14</v>
-      </c>
-      <c r="AD9">
-        <v>1.27</v>
-      </c>
-      <c r="AE9">
-        <v>1.07</v>
-      </c>
-      <c r="AF9">
-        <v>1.7</v>
-      </c>
-      <c r="AG9">
-        <v>2</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.28</v>
-      </c>
       <c r="AK9">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="O10">
-        <v>3.98</v>
+        <v>2.99</v>
       </c>
       <c r="P10">
-        <v>5.47</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
-        <v>1.99</v>
+        <v>3.13</v>
       </c>
       <c r="R10">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="S10">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="U10">
-        <v>2.57</v>
+        <v>3.22</v>
       </c>
       <c r="V10">
+        <v>1.35</v>
+      </c>
+      <c r="W10">
+        <v>1.07</v>
+      </c>
+      <c r="X10">
+        <v>1.04</v>
+      </c>
+      <c r="Y10">
+        <v>1.35</v>
+      </c>
+      <c r="Z10">
+        <v>2.74</v>
+      </c>
+      <c r="AA10">
+        <v>2.19</v>
+      </c>
+      <c r="AB10">
+        <v>1.61</v>
+      </c>
+      <c r="AC10">
+        <v>3.74</v>
+      </c>
+      <c r="AD10">
+        <v>1.19</v>
+      </c>
+      <c r="AE10">
+        <v>1.03</v>
+      </c>
+      <c r="AF10">
+        <v>1.84</v>
+      </c>
+      <c r="AG10">
+        <v>1.82</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>1.29</v>
+      </c>
+      <c r="AK10">
         <v>1.48</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.18</v>
-      </c>
-      <c r="Z10">
-        <v>4.01</v>
-      </c>
-      <c r="AA10">
-        <v>1.82</v>
-      </c>
-      <c r="AB10">
-        <v>1.94</v>
-      </c>
-      <c r="AC10">
-        <v>2.66</v>
-      </c>
-      <c r="AD10">
-        <v>1.41</v>
-      </c>
-      <c r="AE10">
-        <v>1.11</v>
-      </c>
-      <c r="AF10">
-        <v>1.71</v>
-      </c>
-      <c r="AG10">
-        <v>2</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.2</v>
-      </c>
-      <c r="AK10">
-        <v>2.21</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="Q11">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="R11">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="V11">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z11">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="AA11">
+        <v>1.97</v>
+      </c>
+      <c r="AB11">
+        <v>1.79</v>
+      </c>
+      <c r="AC11">
+        <v>3.14</v>
+      </c>
+      <c r="AD11">
+        <v>1.27</v>
+      </c>
+      <c r="AE11">
+        <v>1.07</v>
+      </c>
+      <c r="AF11">
         <v>1.7</v>
       </c>
-      <c r="AB11">
-        <v>2.1</v>
-      </c>
-      <c r="AC11">
-        <v>2.77</v>
-      </c>
-      <c r="AD11">
-        <v>1.37</v>
-      </c>
-      <c r="AE11">
-        <v>1.11</v>
-      </c>
-      <c r="AF11">
-        <v>1.55</v>
-      </c>
       <c r="AG11">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK11">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,61 +6992,61 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.55</v>
+        <v>3.62</v>
       </c>
       <c r="O41">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="P41">
-        <v>4.79</v>
+        <v>1.88</v>
       </c>
       <c r="Q41">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="R41">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
         <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="U41">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V41">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W41">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
-        <v>4.18</v>
+        <v>3.82</v>
       </c>
       <c r="AA41">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB41">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC41">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD41">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG41">
         <v>2.1</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>2.14</v>
+        <v>1.19</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,61 +7155,61 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.62</v>
+        <v>1.55</v>
       </c>
       <c r="O42">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="P42">
-        <v>1.88</v>
+        <v>4.79</v>
       </c>
       <c r="Q42">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
         <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="U42">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>3.82</v>
+        <v>4.18</v>
       </c>
       <c r="AA42">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC42">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD42">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG42">
         <v>2.1</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK42">
-        <v>1.19</v>
+        <v>2.14</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="O48">
-        <v>2.91</v>
+        <v>3.74</v>
       </c>
       <c r="P48">
-        <v>2.57</v>
+        <v>2.13</v>
       </c>
       <c r="Q48">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="R48">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S48">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="U48">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V48">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W48">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
         <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="AA48">
-        <v>2.03</v>
+        <v>1.69</v>
       </c>
       <c r="AB48">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AC48">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD48">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE48">
         <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG48">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AK48">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.19</v>
+        <v>2.73</v>
       </c>
       <c r="O49">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="P49">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="Q49">
-        <v>2.43</v>
+        <v>3.18</v>
       </c>
       <c r="R49">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S49">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T49">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U49">
-        <v>2.47</v>
+        <v>2.96</v>
       </c>
       <c r="V49">
+        <v>1.4</v>
+      </c>
+      <c r="W49">
+        <v>1.06</v>
+      </c>
+      <c r="X49">
+        <v>1.03</v>
+      </c>
+      <c r="Y49">
+        <v>1.3</v>
+      </c>
+      <c r="Z49">
+        <v>3.2</v>
+      </c>
+      <c r="AA49">
+        <v>1.94</v>
+      </c>
+      <c r="AB49">
+        <v>1.8</v>
+      </c>
+      <c r="AC49">
+        <v>3.28</v>
+      </c>
+      <c r="AD49">
+        <v>1.25</v>
+      </c>
+      <c r="AE49">
+        <v>1.05</v>
+      </c>
+      <c r="AF49">
+        <v>1.73</v>
+      </c>
+      <c r="AG49">
+        <v>1.95</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.41</v>
+      </c>
+      <c r="AK49">
         <v>1.44</v>
-      </c>
-      <c r="W49">
-        <v>1.07</v>
-      </c>
-      <c r="X49">
-        <v>1.01</v>
-      </c>
-      <c r="Y49">
-        <v>1.22</v>
-      </c>
-      <c r="Z49">
-        <v>3.5</v>
-      </c>
-      <c r="AA49">
-        <v>1.83</v>
-      </c>
-      <c r="AB49">
-        <v>1.93</v>
-      </c>
-      <c r="AC49">
-        <v>2.83</v>
-      </c>
-      <c r="AD49">
-        <v>1.33</v>
-      </c>
-      <c r="AE49">
-        <v>1.12</v>
-      </c>
-      <c r="AF49">
-        <v>1.64</v>
-      </c>
-      <c r="AG49">
-        <v>2.13</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.27</v>
-      </c>
-      <c r="AK49">
-        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.73</v>
+        <v>2.09</v>
       </c>
       <c r="O50">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="P50">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="Q50">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="R50">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="T50">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="V50">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA50">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB50">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AC50">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AD50">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AE50">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG50">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O51">
-        <v>3.74</v>
+        <v>2.91</v>
       </c>
       <c r="P51">
-        <v>2.13</v>
+        <v>2.57</v>
       </c>
       <c r="Q51">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="U51">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W51">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.2</v>
+        <v>4.07</v>
       </c>
       <c r="AA51">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="AB51">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AC51">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE51">
         <v>1.13</v>
       </c>
       <c r="AF51">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AK51">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="O52">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P52">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="Q52">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="R52">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S52">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T52">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U52">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="V52">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA52">
         <v>1.83</v>
       </c>
       <c r="AB52">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC52">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="AD52">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG52">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK52">
         <v>1.65</v>
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q53">
-        <v>7.5</v>
+        <v>7.55</v>
       </c>
       <c r="R53">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="S53">
         <v>1.22</v>
@@ -8969,10 +8969,10 @@
         <v>3.8</v>
       </c>
       <c r="U53">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="V53">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W53">
         <v>1.16</v>
@@ -8999,13 +8999,13 @@
         <v>1.61</v>
       </c>
       <c r="AE53">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF53">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG53">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X55">
         <v>0</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="O56">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="P56">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X56">
         <v>0</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="O57">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G58">
@@ -9759,68 +9759,68 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N58">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="O58">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="P58">
-        <v>5</v>
+        <v>5.21</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,68 +9922,68 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N59">
+        <v>2.58</v>
+      </c>
+      <c r="O59">
+        <v>3.48</v>
+      </c>
+      <c r="P59">
+        <v>2.5</v>
+      </c>
+      <c r="Q59">
         <v>2.75</v>
       </c>
-      <c r="O59">
-        <v>3.4</v>
-      </c>
-      <c r="P59">
-        <v>2.55</v>
-      </c>
-      <c r="Q59">
-        <v>0</v>
-      </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G60">
@@ -10085,68 +10085,68 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N60">
-        <v>1.57</v>
+        <v>2.36</v>
       </c>
       <c r="O60">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P60">
-        <v>5.21</v>
+        <v>2.95</v>
       </c>
       <c r="Q60">
-        <v>2.13</v>
+        <v>2.94</v>
       </c>
       <c r="R60">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="S60">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T60">
-        <v>3.26</v>
+        <v>2.96</v>
       </c>
       <c r="U60">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="V60">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W60">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z60">
-        <v>4.21</v>
+        <v>3.42</v>
       </c>
       <c r="AA60">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AB60">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AC60">
-        <v>2.53</v>
+        <v>3.08</v>
       </c>
       <c r="AD60">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AE60">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF60">
         <v>1.68</v>
       </c>
       <c r="AG60">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK60">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.58</v>
+        <v>1.89</v>
       </c>
       <c r="O61">
         <v>3.48</v>
       </c>
       <c r="P61">
-        <v>2.5</v>
+        <v>3.94</v>
       </c>
       <c r="Q61">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="R61">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="S61">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T61">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="U61">
-        <v>2.4</v>
+        <v>2.71</v>
       </c>
       <c r="V61">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W61">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z61">
-        <v>4.05</v>
+        <v>3.05</v>
       </c>
       <c r="AA61">
-        <v>1.65</v>
+        <v>2.01</v>
       </c>
       <c r="AB61">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AC61">
-        <v>2.52</v>
+        <v>3.44</v>
       </c>
       <c r="AD61">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AE61">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF61">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AG61">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK61">
-        <v>1.46</v>
+        <v>1.91</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G62">
@@ -10411,84 +10411,84 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N62">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="O62">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="P62">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q62">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="R62">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="S62">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T62">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="U62">
-        <v>2.71</v>
+        <v>2.47</v>
       </c>
       <c r="V62">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W62">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X62">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z62">
-        <v>3.05</v>
+        <v>3.78</v>
       </c>
       <c r="AA62">
+        <v>1.72</v>
+      </c>
+      <c r="AB62">
+        <v>2.05</v>
+      </c>
+      <c r="AC62">
+        <v>2.62</v>
+      </c>
+      <c r="AD62">
+        <v>1.38</v>
+      </c>
+      <c r="AE62">
+        <v>1.12</v>
+      </c>
+      <c r="AF62">
+        <v>1.67</v>
+      </c>
+      <c r="AG62">
+        <v>2.05</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <v>1.25</v>
+      </c>
+      <c r="AK62">
         <v>2.01</v>
-      </c>
-      <c r="AB62">
-        <v>1.79</v>
-      </c>
-      <c r="AC62">
-        <v>3.44</v>
-      </c>
-      <c r="AD62">
-        <v>1.26</v>
-      </c>
-      <c r="AE62">
-        <v>1.06</v>
-      </c>
-      <c r="AF62">
-        <v>1.82</v>
-      </c>
-      <c r="AG62">
-        <v>1.88</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.19</v>
-      </c>
-      <c r="AK62">
-        <v>1.91</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="R90">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T90">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="U90">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="V90">
+        <v>1.4</v>
+      </c>
+      <c r="W90">
+        <v>1.06</v>
+      </c>
+      <c r="X90">
+        <v>1.03</v>
+      </c>
+      <c r="Y90">
         <v>1.3</v>
       </c>
-      <c r="W90">
-        <v>1.02</v>
-      </c>
-      <c r="X90">
-        <v>1.04</v>
-      </c>
-      <c r="Y90">
-        <v>1.36</v>
-      </c>
       <c r="Z90">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AA90">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB90">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC90">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD90">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE90">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG90">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK90">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q91">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="R91">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S91">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T91">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="U91">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="V91">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X91">
+        <v>1.04</v>
+      </c>
+      <c r="Y91">
+        <v>1.36</v>
+      </c>
+      <c r="Z91">
+        <v>2.7</v>
+      </c>
+      <c r="AA91">
+        <v>2.25</v>
+      </c>
+      <c r="AB91">
+        <v>1.57</v>
+      </c>
+      <c r="AC91">
+        <v>3.9</v>
+      </c>
+      <c r="AD91">
+        <v>1.17</v>
+      </c>
+      <c r="AE91">
         <v>1.03</v>
       </c>
-      <c r="Y91">
-        <v>1.3</v>
-      </c>
-      <c r="Z91">
-        <v>3.25</v>
-      </c>
-      <c r="AA91">
-        <v>2.1</v>
-      </c>
-      <c r="AB91">
-        <v>1.7</v>
-      </c>
-      <c r="AC91">
-        <v>3.6</v>
-      </c>
-      <c r="AD91">
-        <v>1.25</v>
-      </c>
-      <c r="AE91">
-        <v>1.06</v>
-      </c>
       <c r="AF91">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AG91">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK91">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="O126">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="P126">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="O127">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="P127">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V127">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W127">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X127">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD127">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21834,55 +21834,55 @@
         <v>3.5</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL132">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,31 +1287,31 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.63</v>
+        <v>3.14</v>
       </c>
       <c r="O6">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="P6">
-        <v>4.87</v>
+        <v>2.09</v>
       </c>
       <c r="Q6">
-        <v>2.23</v>
+        <v>3.5</v>
       </c>
       <c r="R6">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S6">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="U6">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
         <v>1.06</v>
@@ -1320,31 +1320,31 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AB6">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC6">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG6">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK6">
-        <v>2.05</v>
+        <v>1.27</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.14</v>
+        <v>1.49</v>
       </c>
       <c r="O7">
-        <v>3.24</v>
+        <v>3.98</v>
       </c>
       <c r="P7">
-        <v>2.09</v>
+        <v>5.47</v>
       </c>
       <c r="Q7">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="R7">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U7">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>3.2</v>
+        <v>4.01</v>
       </c>
       <c r="AA7">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AB7">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
         <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>1.27</v>
+        <v>2.21</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="O8">
-        <v>3.98</v>
+        <v>2.99</v>
       </c>
       <c r="P8">
-        <v>5.47</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>1.99</v>
+        <v>3.13</v>
       </c>
       <c r="R8">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="S8">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="T8">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="U8">
-        <v>2.57</v>
+        <v>3.22</v>
       </c>
       <c r="V8">
+        <v>1.35</v>
+      </c>
+      <c r="W8">
+        <v>1.07</v>
+      </c>
+      <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>1.35</v>
+      </c>
+      <c r="Z8">
+        <v>2.74</v>
+      </c>
+      <c r="AA8">
+        <v>2.19</v>
+      </c>
+      <c r="AB8">
+        <v>1.61</v>
+      </c>
+      <c r="AC8">
+        <v>3.74</v>
+      </c>
+      <c r="AD8">
+        <v>1.19</v>
+      </c>
+      <c r="AE8">
+        <v>1.03</v>
+      </c>
+      <c r="AF8">
+        <v>1.84</v>
+      </c>
+      <c r="AG8">
+        <v>1.82</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.29</v>
+      </c>
+      <c r="AK8">
         <v>1.48</v>
-      </c>
-      <c r="W8">
-        <v>1.11</v>
-      </c>
-      <c r="X8">
-        <v>1.03</v>
-      </c>
-      <c r="Y8">
-        <v>1.18</v>
-      </c>
-      <c r="Z8">
-        <v>4.01</v>
-      </c>
-      <c r="AA8">
-        <v>1.82</v>
-      </c>
-      <c r="AB8">
-        <v>1.94</v>
-      </c>
-      <c r="AC8">
-        <v>2.66</v>
-      </c>
-      <c r="AD8">
-        <v>1.41</v>
-      </c>
-      <c r="AE8">
-        <v>1.11</v>
-      </c>
-      <c r="AF8">
-        <v>1.71</v>
-      </c>
-      <c r="AG8">
-        <v>2</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.2</v>
-      </c>
-      <c r="AK8">
-        <v>2.21</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="O9">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P9">
-        <v>2.47</v>
+        <v>4.87</v>
       </c>
       <c r="Q9">
-        <v>3.22</v>
+        <v>2.23</v>
       </c>
       <c r="R9">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
+        <v>1.39</v>
+      </c>
+      <c r="T9">
+        <v>2.64</v>
+      </c>
+      <c r="U9">
+        <v>2.89</v>
+      </c>
+      <c r="V9">
+        <v>1.36</v>
+      </c>
+      <c r="W9">
+        <v>1.06</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1.28</v>
+      </c>
+      <c r="Z9">
+        <v>3.08</v>
+      </c>
+      <c r="AA9">
+        <v>2.02</v>
+      </c>
+      <c r="AB9">
+        <v>1.77</v>
+      </c>
+      <c r="AC9">
+        <v>3.48</v>
+      </c>
+      <c r="AD9">
+        <v>1.22</v>
+      </c>
+      <c r="AE9">
+        <v>1.04</v>
+      </c>
+      <c r="AF9">
+        <v>1.85</v>
+      </c>
+      <c r="AG9">
+        <v>1.75</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.3</v>
       </c>
-      <c r="T9">
-        <v>3.2</v>
-      </c>
-      <c r="U9">
-        <v>2.45</v>
-      </c>
-      <c r="V9">
-        <v>1.49</v>
-      </c>
-      <c r="W9">
-        <v>1.11</v>
-      </c>
-      <c r="X9">
-        <v>1.03</v>
-      </c>
-      <c r="Y9">
-        <v>1.17</v>
-      </c>
-      <c r="Z9">
-        <v>4</v>
-      </c>
-      <c r="AA9">
-        <v>1.7</v>
-      </c>
-      <c r="AB9">
-        <v>2.1</v>
-      </c>
-      <c r="AC9">
-        <v>2.77</v>
-      </c>
-      <c r="AD9">
-        <v>1.37</v>
-      </c>
-      <c r="AE9">
-        <v>1.11</v>
-      </c>
-      <c r="AF9">
-        <v>1.55</v>
-      </c>
-      <c r="AG9">
-        <v>2.25</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.26</v>
-      </c>
       <c r="AK9">
-        <v>1.39</v>
+        <v>2.05</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="O10">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q10">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="R10">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>2.42</v>
+        <v>2.98</v>
       </c>
       <c r="U10">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
+        <v>1.05</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>1.26</v>
+      </c>
+      <c r="Z10">
+        <v>3.43</v>
+      </c>
+      <c r="AA10">
+        <v>1.97</v>
+      </c>
+      <c r="AB10">
+        <v>1.79</v>
+      </c>
+      <c r="AC10">
+        <v>3.14</v>
+      </c>
+      <c r="AD10">
+        <v>1.27</v>
+      </c>
+      <c r="AE10">
         <v>1.07</v>
       </c>
-      <c r="X10">
-        <v>1.04</v>
-      </c>
-      <c r="Y10">
-        <v>1.35</v>
-      </c>
-      <c r="Z10">
-        <v>2.74</v>
-      </c>
-      <c r="AA10">
-        <v>2.19</v>
-      </c>
-      <c r="AB10">
-        <v>1.61</v>
-      </c>
-      <c r="AC10">
-        <v>3.74</v>
-      </c>
-      <c r="AD10">
-        <v>1.19</v>
-      </c>
-      <c r="AE10">
-        <v>1.03</v>
-      </c>
       <c r="AF10">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG10">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="Q11">
+        <v>3.22</v>
+      </c>
+      <c r="R11">
+        <v>2.17</v>
+      </c>
+      <c r="S11">
+        <v>1.3</v>
+      </c>
+      <c r="T11">
         <v>3.2</v>
       </c>
-      <c r="R11">
+      <c r="U11">
+        <v>2.45</v>
+      </c>
+      <c r="V11">
+        <v>1.49</v>
+      </c>
+      <c r="W11">
+        <v>1.11</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
+        <v>1.17</v>
+      </c>
+      <c r="Z11">
+        <v>4</v>
+      </c>
+      <c r="AA11">
+        <v>1.7</v>
+      </c>
+      <c r="AB11">
         <v>2.1</v>
       </c>
-      <c r="S11">
+      <c r="AC11">
+        <v>2.77</v>
+      </c>
+      <c r="AD11">
         <v>1.37</v>
       </c>
-      <c r="T11">
-        <v>2.98</v>
-      </c>
-      <c r="U11">
-        <v>2.86</v>
-      </c>
-      <c r="V11">
-        <v>1.37</v>
-      </c>
-      <c r="W11">
-        <v>1.05</v>
-      </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
-      <c r="Y11">
+      <c r="AE11">
+        <v>1.11</v>
+      </c>
+      <c r="AF11">
+        <v>1.55</v>
+      </c>
+      <c r="AG11">
+        <v>2.25</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
         <v>1.26</v>
       </c>
-      <c r="Z11">
-        <v>3.43</v>
-      </c>
-      <c r="AA11">
-        <v>1.97</v>
-      </c>
-      <c r="AB11">
-        <v>1.79</v>
-      </c>
-      <c r="AC11">
-        <v>3.14</v>
-      </c>
-      <c r="AD11">
-        <v>1.27</v>
-      </c>
-      <c r="AE11">
-        <v>1.07</v>
-      </c>
-      <c r="AF11">
-        <v>1.7</v>
-      </c>
-      <c r="AG11">
-        <v>2</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.28</v>
-      </c>
       <c r="AK11">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.09</v>
+        <v>2.83</v>
       </c>
       <c r="O50">
-        <v>3.54</v>
+        <v>2.91</v>
       </c>
       <c r="P50">
-        <v>3.15</v>
+        <v>2.57</v>
       </c>
       <c r="Q50">
+        <v>3.24</v>
+      </c>
+      <c r="R50">
+        <v>2.25</v>
+      </c>
+      <c r="S50">
+        <v>1.37</v>
+      </c>
+      <c r="T50">
+        <v>2.7</v>
+      </c>
+      <c r="U50">
         <v>2.75</v>
       </c>
-      <c r="R50">
-        <v>2.19</v>
-      </c>
-      <c r="S50">
-        <v>1.26</v>
-      </c>
-      <c r="T50">
-        <v>3.4</v>
-      </c>
-      <c r="U50">
-        <v>2.32</v>
-      </c>
       <c r="V50">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>4.33</v>
+        <v>4.07</v>
       </c>
       <c r="AA50">
+        <v>2.03</v>
+      </c>
+      <c r="AB50">
         <v>1.83</v>
       </c>
-      <c r="AB50">
-        <v>2.03</v>
-      </c>
       <c r="AC50">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="AD50">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE50">
         <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK50">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="O51">
-        <v>2.91</v>
+        <v>3.62</v>
       </c>
       <c r="P51">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="Q51">
-        <v>3.24</v>
+        <v>2.43</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S51">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T51">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="U51">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="V51">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
         <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.07</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC51">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG51">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,77 +8785,77 @@
         </is>
       </c>
       <c r="N52">
+        <v>2.09</v>
+      </c>
+      <c r="O52">
+        <v>3.54</v>
+      </c>
+      <c r="P52">
+        <v>3.15</v>
+      </c>
+      <c r="Q52">
+        <v>2.75</v>
+      </c>
+      <c r="R52">
         <v>2.19</v>
       </c>
-      <c r="O52">
-        <v>3.62</v>
-      </c>
-      <c r="P52">
-        <v>2.88</v>
-      </c>
-      <c r="Q52">
-        <v>2.43</v>
-      </c>
-      <c r="R52">
-        <v>2.21</v>
-      </c>
       <c r="S52">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T52">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U52">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z52">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA52">
         <v>1.83</v>
       </c>
       <c r="AB52">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AC52">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="AD52">
+        <v>1.43</v>
+      </c>
+      <c r="AE52">
+        <v>1.13</v>
+      </c>
+      <c r="AF52">
+        <v>1.55</v>
+      </c>
+      <c r="AG52">
+        <v>2.25</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.33</v>
-      </c>
-      <c r="AE52">
-        <v>1.12</v>
-      </c>
-      <c r="AF52">
-        <v>1.64</v>
-      </c>
-      <c r="AG52">
-        <v>2.13</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.27</v>
       </c>
       <c r="AK52">
         <v>1.65</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.14</v>
+        <v>2.23</v>
       </c>
       <c r="O6">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="P6">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q6">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T6">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="U6">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z6">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA6">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="AB6">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AC6">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE6">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG6">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.49</v>
+        <v>2.38</v>
       </c>
       <c r="O7">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>5.47</v>
+        <v>2.47</v>
       </c>
       <c r="Q7">
-        <v>1.99</v>
+        <v>3.22</v>
       </c>
       <c r="R7">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S7">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
         <v>3.2</v>
       </c>
       <c r="U7">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="V7">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W7">
         <v>1.11</v>
@@ -1483,31 +1483,31 @@
         <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="AA7">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AB7">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AD7">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE7">
         <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK7">
-        <v>2.21</v>
+        <v>1.39</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,65 +1613,65 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.23</v>
+        <v>3.14</v>
       </c>
       <c r="O8">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q8">
-        <v>3.13</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
+        <v>2.08</v>
+      </c>
+      <c r="S8">
+        <v>1.33</v>
+      </c>
+      <c r="T8">
+        <v>2.95</v>
+      </c>
+      <c r="U8">
+        <v>2.65</v>
+      </c>
+      <c r="V8">
+        <v>1.38</v>
+      </c>
+      <c r="W8">
+        <v>1.06</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1.26</v>
+      </c>
+      <c r="Z8">
+        <v>3.2</v>
+      </c>
+      <c r="AA8">
+        <v>1.99</v>
+      </c>
+      <c r="AB8">
+        <v>1.78</v>
+      </c>
+      <c r="AC8">
+        <v>3.2</v>
+      </c>
+      <c r="AD8">
+        <v>1.3</v>
+      </c>
+      <c r="AE8">
+        <v>1.11</v>
+      </c>
+      <c r="AF8">
+        <v>1.73</v>
+      </c>
+      <c r="AG8">
         <v>1.98</v>
       </c>
-      <c r="S8">
-        <v>1.45</v>
-      </c>
-      <c r="T8">
-        <v>2.42</v>
-      </c>
-      <c r="U8">
-        <v>3.22</v>
-      </c>
-      <c r="V8">
-        <v>1.35</v>
-      </c>
-      <c r="W8">
-        <v>1.07</v>
-      </c>
-      <c r="X8">
-        <v>1.04</v>
-      </c>
-      <c r="Y8">
-        <v>1.35</v>
-      </c>
-      <c r="Z8">
-        <v>2.74</v>
-      </c>
-      <c r="AA8">
-        <v>2.19</v>
-      </c>
-      <c r="AB8">
-        <v>1.61</v>
-      </c>
-      <c r="AC8">
-        <v>3.74</v>
-      </c>
-      <c r="AD8">
-        <v>1.19</v>
-      </c>
-      <c r="AE8">
-        <v>1.03</v>
-      </c>
-      <c r="AF8">
-        <v>1.84</v>
-      </c>
-      <c r="AG8">
-        <v>1.82</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
       <c r="O9">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>4.87</v>
+        <v>2.32</v>
       </c>
       <c r="Q9">
-        <v>2.23</v>
+        <v>3.2</v>
       </c>
       <c r="R9">
         <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T9">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="U9">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
+        <v>1.26</v>
+      </c>
+      <c r="Z9">
+        <v>3.43</v>
+      </c>
+      <c r="AA9">
+        <v>1.97</v>
+      </c>
+      <c r="AB9">
+        <v>1.79</v>
+      </c>
+      <c r="AC9">
+        <v>3.14</v>
+      </c>
+      <c r="AD9">
+        <v>1.27</v>
+      </c>
+      <c r="AE9">
+        <v>1.07</v>
+      </c>
+      <c r="AF9">
+        <v>1.7</v>
+      </c>
+      <c r="AG9">
+        <v>2</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.28</v>
       </c>
-      <c r="Z9">
-        <v>3.08</v>
-      </c>
-      <c r="AA9">
-        <v>2.02</v>
-      </c>
-      <c r="AB9">
-        <v>1.77</v>
-      </c>
-      <c r="AC9">
-        <v>3.48</v>
-      </c>
-      <c r="AD9">
-        <v>1.22</v>
-      </c>
-      <c r="AE9">
-        <v>1.04</v>
-      </c>
-      <c r="AF9">
-        <v>1.85</v>
-      </c>
-      <c r="AG9">
-        <v>1.75</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.3</v>
-      </c>
       <c r="AK9">
-        <v>2.05</v>
+        <v>1.38</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,61 +1939,61 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.6</v>
+        <v>1.49</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="P10">
-        <v>2.32</v>
+        <v>5.47</v>
       </c>
       <c r="Q10">
+        <v>1.99</v>
+      </c>
+      <c r="R10">
+        <v>2.28</v>
+      </c>
+      <c r="S10">
+        <v>1.32</v>
+      </c>
+      <c r="T10">
         <v>3.2</v>
       </c>
-      <c r="R10">
-        <v>2.1</v>
-      </c>
-      <c r="S10">
-        <v>1.37</v>
-      </c>
-      <c r="T10">
-        <v>2.98</v>
-      </c>
       <c r="U10">
-        <v>2.86</v>
+        <v>2.57</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>3.43</v>
+        <v>4.01</v>
       </c>
       <c r="AA10">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AB10">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AC10">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="AD10">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG10">
         <v>2</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>1.38</v>
+        <v>2.21</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P11">
-        <v>2.47</v>
+        <v>4.87</v>
       </c>
       <c r="Q11">
-        <v>3.22</v>
+        <v>2.23</v>
       </c>
       <c r="R11">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
+        <v>1.39</v>
+      </c>
+      <c r="T11">
+        <v>2.64</v>
+      </c>
+      <c r="U11">
+        <v>2.89</v>
+      </c>
+      <c r="V11">
+        <v>1.36</v>
+      </c>
+      <c r="W11">
+        <v>1.06</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1.28</v>
+      </c>
+      <c r="Z11">
+        <v>3.08</v>
+      </c>
+      <c r="AA11">
+        <v>2.02</v>
+      </c>
+      <c r="AB11">
+        <v>1.77</v>
+      </c>
+      <c r="AC11">
+        <v>3.48</v>
+      </c>
+      <c r="AD11">
+        <v>1.22</v>
+      </c>
+      <c r="AE11">
+        <v>1.04</v>
+      </c>
+      <c r="AF11">
+        <v>1.85</v>
+      </c>
+      <c r="AG11">
+        <v>1.75</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
         <v>1.3</v>
       </c>
-      <c r="T11">
-        <v>3.2</v>
-      </c>
-      <c r="U11">
-        <v>2.45</v>
-      </c>
-      <c r="V11">
-        <v>1.49</v>
-      </c>
-      <c r="W11">
-        <v>1.11</v>
-      </c>
-      <c r="X11">
-        <v>1.03</v>
-      </c>
-      <c r="Y11">
-        <v>1.17</v>
-      </c>
-      <c r="Z11">
-        <v>4</v>
-      </c>
-      <c r="AA11">
-        <v>1.7</v>
-      </c>
-      <c r="AB11">
-        <v>2.1</v>
-      </c>
-      <c r="AC11">
-        <v>2.77</v>
-      </c>
-      <c r="AD11">
-        <v>1.37</v>
-      </c>
-      <c r="AE11">
-        <v>1.11</v>
-      </c>
-      <c r="AF11">
-        <v>1.55</v>
-      </c>
-      <c r="AG11">
-        <v>2.25</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.26</v>
-      </c>
       <c r="AK11">
-        <v>1.39</v>
+        <v>2.05</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,61 +6992,61 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.62</v>
+        <v>1.55</v>
       </c>
       <c r="O41">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="P41">
-        <v>1.88</v>
+        <v>4.79</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S41">
         <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="U41">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>3.82</v>
+        <v>4.18</v>
       </c>
       <c r="AA41">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC41">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD41">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
         <v>2.1</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK41">
-        <v>1.19</v>
+        <v>2.14</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,61 +7155,61 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.55</v>
+        <v>3.62</v>
       </c>
       <c r="O42">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="P42">
-        <v>4.79</v>
+        <v>1.88</v>
       </c>
       <c r="Q42">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="R42">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
         <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V42">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z42">
-        <v>4.18</v>
+        <v>3.82</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB42">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC42">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD42">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG42">
         <v>2.1</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>2.14</v>
+        <v>1.19</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,34 +8133,34 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.92</v>
+        <v>2.19</v>
       </c>
       <c r="O48">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="P48">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="Q48">
-        <v>3.26</v>
+        <v>2.43</v>
       </c>
       <c r="R48">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T48">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U48">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V48">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8169,28 +8169,28 @@
         <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA48">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AC48">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD48">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AG48">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
+        <v>1.27</v>
+      </c>
+      <c r="AK48">
         <v>1.65</v>
-      </c>
-      <c r="AK48">
-        <v>1.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.73</v>
+        <v>2.09</v>
       </c>
       <c r="O49">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="P49">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="Q49">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="R49">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S49">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="T49">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U49">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="V49">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA49">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AC49">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AD49">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK49">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="O50">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="P50">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="Q50">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S50">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T50">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U50">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="V50">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z50">
-        <v>4.07</v>
+        <v>3.2</v>
       </c>
       <c r="AA50">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AB50">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC50">
-        <v>2.74</v>
+        <v>3.28</v>
       </c>
       <c r="AD50">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG50">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AK50">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="O51">
-        <v>3.62</v>
+        <v>2.91</v>
       </c>
       <c r="P51">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="Q51">
-        <v>2.43</v>
+        <v>3.24</v>
       </c>
       <c r="R51">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T51">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="U51">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W51">
         <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>4.07</v>
       </c>
       <c r="AA51">
+        <v>2.03</v>
+      </c>
+      <c r="AB51">
         <v>1.83</v>
       </c>
-      <c r="AB51">
-        <v>1.93</v>
-      </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AD51">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE51">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF51">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AK51">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.09</v>
+        <v>2.92</v>
       </c>
       <c r="O52">
-        <v>3.54</v>
+        <v>3.74</v>
       </c>
       <c r="P52">
-        <v>3.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q52">
-        <v>2.75</v>
+        <v>3.26</v>
       </c>
       <c r="R52">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S52">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="V52">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AB52">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AC52">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AD52">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE52">
         <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG52">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
+        <v>1.65</v>
+      </c>
+      <c r="AK52">
         <v>1.33</v>
-      </c>
-      <c r="AK52">
-        <v>1.65</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q90">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S90">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T90">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="U90">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="V90">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W90">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X90">
+        <v>1.04</v>
+      </c>
+      <c r="Y90">
+        <v>1.36</v>
+      </c>
+      <c r="Z90">
+        <v>2.7</v>
+      </c>
+      <c r="AA90">
+        <v>2.25</v>
+      </c>
+      <c r="AB90">
+        <v>1.57</v>
+      </c>
+      <c r="AC90">
+        <v>3.9</v>
+      </c>
+      <c r="AD90">
+        <v>1.17</v>
+      </c>
+      <c r="AE90">
         <v>1.03</v>
       </c>
-      <c r="Y90">
-        <v>1.3</v>
-      </c>
-      <c r="Z90">
-        <v>3.25</v>
-      </c>
-      <c r="AA90">
-        <v>2.1</v>
-      </c>
-      <c r="AB90">
-        <v>1.7</v>
-      </c>
-      <c r="AC90">
-        <v>3.6</v>
-      </c>
-      <c r="AD90">
-        <v>1.25</v>
-      </c>
-      <c r="AE90">
-        <v>1.06</v>
-      </c>
       <c r="AF90">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AG90">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK90">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="R91">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T91">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="U91">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="V91">
+        <v>1.4</v>
+      </c>
+      <c r="W91">
+        <v>1.06</v>
+      </c>
+      <c r="X91">
+        <v>1.03</v>
+      </c>
+      <c r="Y91">
         <v>1.3</v>
       </c>
-      <c r="W91">
-        <v>1.02</v>
-      </c>
-      <c r="X91">
-        <v>1.04</v>
-      </c>
-      <c r="Y91">
-        <v>1.36</v>
-      </c>
       <c r="Z91">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB91">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC91">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD91">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE91">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG91">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK91">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AL91">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="Q7">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="R7">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T7">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="U7">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="V7">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z7">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="AA7">
+        <v>1.97</v>
+      </c>
+      <c r="AB7">
+        <v>1.79</v>
+      </c>
+      <c r="AC7">
+        <v>3.14</v>
+      </c>
+      <c r="AD7">
+        <v>1.27</v>
+      </c>
+      <c r="AE7">
+        <v>1.07</v>
+      </c>
+      <c r="AF7">
         <v>1.7</v>
       </c>
-      <c r="AB7">
-        <v>2.1</v>
-      </c>
-      <c r="AC7">
-        <v>2.77</v>
-      </c>
-      <c r="AD7">
-        <v>1.37</v>
-      </c>
-      <c r="AE7">
-        <v>1.11</v>
-      </c>
-      <c r="AF7">
-        <v>1.55</v>
-      </c>
       <c r="AG7">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.14</v>
+        <v>1.63</v>
       </c>
       <c r="O8">
-        <v>3.24</v>
+        <v>3.48</v>
       </c>
       <c r="P8">
-        <v>2.09</v>
+        <v>4.87</v>
       </c>
       <c r="Q8">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="R8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T8">
-        <v>2.95</v>
+        <v>2.64</v>
       </c>
       <c r="U8">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
         <v>1.06</v>
@@ -1646,47 +1646,47 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z8">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA8">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AB8">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC8">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD8">
+        <v>1.22</v>
+      </c>
+      <c r="AE8">
+        <v>1.04</v>
+      </c>
+      <c r="AF8">
+        <v>1.85</v>
+      </c>
+      <c r="AG8">
+        <v>1.75</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.3</v>
       </c>
-      <c r="AE8">
-        <v>1.11</v>
-      </c>
-      <c r="AF8">
-        <v>1.73</v>
-      </c>
-      <c r="AG8">
-        <v>1.98</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.24</v>
-      </c>
       <c r="AK8">
-        <v>1.27</v>
+        <v>2.05</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P9">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="Q9">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S9">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="U9">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="V9">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9">
         <v>1.26</v>
       </c>
       <c r="Z9">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="AA9">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB9">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC9">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD9">
+        <v>1.3</v>
+      </c>
+      <c r="AE9">
+        <v>1.11</v>
+      </c>
+      <c r="AF9">
+        <v>1.73</v>
+      </c>
+      <c r="AG9">
+        <v>1.98</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.24</v>
+      </c>
+      <c r="AK9">
         <v>1.27</v>
-      </c>
-      <c r="AE9">
-        <v>1.07</v>
-      </c>
-      <c r="AF9">
-        <v>1.7</v>
-      </c>
-      <c r="AG9">
-        <v>2</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.28</v>
-      </c>
-      <c r="AK9">
-        <v>1.38</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="O11">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>4.87</v>
+        <v>2.47</v>
       </c>
       <c r="Q11">
-        <v>2.23</v>
+        <v>3.22</v>
       </c>
       <c r="R11">
+        <v>2.17</v>
+      </c>
+      <c r="S11">
+        <v>1.3</v>
+      </c>
+      <c r="T11">
+        <v>3.2</v>
+      </c>
+      <c r="U11">
+        <v>2.45</v>
+      </c>
+      <c r="V11">
+        <v>1.49</v>
+      </c>
+      <c r="W11">
+        <v>1.11</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
+        <v>1.17</v>
+      </c>
+      <c r="Z11">
+        <v>4</v>
+      </c>
+      <c r="AA11">
+        <v>1.7</v>
+      </c>
+      <c r="AB11">
         <v>2.1</v>
       </c>
-      <c r="S11">
+      <c r="AC11">
+        <v>2.77</v>
+      </c>
+      <c r="AD11">
+        <v>1.37</v>
+      </c>
+      <c r="AE11">
+        <v>1.11</v>
+      </c>
+      <c r="AF11">
+        <v>1.55</v>
+      </c>
+      <c r="AG11">
+        <v>2.25</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.26</v>
+      </c>
+      <c r="AK11">
         <v>1.39</v>
-      </c>
-      <c r="T11">
-        <v>2.64</v>
-      </c>
-      <c r="U11">
-        <v>2.89</v>
-      </c>
-      <c r="V11">
-        <v>1.36</v>
-      </c>
-      <c r="W11">
-        <v>1.06</v>
-      </c>
-      <c r="X11">
-        <v>1</v>
-      </c>
-      <c r="Y11">
-        <v>1.28</v>
-      </c>
-      <c r="Z11">
-        <v>3.08</v>
-      </c>
-      <c r="AA11">
-        <v>2.02</v>
-      </c>
-      <c r="AB11">
-        <v>1.77</v>
-      </c>
-      <c r="AC11">
-        <v>3.48</v>
-      </c>
-      <c r="AD11">
-        <v>1.22</v>
-      </c>
-      <c r="AE11">
-        <v>1.04</v>
-      </c>
-      <c r="AF11">
-        <v>1.85</v>
-      </c>
-      <c r="AG11">
-        <v>1.75</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.3</v>
-      </c>
-      <c r="AK11">
-        <v>2.05</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.19</v>
+        <v>2.73</v>
       </c>
       <c r="O48">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="P48">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="Q48">
-        <v>2.43</v>
+        <v>3.18</v>
       </c>
       <c r="R48">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S48">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T48">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U48">
-        <v>2.47</v>
+        <v>2.96</v>
       </c>
       <c r="V48">
+        <v>1.4</v>
+      </c>
+      <c r="W48">
+        <v>1.06</v>
+      </c>
+      <c r="X48">
+        <v>1.03</v>
+      </c>
+      <c r="Y48">
+        <v>1.3</v>
+      </c>
+      <c r="Z48">
+        <v>3.2</v>
+      </c>
+      <c r="AA48">
+        <v>1.94</v>
+      </c>
+      <c r="AB48">
+        <v>1.8</v>
+      </c>
+      <c r="AC48">
+        <v>3.28</v>
+      </c>
+      <c r="AD48">
+        <v>1.25</v>
+      </c>
+      <c r="AE48">
+        <v>1.05</v>
+      </c>
+      <c r="AF48">
+        <v>1.73</v>
+      </c>
+      <c r="AG48">
+        <v>1.95</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.41</v>
+      </c>
+      <c r="AK48">
         <v>1.44</v>
-      </c>
-      <c r="W48">
-        <v>1.07</v>
-      </c>
-      <c r="X48">
-        <v>1.01</v>
-      </c>
-      <c r="Y48">
-        <v>1.22</v>
-      </c>
-      <c r="Z48">
-        <v>3.5</v>
-      </c>
-      <c r="AA48">
-        <v>1.83</v>
-      </c>
-      <c r="AB48">
-        <v>1.93</v>
-      </c>
-      <c r="AC48">
-        <v>2.83</v>
-      </c>
-      <c r="AD48">
-        <v>1.33</v>
-      </c>
-      <c r="AE48">
-        <v>1.12</v>
-      </c>
-      <c r="AF48">
-        <v>1.64</v>
-      </c>
-      <c r="AG48">
-        <v>2.13</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.27</v>
-      </c>
-      <c r="AK48">
-        <v>1.65</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.09</v>
+        <v>2.83</v>
       </c>
       <c r="O49">
-        <v>3.54</v>
+        <v>2.91</v>
       </c>
       <c r="P49">
-        <v>3.15</v>
+        <v>2.57</v>
       </c>
       <c r="Q49">
+        <v>3.24</v>
+      </c>
+      <c r="R49">
+        <v>2.25</v>
+      </c>
+      <c r="S49">
+        <v>1.37</v>
+      </c>
+      <c r="T49">
+        <v>2.7</v>
+      </c>
+      <c r="U49">
         <v>2.75</v>
       </c>
-      <c r="R49">
-        <v>2.19</v>
-      </c>
-      <c r="S49">
-        <v>1.26</v>
-      </c>
-      <c r="T49">
-        <v>3.4</v>
-      </c>
-      <c r="U49">
-        <v>2.32</v>
-      </c>
       <c r="V49">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>4.33</v>
+        <v>4.07</v>
       </c>
       <c r="AA49">
+        <v>2.03</v>
+      </c>
+      <c r="AB49">
         <v>1.83</v>
       </c>
-      <c r="AB49">
-        <v>2.03</v>
-      </c>
       <c r="AC49">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="AD49">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE49">
         <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK49">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.73</v>
+        <v>2.09</v>
       </c>
       <c r="O50">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="P50">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="Q50">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="R50">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="T50">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="V50">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA50">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB50">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AC50">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AD50">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AE50">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG50">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="O51">
-        <v>2.91</v>
+        <v>3.62</v>
       </c>
       <c r="P51">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="Q51">
-        <v>3.24</v>
+        <v>2.43</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S51">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T51">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="U51">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="V51">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
         <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.07</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC51">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG51">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="R90">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T90">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="U90">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="V90">
+        <v>1.4</v>
+      </c>
+      <c r="W90">
+        <v>1.06</v>
+      </c>
+      <c r="X90">
+        <v>1.03</v>
+      </c>
+      <c r="Y90">
         <v>1.3</v>
       </c>
-      <c r="W90">
-        <v>1.02</v>
-      </c>
-      <c r="X90">
-        <v>1.04</v>
-      </c>
-      <c r="Y90">
-        <v>1.36</v>
-      </c>
       <c r="Z90">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AA90">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB90">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC90">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD90">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE90">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG90">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK90">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q91">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="R91">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S91">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T91">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="U91">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="V91">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X91">
+        <v>1.04</v>
+      </c>
+      <c r="Y91">
+        <v>1.36</v>
+      </c>
+      <c r="Z91">
+        <v>2.7</v>
+      </c>
+      <c r="AA91">
+        <v>2.25</v>
+      </c>
+      <c r="AB91">
+        <v>1.57</v>
+      </c>
+      <c r="AC91">
+        <v>3.9</v>
+      </c>
+      <c r="AD91">
+        <v>1.17</v>
+      </c>
+      <c r="AE91">
         <v>1.03</v>
       </c>
-      <c r="Y91">
-        <v>1.3</v>
-      </c>
-      <c r="Z91">
-        <v>3.25</v>
-      </c>
-      <c r="AA91">
-        <v>2.1</v>
-      </c>
-      <c r="AB91">
-        <v>1.7</v>
-      </c>
-      <c r="AC91">
-        <v>3.6</v>
-      </c>
-      <c r="AD91">
-        <v>1.25</v>
-      </c>
-      <c r="AE91">
-        <v>1.06</v>
-      </c>
       <c r="AF91">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AG91">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK91">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL93">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU158"/>
+  <dimension ref="A1:AU159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
+        <v>1.63</v>
+      </c>
+      <c r="O6">
+        <v>3.48</v>
+      </c>
+      <c r="P6">
+        <v>4.87</v>
+      </c>
+      <c r="Q6">
         <v>2.23</v>
       </c>
-      <c r="O6">
-        <v>2.99</v>
-      </c>
-      <c r="P6">
-        <v>3.1</v>
-      </c>
-      <c r="Q6">
-        <v>3.13</v>
-      </c>
       <c r="R6">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="T6">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="U6">
-        <v>3.22</v>
+        <v>2.89</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1.28</v>
+      </c>
+      <c r="Z6">
+        <v>3.08</v>
+      </c>
+      <c r="AA6">
+        <v>2.02</v>
+      </c>
+      <c r="AB6">
+        <v>1.77</v>
+      </c>
+      <c r="AC6">
+        <v>3.48</v>
+      </c>
+      <c r="AD6">
+        <v>1.22</v>
+      </c>
+      <c r="AE6">
         <v>1.04</v>
       </c>
-      <c r="Y6">
-        <v>1.35</v>
-      </c>
-      <c r="Z6">
-        <v>2.74</v>
-      </c>
-      <c r="AA6">
-        <v>2.19</v>
-      </c>
-      <c r="AB6">
-        <v>1.61</v>
-      </c>
-      <c r="AC6">
-        <v>3.74</v>
-      </c>
-      <c r="AD6">
-        <v>1.19</v>
-      </c>
-      <c r="AE6">
-        <v>1.03</v>
-      </c>
       <c r="AF6">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG6">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,61 +1450,61 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.6</v>
+        <v>1.49</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="P7">
-        <v>2.32</v>
+        <v>5.47</v>
       </c>
       <c r="Q7">
+        <v>1.99</v>
+      </c>
+      <c r="R7">
+        <v>2.28</v>
+      </c>
+      <c r="S7">
+        <v>1.32</v>
+      </c>
+      <c r="T7">
         <v>3.2</v>
       </c>
-      <c r="R7">
-        <v>2.1</v>
-      </c>
-      <c r="S7">
-        <v>1.37</v>
-      </c>
-      <c r="T7">
-        <v>2.98</v>
-      </c>
       <c r="U7">
-        <v>2.86</v>
+        <v>2.57</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>3.43</v>
+        <v>4.01</v>
       </c>
       <c r="AA7">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AB7">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="AD7">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG7">
         <v>2</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>1.38</v>
+        <v>2.21</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.63</v>
+        <v>3.14</v>
       </c>
       <c r="O8">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="P8">
-        <v>4.87</v>
+        <v>2.09</v>
       </c>
       <c r="Q8">
-        <v>2.23</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S8">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="U8">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W8">
         <v>1.06</v>
@@ -1646,31 +1646,31 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z8">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA8">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AB8">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC8">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE8">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>2.05</v>
+        <v>1.27</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.14</v>
+        <v>2.23</v>
       </c>
       <c r="O9">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="P9">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="R9">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T9">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="U9">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z9">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA9">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="AB9">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AC9">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD9">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG9">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,61 +1939,61 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.49</v>
+        <v>2.6</v>
       </c>
       <c r="O10">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>5.47</v>
+        <v>2.32</v>
       </c>
       <c r="Q10">
-        <v>1.99</v>
+        <v>3.2</v>
       </c>
       <c r="R10">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="U10">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="V10">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z10">
-        <v>4.01</v>
+        <v>3.43</v>
       </c>
       <c r="AA10">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AB10">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC10">
-        <v>2.66</v>
+        <v>3.14</v>
       </c>
       <c r="AD10">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AE10">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG10">
         <v>2</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>2.21</v>
+        <v>1.38</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -6349,46 +6349,46 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
         <v>0</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE37">
         <v>0</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.63</v>
+        <v>2.73</v>
       </c>
       <c r="O47">
-        <v>4.25</v>
+        <v>3.02</v>
       </c>
       <c r="P47">
-        <v>4.34</v>
+        <v>2.58</v>
       </c>
       <c r="Q47">
-        <v>2.2</v>
+        <v>3.18</v>
       </c>
       <c r="R47">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S47">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="T47">
+        <v>2.75</v>
+      </c>
+      <c r="U47">
+        <v>2.96</v>
+      </c>
+      <c r="V47">
+        <v>1.4</v>
+      </c>
+      <c r="W47">
+        <v>1.06</v>
+      </c>
+      <c r="X47">
+        <v>1.03</v>
+      </c>
+      <c r="Y47">
+        <v>1.3</v>
+      </c>
+      <c r="Z47">
         <v>3.2</v>
       </c>
-      <c r="U47">
-        <v>2.42</v>
-      </c>
-      <c r="V47">
-        <v>1.48</v>
-      </c>
-      <c r="W47">
-        <v>1.08</v>
-      </c>
-      <c r="X47">
-        <v>1.02</v>
-      </c>
-      <c r="Y47">
-        <v>1.26</v>
-      </c>
-      <c r="Z47">
-        <v>3.82</v>
-      </c>
       <c r="AA47">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AB47">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AC47">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD47">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF47">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG47">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AK47">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.73</v>
+        <v>2.09</v>
       </c>
       <c r="O48">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="P48">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="Q48">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="R48">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="T48">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U48">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="V48">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA48">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AC48">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AD48">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AE48">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="O49">
-        <v>2.91</v>
+        <v>3.62</v>
       </c>
       <c r="P49">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="Q49">
-        <v>3.24</v>
+        <v>2.43</v>
       </c>
       <c r="R49">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S49">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="U49">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="V49">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
         <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
         <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>4.07</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC49">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD49">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG49">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK49">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.09</v>
+        <v>2.83</v>
       </c>
       <c r="O50">
-        <v>3.54</v>
+        <v>2.91</v>
       </c>
       <c r="P50">
-        <v>3.15</v>
+        <v>2.57</v>
       </c>
       <c r="Q50">
+        <v>3.24</v>
+      </c>
+      <c r="R50">
+        <v>2.25</v>
+      </c>
+      <c r="S50">
+        <v>1.37</v>
+      </c>
+      <c r="T50">
+        <v>2.7</v>
+      </c>
+      <c r="U50">
         <v>2.75</v>
       </c>
-      <c r="R50">
-        <v>2.19</v>
-      </c>
-      <c r="S50">
-        <v>1.26</v>
-      </c>
-      <c r="T50">
-        <v>3.4</v>
-      </c>
-      <c r="U50">
-        <v>2.32</v>
-      </c>
       <c r="V50">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>4.33</v>
+        <v>4.07</v>
       </c>
       <c r="AA50">
+        <v>2.03</v>
+      </c>
+      <c r="AB50">
         <v>1.83</v>
       </c>
-      <c r="AB50">
-        <v>2.03</v>
-      </c>
       <c r="AC50">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="AD50">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE50">
         <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK50">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,34 +8622,34 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.19</v>
+        <v>2.92</v>
       </c>
       <c r="O51">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="P51">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="Q51">
-        <v>2.43</v>
+        <v>3.26</v>
       </c>
       <c r="R51">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X51">
         <v>1.01</v>
@@ -8658,44 +8658,44 @@
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA51">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AB51">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD51">
+        <v>1.36</v>
+      </c>
+      <c r="AE51">
+        <v>1.13</v>
+      </c>
+      <c r="AF51">
+        <v>1.58</v>
+      </c>
+      <c r="AG51">
+        <v>2.3</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.65</v>
+      </c>
+      <c r="AK51">
         <v>1.33</v>
-      </c>
-      <c r="AE51">
-        <v>1.12</v>
-      </c>
-      <c r="AF51">
-        <v>1.64</v>
-      </c>
-      <c r="AG51">
-        <v>2.13</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.27</v>
-      </c>
-      <c r="AK51">
-        <v>1.65</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,49 +8785,49 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.92</v>
+        <v>1.63</v>
       </c>
       <c r="O52">
-        <v>3.74</v>
+        <v>4.25</v>
       </c>
       <c r="P52">
-        <v>2.13</v>
+        <v>4.34</v>
       </c>
       <c r="Q52">
-        <v>3.26</v>
+        <v>2.2</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U52">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W52">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z52">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="AA52">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB52">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AC52">
         <v>2.7</v>
@@ -8836,13 +8836,13 @@
         <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG52">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.65</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.33</v>
+        <v>2.03</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
+        <v>2.25</v>
+      </c>
+      <c r="O96">
         <v>3.25</v>
       </c>
-      <c r="O96">
-        <v>3.3</v>
-      </c>
       <c r="P96">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q96">
-        <v>3.92</v>
+        <v>2.98</v>
       </c>
       <c r="R96">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="S96">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T96">
-        <v>2.73</v>
+        <v>2.54</v>
       </c>
       <c r="U96">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="V96">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W96">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z96">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA96">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AB96">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AC96">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD96">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE96">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF96">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG96">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK96">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="O97">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P97">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q97">
-        <v>2.98</v>
+        <v>3.92</v>
       </c>
       <c r="R97">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="S97">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T97">
-        <v>2.54</v>
+        <v>2.73</v>
       </c>
       <c r="U97">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="V97">
+        <v>1.35</v>
+      </c>
+      <c r="W97">
+        <v>1.05</v>
+      </c>
+      <c r="X97">
+        <v>1.01</v>
+      </c>
+      <c r="Y97">
         <v>1.3</v>
       </c>
-      <c r="W97">
-        <v>1.02</v>
-      </c>
-      <c r="X97">
-        <v>1.02</v>
-      </c>
-      <c r="Y97">
-        <v>1.33</v>
-      </c>
       <c r="Z97">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA97">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AB97">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AC97">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD97">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE97">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF97">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG97">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK97">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
+        <v>1.71</v>
+      </c>
+      <c r="O110">
+        <v>3.04</v>
+      </c>
+      <c r="P110">
+        <v>5.19</v>
+      </c>
+      <c r="Q110">
+        <v>2.4</v>
+      </c>
+      <c r="R110">
         <v>1.85</v>
       </c>
-      <c r="O110">
-        <v>3.22</v>
-      </c>
-      <c r="P110">
-        <v>3.89</v>
-      </c>
-      <c r="Q110">
-        <v>2.75</v>
-      </c>
-      <c r="R110">
-        <v>2</v>
-      </c>
       <c r="S110">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="T110">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="U110">
-        <v>3.08</v>
+        <v>3.78</v>
       </c>
       <c r="V110">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="W110">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y110">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="Z110">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="AA110">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="AB110">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="AC110">
-        <v>3.86</v>
+        <v>5.19</v>
       </c>
       <c r="AD110">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE110">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF110">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="AG110">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18360,22 +18360,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>4.88</v>
+        <v>1.85</v>
       </c>
       <c r="O111">
-        <v>4.19</v>
+        <v>3.22</v>
       </c>
       <c r="P111">
-        <v>1.56</v>
+        <v>3.89</v>
       </c>
       <c r="Q111">
-        <v>4.04</v>
+        <v>2.75</v>
       </c>
       <c r="R111">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S111">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="T111">
-        <v>3.46</v>
+        <v>2.54</v>
       </c>
       <c r="U111">
-        <v>2.34</v>
+        <v>3.08</v>
       </c>
       <c r="V111">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="W111">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="X111">
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="Z111">
-        <v>4.66</v>
+        <v>2.88</v>
       </c>
       <c r="AA111">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AB111">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="AC111">
-        <v>2.42</v>
+        <v>3.86</v>
       </c>
       <c r="AD111">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="AE111">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AF111">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AG111">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>2.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK111">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18523,22 +18523,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.84</v>
+        <v>4.88</v>
       </c>
       <c r="O112">
-        <v>3.28</v>
+        <v>4.19</v>
       </c>
       <c r="P112">
-        <v>3.84</v>
+        <v>1.56</v>
       </c>
       <c r="Q112">
-        <v>2.17</v>
+        <v>4.04</v>
       </c>
       <c r="R112">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="S112">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="T112">
-        <v>2.57</v>
+        <v>3.46</v>
       </c>
       <c r="U112">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="V112">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z112">
-        <v>2.88</v>
+        <v>4.66</v>
       </c>
       <c r="AA112">
-        <v>2.03</v>
+        <v>1.55</v>
       </c>
       <c r="AB112">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="AC112">
-        <v>3.5</v>
+        <v>2.42</v>
       </c>
       <c r="AD112">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AE112">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AF112">
-        <v>1.99</v>
+        <v>1.61</v>
       </c>
       <c r="AG112">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.2</v>
+        <v>2.18</v>
       </c>
       <c r="AK112">
-        <v>2.05</v>
+        <v>1.1</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,65 +18728,65 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q113">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="R113">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S113">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T113">
+        <v>2.57</v>
+      </c>
+      <c r="U113">
         <v>3</v>
       </c>
-      <c r="U113">
-        <v>2.68</v>
-      </c>
       <c r="V113">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W113">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X113">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z113">
-        <v>3.61</v>
+        <v>2.88</v>
       </c>
       <c r="AA113">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="AB113">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AC113">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AD113">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE113">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF113">
+        <v>1.99</v>
+      </c>
+      <c r="AG113">
         <v>1.7</v>
       </c>
-      <c r="AG113">
-        <v>2.04</v>
-      </c>
       <c r="AH113" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK113">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-09-26 15:45:00</t>
+          <t>2026-09-26 15:30:00</t>
         </is>
       </c>
     </row>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,80 +18891,80 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O114">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P114">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q114">
-        <v>4.64</v>
+        <v>2.5</v>
       </c>
       <c r="R114">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S114">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T114">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U114">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="V114">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W114">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y114">
+        <v>1.26</v>
+      </c>
+      <c r="Z114">
+        <v>3.61</v>
+      </c>
+      <c r="AA114">
+        <v>1.83</v>
+      </c>
+      <c r="AB114">
+        <v>1.84</v>
+      </c>
+      <c r="AC114">
+        <v>3.08</v>
+      </c>
+      <c r="AD114">
+        <v>1.28</v>
+      </c>
+      <c r="AE114">
+        <v>1.06</v>
+      </c>
+      <c r="AF114">
+        <v>1.7</v>
+      </c>
+      <c r="AG114">
+        <v>2.04</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ114">
         <v>1.3</v>
       </c>
-      <c r="Z114">
-        <v>3.21</v>
-      </c>
-      <c r="AA114">
-        <v>2.01</v>
-      </c>
-      <c r="AB114">
-        <v>1.74</v>
-      </c>
-      <c r="AC114">
-        <v>3.6</v>
-      </c>
-      <c r="AD114">
-        <v>1.23</v>
-      </c>
-      <c r="AE114">
-        <v>1.04</v>
-      </c>
-      <c r="AF114">
-        <v>1.83</v>
-      </c>
-      <c r="AG114">
-        <v>1.82</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ114">
-        <v>1.76</v>
-      </c>
       <c r="AK114">
-        <v>1.16</v>
+        <v>1.61</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="O115">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P115">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="Q115">
-        <v>3.48</v>
+        <v>4.64</v>
       </c>
       <c r="R115">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S115">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T115">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="U115">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V115">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W115">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z115">
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="AA115">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AB115">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="AC115">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AD115">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AE115">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF115">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG115">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="AK115">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,31 +19217,31 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="O116">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P116">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="Q116">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="R116">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S116">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T116">
+        <v>2.65</v>
+      </c>
+      <c r="U116">
         <v>3</v>
       </c>
-      <c r="U116">
-        <v>2.68</v>
-      </c>
       <c r="V116">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="W116">
         <v>1.05</v>
@@ -19250,31 +19250,31 @@
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Z116">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="AA116">
+        <v>2.15</v>
+      </c>
+      <c r="AB116">
+        <v>1.64</v>
+      </c>
+      <c r="AC116">
+        <v>4</v>
+      </c>
+      <c r="AD116">
+        <v>1.17</v>
+      </c>
+      <c r="AE116">
+        <v>1.01</v>
+      </c>
+      <c r="AF116">
         <v>1.86</v>
       </c>
-      <c r="AB116">
-        <v>1.81</v>
-      </c>
-      <c r="AC116">
-        <v>3.08</v>
-      </c>
-      <c r="AD116">
-        <v>1.28</v>
-      </c>
-      <c r="AE116">
-        <v>1.08</v>
-      </c>
-      <c r="AF116">
-        <v>1.68</v>
-      </c>
       <c r="AG116">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK116">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,34 +19380,34 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="O117">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="P117">
-        <v>2.04</v>
+        <v>2.37</v>
       </c>
       <c r="Q117">
-        <v>4.03</v>
+        <v>3.1</v>
       </c>
       <c r="R117">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S117">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T117">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U117">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="V117">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W117">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X117">
         <v>1.01</v>
@@ -19416,19 +19416,19 @@
         <v>1.26</v>
       </c>
       <c r="Z117">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AA117">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AB117">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC117">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD117">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE117">
         <v>1.08</v>
@@ -19437,7 +19437,7 @@
         <v>1.68</v>
       </c>
       <c r="AG117">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK117">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,65 +19543,65 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="O118">
+        <v>3.5</v>
+      </c>
+      <c r="P118">
+        <v>2.04</v>
+      </c>
+      <c r="Q118">
+        <v>4.03</v>
+      </c>
+      <c r="R118">
+        <v>2.1</v>
+      </c>
+      <c r="S118">
+        <v>1.33</v>
+      </c>
+      <c r="T118">
         <v>3.2</v>
       </c>
-      <c r="P118">
-        <v>2.41</v>
-      </c>
-      <c r="Q118">
-        <v>3.3</v>
-      </c>
-      <c r="R118">
+      <c r="U118">
+        <v>2.78</v>
+      </c>
+      <c r="V118">
+        <v>1.41</v>
+      </c>
+      <c r="W118">
+        <v>1.1</v>
+      </c>
+      <c r="X118">
+        <v>1.01</v>
+      </c>
+      <c r="Y118">
+        <v>1.26</v>
+      </c>
+      <c r="Z118">
+        <v>3.42</v>
+      </c>
+      <c r="AA118">
+        <v>1.82</v>
+      </c>
+      <c r="AB118">
+        <v>1.85</v>
+      </c>
+      <c r="AC118">
+        <v>2.97</v>
+      </c>
+      <c r="AD118">
+        <v>1.3</v>
+      </c>
+      <c r="AE118">
+        <v>1.08</v>
+      </c>
+      <c r="AF118">
+        <v>1.68</v>
+      </c>
+      <c r="AG118">
         <v>2</v>
       </c>
-      <c r="S118">
-        <v>1.45</v>
-      </c>
-      <c r="T118">
-        <v>2.45</v>
-      </c>
-      <c r="U118">
-        <v>3.12</v>
-      </c>
-      <c r="V118">
-        <v>1.28</v>
-      </c>
-      <c r="W118">
-        <v>1.01</v>
-      </c>
-      <c r="X118">
-        <v>1.03</v>
-      </c>
-      <c r="Y118">
-        <v>1.38</v>
-      </c>
-      <c r="Z118">
-        <v>2.74</v>
-      </c>
-      <c r="AA118">
-        <v>2.25</v>
-      </c>
-      <c r="AB118">
-        <v>1.59</v>
-      </c>
-      <c r="AC118">
-        <v>3.96</v>
-      </c>
-      <c r="AD118">
-        <v>1.17</v>
-      </c>
-      <c r="AE118">
-        <v>1.02</v>
-      </c>
-      <c r="AF118">
-        <v>1.87</v>
-      </c>
-      <c r="AG118">
-        <v>1.82</v>
-      </c>
       <c r="AH118" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK118">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,80 +19706,80 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q119">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="R119">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S119">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="T119">
-        <v>2.86</v>
+        <v>2.45</v>
       </c>
       <c r="U119">
-        <v>2.62</v>
+        <v>3.12</v>
       </c>
       <c r="V119">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="W119">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y119">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="Z119">
-        <v>3.86</v>
+        <v>2.74</v>
       </c>
       <c r="AA119">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="AB119">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AC119">
-        <v>2.83</v>
+        <v>3.96</v>
       </c>
       <c r="AD119">
+        <v>1.17</v>
+      </c>
+      <c r="AE119">
+        <v>1.02</v>
+      </c>
+      <c r="AF119">
+        <v>1.87</v>
+      </c>
+      <c r="AG119">
+        <v>1.82</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ119">
+        <v>1.28</v>
+      </c>
+      <c r="AK119">
         <v>1.33</v>
-      </c>
-      <c r="AE119">
-        <v>1.09</v>
-      </c>
-      <c r="AF119">
-        <v>1.65</v>
-      </c>
-      <c r="AG119">
-        <v>2.16</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>1.25</v>
-      </c>
-      <c r="AK119">
-        <v>1.62</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
         <v>2.75</v>
       </c>
-      <c r="O120">
-        <v>3.2</v>
-      </c>
-      <c r="P120">
-        <v>2.47</v>
-      </c>
-      <c r="Q120">
-        <v>3.48</v>
-      </c>
       <c r="R120">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="S120">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T120">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="U120">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V120">
         <v>1.4</v>
       </c>
       <c r="W120">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X120">
         <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z120">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="AA120">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB120">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AC120">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="AD120">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE120">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF120">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AG120">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK120">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -19985,27 +19985,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O121">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="P121">
-        <v>2.96</v>
+        <v>2.47</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="Z121">
-        <v>1.98</v>
+        <v>3.2</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-09-26 16:00:00</t>
+          <t>2026-09-26 15:45:00</t>
         </is>
       </c>
     </row>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="O122">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="P122">
-        <v>3.57</v>
+        <v>2.96</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20228,10 +20228,10 @@
         <v>0</v>
       </c>
       <c r="Y122">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="Z122">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AA122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.44</v>
+        <v>2.21</v>
       </c>
       <c r="O123">
-        <v>3.66</v>
+        <v>2.68</v>
       </c>
       <c r="P123">
-        <v>7.23</v>
+        <v>3.57</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20391,16 +20391,16 @@
         <v>0</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA123">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB123">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC123">
         <v>0</v>
@@ -20474,12 +20474,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="O124">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="P124">
-        <v>3.1</v>
+        <v>7.23</v>
       </c>
       <c r="Q124">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R124">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S124">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T124">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U124">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V124">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W124">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X124">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y124">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z124">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AA124">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="AB124">
-        <v>2.01</v>
+        <v>1.53</v>
       </c>
       <c r="AC124">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD124">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE124">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF124">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG124">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK124">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30:00</t>
+          <t>2026-09-26 16:00:00</t>
         </is>
       </c>
     </row>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="O125">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P125">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q125">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="R125">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S125">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T125">
-        <v>2.64</v>
+        <v>3.25</v>
       </c>
       <c r="U125">
-        <v>2.92</v>
+        <v>2.45</v>
       </c>
       <c r="V125">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W125">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X125">
         <v>1.03</v>
       </c>
       <c r="Y125">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Z125">
-        <v>2.7</v>
+        <v>3.82</v>
       </c>
       <c r="AA125">
-        <v>2.21</v>
+        <v>1.74</v>
       </c>
       <c r="AB125">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="AC125">
-        <v>3.9</v>
+        <v>2.78</v>
       </c>
       <c r="AD125">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AE125">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF125">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AG125">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK125">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20800,12 +20800,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="O126">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P126">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="Q126">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R126">
         <v>2</v>
       </c>
       <c r="S126">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T126">
-        <v>2.41</v>
+        <v>2.64</v>
       </c>
       <c r="U126">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="V126">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W126">
+        <v>1.05</v>
+      </c>
+      <c r="X126">
         <v>1.03</v>
       </c>
-      <c r="X126">
-        <v>1.02</v>
-      </c>
       <c r="Y126">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z126">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AA126">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AB126">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC126">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AD126">
         <v>1.18</v>
       </c>
       <c r="AE126">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF126">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG126">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK126">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-09-26 17:00:00</t>
+          <t>2026-09-26 16:30:00</t>
         </is>
       </c>
     </row>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="O127">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="P127">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q127">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R127">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="S127">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="T127">
-        <v>2.04</v>
+        <v>2.41</v>
       </c>
       <c r="U127">
-        <v>4.4</v>
+        <v>3.08</v>
       </c>
       <c r="V127">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="W127">
         <v>1.03</v>
       </c>
       <c r="X127">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.68</v>
+        <v>1.34</v>
       </c>
       <c r="Z127">
-        <v>2.02</v>
+        <v>2.78</v>
       </c>
       <c r="AA127">
-        <v>3.14</v>
+        <v>2.3</v>
       </c>
       <c r="AB127">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="AC127">
-        <v>7</v>
+        <v>3.88</v>
       </c>
       <c r="AD127">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AE127">
         <v>1.02</v>
       </c>
       <c r="AF127">
-        <v>2.44</v>
+        <v>1.85</v>
       </c>
       <c r="AG127">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AK127">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="O128">
-        <v>3.54</v>
+        <v>2.63</v>
       </c>
       <c r="P128">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA128">
-        <v>1.6</v>
+        <v>3.14</v>
       </c>
       <c r="AB128">
-        <v>2.3</v>
+        <v>1.27</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21294,22 +21294,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21375,10 +21375,10 @@
         <v>0</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC129">
         <v>0</v>
@@ -21452,27 +21452,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O130">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P130">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q130">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R130">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S130">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T130">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U130">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="V130">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W130">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X130">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y130">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z130">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA130">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB130">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC130">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AD130">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE130">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF130">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG130">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK130">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-09-26 18:30:00</t>
+          <t>2026-09-26 17:00:00</t>
         </is>
       </c>
     </row>
@@ -21615,12 +21615,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.69</v>
+        <v>2.41</v>
       </c>
       <c r="O131">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="P131">
-        <v>5.19</v>
+        <v>3.19</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T131">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U131">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="V131">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W131">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X131">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y131">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Z131">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD131">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE131">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF131">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG131">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK131">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-09-26 19:00:00</t>
+          <t>2026-09-26 18:30:00</t>
         </is>
       </c>
     </row>
@@ -21778,12 +21778,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="O132">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="P132">
-        <v>3.5</v>
+        <v>5.19</v>
       </c>
       <c r="Q132">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="R132">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S132">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T132">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U132">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="V132">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W132">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X132">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y132">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="Z132">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AA132">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB132">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC132">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD132">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE132">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF132">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG132">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK132">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30:00</t>
+          <t>2026-09-26 19:00:00</t>
         </is>
       </c>
     </row>
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="O133">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="P133">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q133">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="R133">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S133">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="T133">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="U133">
-        <v>2.27</v>
+        <v>2.86</v>
       </c>
       <c r="V133">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="W133">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X133">
+        <v>1.02</v>
+      </c>
+      <c r="Y133">
+        <v>1.32</v>
+      </c>
+      <c r="Z133">
+        <v>2.88</v>
+      </c>
+      <c r="AA133">
+        <v>2.06</v>
+      </c>
+      <c r="AB133">
+        <v>1.65</v>
+      </c>
+      <c r="AC133">
+        <v>3.7</v>
+      </c>
+      <c r="AD133">
+        <v>1.2</v>
+      </c>
+      <c r="AE133">
         <v>1.03</v>
       </c>
-      <c r="Y133">
-        <v>1.16</v>
-      </c>
-      <c r="Z133">
-        <v>4.05</v>
-      </c>
-      <c r="AA133">
-        <v>1.78</v>
-      </c>
-      <c r="AB133">
-        <v>1.97</v>
-      </c>
-      <c r="AC133">
-        <v>2.56</v>
-      </c>
-      <c r="AD133">
-        <v>1.4</v>
-      </c>
-      <c r="AE133">
-        <v>1.12</v>
-      </c>
       <c r="AF133">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AG133">
-        <v>2.24</v>
+        <v>1.83</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK133">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22104,12 +22104,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="O134">
-        <v>3.72</v>
+        <v>3.44</v>
       </c>
       <c r="P134">
-        <v>3.86</v>
+        <v>2.9</v>
       </c>
       <c r="Q134">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="R134">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S134">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T134">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U134">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="V134">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="W134">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X134">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y134">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z134">
-        <v>5.15</v>
+        <v>4.05</v>
       </c>
       <c r="AA134">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="AB134">
-        <v>2.66</v>
+        <v>1.97</v>
       </c>
       <c r="AC134">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="AD134">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AE134">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AF134">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AG134">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK134">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-09-26 20:00:00</t>
+          <t>2026-09-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="O135">
-        <v>3.54</v>
+        <v>3.72</v>
       </c>
       <c r="P135">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="Q135">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="R135">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S135">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T135">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U135">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="V135">
+        <v>1.68</v>
+      </c>
+      <c r="W135">
+        <v>1.15</v>
+      </c>
+      <c r="X135">
+        <v>1.02</v>
+      </c>
+      <c r="Y135">
+        <v>1.1</v>
+      </c>
+      <c r="Z135">
+        <v>5.15</v>
+      </c>
+      <c r="AA135">
         <v>1.44</v>
       </c>
-      <c r="W135">
-        <v>1.1</v>
-      </c>
-      <c r="X135">
-        <v>1.01</v>
-      </c>
-      <c r="Y135">
-        <v>1.21</v>
-      </c>
-      <c r="Z135">
-        <v>3.58</v>
-      </c>
-      <c r="AA135">
-        <v>1.83</v>
-      </c>
       <c r="AB135">
-        <v>1.93</v>
+        <v>2.66</v>
       </c>
       <c r="AC135">
-        <v>2.74</v>
+        <v>2.08</v>
       </c>
       <c r="AD135">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="AE135">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AF135">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AG135">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK135">
-        <v>1.62</v>
+        <v>1.99</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="O136">
-        <v>3.16</v>
+        <v>3.54</v>
       </c>
       <c r="P136">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="Q136">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R136">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S136">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T136">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U136">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="V136">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W136">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X136">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z136">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="AA136">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB136">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC136">
-        <v>3.47</v>
+        <v>2.74</v>
       </c>
       <c r="AD136">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE136">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF136">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG136">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK136">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="O137">
-        <v>2.79</v>
+        <v>3.16</v>
       </c>
       <c r="P137">
-        <v>4.38</v>
+        <v>3.24</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T137">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U137">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V137">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W137">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y137">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="Z137">
-        <v>2.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE137">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK137">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>3.17</v>
+        <v>1.93</v>
       </c>
       <c r="O138">
-        <v>3.2</v>
+        <v>2.79</v>
       </c>
       <c r="P138">
-        <v>2.08</v>
+        <v>4.38</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22836,16 +22836,16 @@
         <v>0</v>
       </c>
       <c r="Y138">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z138">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA138">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB138">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC138">
         <v>0</v>
@@ -22919,12 +22919,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.62</v>
+        <v>3.17</v>
       </c>
       <c r="O139">
-        <v>3.98</v>
+        <v>3.2</v>
       </c>
       <c r="P139">
-        <v>2.51</v>
+        <v>2.08</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23005,16 +23005,16 @@
         <v>0</v>
       </c>
       <c r="AA139">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC139">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD139">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE139">
         <v>0</v>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>2026-09-26 20:30:00</t>
+          <t>2026-09-26 20:00:00</t>
         </is>
       </c>
     </row>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="O140">
-        <v>3.73</v>
+        <v>3.98</v>
       </c>
       <c r="P140">
-        <v>2.83</v>
+        <v>2.51</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23168,16 +23168,16 @@
         <v>0</v>
       </c>
       <c r="AA140">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB140">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD140">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.55</v>
+        <v>2.44</v>
       </c>
       <c r="O141">
-        <v>4.8</v>
+        <v>3.73</v>
       </c>
       <c r="P141">
-        <v>5.58</v>
+        <v>2.83</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23331,16 +23331,16 @@
         <v>0</v>
       </c>
       <c r="AA141">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB141">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC141">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD141">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="O142">
-        <v>4.01</v>
+        <v>4.8</v>
       </c>
       <c r="P142">
-        <v>3.23</v>
+        <v>5.58</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23500,10 +23500,10 @@
         <v>0</v>
       </c>
       <c r="AC142">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AD142">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AE142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="O143">
-        <v>4.09</v>
+        <v>4.01</v>
       </c>
       <c r="P143">
-        <v>2.44</v>
+        <v>3.23</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23663,10 +23663,10 @@
         <v>0</v>
       </c>
       <c r="AC143">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AD143">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE143">
         <v>0</v>
@@ -23734,12 +23734,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.99</v>
+        <v>2.66</v>
       </c>
       <c r="O144">
-        <v>3.2</v>
+        <v>4.09</v>
       </c>
       <c r="P144">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="Q144">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R144">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S144">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T144">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U144">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V144">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W144">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X144">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y144">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z144">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="AA144">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB144">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC144">
-        <v>3.45</v>
+        <v>1.98</v>
       </c>
       <c r="AD144">
-        <v>1.28</v>
+        <v>1.73</v>
       </c>
       <c r="AE144">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF144">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG144">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AK144">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>2026-09-26 21:30:00</t>
+          <t>2026-09-26 20:30:00</t>
         </is>
       </c>
     </row>
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.5</v>
+        <v>2.99</v>
       </c>
       <c r="O145">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P145">
-        <v>6.36</v>
+        <v>2.18</v>
       </c>
       <c r="Q145">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R145">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S145">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T145">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U145">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V145">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W145">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X145">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y145">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z145">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AA145">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB145">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC145">
-        <v>2.25</v>
+        <v>3.45</v>
       </c>
       <c r="AD145">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AE145">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF145">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG145">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK145">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.19</v>
+        <v>1.5</v>
       </c>
       <c r="O146">
-        <v>3.86</v>
+        <v>4.8</v>
       </c>
       <c r="P146">
-        <v>3.17</v>
+        <v>6.36</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24155,7 +24155,7 @@
         <v>2.25</v>
       </c>
       <c r="AD146">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="O147">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="P147">
-        <v>3.03</v>
+        <v>3.17</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.39</v>
+        <v>2.27</v>
       </c>
       <c r="O148">
-        <v>5.47</v>
+        <v>3.84</v>
       </c>
       <c r="P148">
-        <v>7.9</v>
+        <v>3.03</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24478,10 +24478,10 @@
         <v>0</v>
       </c>
       <c r="AC148">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD148">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE148">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.5</v>
+        <v>1.39</v>
       </c>
       <c r="O149">
-        <v>3.84</v>
+        <v>5.47</v>
       </c>
       <c r="P149">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24641,10 +24641,10 @@
         <v>0</v>
       </c>
       <c r="AC149">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD149">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE149">
         <v>0</v>
@@ -24712,12 +24712,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,64 +24759,64 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="O150">
-        <v>4.36</v>
+        <v>3.84</v>
       </c>
       <c r="P150">
-        <v>4.59</v>
+        <v>2.7</v>
       </c>
       <c r="Q150">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="R150">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S150">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T150">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U150">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V150">
+        <v>0</v>
+      </c>
+      <c r="W150">
+        <v>0</v>
+      </c>
+      <c r="X150">
+        <v>0</v>
+      </c>
+      <c r="Y150">
+        <v>0</v>
+      </c>
+      <c r="Z150">
+        <v>0</v>
+      </c>
+      <c r="AA150">
+        <v>0</v>
+      </c>
+      <c r="AB150">
+        <v>0</v>
+      </c>
+      <c r="AC150">
+        <v>2.25</v>
+      </c>
+      <c r="AD150">
         <v>1.57</v>
       </c>
-      <c r="W150">
-        <v>1.11</v>
-      </c>
-      <c r="X150">
-        <v>1.02</v>
-      </c>
-      <c r="Y150">
-        <v>1.14</v>
-      </c>
-      <c r="Z150">
-        <v>4.7</v>
-      </c>
-      <c r="AA150">
-        <v>1.49</v>
-      </c>
-      <c r="AB150">
-        <v>2.3</v>
-      </c>
-      <c r="AC150">
-        <v>2.29</v>
-      </c>
-      <c r="AD150">
-        <v>1.53</v>
-      </c>
       <c r="AE150">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF150">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG150">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK150">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>2026-09-26 21:45:00</t>
+          <t>2026-09-26 21:30:00</t>
         </is>
       </c>
     </row>
@@ -24875,12 +24875,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="O151">
-        <v>3.18</v>
+        <v>4.36</v>
       </c>
       <c r="P151">
-        <v>2.09</v>
+        <v>4.59</v>
       </c>
       <c r="Q151">
-        <v>3.79</v>
+        <v>1.96</v>
       </c>
       <c r="R151">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="S151">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T151">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="U151">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="V151">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="W151">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X151">
         <v>1.02</v>
       </c>
       <c r="Y151">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="Z151">
-        <v>3.08</v>
+        <v>4.7</v>
       </c>
       <c r="AA151">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AB151">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AC151">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="AD151">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="AE151">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF151">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="AG151">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="AK151">
-        <v>1.28</v>
+        <v>2.27</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25026,7 +25026,7 @@
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>2026-09-26 22:00:00</t>
+          <t>2026-09-26 21:45:00</t>
         </is>
       </c>
     </row>
@@ -25038,12 +25038,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="O152">
-        <v>3.94</v>
+        <v>3.18</v>
       </c>
       <c r="P152">
-        <v>3.18</v>
+        <v>2.09</v>
       </c>
       <c r="Q152">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R152">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S152">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T152">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U152">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V152">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W152">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X152">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y152">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z152">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA152">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB152">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC152">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD152">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AE152">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF152">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG152">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK152">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25189,7 +25189,7 @@
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>2026-09-26 22:30:00</t>
+          <t>2026-09-26 22:00:00</t>
         </is>
       </c>
     </row>
@@ -25201,12 +25201,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>3.09</v>
+        <v>2.16</v>
       </c>
       <c r="O153">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="P153">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="Q153">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R153">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S153">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T153">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U153">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V153">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W153">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y153">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z153">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA153">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB153">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC153">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AD153">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE153">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF153">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG153">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AK153">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25352,7 +25352,7 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>2026-09-26 23:00:00</t>
+          <t>2026-09-26 22:30:00</t>
         </is>
       </c>
     </row>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.12</v>
+        <v>3.09</v>
       </c>
       <c r="O154">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P154">
-        <v>2.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q154">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="R154">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S154">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T154">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U154">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="V154">
         <v>1.5</v>
       </c>
       <c r="W154">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X154">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y154">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z154">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="AA154">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB154">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AC154">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD154">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE154">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF154">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG154">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AK154">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="O155">
-        <v>3.02</v>
+        <v>3.38</v>
       </c>
       <c r="P155">
-        <v>2.27</v>
+        <v>2.96</v>
       </c>
       <c r="Q155">
-        <v>3.86</v>
+        <v>2.72</v>
       </c>
       <c r="R155">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S155">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="T155">
-        <v>2.58</v>
+        <v>3.28</v>
       </c>
       <c r="U155">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="V155">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W155">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X155">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y155">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Z155">
-        <v>2.7</v>
+        <v>3.78</v>
       </c>
       <c r="AA155">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AB155">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AC155">
-        <v>3.86</v>
+        <v>2.74</v>
       </c>
       <c r="AD155">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AE155">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AF155">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AG155">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK155">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25690,12 +25690,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.26</v>
+        <v>3</v>
       </c>
       <c r="O156">
-        <v>3.77</v>
+        <v>3.02</v>
       </c>
       <c r="P156">
-        <v>3.09</v>
+        <v>2.27</v>
       </c>
       <c r="Q156">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S156">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T156">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U156">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V156">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W156">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y156">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z156">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA156">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AB156">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AC156">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD156">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE156">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF156">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG156">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK156">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25841,7 +25841,7 @@
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>2026-09-26 23:30:00</t>
+          <t>2026-09-26 23:00:00</t>
         </is>
       </c>
     </row>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.26</v>
+        <v>2.26</v>
       </c>
       <c r="O157">
-        <v>6.55</v>
+        <v>3.77</v>
       </c>
       <c r="P157">
-        <v>11.4</v>
+        <v>3.09</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -25939,16 +25939,16 @@
         <v>0</v>
       </c>
       <c r="AA157">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB157">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC157">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD157">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE157">
         <v>0</v>
@@ -26031,141 +26031,304 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N158">
+        <v>1.26</v>
+      </c>
+      <c r="O158">
+        <v>6.55</v>
+      </c>
+      <c r="P158">
+        <v>11.4</v>
+      </c>
+      <c r="Q158">
+        <v>0</v>
+      </c>
+      <c r="R158">
+        <v>0</v>
+      </c>
+      <c r="S158">
+        <v>0</v>
+      </c>
+      <c r="T158">
+        <v>0</v>
+      </c>
+      <c r="U158">
+        <v>0</v>
+      </c>
+      <c r="V158">
+        <v>0</v>
+      </c>
+      <c r="W158">
+        <v>0</v>
+      </c>
+      <c r="X158">
+        <v>0</v>
+      </c>
+      <c r="Y158">
+        <v>0</v>
+      </c>
+      <c r="Z158">
+        <v>0</v>
+      </c>
+      <c r="AA158">
+        <v>0</v>
+      </c>
+      <c r="AB158">
+        <v>0</v>
+      </c>
+      <c r="AC158">
+        <v>1.85</v>
+      </c>
+      <c r="AD158">
+        <v>1.82</v>
+      </c>
+      <c r="AE158">
+        <v>0</v>
+      </c>
+      <c r="AF158">
+        <v>0</v>
+      </c>
+      <c r="AG158">
+        <v>0</v>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ158">
+        <v>0</v>
+      </c>
+      <c r="AK158">
+        <v>0</v>
+      </c>
+      <c r="AL158">
+        <v>0</v>
+      </c>
+      <c r="AM158">
+        <v>-1</v>
+      </c>
+      <c r="AN158">
+        <v>-1</v>
+      </c>
+      <c r="AO158">
+        <v>-1</v>
+      </c>
+      <c r="AP158">
+        <v>-1</v>
+      </c>
+      <c r="AQ158">
+        <v>0</v>
+      </c>
+      <c r="AR158">
+        <v>0</v>
+      </c>
+      <c r="AS158">
+        <v>0</v>
+      </c>
+      <c r="AT158">
+        <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
           <t>SJ Earthquakes</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>Portland Timbers</t>
         </is>
       </c>
-      <c r="G158">
-        <v>0</v>
-      </c>
-      <c r="H158">
-        <v>0</v>
-      </c>
-      <c r="I158">
-        <v>0</v>
-      </c>
-      <c r="J158">
-        <v>0</v>
-      </c>
-      <c r="K158">
-        <v>0</v>
-      </c>
-      <c r="L158">
-        <v>0</v>
-      </c>
-      <c r="M158" t="inlineStr">
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N158">
+      <c r="N159">
         <v>1.98</v>
       </c>
-      <c r="O158">
+      <c r="O159">
         <v>4.07</v>
       </c>
-      <c r="P158">
+      <c r="P159">
         <v>3.57</v>
       </c>
-      <c r="Q158">
-        <v>0</v>
-      </c>
-      <c r="R158">
-        <v>0</v>
-      </c>
-      <c r="S158">
-        <v>0</v>
-      </c>
-      <c r="T158">
-        <v>0</v>
-      </c>
-      <c r="U158">
-        <v>0</v>
-      </c>
-      <c r="V158">
-        <v>0</v>
-      </c>
-      <c r="W158">
-        <v>0</v>
-      </c>
-      <c r="X158">
-        <v>0</v>
-      </c>
-      <c r="Y158">
-        <v>0</v>
-      </c>
-      <c r="Z158">
-        <v>0</v>
-      </c>
-      <c r="AA158">
-        <v>0</v>
-      </c>
-      <c r="AB158">
-        <v>0</v>
-      </c>
-      <c r="AC158">
+      <c r="Q159">
+        <v>0</v>
+      </c>
+      <c r="R159">
+        <v>0</v>
+      </c>
+      <c r="S159">
+        <v>0</v>
+      </c>
+      <c r="T159">
+        <v>0</v>
+      </c>
+      <c r="U159">
+        <v>0</v>
+      </c>
+      <c r="V159">
+        <v>0</v>
+      </c>
+      <c r="W159">
+        <v>0</v>
+      </c>
+      <c r="X159">
+        <v>0</v>
+      </c>
+      <c r="Y159">
+        <v>0</v>
+      </c>
+      <c r="Z159">
+        <v>0</v>
+      </c>
+      <c r="AA159">
+        <v>0</v>
+      </c>
+      <c r="AB159">
+        <v>0</v>
+      </c>
+      <c r="AC159">
         <v>1.9</v>
       </c>
-      <c r="AD158">
+      <c r="AD159">
         <v>1.77</v>
       </c>
-      <c r="AE158">
-        <v>0</v>
-      </c>
-      <c r="AF158">
-        <v>0</v>
-      </c>
-      <c r="AG158">
-        <v>0</v>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ158">
-        <v>0</v>
-      </c>
-      <c r="AK158">
-        <v>0</v>
-      </c>
-      <c r="AL158">
-        <v>0</v>
-      </c>
-      <c r="AM158">
-        <v>-1</v>
-      </c>
-      <c r="AN158">
-        <v>-1</v>
-      </c>
-      <c r="AO158">
-        <v>-1</v>
-      </c>
-      <c r="AP158">
-        <v>-1</v>
-      </c>
-      <c r="AQ158">
-        <v>0</v>
-      </c>
-      <c r="AR158">
-        <v>0</v>
-      </c>
-      <c r="AS158">
-        <v>0</v>
-      </c>
-      <c r="AT158">
-        <v>0</v>
-      </c>
-      <c r="AU158" t="inlineStr">
+      <c r="AE159">
+        <v>0</v>
+      </c>
+      <c r="AF159">
+        <v>0</v>
+      </c>
+      <c r="AG159">
+        <v>0</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ159">
+        <v>0</v>
+      </c>
+      <c r="AK159">
+        <v>0</v>
+      </c>
+      <c r="AL159">
+        <v>0</v>
+      </c>
+      <c r="AM159">
+        <v>-1</v>
+      </c>
+      <c r="AN159">
+        <v>-1</v>
+      </c>
+      <c r="AO159">
+        <v>-1</v>
+      </c>
+      <c r="AP159">
+        <v>-1</v>
+      </c>
+      <c r="AQ159">
+        <v>0</v>
+      </c>
+      <c r="AR159">
+        <v>0</v>
+      </c>
+      <c r="AS159">
+        <v>0</v>
+      </c>
+      <c r="AT159">
+        <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
         <is>
           <t>2026-09-26 23:30:00</t>
         </is>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="O6">
-        <v>3.48</v>
+        <v>3.98</v>
       </c>
       <c r="P6">
-        <v>4.87</v>
+        <v>5.47</v>
       </c>
       <c r="Q6">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="R6">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S6">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T6">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="AA6">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AB6">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AC6">
-        <v>3.48</v>
+        <v>2.66</v>
       </c>
       <c r="AD6">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG6">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.49</v>
+        <v>3.14</v>
       </c>
       <c r="O7">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="P7">
-        <v>5.47</v>
+        <v>2.09</v>
       </c>
       <c r="Q7">
+        <v>3.5</v>
+      </c>
+      <c r="R7">
+        <v>2.08</v>
+      </c>
+      <c r="S7">
+        <v>1.33</v>
+      </c>
+      <c r="T7">
+        <v>2.95</v>
+      </c>
+      <c r="U7">
+        <v>2.65</v>
+      </c>
+      <c r="V7">
+        <v>1.38</v>
+      </c>
+      <c r="W7">
+        <v>1.06</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1.26</v>
+      </c>
+      <c r="Z7">
+        <v>3.2</v>
+      </c>
+      <c r="AA7">
         <v>1.99</v>
       </c>
-      <c r="R7">
-        <v>2.28</v>
-      </c>
-      <c r="S7">
-        <v>1.32</v>
-      </c>
-      <c r="T7">
+      <c r="AB7">
+        <v>1.78</v>
+      </c>
+      <c r="AC7">
         <v>3.2</v>
       </c>
-      <c r="U7">
-        <v>2.57</v>
-      </c>
-      <c r="V7">
-        <v>1.48</v>
-      </c>
-      <c r="W7">
-        <v>1.11</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.18</v>
-      </c>
-      <c r="Z7">
-        <v>4.01</v>
-      </c>
-      <c r="AA7">
-        <v>1.82</v>
-      </c>
-      <c r="AB7">
-        <v>1.94</v>
-      </c>
-      <c r="AC7">
-        <v>2.66</v>
-      </c>
       <c r="AD7">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
         <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="O8">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="Q8">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T8">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="U8">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
         <v>1.26</v>
       </c>
       <c r="Z8">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="AA8">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AB8">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC8">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD8">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE8">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
+        <v>1.63</v>
+      </c>
+      <c r="O9">
+        <v>3.48</v>
+      </c>
+      <c r="P9">
+        <v>4.87</v>
+      </c>
+      <c r="Q9">
         <v>2.23</v>
       </c>
-      <c r="O9">
-        <v>2.99</v>
-      </c>
-      <c r="P9">
-        <v>3.1</v>
-      </c>
-      <c r="Q9">
-        <v>3.13</v>
-      </c>
       <c r="R9">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="T9">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="U9">
-        <v>3.22</v>
+        <v>2.89</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1.28</v>
+      </c>
+      <c r="Z9">
+        <v>3.08</v>
+      </c>
+      <c r="AA9">
+        <v>2.02</v>
+      </c>
+      <c r="AB9">
+        <v>1.77</v>
+      </c>
+      <c r="AC9">
+        <v>3.48</v>
+      </c>
+      <c r="AD9">
+        <v>1.22</v>
+      </c>
+      <c r="AE9">
         <v>1.04</v>
       </c>
-      <c r="Y9">
-        <v>1.35</v>
-      </c>
-      <c r="Z9">
-        <v>2.74</v>
-      </c>
-      <c r="AA9">
-        <v>2.19</v>
-      </c>
-      <c r="AB9">
-        <v>1.61</v>
-      </c>
-      <c r="AC9">
-        <v>3.74</v>
-      </c>
-      <c r="AD9">
-        <v>1.19</v>
-      </c>
-      <c r="AE9">
-        <v>1.03</v>
-      </c>
       <c r="AF9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="P10">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="R10">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T10">
-        <v>2.98</v>
+        <v>2.42</v>
       </c>
       <c r="U10">
-        <v>2.86</v>
+        <v>3.22</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z10">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="AA10">
-        <v>1.97</v>
+        <v>2.19</v>
       </c>
       <c r="AB10">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AC10">
-        <v>3.14</v>
+        <v>3.74</v>
       </c>
       <c r="AD10">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,61 +6992,61 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.55</v>
+        <v>3.62</v>
       </c>
       <c r="O41">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="P41">
-        <v>4.79</v>
+        <v>1.88</v>
       </c>
       <c r="Q41">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="R41">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
         <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="U41">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V41">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W41">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
-        <v>4.18</v>
+        <v>3.82</v>
       </c>
       <c r="AA41">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB41">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC41">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD41">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG41">
         <v>2.1</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>2.14</v>
+        <v>1.19</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,61 +7155,61 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.62</v>
+        <v>1.55</v>
       </c>
       <c r="O42">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="P42">
-        <v>1.88</v>
+        <v>4.79</v>
       </c>
       <c r="Q42">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
         <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="U42">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>3.82</v>
+        <v>4.18</v>
       </c>
       <c r="AA42">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC42">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD42">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG42">
         <v>2.1</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK42">
-        <v>1.19</v>
+        <v>2.14</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="O44">
-        <v>3.68</v>
+        <v>4.6</v>
       </c>
       <c r="P44">
-        <v>4.3</v>
+        <v>5.36</v>
       </c>
       <c r="Q44">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="R44">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="S44">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="U44">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="V44">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z44">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA44">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AB44">
-        <v>1.86</v>
+        <v>2.19</v>
       </c>
       <c r="AC44">
-        <v>3.01</v>
+        <v>2.36</v>
       </c>
       <c r="AD44">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AE44">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF44">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG44">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK44">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G45">
@@ -7640,68 +7640,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="O45">
-        <v>4.6</v>
+        <v>3.26</v>
       </c>
       <c r="P45">
-        <v>5.36</v>
+        <v>3.54</v>
       </c>
       <c r="Q45">
-        <v>1.93</v>
+        <v>2.69</v>
       </c>
       <c r="R45">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="S45">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="T45">
-        <v>3.54</v>
+        <v>2.71</v>
       </c>
       <c r="U45">
-        <v>2.24</v>
+        <v>2.9</v>
       </c>
       <c r="V45">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="Z45">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="AA45">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="AB45">
-        <v>2.19</v>
+        <v>1.61</v>
       </c>
       <c r="AC45">
-        <v>2.36</v>
+        <v>3.76</v>
       </c>
       <c r="AD45">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AE45">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AF45">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AG45">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK45">
-        <v>2.45</v>
+        <v>1.66</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G46">
@@ -7803,68 +7803,68 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="O46">
-        <v>3.26</v>
+        <v>3.62</v>
       </c>
       <c r="P46">
-        <v>3.54</v>
+        <v>2.88</v>
       </c>
       <c r="Q46">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="R46">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="S46">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="T46">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="U46">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="V46">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AA46">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AB46">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AC46">
-        <v>3.76</v>
+        <v>2.83</v>
       </c>
       <c r="AD46">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AE46">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF46">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="AG46">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK46">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.73</v>
+        <v>1.63</v>
       </c>
       <c r="O47">
-        <v>3.02</v>
+        <v>4.25</v>
       </c>
       <c r="P47">
-        <v>2.58</v>
+        <v>4.34</v>
       </c>
       <c r="Q47">
-        <v>3.18</v>
+        <v>2.2</v>
       </c>
       <c r="R47">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S47">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="T47">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U47">
-        <v>2.96</v>
+        <v>2.42</v>
       </c>
       <c r="V47">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z47">
-        <v>3.2</v>
+        <v>3.82</v>
       </c>
       <c r="AA47">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AB47">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AC47">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="AD47">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE47">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG47">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AK47">
-        <v>1.44</v>
+        <v>2.03</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.09</v>
+        <v>2.73</v>
       </c>
       <c r="O48">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
       <c r="P48">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="Q48">
+        <v>3.18</v>
+      </c>
+      <c r="R48">
+        <v>2.18</v>
+      </c>
+      <c r="S48">
+        <v>1.38</v>
+      </c>
+      <c r="T48">
         <v>2.75</v>
       </c>
-      <c r="R48">
-        <v>2.19</v>
-      </c>
-      <c r="S48">
-        <v>1.26</v>
-      </c>
-      <c r="T48">
-        <v>3.4</v>
-      </c>
       <c r="U48">
-        <v>2.32</v>
+        <v>2.96</v>
       </c>
       <c r="V48">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z48">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AA48">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AB48">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AC48">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="AD48">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AK48">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,34 +8296,34 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.19</v>
+        <v>2.92</v>
       </c>
       <c r="O49">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="P49">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="Q49">
-        <v>2.43</v>
+        <v>3.26</v>
       </c>
       <c r="R49">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S49">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X49">
         <v>1.01</v>
@@ -8332,44 +8332,44 @@
         <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA49">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AB49">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AC49">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD49">
+        <v>1.36</v>
+      </c>
+      <c r="AE49">
+        <v>1.13</v>
+      </c>
+      <c r="AF49">
+        <v>1.58</v>
+      </c>
+      <c r="AG49">
+        <v>2.3</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.65</v>
+      </c>
+      <c r="AK49">
         <v>1.33</v>
-      </c>
-      <c r="AE49">
-        <v>1.12</v>
-      </c>
-      <c r="AF49">
-        <v>1.64</v>
-      </c>
-      <c r="AG49">
-        <v>2.13</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.27</v>
-      </c>
-      <c r="AK49">
-        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.83</v>
+        <v>2.09</v>
       </c>
       <c r="O50">
-        <v>2.91</v>
+        <v>3.54</v>
       </c>
       <c r="P50">
-        <v>2.57</v>
+        <v>3.15</v>
       </c>
       <c r="Q50">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S50">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="T50">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="V50">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>4.07</v>
+        <v>4.33</v>
       </c>
       <c r="AA50">
+        <v>1.83</v>
+      </c>
+      <c r="AB50">
         <v>2.03</v>
       </c>
-      <c r="AB50">
-        <v>1.83</v>
-      </c>
       <c r="AC50">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="AD50">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE50">
         <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG50">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK50">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.92</v>
+        <v>1.74</v>
       </c>
       <c r="O51">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="P51">
+        <v>4.3</v>
+      </c>
+      <c r="Q51">
+        <v>2.28</v>
+      </c>
+      <c r="R51">
         <v>2.13</v>
-      </c>
-      <c r="Q51">
-        <v>3.26</v>
-      </c>
-      <c r="R51">
-        <v>2.2</v>
       </c>
       <c r="S51">
         <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="AB51">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="AC51">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG51">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.63</v>
+        <v>2.83</v>
       </c>
       <c r="O52">
-        <v>4.25</v>
+        <v>2.91</v>
       </c>
       <c r="P52">
-        <v>4.34</v>
+        <v>2.57</v>
       </c>
       <c r="Q52">
-        <v>2.2</v>
+        <v>3.24</v>
       </c>
       <c r="R52">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S52">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="T52">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="U52">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="V52">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.82</v>
+        <v>4.07</v>
       </c>
       <c r="AA52">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AB52">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AC52">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD52">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE52">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AK52">
-        <v>2.03</v>
+        <v>1.43</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q90">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S90">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T90">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="U90">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="V90">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W90">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X90">
+        <v>1.04</v>
+      </c>
+      <c r="Y90">
+        <v>1.36</v>
+      </c>
+      <c r="Z90">
+        <v>2.7</v>
+      </c>
+      <c r="AA90">
+        <v>2.25</v>
+      </c>
+      <c r="AB90">
+        <v>1.57</v>
+      </c>
+      <c r="AC90">
+        <v>3.9</v>
+      </c>
+      <c r="AD90">
+        <v>1.17</v>
+      </c>
+      <c r="AE90">
         <v>1.03</v>
       </c>
-      <c r="Y90">
-        <v>1.3</v>
-      </c>
-      <c r="Z90">
-        <v>3.25</v>
-      </c>
-      <c r="AA90">
-        <v>2.1</v>
-      </c>
-      <c r="AB90">
-        <v>1.7</v>
-      </c>
-      <c r="AC90">
-        <v>3.6</v>
-      </c>
-      <c r="AD90">
-        <v>1.25</v>
-      </c>
-      <c r="AE90">
-        <v>1.06</v>
-      </c>
       <c r="AF90">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AG90">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK90">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="R91">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T91">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="U91">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="V91">
+        <v>1.4</v>
+      </c>
+      <c r="W91">
+        <v>1.06</v>
+      </c>
+      <c r="X91">
+        <v>1.03</v>
+      </c>
+      <c r="Y91">
         <v>1.3</v>
       </c>
-      <c r="W91">
-        <v>1.02</v>
-      </c>
-      <c r="X91">
-        <v>1.04</v>
-      </c>
-      <c r="Y91">
-        <v>1.36</v>
-      </c>
       <c r="Z91">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB91">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC91">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD91">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE91">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG91">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK91">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AL91">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="O6">
-        <v>3.98</v>
+        <v>3.48</v>
       </c>
       <c r="P6">
-        <v>5.47</v>
+        <v>4.87</v>
       </c>
       <c r="Q6">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="R6">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T6">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="U6">
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="V6">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z6">
-        <v>4.01</v>
+        <v>3.08</v>
       </c>
       <c r="AA6">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AB6">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AC6">
-        <v>2.66</v>
+        <v>3.48</v>
       </c>
       <c r="AD6">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AE6">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="O7">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="Q7">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T7">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="U7">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
         <v>1.26</v>
       </c>
       <c r="Z7">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="AA7">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AB7">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC7">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE7">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,61 +1613,61 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.6</v>
+        <v>1.49</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="P8">
-        <v>2.32</v>
+        <v>5.47</v>
       </c>
       <c r="Q8">
+        <v>1.99</v>
+      </c>
+      <c r="R8">
+        <v>2.28</v>
+      </c>
+      <c r="S8">
+        <v>1.32</v>
+      </c>
+      <c r="T8">
         <v>3.2</v>
       </c>
-      <c r="R8">
-        <v>2.1</v>
-      </c>
-      <c r="S8">
-        <v>1.37</v>
-      </c>
-      <c r="T8">
-        <v>2.98</v>
-      </c>
       <c r="U8">
-        <v>2.86</v>
+        <v>2.57</v>
       </c>
       <c r="V8">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>3.43</v>
+        <v>4.01</v>
       </c>
       <c r="AA8">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AB8">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AC8">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="AD8">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AE8">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG8">
         <v>2</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.38</v>
+        <v>2.21</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.63</v>
+        <v>3.14</v>
       </c>
       <c r="O9">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="P9">
-        <v>4.87</v>
+        <v>2.09</v>
       </c>
       <c r="Q9">
-        <v>2.23</v>
+        <v>3.5</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S9">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="U9">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
         <v>1.06</v>
@@ -1809,31 +1809,31 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z9">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA9">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AB9">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC9">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AD9">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>2.05</v>
+        <v>1.27</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,49 +7970,49 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.63</v>
+        <v>2.92</v>
       </c>
       <c r="O47">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="P47">
-        <v>4.34</v>
+        <v>2.13</v>
       </c>
       <c r="Q47">
+        <v>3.26</v>
+      </c>
+      <c r="R47">
         <v>2.2</v>
       </c>
-      <c r="R47">
-        <v>2.22</v>
-      </c>
       <c r="S47">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="V47">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB47">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AC47">
         <v>2.7</v>
@@ -8021,13 +8021,13 @@
         <v>1.36</v>
       </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF47">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG47">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="AK47">
-        <v>2.03</v>
+        <v>1.33</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.73</v>
+        <v>2.09</v>
       </c>
       <c r="O48">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="P48">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="Q48">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="R48">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="T48">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U48">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="V48">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA48">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AC48">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AD48">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AE48">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
       <c r="O49">
-        <v>3.74</v>
+        <v>3.02</v>
       </c>
       <c r="P49">
-        <v>2.13</v>
+        <v>2.58</v>
       </c>
       <c r="Q49">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="R49">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S49">
+        <v>1.38</v>
+      </c>
+      <c r="T49">
+        <v>2.75</v>
+      </c>
+      <c r="U49">
+        <v>2.96</v>
+      </c>
+      <c r="V49">
+        <v>1.4</v>
+      </c>
+      <c r="W49">
+        <v>1.06</v>
+      </c>
+      <c r="X49">
+        <v>1.03</v>
+      </c>
+      <c r="Y49">
         <v>1.3</v>
       </c>
-      <c r="T49">
-        <v>3.3</v>
-      </c>
-      <c r="U49">
-        <v>2.45</v>
-      </c>
-      <c r="V49">
-        <v>1.51</v>
-      </c>
-      <c r="W49">
-        <v>1.09</v>
-      </c>
-      <c r="X49">
-        <v>1.01</v>
-      </c>
-      <c r="Y49">
-        <v>1.22</v>
-      </c>
       <c r="Z49">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA49">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="AB49">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC49">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD49">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AG49">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AK49">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.09</v>
+        <v>2.83</v>
       </c>
       <c r="O50">
-        <v>3.54</v>
+        <v>2.91</v>
       </c>
       <c r="P50">
-        <v>3.15</v>
+        <v>2.57</v>
       </c>
       <c r="Q50">
+        <v>3.24</v>
+      </c>
+      <c r="R50">
+        <v>2.25</v>
+      </c>
+      <c r="S50">
+        <v>1.37</v>
+      </c>
+      <c r="T50">
+        <v>2.7</v>
+      </c>
+      <c r="U50">
         <v>2.75</v>
       </c>
-      <c r="R50">
-        <v>2.19</v>
-      </c>
-      <c r="S50">
-        <v>1.26</v>
-      </c>
-      <c r="T50">
-        <v>3.4</v>
-      </c>
-      <c r="U50">
-        <v>2.32</v>
-      </c>
       <c r="V50">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>4.33</v>
+        <v>4.07</v>
       </c>
       <c r="AA50">
+        <v>2.03</v>
+      </c>
+      <c r="AB50">
         <v>1.83</v>
       </c>
-      <c r="AB50">
-        <v>2.03</v>
-      </c>
       <c r="AC50">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="AD50">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE50">
         <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK50">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.83</v>
+        <v>1.63</v>
       </c>
       <c r="O52">
-        <v>2.91</v>
+        <v>4.25</v>
       </c>
       <c r="P52">
-        <v>2.57</v>
+        <v>4.34</v>
       </c>
       <c r="Q52">
-        <v>3.24</v>
+        <v>2.2</v>
       </c>
       <c r="R52">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S52">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="T52">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U52">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="V52">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z52">
-        <v>4.07</v>
+        <v>3.82</v>
       </c>
       <c r="AA52">
+        <v>1.65</v>
+      </c>
+      <c r="AB52">
+        <v>2.06</v>
+      </c>
+      <c r="AC52">
+        <v>2.7</v>
+      </c>
+      <c r="AD52">
+        <v>1.36</v>
+      </c>
+      <c r="AE52">
+        <v>1.11</v>
+      </c>
+      <c r="AF52">
+        <v>1.67</v>
+      </c>
+      <c r="AG52">
+        <v>2.1</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>1.19</v>
+      </c>
+      <c r="AK52">
         <v>2.03</v>
-      </c>
-      <c r="AB52">
-        <v>1.83</v>
-      </c>
-      <c r="AC52">
-        <v>2.74</v>
-      </c>
-      <c r="AD52">
-        <v>1.35</v>
-      </c>
-      <c r="AE52">
-        <v>1.13</v>
-      </c>
-      <c r="AF52">
-        <v>1.6</v>
-      </c>
-      <c r="AG52">
-        <v>2.19</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.4</v>
-      </c>
-      <c r="AK52">
-        <v>1.43</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.49</v>
+        <v>2.38</v>
       </c>
       <c r="O8">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>5.47</v>
+        <v>2.47</v>
       </c>
       <c r="Q8">
-        <v>1.99</v>
+        <v>3.22</v>
       </c>
       <c r="R8">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S8">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
         <v>3.2</v>
       </c>
       <c r="U8">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="V8">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W8">
         <v>1.11</v>
@@ -1646,31 +1646,31 @@
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z8">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="AA8">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AB8">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC8">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AD8">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE8">
         <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK8">
-        <v>2.21</v>
+        <v>1.39</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.14</v>
+        <v>2.23</v>
       </c>
       <c r="O9">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="P9">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="R9">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T9">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="U9">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z9">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA9">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="AB9">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AC9">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD9">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG9">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="O10">
-        <v>2.99</v>
+        <v>3.98</v>
       </c>
       <c r="P10">
-        <v>3.1</v>
+        <v>5.47</v>
       </c>
       <c r="Q10">
-        <v>3.13</v>
+        <v>1.99</v>
       </c>
       <c r="R10">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="S10">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>3.22</v>
+        <v>2.57</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>2.74</v>
+        <v>4.01</v>
       </c>
       <c r="AA10">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="AB10">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AC10">
-        <v>3.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD10">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AE10">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AG10">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>1.48</v>
+        <v>2.21</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="P11">
-        <v>2.47</v>
+        <v>2.09</v>
       </c>
       <c r="Q11">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="R11">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="S11">
+        <v>1.33</v>
+      </c>
+      <c r="T11">
+        <v>2.95</v>
+      </c>
+      <c r="U11">
+        <v>2.65</v>
+      </c>
+      <c r="V11">
+        <v>1.38</v>
+      </c>
+      <c r="W11">
+        <v>1.06</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1.26</v>
+      </c>
+      <c r="Z11">
+        <v>3.2</v>
+      </c>
+      <c r="AA11">
+        <v>1.99</v>
+      </c>
+      <c r="AB11">
+        <v>1.78</v>
+      </c>
+      <c r="AC11">
+        <v>3.2</v>
+      </c>
+      <c r="AD11">
         <v>1.3</v>
-      </c>
-      <c r="T11">
-        <v>3.2</v>
-      </c>
-      <c r="U11">
-        <v>2.45</v>
-      </c>
-      <c r="V11">
-        <v>1.49</v>
-      </c>
-      <c r="W11">
-        <v>1.11</v>
-      </c>
-      <c r="X11">
-        <v>1.03</v>
-      </c>
-      <c r="Y11">
-        <v>1.17</v>
-      </c>
-      <c r="Z11">
-        <v>4</v>
-      </c>
-      <c r="AA11">
-        <v>1.7</v>
-      </c>
-      <c r="AB11">
-        <v>2.1</v>
-      </c>
-      <c r="AC11">
-        <v>2.77</v>
-      </c>
-      <c r="AD11">
-        <v>1.37</v>
       </c>
       <c r="AE11">
         <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="O46">
-        <v>3.62</v>
+        <v>2.91</v>
       </c>
       <c r="P46">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="Q46">
-        <v>2.43</v>
+        <v>3.24</v>
       </c>
       <c r="R46">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S46">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T46">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="U46">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="V46">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W46">
         <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
         <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>3.5</v>
+        <v>4.07</v>
       </c>
       <c r="AA46">
+        <v>2.03</v>
+      </c>
+      <c r="AB46">
         <v>1.83</v>
       </c>
-      <c r="AB46">
-        <v>1.93</v>
-      </c>
       <c r="AC46">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AD46">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE46">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG46">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AK46">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.92</v>
+        <v>1.74</v>
       </c>
       <c r="O47">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="P47">
+        <v>4.3</v>
+      </c>
+      <c r="Q47">
+        <v>2.28</v>
+      </c>
+      <c r="R47">
         <v>2.13</v>
-      </c>
-      <c r="Q47">
-        <v>3.26</v>
-      </c>
-      <c r="R47">
-        <v>2.2</v>
       </c>
       <c r="S47">
         <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U47">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V47">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W47">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y47">
         <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA47">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="AB47">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="AC47">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="AD47">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE47">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF47">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG47">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="O48">
-        <v>3.54</v>
+        <v>4.25</v>
       </c>
       <c r="P48">
-        <v>3.15</v>
+        <v>4.34</v>
       </c>
       <c r="Q48">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="R48">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="S48">
         <v>1.26</v>
       </c>
       <c r="T48">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U48">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="V48">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z48">
-        <v>4.33</v>
+        <v>3.82</v>
       </c>
       <c r="AA48">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AB48">
+        <v>2.06</v>
+      </c>
+      <c r="AC48">
+        <v>2.7</v>
+      </c>
+      <c r="AD48">
+        <v>1.36</v>
+      </c>
+      <c r="AE48">
+        <v>1.11</v>
+      </c>
+      <c r="AF48">
+        <v>1.67</v>
+      </c>
+      <c r="AG48">
+        <v>2.1</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.19</v>
+      </c>
+      <c r="AK48">
         <v>2.03</v>
-      </c>
-      <c r="AC48">
-        <v>2.77</v>
-      </c>
-      <c r="AD48">
-        <v>1.43</v>
-      </c>
-      <c r="AE48">
-        <v>1.13</v>
-      </c>
-      <c r="AF48">
-        <v>1.55</v>
-      </c>
-      <c r="AG48">
-        <v>2.25</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.33</v>
-      </c>
-      <c r="AK48">
-        <v>1.65</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.73</v>
+        <v>2.09</v>
       </c>
       <c r="O49">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="P49">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="Q49">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="R49">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S49">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="T49">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U49">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="V49">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA49">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AC49">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AD49">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK49">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="O50">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="P50">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="Q50">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S50">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T50">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U50">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="V50">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z50">
-        <v>4.07</v>
+        <v>3.2</v>
       </c>
       <c r="AA50">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AB50">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC50">
-        <v>2.74</v>
+        <v>3.28</v>
       </c>
       <c r="AD50">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG50">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AK50">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,28 +8622,28 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.74</v>
+        <v>2.19</v>
       </c>
       <c r="O51">
-        <v>3.68</v>
+        <v>3.62</v>
       </c>
       <c r="P51">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="Q51">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="R51">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V51">
         <v>1.44</v>
@@ -8652,7 +8652,7 @@
         <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
@@ -8661,25 +8661,25 @@
         <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC51">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG51">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,49 +8785,49 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.63</v>
+        <v>2.92</v>
       </c>
       <c r="O52">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="P52">
-        <v>4.34</v>
+        <v>2.13</v>
       </c>
       <c r="Q52">
+        <v>3.26</v>
+      </c>
+      <c r="R52">
         <v>2.2</v>
       </c>
-      <c r="R52">
-        <v>2.22</v>
-      </c>
       <c r="S52">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="V52">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB52">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AC52">
         <v>2.7</v>
@@ -8836,13 +8836,13 @@
         <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG52">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="AK52">
-        <v>2.03</v>
+        <v>1.33</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11281,7 +11281,7 @@
         <v>1.2</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF67">
         <v>1.91</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="P8">
-        <v>2.47</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
+        <v>3.13</v>
+      </c>
+      <c r="R8">
+        <v>1.98</v>
+      </c>
+      <c r="S8">
+        <v>1.45</v>
+      </c>
+      <c r="T8">
+        <v>2.42</v>
+      </c>
+      <c r="U8">
         <v>3.22</v>
       </c>
-      <c r="R8">
-        <v>2.17</v>
-      </c>
-      <c r="S8">
-        <v>1.3</v>
-      </c>
-      <c r="T8">
-        <v>3.2</v>
-      </c>
-      <c r="U8">
-        <v>2.45</v>
-      </c>
       <c r="V8">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>1.35</v>
+      </c>
+      <c r="Z8">
+        <v>2.74</v>
+      </c>
+      <c r="AA8">
+        <v>2.19</v>
+      </c>
+      <c r="AB8">
+        <v>1.61</v>
+      </c>
+      <c r="AC8">
+        <v>3.74</v>
+      </c>
+      <c r="AD8">
+        <v>1.19</v>
+      </c>
+      <c r="AE8">
         <v>1.03</v>
       </c>
-      <c r="Y8">
-        <v>1.17</v>
-      </c>
-      <c r="Z8">
-        <v>4</v>
-      </c>
-      <c r="AA8">
-        <v>1.7</v>
-      </c>
-      <c r="AB8">
-        <v>2.1</v>
-      </c>
-      <c r="AC8">
-        <v>2.77</v>
-      </c>
-      <c r="AD8">
-        <v>1.37</v>
-      </c>
-      <c r="AE8">
-        <v>1.11</v>
-      </c>
       <c r="AF8">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AG8">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="O9">
-        <v>2.99</v>
+        <v>3.98</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>5.47</v>
       </c>
       <c r="Q9">
-        <v>3.13</v>
+        <v>1.99</v>
       </c>
       <c r="R9">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="S9">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="T9">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="U9">
-        <v>3.22</v>
+        <v>2.57</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>2.74</v>
+        <v>4.01</v>
       </c>
       <c r="AA9">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="AB9">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AC9">
-        <v>3.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD9">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AE9">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AG9">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.48</v>
+        <v>2.21</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.49</v>
+        <v>3.14</v>
       </c>
       <c r="O10">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="P10">
-        <v>5.47</v>
+        <v>2.09</v>
       </c>
       <c r="Q10">
+        <v>3.5</v>
+      </c>
+      <c r="R10">
+        <v>2.08</v>
+      </c>
+      <c r="S10">
+        <v>1.33</v>
+      </c>
+      <c r="T10">
+        <v>2.95</v>
+      </c>
+      <c r="U10">
+        <v>2.65</v>
+      </c>
+      <c r="V10">
+        <v>1.38</v>
+      </c>
+      <c r="W10">
+        <v>1.06</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1.26</v>
+      </c>
+      <c r="Z10">
+        <v>3.2</v>
+      </c>
+      <c r="AA10">
         <v>1.99</v>
       </c>
-      <c r="R10">
-        <v>2.28</v>
-      </c>
-      <c r="S10">
-        <v>1.32</v>
-      </c>
-      <c r="T10">
+      <c r="AB10">
+        <v>1.78</v>
+      </c>
+      <c r="AC10">
         <v>3.2</v>
       </c>
-      <c r="U10">
-        <v>2.57</v>
-      </c>
-      <c r="V10">
-        <v>1.48</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.18</v>
-      </c>
-      <c r="Z10">
-        <v>4.01</v>
-      </c>
-      <c r="AA10">
-        <v>1.82</v>
-      </c>
-      <c r="AB10">
-        <v>1.94</v>
-      </c>
-      <c r="AC10">
-        <v>2.66</v>
-      </c>
       <c r="AD10">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE10">
         <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="O11">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.09</v>
+        <v>2.47</v>
       </c>
       <c r="Q11">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="R11">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="V11">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AA11">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AB11">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AC11">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE11">
         <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG11">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="O49">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P49">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="Q49">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="R49">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S49">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U49">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="V49">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
         <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC49">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="AD49">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG49">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK49">
         <v>1.65</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,77 +8622,77 @@
         </is>
       </c>
       <c r="N51">
+        <v>2.09</v>
+      </c>
+      <c r="O51">
+        <v>3.54</v>
+      </c>
+      <c r="P51">
+        <v>3.15</v>
+      </c>
+      <c r="Q51">
+        <v>2.75</v>
+      </c>
+      <c r="R51">
         <v>2.19</v>
       </c>
-      <c r="O51">
-        <v>3.62</v>
-      </c>
-      <c r="P51">
-        <v>2.88</v>
-      </c>
-      <c r="Q51">
-        <v>2.43</v>
-      </c>
-      <c r="R51">
-        <v>2.21</v>
-      </c>
       <c r="S51">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T51">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U51">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA51">
         <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="AD51">
+        <v>1.43</v>
+      </c>
+      <c r="AE51">
+        <v>1.13</v>
+      </c>
+      <c r="AF51">
+        <v>1.55</v>
+      </c>
+      <c r="AG51">
+        <v>2.25</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.33</v>
-      </c>
-      <c r="AE51">
-        <v>1.12</v>
-      </c>
-      <c r="AF51">
-        <v>1.64</v>
-      </c>
-      <c r="AG51">
-        <v>2.13</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.27</v>
       </c>
       <c r="AK51">
         <v>1.65</v>
@@ -21345,34 +21345,34 @@
         <v>3.04</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X129">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA129">
         <v>1.6</v>
@@ -21381,19 +21381,19 @@
         <v>2.3</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -22975,34 +22975,34 @@
         <v>2.08</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S139">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T139">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U139">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V139">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W139">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X139">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y139">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z139">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA139">
         <v>1.88</v>
@@ -23011,19 +23011,19 @@
         <v>1.93</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD139">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE139">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF139">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG139">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK139">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL139">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>4.87</v>
+        <v>2.32</v>
       </c>
       <c r="Q6">
-        <v>2.23</v>
+        <v>3.2</v>
       </c>
       <c r="R6">
         <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T6">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="U6">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
+        <v>1.26</v>
+      </c>
+      <c r="Z6">
+        <v>3.43</v>
+      </c>
+      <c r="AA6">
+        <v>1.97</v>
+      </c>
+      <c r="AB6">
+        <v>1.79</v>
+      </c>
+      <c r="AC6">
+        <v>3.14</v>
+      </c>
+      <c r="AD6">
+        <v>1.27</v>
+      </c>
+      <c r="AE6">
+        <v>1.07</v>
+      </c>
+      <c r="AF6">
+        <v>1.7</v>
+      </c>
+      <c r="AG6">
+        <v>2</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.28</v>
       </c>
-      <c r="Z6">
-        <v>3.08</v>
-      </c>
-      <c r="AA6">
-        <v>2.02</v>
-      </c>
-      <c r="AB6">
-        <v>1.77</v>
-      </c>
-      <c r="AC6">
-        <v>3.48</v>
-      </c>
-      <c r="AD6">
-        <v>1.22</v>
-      </c>
-      <c r="AE6">
-        <v>1.04</v>
-      </c>
-      <c r="AF6">
-        <v>1.85</v>
-      </c>
-      <c r="AG6">
-        <v>1.75</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.3</v>
-      </c>
       <c r="AK6">
-        <v>2.05</v>
+        <v>1.38</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="P7">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="Q7">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S7">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T7">
-        <v>2.98</v>
+        <v>2.42</v>
       </c>
       <c r="U7">
-        <v>2.86</v>
+        <v>3.22</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z7">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="AA7">
-        <v>1.97</v>
+        <v>2.19</v>
       </c>
       <c r="AB7">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AC7">
-        <v>3.14</v>
+        <v>3.74</v>
       </c>
       <c r="AD7">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="O8">
-        <v>2.99</v>
+        <v>3.98</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>5.47</v>
       </c>
       <c r="Q8">
-        <v>3.13</v>
+        <v>1.99</v>
       </c>
       <c r="R8">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>3.22</v>
+        <v>2.57</v>
       </c>
       <c r="V8">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>2.74</v>
+        <v>4.01</v>
       </c>
       <c r="AA8">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="AB8">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AC8">
-        <v>3.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD8">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AG8">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.48</v>
+        <v>2.21</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.49</v>
+        <v>3.14</v>
       </c>
       <c r="O9">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="P9">
-        <v>5.47</v>
+        <v>2.09</v>
       </c>
       <c r="Q9">
+        <v>3.5</v>
+      </c>
+      <c r="R9">
+        <v>2.08</v>
+      </c>
+      <c r="S9">
+        <v>1.33</v>
+      </c>
+      <c r="T9">
+        <v>2.95</v>
+      </c>
+      <c r="U9">
+        <v>2.65</v>
+      </c>
+      <c r="V9">
+        <v>1.38</v>
+      </c>
+      <c r="W9">
+        <v>1.06</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1.26</v>
+      </c>
+      <c r="Z9">
+        <v>3.2</v>
+      </c>
+      <c r="AA9">
         <v>1.99</v>
       </c>
-      <c r="R9">
-        <v>2.28</v>
-      </c>
-      <c r="S9">
-        <v>1.32</v>
-      </c>
-      <c r="T9">
+      <c r="AB9">
+        <v>1.78</v>
+      </c>
+      <c r="AC9">
         <v>3.2</v>
       </c>
-      <c r="U9">
-        <v>2.57</v>
-      </c>
-      <c r="V9">
-        <v>1.48</v>
-      </c>
-      <c r="W9">
-        <v>1.11</v>
-      </c>
-      <c r="X9">
-        <v>1.03</v>
-      </c>
-      <c r="Y9">
-        <v>1.18</v>
-      </c>
-      <c r="Z9">
-        <v>4.01</v>
-      </c>
-      <c r="AA9">
-        <v>1.82</v>
-      </c>
-      <c r="AB9">
-        <v>1.94</v>
-      </c>
-      <c r="AC9">
-        <v>2.66</v>
-      </c>
       <c r="AD9">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE9">
         <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="O10">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>2.09</v>
+        <v>2.47</v>
       </c>
       <c r="Q10">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="R10">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="V10">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z10">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AA10">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AB10">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AC10">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="AD10">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE10">
         <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG10">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P11">
-        <v>2.47</v>
+        <v>4.87</v>
       </c>
       <c r="Q11">
-        <v>3.22</v>
+        <v>2.23</v>
       </c>
       <c r="R11">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
+        <v>1.39</v>
+      </c>
+      <c r="T11">
+        <v>2.64</v>
+      </c>
+      <c r="U11">
+        <v>2.89</v>
+      </c>
+      <c r="V11">
+        <v>1.36</v>
+      </c>
+      <c r="W11">
+        <v>1.06</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1.28</v>
+      </c>
+      <c r="Z11">
+        <v>3.08</v>
+      </c>
+      <c r="AA11">
+        <v>2.02</v>
+      </c>
+      <c r="AB11">
+        <v>1.77</v>
+      </c>
+      <c r="AC11">
+        <v>3.48</v>
+      </c>
+      <c r="AD11">
+        <v>1.22</v>
+      </c>
+      <c r="AE11">
+        <v>1.04</v>
+      </c>
+      <c r="AF11">
+        <v>1.85</v>
+      </c>
+      <c r="AG11">
+        <v>1.75</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
         <v>1.3</v>
       </c>
-      <c r="T11">
-        <v>3.2</v>
-      </c>
-      <c r="U11">
-        <v>2.45</v>
-      </c>
-      <c r="V11">
-        <v>1.49</v>
-      </c>
-      <c r="W11">
-        <v>1.11</v>
-      </c>
-      <c r="X11">
-        <v>1.03</v>
-      </c>
-      <c r="Y11">
-        <v>1.17</v>
-      </c>
-      <c r="Z11">
-        <v>4</v>
-      </c>
-      <c r="AA11">
-        <v>1.7</v>
-      </c>
-      <c r="AB11">
-        <v>2.1</v>
-      </c>
-      <c r="AC11">
-        <v>2.77</v>
-      </c>
-      <c r="AD11">
-        <v>1.37</v>
-      </c>
-      <c r="AE11">
-        <v>1.11</v>
-      </c>
-      <c r="AF11">
-        <v>1.55</v>
-      </c>
-      <c r="AG11">
-        <v>2.25</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.26</v>
-      </c>
       <c r="AK11">
-        <v>1.39</v>
+        <v>2.05</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="O13">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P13">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.22</v>
+        <v>1.81</v>
       </c>
       <c r="O14">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="P14">
-        <v>1.97</v>
+        <v>3.88</v>
       </c>
       <c r="Q14">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.1</v>
+        <v>3.22</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="P15">
-        <v>3.5</v>
+        <v>1.97</v>
       </c>
       <c r="Q15">
-        <v>2.74</v>
+        <v>3.88</v>
       </c>
       <c r="R15">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="S15">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T15">
-        <v>2.58</v>
+        <v>3.18</v>
       </c>
       <c r="U15">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="V15">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>2.74</v>
+        <v>3.86</v>
       </c>
       <c r="AA15">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="AB15">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AC15">
-        <v>3.8</v>
+        <v>2.69</v>
       </c>
       <c r="AD15">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK15">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-26 08:00:00</t>
+          <t>2026-09-26 07:00:00</t>
         </is>
       </c>
     </row>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="O46">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="P46">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="Q46">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="R46">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S46">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T46">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U46">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="V46">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W46">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z46">
-        <v>4.07</v>
+        <v>3.2</v>
       </c>
       <c r="AA46">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AB46">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC46">
-        <v>2.74</v>
+        <v>3.28</v>
       </c>
       <c r="AD46">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE46">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF46">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG46">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AK46">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,49 +8133,49 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.63</v>
+        <v>2.92</v>
       </c>
       <c r="O48">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="P48">
-        <v>4.34</v>
+        <v>2.13</v>
       </c>
       <c r="Q48">
+        <v>3.26</v>
+      </c>
+      <c r="R48">
         <v>2.2</v>
       </c>
-      <c r="R48">
-        <v>2.22</v>
-      </c>
       <c r="S48">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U48">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="V48">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W48">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AA48">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB48">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AC48">
         <v>2.7</v>
@@ -8184,13 +8184,13 @@
         <v>1.36</v>
       </c>
       <c r="AE48">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG48">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="AK48">
-        <v>2.03</v>
+        <v>1.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,77 +8296,77 @@
         </is>
       </c>
       <c r="N49">
+        <v>2.09</v>
+      </c>
+      <c r="O49">
+        <v>3.54</v>
+      </c>
+      <c r="P49">
+        <v>3.15</v>
+      </c>
+      <c r="Q49">
+        <v>2.75</v>
+      </c>
+      <c r="R49">
         <v>2.19</v>
       </c>
-      <c r="O49">
-        <v>3.62</v>
-      </c>
-      <c r="P49">
-        <v>2.88</v>
-      </c>
-      <c r="Q49">
-        <v>2.43</v>
-      </c>
-      <c r="R49">
-        <v>2.21</v>
-      </c>
       <c r="S49">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T49">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U49">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA49">
         <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AC49">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="AD49">
+        <v>1.43</v>
+      </c>
+      <c r="AE49">
+        <v>1.13</v>
+      </c>
+      <c r="AF49">
+        <v>1.55</v>
+      </c>
+      <c r="AG49">
+        <v>2.25</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
         <v>1.33</v>
-      </c>
-      <c r="AE49">
-        <v>1.12</v>
-      </c>
-      <c r="AF49">
-        <v>1.64</v>
-      </c>
-      <c r="AG49">
-        <v>2.13</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.27</v>
       </c>
       <c r="AK49">
         <v>1.65</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="O50">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="P50">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="Q50">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="R50">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T50">
+        <v>2.7</v>
+      </c>
+      <c r="U50">
         <v>2.75</v>
       </c>
-      <c r="U50">
-        <v>2.96</v>
-      </c>
       <c r="V50">
+        <v>1.43</v>
+      </c>
+      <c r="W50">
+        <v>1.07</v>
+      </c>
+      <c r="X50">
+        <v>1.02</v>
+      </c>
+      <c r="Y50">
+        <v>1.22</v>
+      </c>
+      <c r="Z50">
+        <v>4.07</v>
+      </c>
+      <c r="AA50">
+        <v>2.03</v>
+      </c>
+      <c r="AB50">
+        <v>1.83</v>
+      </c>
+      <c r="AC50">
+        <v>2.74</v>
+      </c>
+      <c r="AD50">
+        <v>1.35</v>
+      </c>
+      <c r="AE50">
+        <v>1.13</v>
+      </c>
+      <c r="AF50">
+        <v>1.6</v>
+      </c>
+      <c r="AG50">
+        <v>2.19</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.4</v>
       </c>
-      <c r="W50">
-        <v>1.06</v>
-      </c>
-      <c r="X50">
-        <v>1.03</v>
-      </c>
-      <c r="Y50">
-        <v>1.3</v>
-      </c>
-      <c r="Z50">
-        <v>3.2</v>
-      </c>
-      <c r="AA50">
-        <v>1.94</v>
-      </c>
-      <c r="AB50">
-        <v>1.8</v>
-      </c>
-      <c r="AC50">
-        <v>3.28</v>
-      </c>
-      <c r="AD50">
-        <v>1.25</v>
-      </c>
-      <c r="AE50">
-        <v>1.05</v>
-      </c>
-      <c r="AF50">
-        <v>1.73</v>
-      </c>
-      <c r="AG50">
-        <v>1.95</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.41</v>
-      </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="O51">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P51">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="Q51">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="R51">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S51">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T51">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U51">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="V51">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
         <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC51">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG51">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
         <v>1.65</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,49 +8785,49 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.92</v>
+        <v>1.63</v>
       </c>
       <c r="O52">
-        <v>3.74</v>
+        <v>4.25</v>
       </c>
       <c r="P52">
-        <v>2.13</v>
+        <v>4.34</v>
       </c>
       <c r="Q52">
-        <v>3.26</v>
+        <v>2.2</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U52">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W52">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z52">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="AA52">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB52">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AC52">
         <v>2.7</v>
@@ -8836,13 +8836,13 @@
         <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG52">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.65</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.33</v>
+        <v>2.03</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="R90">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T90">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="U90">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="V90">
+        <v>1.4</v>
+      </c>
+      <c r="W90">
+        <v>1.06</v>
+      </c>
+      <c r="X90">
+        <v>1.03</v>
+      </c>
+      <c r="Y90">
         <v>1.3</v>
       </c>
-      <c r="W90">
-        <v>1.02</v>
-      </c>
-      <c r="X90">
-        <v>1.04</v>
-      </c>
-      <c r="Y90">
-        <v>1.36</v>
-      </c>
       <c r="Z90">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AA90">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB90">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC90">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD90">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE90">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG90">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK90">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q91">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="R91">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S91">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T91">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="U91">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="V91">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X91">
+        <v>1.04</v>
+      </c>
+      <c r="Y91">
+        <v>1.36</v>
+      </c>
+      <c r="Z91">
+        <v>2.7</v>
+      </c>
+      <c r="AA91">
+        <v>2.25</v>
+      </c>
+      <c r="AB91">
+        <v>1.57</v>
+      </c>
+      <c r="AC91">
+        <v>3.9</v>
+      </c>
+      <c r="AD91">
+        <v>1.17</v>
+      </c>
+      <c r="AE91">
         <v>1.03</v>
       </c>
-      <c r="Y91">
-        <v>1.3</v>
-      </c>
-      <c r="Z91">
-        <v>3.25</v>
-      </c>
-      <c r="AA91">
-        <v>2.1</v>
-      </c>
-      <c r="AB91">
-        <v>1.7</v>
-      </c>
-      <c r="AC91">
-        <v>3.6</v>
-      </c>
-      <c r="AD91">
-        <v>1.25</v>
-      </c>
-      <c r="AE91">
-        <v>1.06</v>
-      </c>
       <c r="AF91">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AG91">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK91">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="AL91">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P6">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="Q6">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R6">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S6">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="U6">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="V6">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
         <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB6">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC6">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
+        <v>1.3</v>
+      </c>
+      <c r="AE6">
+        <v>1.11</v>
+      </c>
+      <c r="AF6">
+        <v>1.73</v>
+      </c>
+      <c r="AG6">
+        <v>1.98</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.24</v>
+      </c>
+      <c r="AK6">
         <v>1.27</v>
-      </c>
-      <c r="AE6">
-        <v>1.07</v>
-      </c>
-      <c r="AF6">
-        <v>1.7</v>
-      </c>
-      <c r="AG6">
-        <v>2</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.28</v>
-      </c>
-      <c r="AK6">
-        <v>1.38</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="O7">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q7">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="R7">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T7">
-        <v>2.42</v>
+        <v>2.98</v>
       </c>
       <c r="U7">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="V7">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
+        <v>1.05</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>1.26</v>
+      </c>
+      <c r="Z7">
+        <v>3.43</v>
+      </c>
+      <c r="AA7">
+        <v>1.97</v>
+      </c>
+      <c r="AB7">
+        <v>1.79</v>
+      </c>
+      <c r="AC7">
+        <v>3.14</v>
+      </c>
+      <c r="AD7">
+        <v>1.27</v>
+      </c>
+      <c r="AE7">
         <v>1.07</v>
       </c>
-      <c r="X7">
-        <v>1.04</v>
-      </c>
-      <c r="Y7">
-        <v>1.35</v>
-      </c>
-      <c r="Z7">
-        <v>2.74</v>
-      </c>
-      <c r="AA7">
-        <v>2.19</v>
-      </c>
-      <c r="AB7">
-        <v>1.61</v>
-      </c>
-      <c r="AC7">
-        <v>3.74</v>
-      </c>
-      <c r="AD7">
-        <v>1.19</v>
-      </c>
-      <c r="AE7">
-        <v>1.03</v>
-      </c>
       <c r="AF7">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="O8">
-        <v>3.98</v>
+        <v>2.99</v>
       </c>
       <c r="P8">
-        <v>5.47</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>1.99</v>
+        <v>3.13</v>
       </c>
       <c r="R8">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="S8">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="T8">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="U8">
-        <v>2.57</v>
+        <v>3.22</v>
       </c>
       <c r="V8">
+        <v>1.35</v>
+      </c>
+      <c r="W8">
+        <v>1.07</v>
+      </c>
+      <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>1.35</v>
+      </c>
+      <c r="Z8">
+        <v>2.74</v>
+      </c>
+      <c r="AA8">
+        <v>2.19</v>
+      </c>
+      <c r="AB8">
+        <v>1.61</v>
+      </c>
+      <c r="AC8">
+        <v>3.74</v>
+      </c>
+      <c r="AD8">
+        <v>1.19</v>
+      </c>
+      <c r="AE8">
+        <v>1.03</v>
+      </c>
+      <c r="AF8">
+        <v>1.84</v>
+      </c>
+      <c r="AG8">
+        <v>1.82</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.29</v>
+      </c>
+      <c r="AK8">
         <v>1.48</v>
-      </c>
-      <c r="W8">
-        <v>1.11</v>
-      </c>
-      <c r="X8">
-        <v>1.03</v>
-      </c>
-      <c r="Y8">
-        <v>1.18</v>
-      </c>
-      <c r="Z8">
-        <v>4.01</v>
-      </c>
-      <c r="AA8">
-        <v>1.82</v>
-      </c>
-      <c r="AB8">
-        <v>1.94</v>
-      </c>
-      <c r="AC8">
-        <v>2.66</v>
-      </c>
-      <c r="AD8">
-        <v>1.41</v>
-      </c>
-      <c r="AE8">
-        <v>1.11</v>
-      </c>
-      <c r="AF8">
-        <v>1.71</v>
-      </c>
-      <c r="AG8">
-        <v>2</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.2</v>
-      </c>
-      <c r="AK8">
-        <v>2.21</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.14</v>
+        <v>1.49</v>
       </c>
       <c r="O9">
-        <v>3.24</v>
+        <v>3.98</v>
       </c>
       <c r="P9">
-        <v>2.09</v>
+        <v>5.47</v>
       </c>
       <c r="Q9">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="R9">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T9">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U9">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>3.2</v>
+        <v>4.01</v>
       </c>
       <c r="AA9">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AB9">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC9">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD9">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE9">
         <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG9">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.27</v>
+        <v>2.21</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P10">
-        <v>2.47</v>
+        <v>4.87</v>
       </c>
       <c r="Q10">
-        <v>3.22</v>
+        <v>2.23</v>
       </c>
       <c r="R10">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
+        <v>1.39</v>
+      </c>
+      <c r="T10">
+        <v>2.64</v>
+      </c>
+      <c r="U10">
+        <v>2.89</v>
+      </c>
+      <c r="V10">
+        <v>1.36</v>
+      </c>
+      <c r="W10">
+        <v>1.06</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1.28</v>
+      </c>
+      <c r="Z10">
+        <v>3.08</v>
+      </c>
+      <c r="AA10">
+        <v>2.02</v>
+      </c>
+      <c r="AB10">
+        <v>1.77</v>
+      </c>
+      <c r="AC10">
+        <v>3.48</v>
+      </c>
+      <c r="AD10">
+        <v>1.22</v>
+      </c>
+      <c r="AE10">
+        <v>1.04</v>
+      </c>
+      <c r="AF10">
+        <v>1.85</v>
+      </c>
+      <c r="AG10">
+        <v>1.75</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.3</v>
       </c>
-      <c r="T10">
-        <v>3.2</v>
-      </c>
-      <c r="U10">
-        <v>2.45</v>
-      </c>
-      <c r="V10">
-        <v>1.49</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.17</v>
-      </c>
-      <c r="Z10">
-        <v>4</v>
-      </c>
-      <c r="AA10">
-        <v>1.7</v>
-      </c>
-      <c r="AB10">
-        <v>2.1</v>
-      </c>
-      <c r="AC10">
-        <v>2.77</v>
-      </c>
-      <c r="AD10">
-        <v>1.37</v>
-      </c>
-      <c r="AE10">
-        <v>1.11</v>
-      </c>
-      <c r="AF10">
-        <v>1.55</v>
-      </c>
-      <c r="AG10">
-        <v>2.25</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.26</v>
-      </c>
       <c r="AK10">
-        <v>1.39</v>
+        <v>2.05</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="O11">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>4.87</v>
+        <v>2.47</v>
       </c>
       <c r="Q11">
-        <v>2.23</v>
+        <v>3.22</v>
       </c>
       <c r="R11">
+        <v>2.17</v>
+      </c>
+      <c r="S11">
+        <v>1.3</v>
+      </c>
+      <c r="T11">
+        <v>3.2</v>
+      </c>
+      <c r="U11">
+        <v>2.45</v>
+      </c>
+      <c r="V11">
+        <v>1.49</v>
+      </c>
+      <c r="W11">
+        <v>1.11</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
+        <v>1.17</v>
+      </c>
+      <c r="Z11">
+        <v>4</v>
+      </c>
+      <c r="AA11">
+        <v>1.7</v>
+      </c>
+      <c r="AB11">
         <v>2.1</v>
       </c>
-      <c r="S11">
+      <c r="AC11">
+        <v>2.77</v>
+      </c>
+      <c r="AD11">
+        <v>1.37</v>
+      </c>
+      <c r="AE11">
+        <v>1.11</v>
+      </c>
+      <c r="AF11">
+        <v>1.55</v>
+      </c>
+      <c r="AG11">
+        <v>2.25</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.26</v>
+      </c>
+      <c r="AK11">
         <v>1.39</v>
-      </c>
-      <c r="T11">
-        <v>2.64</v>
-      </c>
-      <c r="U11">
-        <v>2.89</v>
-      </c>
-      <c r="V11">
-        <v>1.36</v>
-      </c>
-      <c r="W11">
-        <v>1.06</v>
-      </c>
-      <c r="X11">
-        <v>1</v>
-      </c>
-      <c r="Y11">
-        <v>1.28</v>
-      </c>
-      <c r="Z11">
-        <v>3.08</v>
-      </c>
-      <c r="AA11">
-        <v>2.02</v>
-      </c>
-      <c r="AB11">
-        <v>1.77</v>
-      </c>
-      <c r="AC11">
-        <v>3.48</v>
-      </c>
-      <c r="AD11">
-        <v>1.22</v>
-      </c>
-      <c r="AE11">
-        <v>1.04</v>
-      </c>
-      <c r="AF11">
-        <v>1.85</v>
-      </c>
-      <c r="AG11">
-        <v>1.75</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.3</v>
-      </c>
-      <c r="AK11">
-        <v>2.05</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.92</v>
+        <v>2.09</v>
       </c>
       <c r="O48">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="P48">
-        <v>2.13</v>
+        <v>3.15</v>
       </c>
       <c r="Q48">
-        <v>3.26</v>
+        <v>2.75</v>
       </c>
       <c r="R48">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T48">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U48">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="V48">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W48">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA48">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AC48">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="AD48">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE48">
         <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
+        <v>1.33</v>
+      </c>
+      <c r="AK48">
         <v>1.65</v>
-      </c>
-      <c r="AK48">
-        <v>1.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.09</v>
+        <v>2.83</v>
       </c>
       <c r="O49">
-        <v>3.54</v>
+        <v>2.91</v>
       </c>
       <c r="P49">
-        <v>3.15</v>
+        <v>2.57</v>
       </c>
       <c r="Q49">
+        <v>3.24</v>
+      </c>
+      <c r="R49">
+        <v>2.25</v>
+      </c>
+      <c r="S49">
+        <v>1.37</v>
+      </c>
+      <c r="T49">
+        <v>2.7</v>
+      </c>
+      <c r="U49">
         <v>2.75</v>
       </c>
-      <c r="R49">
-        <v>2.19</v>
-      </c>
-      <c r="S49">
-        <v>1.26</v>
-      </c>
-      <c r="T49">
-        <v>3.4</v>
-      </c>
-      <c r="U49">
-        <v>2.32</v>
-      </c>
       <c r="V49">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>4.33</v>
+        <v>4.07</v>
       </c>
       <c r="AA49">
+        <v>2.03</v>
+      </c>
+      <c r="AB49">
         <v>1.83</v>
       </c>
-      <c r="AB49">
-        <v>2.03</v>
-      </c>
       <c r="AC49">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="AD49">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE49">
         <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK49">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="O50">
-        <v>2.91</v>
+        <v>3.62</v>
       </c>
       <c r="P50">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="Q50">
-        <v>3.24</v>
+        <v>2.43</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S50">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T50">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="U50">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="V50">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
         <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
         <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>4.07</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AB50">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC50">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD50">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE50">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG50">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK50">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,34 +8622,34 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.19</v>
+        <v>2.92</v>
       </c>
       <c r="O51">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="P51">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="Q51">
-        <v>2.43</v>
+        <v>3.26</v>
       </c>
       <c r="R51">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X51">
         <v>1.01</v>
@@ -8658,44 +8658,44 @@
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA51">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AB51">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD51">
+        <v>1.36</v>
+      </c>
+      <c r="AE51">
+        <v>1.13</v>
+      </c>
+      <c r="AF51">
+        <v>1.58</v>
+      </c>
+      <c r="AG51">
+        <v>2.3</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.65</v>
+      </c>
+      <c r="AK51">
         <v>1.33</v>
-      </c>
-      <c r="AE51">
-        <v>1.12</v>
-      </c>
-      <c r="AF51">
-        <v>1.64</v>
-      </c>
-      <c r="AG51">
-        <v>2.13</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.27</v>
-      </c>
-      <c r="AK51">
-        <v>1.65</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q90">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S90">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T90">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="U90">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="V90">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W90">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X90">
+        <v>1.04</v>
+      </c>
+      <c r="Y90">
+        <v>1.36</v>
+      </c>
+      <c r="Z90">
+        <v>2.7</v>
+      </c>
+      <c r="AA90">
+        <v>2.25</v>
+      </c>
+      <c r="AB90">
+        <v>1.57</v>
+      </c>
+      <c r="AC90">
+        <v>3.9</v>
+      </c>
+      <c r="AD90">
+        <v>1.17</v>
+      </c>
+      <c r="AE90">
         <v>1.03</v>
       </c>
-      <c r="Y90">
-        <v>1.3</v>
-      </c>
-      <c r="Z90">
-        <v>3.25</v>
-      </c>
-      <c r="AA90">
-        <v>2.1</v>
-      </c>
-      <c r="AB90">
-        <v>1.7</v>
-      </c>
-      <c r="AC90">
-        <v>3.6</v>
-      </c>
-      <c r="AD90">
-        <v>1.25</v>
-      </c>
-      <c r="AE90">
-        <v>1.06</v>
-      </c>
       <c r="AF90">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AG90">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK90">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="R91">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T91">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="U91">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="V91">
+        <v>1.4</v>
+      </c>
+      <c r="W91">
+        <v>1.06</v>
+      </c>
+      <c r="X91">
+        <v>1.03</v>
+      </c>
+      <c r="Y91">
         <v>1.3</v>
       </c>
-      <c r="W91">
-        <v>1.02</v>
-      </c>
-      <c r="X91">
-        <v>1.04</v>
-      </c>
-      <c r="Y91">
-        <v>1.36</v>
-      </c>
       <c r="Z91">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB91">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC91">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD91">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE91">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG91">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK91">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AL91">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.14</v>
+        <v>1.49</v>
       </c>
       <c r="O6">
-        <v>3.24</v>
+        <v>3.98</v>
       </c>
       <c r="P6">
-        <v>2.09</v>
+        <v>5.47</v>
       </c>
       <c r="Q6">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T6">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>3.2</v>
+        <v>4.01</v>
       </c>
       <c r="AA6">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AB6">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC6">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE6">
         <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG6">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>1.27</v>
+        <v>2.21</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P7">
-        <v>2.32</v>
+        <v>4.87</v>
       </c>
       <c r="Q7">
-        <v>3.2</v>
+        <v>2.23</v>
       </c>
       <c r="R7">
         <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T7">
-        <v>2.98</v>
+        <v>2.64</v>
       </c>
       <c r="U7">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z7">
-        <v>3.43</v>
+        <v>3.08</v>
       </c>
       <c r="AA7">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AB7">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AC7">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="AD7">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="O8">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>2.47</v>
       </c>
       <c r="Q8">
-        <v>3.13</v>
+        <v>3.22</v>
       </c>
       <c r="R8">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="S8">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>3.22</v>
+        <v>2.45</v>
       </c>
       <c r="V8">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="Z8">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="AA8">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AB8">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AC8">
-        <v>3.74</v>
+        <v>2.77</v>
       </c>
       <c r="AD8">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AG8">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK8">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.49</v>
+        <v>3.14</v>
       </c>
       <c r="O9">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="P9">
-        <v>5.47</v>
+        <v>2.09</v>
       </c>
       <c r="Q9">
+        <v>3.5</v>
+      </c>
+      <c r="R9">
+        <v>2.08</v>
+      </c>
+      <c r="S9">
+        <v>1.33</v>
+      </c>
+      <c r="T9">
+        <v>2.95</v>
+      </c>
+      <c r="U9">
+        <v>2.65</v>
+      </c>
+      <c r="V9">
+        <v>1.38</v>
+      </c>
+      <c r="W9">
+        <v>1.06</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1.26</v>
+      </c>
+      <c r="Z9">
+        <v>3.2</v>
+      </c>
+      <c r="AA9">
         <v>1.99</v>
       </c>
-      <c r="R9">
-        <v>2.28</v>
-      </c>
-      <c r="S9">
-        <v>1.32</v>
-      </c>
-      <c r="T9">
+      <c r="AB9">
+        <v>1.78</v>
+      </c>
+      <c r="AC9">
         <v>3.2</v>
       </c>
-      <c r="U9">
-        <v>2.57</v>
-      </c>
-      <c r="V9">
-        <v>1.48</v>
-      </c>
-      <c r="W9">
-        <v>1.11</v>
-      </c>
-      <c r="X9">
-        <v>1.03</v>
-      </c>
-      <c r="Y9">
-        <v>1.18</v>
-      </c>
-      <c r="Z9">
-        <v>4.01</v>
-      </c>
-      <c r="AA9">
-        <v>1.82</v>
-      </c>
-      <c r="AB9">
-        <v>1.94</v>
-      </c>
-      <c r="AC9">
-        <v>2.66</v>
-      </c>
       <c r="AD9">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE9">
         <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.63</v>
+        <v>2.23</v>
       </c>
       <c r="O10">
-        <v>3.48</v>
+        <v>2.99</v>
       </c>
       <c r="P10">
-        <v>4.87</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
-        <v>2.23</v>
+        <v>3.13</v>
       </c>
       <c r="R10">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S10">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="T10">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="U10">
-        <v>2.89</v>
+        <v>3.22</v>
       </c>
       <c r="V10">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z10">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="AA10">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="AB10">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AC10">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="AD10">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG10">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="Q11">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="R11">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="V11">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z11">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="AA11">
+        <v>1.97</v>
+      </c>
+      <c r="AB11">
+        <v>1.79</v>
+      </c>
+      <c r="AC11">
+        <v>3.14</v>
+      </c>
+      <c r="AD11">
+        <v>1.27</v>
+      </c>
+      <c r="AE11">
+        <v>1.07</v>
+      </c>
+      <c r="AF11">
         <v>1.7</v>
       </c>
-      <c r="AB11">
-        <v>2.1</v>
-      </c>
-      <c r="AC11">
-        <v>2.77</v>
-      </c>
-      <c r="AD11">
-        <v>1.37</v>
-      </c>
-      <c r="AE11">
-        <v>1.11</v>
-      </c>
-      <c r="AF11">
-        <v>1.55</v>
-      </c>
       <c r="AG11">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK11">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.73</v>
+        <v>2.19</v>
       </c>
       <c r="O46">
-        <v>3.02</v>
+        <v>3.62</v>
       </c>
       <c r="P46">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="Q46">
-        <v>3.18</v>
+        <v>2.43</v>
       </c>
       <c r="R46">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="S46">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T46">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="U46">
-        <v>2.96</v>
+        <v>2.47</v>
       </c>
       <c r="V46">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA46">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB46">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC46">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD46">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE46">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF46">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG46">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AK46">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="O47">
-        <v>3.68</v>
+        <v>4.25</v>
       </c>
       <c r="P47">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="Q47">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="R47">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T47">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U47">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="V47">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z47">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AA47">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AB47">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AC47">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="AD47">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE47">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
         <v>1.67</v>
       </c>
       <c r="AG47">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK47">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.19</v>
+        <v>2.73</v>
       </c>
       <c r="O50">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="P50">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="Q50">
-        <v>2.43</v>
+        <v>3.18</v>
       </c>
       <c r="R50">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S50">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T50">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U50">
-        <v>2.47</v>
+        <v>2.96</v>
       </c>
       <c r="V50">
+        <v>1.4</v>
+      </c>
+      <c r="W50">
+        <v>1.06</v>
+      </c>
+      <c r="X50">
+        <v>1.03</v>
+      </c>
+      <c r="Y50">
+        <v>1.3</v>
+      </c>
+      <c r="Z50">
+        <v>3.2</v>
+      </c>
+      <c r="AA50">
+        <v>1.94</v>
+      </c>
+      <c r="AB50">
+        <v>1.8</v>
+      </c>
+      <c r="AC50">
+        <v>3.28</v>
+      </c>
+      <c r="AD50">
+        <v>1.25</v>
+      </c>
+      <c r="AE50">
+        <v>1.05</v>
+      </c>
+      <c r="AF50">
+        <v>1.73</v>
+      </c>
+      <c r="AG50">
+        <v>1.95</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.41</v>
+      </c>
+      <c r="AK50">
         <v>1.44</v>
-      </c>
-      <c r="W50">
-        <v>1.07</v>
-      </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.22</v>
-      </c>
-      <c r="Z50">
-        <v>3.5</v>
-      </c>
-      <c r="AA50">
-        <v>1.83</v>
-      </c>
-      <c r="AB50">
-        <v>1.93</v>
-      </c>
-      <c r="AC50">
-        <v>2.83</v>
-      </c>
-      <c r="AD50">
-        <v>1.33</v>
-      </c>
-      <c r="AE50">
-        <v>1.12</v>
-      </c>
-      <c r="AF50">
-        <v>1.64</v>
-      </c>
-      <c r="AG50">
-        <v>2.13</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.27</v>
-      </c>
-      <c r="AK50">
-        <v>1.65</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.92</v>
+        <v>1.74</v>
       </c>
       <c r="O51">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="P51">
+        <v>4.3</v>
+      </c>
+      <c r="Q51">
+        <v>2.28</v>
+      </c>
+      <c r="R51">
         <v>2.13</v>
-      </c>
-      <c r="Q51">
-        <v>3.26</v>
-      </c>
-      <c r="R51">
-        <v>2.2</v>
       </c>
       <c r="S51">
         <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="AB51">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="AC51">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG51">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,49 +8785,49 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.63</v>
+        <v>2.92</v>
       </c>
       <c r="O52">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="P52">
-        <v>4.34</v>
+        <v>2.13</v>
       </c>
       <c r="Q52">
+        <v>3.26</v>
+      </c>
+      <c r="R52">
         <v>2.2</v>
       </c>
-      <c r="R52">
-        <v>2.22</v>
-      </c>
       <c r="S52">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="V52">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB52">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AC52">
         <v>2.7</v>
@@ -8836,13 +8836,13 @@
         <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG52">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="AK52">
-        <v>2.03</v>
+        <v>1.33</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AL130">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="P8">
-        <v>2.47</v>
+        <v>2.09</v>
       </c>
       <c r="Q8">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="S8">
+        <v>1.33</v>
+      </c>
+      <c r="T8">
+        <v>2.95</v>
+      </c>
+      <c r="U8">
+        <v>2.65</v>
+      </c>
+      <c r="V8">
+        <v>1.38</v>
+      </c>
+      <c r="W8">
+        <v>1.06</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1.26</v>
+      </c>
+      <c r="Z8">
+        <v>3.2</v>
+      </c>
+      <c r="AA8">
+        <v>1.99</v>
+      </c>
+      <c r="AB8">
+        <v>1.78</v>
+      </c>
+      <c r="AC8">
+        <v>3.2</v>
+      </c>
+      <c r="AD8">
         <v>1.3</v>
-      </c>
-      <c r="T8">
-        <v>3.2</v>
-      </c>
-      <c r="U8">
-        <v>2.45</v>
-      </c>
-      <c r="V8">
-        <v>1.49</v>
-      </c>
-      <c r="W8">
-        <v>1.11</v>
-      </c>
-      <c r="X8">
-        <v>1.03</v>
-      </c>
-      <c r="Y8">
-        <v>1.17</v>
-      </c>
-      <c r="Z8">
-        <v>4</v>
-      </c>
-      <c r="AA8">
-        <v>1.7</v>
-      </c>
-      <c r="AB8">
-        <v>2.1</v>
-      </c>
-      <c r="AC8">
-        <v>2.77</v>
-      </c>
-      <c r="AD8">
-        <v>1.37</v>
       </c>
       <c r="AE8">
         <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.14</v>
+        <v>2.23</v>
       </c>
       <c r="O9">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="P9">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="R9">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T9">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="U9">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z9">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA9">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="AB9">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AC9">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD9">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG9">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="O10">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>3.1</v>
+        <v>2.47</v>
       </c>
       <c r="Q10">
-        <v>3.13</v>
+        <v>3.22</v>
       </c>
       <c r="R10">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="S10">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>3.22</v>
+        <v>2.45</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="Z10">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="AA10">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AB10">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AC10">
-        <v>3.74</v>
+        <v>2.77</v>
       </c>
       <c r="AD10">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AE10">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AG10">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.81</v>
+        <v>3.22</v>
       </c>
       <c r="O14">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P14">
+        <v>1.97</v>
+      </c>
+      <c r="Q14">
         <v>3.88</v>
       </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.22</v>
+        <v>1.81</v>
       </c>
       <c r="O15">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="P15">
-        <v>1.97</v>
+        <v>3.88</v>
       </c>
       <c r="Q15">
-        <v>3.88</v>
+        <v>2.42</v>
       </c>
       <c r="R15">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="S15">
+        <v>1.34</v>
+      </c>
+      <c r="T15">
+        <v>2.81</v>
+      </c>
+      <c r="U15">
+        <v>2.69</v>
+      </c>
+      <c r="V15">
+        <v>1.37</v>
+      </c>
+      <c r="W15">
+        <v>1.05</v>
+      </c>
+      <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
         <v>1.27</v>
       </c>
-      <c r="T15">
-        <v>3.18</v>
-      </c>
-      <c r="U15">
-        <v>2.34</v>
-      </c>
-      <c r="V15">
-        <v>1.48</v>
-      </c>
-      <c r="W15">
-        <v>1.09</v>
-      </c>
-      <c r="X15">
-        <v>1.01</v>
-      </c>
-      <c r="Y15">
-        <v>1.18</v>
-      </c>
       <c r="Z15">
-        <v>3.86</v>
+        <v>3.14</v>
       </c>
       <c r="AA15">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AB15">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="AD15">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE15">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3436,7 +3436,7 @@
         <v>1.13</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>1.14</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC23">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.27</v>
+        <v>1.64</v>
       </c>
       <c r="O26">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>2.86</v>
+        <v>5.2</v>
       </c>
       <c r="Q26">
-        <v>2.91</v>
+        <v>2.14</v>
       </c>
       <c r="R26">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="S26">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="U26">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA26">
         <v>2</v>
       </c>
       <c r="AB26">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC26">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD26">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE26">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="AG26">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK26">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.64</v>
+        <v>2.27</v>
       </c>
       <c r="O27">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="P27">
-        <v>5.2</v>
+        <v>2.86</v>
       </c>
       <c r="Q27">
-        <v>2.14</v>
+        <v>2.91</v>
       </c>
       <c r="R27">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="S27">
+        <v>1.4</v>
+      </c>
+      <c r="T27">
+        <v>2.75</v>
+      </c>
+      <c r="U27">
+        <v>2.73</v>
+      </c>
+      <c r="V27">
         <v>1.36</v>
       </c>
-      <c r="T27">
-        <v>2.64</v>
-      </c>
-      <c r="U27">
-        <v>2.8</v>
-      </c>
-      <c r="V27">
-        <v>1.34</v>
-      </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA27">
         <v>2</v>
       </c>
       <c r="AB27">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC27">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD27">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6044,7 +6044,7 @@
         <v>1.14</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
         <v>1.13</v>
@@ -6186,55 +6186,55 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q37">
         <v>1.55</v>
@@ -6370,7 +6370,7 @@
         <v>1.17</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
         <v>1.11</v>
@@ -6391,13 +6391,13 @@
         <v>1.6</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="O39">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>4.49</v>
+        <v>3.94</v>
       </c>
       <c r="Q39">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="R39">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="U39">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="V39">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
         <v>1.13</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z39">
-        <v>4.55</v>
+        <v>3.9</v>
       </c>
       <c r="AA39">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AB39">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="AC39">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AD39">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE39">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK39">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="O40">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="P40">
-        <v>3.94</v>
+        <v>4.79</v>
       </c>
       <c r="Q40">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="R40">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="U40">
         <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W40">
         <v>1.13</v>
@@ -6862,31 +6862,31 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z40">
-        <v>3.9</v>
+        <v>4.18</v>
       </c>
       <c r="AA40">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB40">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC40">
         <v>2.56</v>
       </c>
       <c r="AD40">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
         <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK40">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O42">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="P42">
-        <v>4.79</v>
+        <v>4.49</v>
       </c>
       <c r="Q42">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R42">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="T42">
-        <v>3.16</v>
+        <v>3.46</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="V42">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
         <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>4.18</v>
+        <v>4.55</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AB42">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AC42">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AD42">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF42">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AG42">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK42">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="O47">
-        <v>4.25</v>
+        <v>3.68</v>
       </c>
       <c r="P47">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="Q47">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R47">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="S47">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U47">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V47">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y47">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AA47">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AB47">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="AC47">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="AD47">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF47">
         <v>1.67</v>
       </c>
       <c r="AG47">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.83</v>
+        <v>1.63</v>
       </c>
       <c r="O49">
-        <v>2.91</v>
+        <v>4.25</v>
       </c>
       <c r="P49">
-        <v>2.57</v>
+        <v>4.34</v>
       </c>
       <c r="Q49">
-        <v>3.24</v>
+        <v>2.2</v>
       </c>
       <c r="R49">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S49">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="T49">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="V49">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X49">
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z49">
-        <v>4.07</v>
+        <v>3.82</v>
       </c>
       <c r="AA49">
+        <v>1.65</v>
+      </c>
+      <c r="AB49">
+        <v>2.06</v>
+      </c>
+      <c r="AC49">
+        <v>2.7</v>
+      </c>
+      <c r="AD49">
+        <v>1.36</v>
+      </c>
+      <c r="AE49">
+        <v>1.11</v>
+      </c>
+      <c r="AF49">
+        <v>1.67</v>
+      </c>
+      <c r="AG49">
+        <v>2.1</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.19</v>
+      </c>
+      <c r="AK49">
         <v>2.03</v>
-      </c>
-      <c r="AB49">
-        <v>1.83</v>
-      </c>
-      <c r="AC49">
-        <v>2.74</v>
-      </c>
-      <c r="AD49">
-        <v>1.35</v>
-      </c>
-      <c r="AE49">
-        <v>1.13</v>
-      </c>
-      <c r="AF49">
-        <v>1.6</v>
-      </c>
-      <c r="AG49">
-        <v>2.19</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.4</v>
-      </c>
-      <c r="AK49">
-        <v>1.43</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.74</v>
+        <v>2.83</v>
       </c>
       <c r="O51">
-        <v>3.68</v>
+        <v>2.91</v>
       </c>
       <c r="P51">
-        <v>4.3</v>
+        <v>2.57</v>
       </c>
       <c r="Q51">
-        <v>2.28</v>
+        <v>3.24</v>
       </c>
       <c r="R51">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W51">
         <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>4.07</v>
       </c>
       <c r="AA51">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AB51">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC51">
-        <v>3.01</v>
+        <v>2.74</v>
       </c>
       <c r="AD51">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF51">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AK51">
-        <v>1.91</v>
+        <v>1.43</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8978,7 +8978,7 @@
         <v>1.16</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
         <v>1.11</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P79">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="Q79">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="R79">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S79">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T79">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="U79">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V79">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W79">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z79">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA79">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB79">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC79">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD79">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE79">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF79">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG79">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK79">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -14662,34 +14662,34 @@
         <v>3.14</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA88">
         <v>1.75</v>
@@ -14698,19 +14698,19 @@
         <v>2.05</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="O104">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="P104">
-        <v>5.26</v>
+        <v>4</v>
       </c>
       <c r="Q104">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="R104">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="S104">
+        <v>1.15</v>
+      </c>
+      <c r="T104">
+        <v>5</v>
+      </c>
+      <c r="U104">
+        <v>1.73</v>
+      </c>
+      <c r="V104">
+        <v>2</v>
+      </c>
+      <c r="W104">
+        <v>1.29</v>
+      </c>
+      <c r="X104">
+        <v>1</v>
+      </c>
+      <c r="Y104">
+        <v>1.02</v>
+      </c>
+      <c r="Z104">
+        <v>7.8</v>
+      </c>
+      <c r="AA104">
         <v>1.2</v>
       </c>
-      <c r="T104">
-        <v>4.8</v>
-      </c>
-      <c r="U104">
-        <v>1.99</v>
-      </c>
-      <c r="V104">
-        <v>1.85</v>
-      </c>
-      <c r="W104">
-        <v>1.2</v>
-      </c>
-      <c r="X104">
-        <v>1.01</v>
-      </c>
-      <c r="Y104">
-        <v>1.06</v>
-      </c>
-      <c r="Z104">
-        <v>6.15</v>
-      </c>
-      <c r="AA104">
-        <v>1.32</v>
-      </c>
       <c r="AB104">
-        <v>3.1</v>
+        <v>3.83</v>
       </c>
       <c r="AC104">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AD104">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="AE104">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AF104">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG104">
-        <v>2.5</v>
+        <v>3.42</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK104">
-        <v>2.42</v>
+        <v>2.07</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,80 +17587,80 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="O106">
-        <v>3.78</v>
+        <v>4.6</v>
       </c>
       <c r="P106">
-        <v>3.07</v>
+        <v>5.26</v>
       </c>
       <c r="Q106">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="R106">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="S106">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T106">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="U106">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="V106">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="W106">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
+        <v>1.06</v>
+      </c>
+      <c r="Z106">
+        <v>6.15</v>
+      </c>
+      <c r="AA106">
+        <v>1.32</v>
+      </c>
+      <c r="AB106">
+        <v>3.1</v>
+      </c>
+      <c r="AC106">
+        <v>1.91</v>
+      </c>
+      <c r="AD106">
+        <v>1.82</v>
+      </c>
+      <c r="AE106">
+        <v>1.31</v>
+      </c>
+      <c r="AF106">
+        <v>1.44</v>
+      </c>
+      <c r="AG106">
+        <v>2.5</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ106">
         <v>1.12</v>
       </c>
-      <c r="Z106">
-        <v>4.7</v>
-      </c>
-      <c r="AA106">
-        <v>1.57</v>
-      </c>
-      <c r="AB106">
-        <v>2.35</v>
-      </c>
-      <c r="AC106">
-        <v>2.33</v>
-      </c>
-      <c r="AD106">
-        <v>1.48</v>
-      </c>
-      <c r="AE106">
-        <v>1.16</v>
-      </c>
-      <c r="AF106">
-        <v>1.5</v>
-      </c>
-      <c r="AG106">
-        <v>2.38</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ106">
-        <v>1.22</v>
-      </c>
       <c r="AK106">
-        <v>1.81</v>
+        <v>2.42</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="O107">
-        <v>4.45</v>
+        <v>3.78</v>
       </c>
       <c r="P107">
-        <v>4</v>
+        <v>3.07</v>
       </c>
       <c r="Q107">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="R107">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="S107">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="T107">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="U107">
-        <v>1.73</v>
+        <v>2.21</v>
       </c>
       <c r="V107">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="W107">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="X107">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="Z107">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="AA107">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AB107">
-        <v>3.83</v>
+        <v>2.35</v>
       </c>
       <c r="AC107">
-        <v>1.62</v>
+        <v>2.33</v>
       </c>
       <c r="AD107">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="AE107">
+        <v>1.16</v>
+      </c>
+      <c r="AF107">
         <v>1.5</v>
       </c>
-      <c r="AF107">
-        <v>1.3</v>
-      </c>
       <c r="AG107">
-        <v>3.42</v>
+        <v>2.38</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.22</v>
       </c>
       <c r="AK107">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="O136">
-        <v>3.54</v>
+        <v>3.16</v>
       </c>
       <c r="P136">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="Q136">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R136">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S136">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T136">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U136">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="V136">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W136">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X136">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y136">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z136">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="AA136">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB136">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC136">
-        <v>2.74</v>
+        <v>3.47</v>
       </c>
       <c r="AD136">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE136">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF136">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG136">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK136">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="O137">
-        <v>3.16</v>
+        <v>3.54</v>
       </c>
       <c r="P137">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="Q137">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R137">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S137">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T137">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U137">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="V137">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W137">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X137">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z137">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="AA137">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB137">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC137">
-        <v>3.47</v>
+        <v>2.74</v>
       </c>
       <c r="AD137">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE137">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF137">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG137">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK137">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="O155">
-        <v>3.38</v>
+        <v>3.02</v>
       </c>
       <c r="P155">
-        <v>2.96</v>
+        <v>2.27</v>
       </c>
       <c r="Q155">
-        <v>2.72</v>
+        <v>3.86</v>
       </c>
       <c r="R155">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S155">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="T155">
-        <v>3.28</v>
+        <v>2.58</v>
       </c>
       <c r="U155">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="V155">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W155">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X155">
+        <v>1.04</v>
+      </c>
+      <c r="Y155">
+        <v>1.36</v>
+      </c>
+      <c r="Z155">
+        <v>2.7</v>
+      </c>
+      <c r="AA155">
+        <v>2.15</v>
+      </c>
+      <c r="AB155">
+        <v>1.6</v>
+      </c>
+      <c r="AC155">
+        <v>3.86</v>
+      </c>
+      <c r="AD155">
+        <v>1.18</v>
+      </c>
+      <c r="AE155">
         <v>1.03</v>
       </c>
-      <c r="Y155">
-        <v>1.23</v>
-      </c>
-      <c r="Z155">
-        <v>3.78</v>
-      </c>
-      <c r="AA155">
-        <v>1.72</v>
-      </c>
-      <c r="AB155">
-        <v>1.98</v>
-      </c>
-      <c r="AC155">
-        <v>2.74</v>
-      </c>
-      <c r="AD155">
-        <v>1.35</v>
-      </c>
-      <c r="AE155">
-        <v>1.15</v>
-      </c>
       <c r="AF155">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AG155">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK155">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="O156">
-        <v>3.02</v>
+        <v>3.38</v>
       </c>
       <c r="P156">
-        <v>2.27</v>
+        <v>2.96</v>
       </c>
       <c r="Q156">
-        <v>3.86</v>
+        <v>2.72</v>
       </c>
       <c r="R156">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S156">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="T156">
-        <v>2.58</v>
+        <v>3.28</v>
       </c>
       <c r="U156">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="V156">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W156">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X156">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Z156">
-        <v>2.7</v>
+        <v>3.78</v>
       </c>
       <c r="AA156">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AB156">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AC156">
-        <v>3.86</v>
+        <v>2.74</v>
       </c>
       <c r="AD156">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AE156">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AF156">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AG156">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK156">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AL156">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="Q10">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="R10">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="U10">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="V10">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z10">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="AA10">
+        <v>1.97</v>
+      </c>
+      <c r="AB10">
+        <v>1.79</v>
+      </c>
+      <c r="AC10">
+        <v>3.14</v>
+      </c>
+      <c r="AD10">
+        <v>1.27</v>
+      </c>
+      <c r="AE10">
+        <v>1.07</v>
+      </c>
+      <c r="AF10">
         <v>1.7</v>
       </c>
-      <c r="AB10">
-        <v>2.1</v>
-      </c>
-      <c r="AC10">
-        <v>2.77</v>
-      </c>
-      <c r="AD10">
-        <v>1.37</v>
-      </c>
-      <c r="AE10">
-        <v>1.11</v>
-      </c>
-      <c r="AF10">
-        <v>1.55</v>
-      </c>
       <c r="AG10">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="Q11">
+        <v>3.22</v>
+      </c>
+      <c r="R11">
+        <v>2.17</v>
+      </c>
+      <c r="S11">
+        <v>1.3</v>
+      </c>
+      <c r="T11">
         <v>3.2</v>
       </c>
-      <c r="R11">
+      <c r="U11">
+        <v>2.45</v>
+      </c>
+      <c r="V11">
+        <v>1.49</v>
+      </c>
+      <c r="W11">
+        <v>1.11</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
+        <v>1.17</v>
+      </c>
+      <c r="Z11">
+        <v>4</v>
+      </c>
+      <c r="AA11">
+        <v>1.7</v>
+      </c>
+      <c r="AB11">
         <v>2.1</v>
       </c>
-      <c r="S11">
+      <c r="AC11">
+        <v>2.77</v>
+      </c>
+      <c r="AD11">
         <v>1.37</v>
       </c>
-      <c r="T11">
-        <v>2.98</v>
-      </c>
-      <c r="U11">
-        <v>2.86</v>
-      </c>
-      <c r="V11">
-        <v>1.37</v>
-      </c>
-      <c r="W11">
-        <v>1.05</v>
-      </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
-      <c r="Y11">
+      <c r="AE11">
+        <v>1.11</v>
+      </c>
+      <c r="AF11">
+        <v>1.55</v>
+      </c>
+      <c r="AG11">
+        <v>2.25</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
         <v>1.26</v>
       </c>
-      <c r="Z11">
-        <v>3.43</v>
-      </c>
-      <c r="AA11">
-        <v>1.97</v>
-      </c>
-      <c r="AB11">
-        <v>1.79</v>
-      </c>
-      <c r="AC11">
-        <v>3.14</v>
-      </c>
-      <c r="AD11">
-        <v>1.27</v>
-      </c>
-      <c r="AE11">
-        <v>1.07</v>
-      </c>
-      <c r="AF11">
-        <v>1.7</v>
-      </c>
-      <c r="AG11">
-        <v>2</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.28</v>
-      </c>
       <c r="AK11">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.64</v>
+        <v>2.27</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="P26">
-        <v>5.2</v>
+        <v>2.86</v>
       </c>
       <c r="Q26">
-        <v>2.14</v>
+        <v>2.91</v>
       </c>
       <c r="R26">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="S26">
+        <v>1.4</v>
+      </c>
+      <c r="T26">
+        <v>2.75</v>
+      </c>
+      <c r="U26">
+        <v>2.73</v>
+      </c>
+      <c r="V26">
         <v>1.36</v>
       </c>
-      <c r="T26">
-        <v>2.64</v>
-      </c>
-      <c r="U26">
-        <v>2.8</v>
-      </c>
-      <c r="V26">
-        <v>1.34</v>
-      </c>
       <c r="W26">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA26">
         <v>2</v>
       </c>
       <c r="AB26">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC26">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD26">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AG26">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.27</v>
+        <v>1.64</v>
       </c>
       <c r="O27">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>2.86</v>
+        <v>5.2</v>
       </c>
       <c r="Q27">
-        <v>2.91</v>
+        <v>2.14</v>
       </c>
       <c r="R27">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="S27">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="U27">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA27">
         <v>2</v>
       </c>
       <c r="AB27">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC27">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD27">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="AG27">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK27">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,77 +7807,77 @@
         </is>
       </c>
       <c r="N46">
+        <v>2.09</v>
+      </c>
+      <c r="O46">
+        <v>3.54</v>
+      </c>
+      <c r="P46">
+        <v>3.15</v>
+      </c>
+      <c r="Q46">
+        <v>2.75</v>
+      </c>
+      <c r="R46">
         <v>2.19</v>
       </c>
-      <c r="O46">
-        <v>3.62</v>
-      </c>
-      <c r="P46">
-        <v>2.88</v>
-      </c>
-      <c r="Q46">
-        <v>2.43</v>
-      </c>
-      <c r="R46">
-        <v>2.21</v>
-      </c>
       <c r="S46">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T46">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U46">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="V46">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W46">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA46">
         <v>1.83</v>
       </c>
       <c r="AB46">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AC46">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="AD46">
+        <v>1.43</v>
+      </c>
+      <c r="AE46">
+        <v>1.13</v>
+      </c>
+      <c r="AF46">
+        <v>1.55</v>
+      </c>
+      <c r="AG46">
+        <v>2.25</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.33</v>
-      </c>
-      <c r="AE46">
-        <v>1.12</v>
-      </c>
-      <c r="AF46">
-        <v>1.64</v>
-      </c>
-      <c r="AG46">
-        <v>2.13</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.27</v>
       </c>
       <c r="AK46">
         <v>1.65</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="O47">
-        <v>3.68</v>
+        <v>4.25</v>
       </c>
       <c r="P47">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="Q47">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="R47">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T47">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U47">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="V47">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z47">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AA47">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AB47">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AC47">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="AD47">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE47">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
         <v>1.67</v>
       </c>
       <c r="AG47">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK47">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.09</v>
+        <v>2.73</v>
       </c>
       <c r="O48">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
       <c r="P48">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="Q48">
+        <v>3.18</v>
+      </c>
+      <c r="R48">
+        <v>2.18</v>
+      </c>
+      <c r="S48">
+        <v>1.38</v>
+      </c>
+      <c r="T48">
         <v>2.75</v>
       </c>
-      <c r="R48">
-        <v>2.19</v>
-      </c>
-      <c r="S48">
-        <v>1.26</v>
-      </c>
-      <c r="T48">
-        <v>3.4</v>
-      </c>
       <c r="U48">
-        <v>2.32</v>
+        <v>2.96</v>
       </c>
       <c r="V48">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z48">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AA48">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AB48">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AC48">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="AD48">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AK48">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.63</v>
+        <v>2.83</v>
       </c>
       <c r="O49">
-        <v>4.25</v>
+        <v>2.91</v>
       </c>
       <c r="P49">
-        <v>4.34</v>
+        <v>2.57</v>
       </c>
       <c r="Q49">
-        <v>2.2</v>
+        <v>3.24</v>
       </c>
       <c r="R49">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="T49">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="U49">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="V49">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>3.82</v>
+        <v>4.07</v>
       </c>
       <c r="AA49">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AB49">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AC49">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD49">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE49">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AK49">
-        <v>2.03</v>
+        <v>1.43</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="O50">
-        <v>3.02</v>
+        <v>3.74</v>
       </c>
       <c r="P50">
-        <v>2.58</v>
+        <v>2.13</v>
       </c>
       <c r="Q50">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="R50">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.96</v>
+        <v>2.45</v>
       </c>
       <c r="V50">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA50">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="AB50">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC50">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="AD50">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG50">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.83</v>
+        <v>1.74</v>
       </c>
       <c r="O51">
-        <v>2.91</v>
+        <v>3.68</v>
       </c>
       <c r="P51">
-        <v>2.57</v>
+        <v>4.3</v>
       </c>
       <c r="Q51">
-        <v>3.24</v>
+        <v>2.28</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S51">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V51">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
         <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.07</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AB51">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC51">
-        <v>2.74</v>
+        <v>3.01</v>
       </c>
       <c r="AD51">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG51">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>1.43</v>
+        <v>1.91</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,34 +8785,34 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.92</v>
+        <v>2.19</v>
       </c>
       <c r="O52">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="P52">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="Q52">
-        <v>3.26</v>
+        <v>2.43</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U52">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
         <v>1.01</v>
@@ -8821,28 +8821,28 @@
         <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA52">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AB52">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AC52">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD52">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AG52">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
+        <v>1.27</v>
+      </c>
+      <c r="AK52">
         <v>1.65</v>
-      </c>
-      <c r="AK52">
-        <v>1.33</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,84 +9922,84 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="O59">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P59">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="Q59">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="R59">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="S59">
+        <v>1.33</v>
+      </c>
+      <c r="T59">
+        <v>2.96</v>
+      </c>
+      <c r="U59">
+        <v>2.64</v>
+      </c>
+      <c r="V59">
+        <v>1.41</v>
+      </c>
+      <c r="W59">
+        <v>1.06</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>1.23</v>
+      </c>
+      <c r="Z59">
+        <v>3.42</v>
+      </c>
+      <c r="AA59">
+        <v>1.88</v>
+      </c>
+      <c r="AB59">
+        <v>1.86</v>
+      </c>
+      <c r="AC59">
+        <v>3.08</v>
+      </c>
+      <c r="AD59">
+        <v>1.28</v>
+      </c>
+      <c r="AE59">
+        <v>1.06</v>
+      </c>
+      <c r="AF59">
+        <v>1.68</v>
+      </c>
+      <c r="AG59">
+        <v>2.03</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ59">
         <v>1.3</v>
       </c>
-      <c r="T59">
-        <v>3.08</v>
-      </c>
-      <c r="U59">
-        <v>2.4</v>
-      </c>
-      <c r="V59">
-        <v>1.5</v>
-      </c>
-      <c r="W59">
-        <v>1.08</v>
-      </c>
-      <c r="X59">
-        <v>1.01</v>
-      </c>
-      <c r="Y59">
-        <v>1.22</v>
-      </c>
-      <c r="Z59">
-        <v>4.05</v>
-      </c>
-      <c r="AA59">
-        <v>1.65</v>
-      </c>
-      <c r="AB59">
-        <v>2.1</v>
-      </c>
-      <c r="AC59">
-        <v>2.52</v>
-      </c>
-      <c r="AD59">
-        <v>1.41</v>
-      </c>
-      <c r="AE59">
-        <v>1.13</v>
-      </c>
-      <c r="AF59">
-        <v>1.57</v>
-      </c>
-      <c r="AG59">
-        <v>2.3</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ59">
-        <v>1.22</v>
-      </c>
       <c r="AK59">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G60">
@@ -10085,68 +10085,68 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N60">
-        <v>2.36</v>
+        <v>1.89</v>
       </c>
       <c r="O60">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P60">
-        <v>2.95</v>
+        <v>3.94</v>
       </c>
       <c r="Q60">
-        <v>2.94</v>
+        <v>2.39</v>
       </c>
       <c r="R60">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="S60">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T60">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="U60">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="V60">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W60">
         <v>1.06</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z60">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="AA60">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AB60">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AC60">
-        <v>3.08</v>
+        <v>3.44</v>
       </c>
       <c r="AD60">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE60">
         <v>1.06</v>
       </c>
       <c r="AF60">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AG60">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK60">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G61">
@@ -10248,84 +10248,84 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N61">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="O61">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="P61">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q61">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="R61">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="S61">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T61">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="U61">
-        <v>2.71</v>
+        <v>2.47</v>
       </c>
       <c r="V61">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W61">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z61">
-        <v>3.05</v>
+        <v>3.78</v>
       </c>
       <c r="AA61">
+        <v>1.72</v>
+      </c>
+      <c r="AB61">
+        <v>2.05</v>
+      </c>
+      <c r="AC61">
+        <v>2.62</v>
+      </c>
+      <c r="AD61">
+        <v>1.38</v>
+      </c>
+      <c r="AE61">
+        <v>1.12</v>
+      </c>
+      <c r="AF61">
+        <v>1.67</v>
+      </c>
+      <c r="AG61">
+        <v>2.05</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
+        <v>1.25</v>
+      </c>
+      <c r="AK61">
         <v>2.01</v>
-      </c>
-      <c r="AB61">
-        <v>1.79</v>
-      </c>
-      <c r="AC61">
-        <v>3.44</v>
-      </c>
-      <c r="AD61">
-        <v>1.26</v>
-      </c>
-      <c r="AE61">
-        <v>1.06</v>
-      </c>
-      <c r="AF61">
-        <v>1.82</v>
-      </c>
-      <c r="AG61">
-        <v>1.88</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>1.19</v>
-      </c>
-      <c r="AK61">
-        <v>1.91</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G62">
@@ -10411,68 +10411,68 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N62">
-        <v>1.76</v>
+        <v>2.58</v>
       </c>
       <c r="O62">
-        <v>3.9</v>
+        <v>3.48</v>
       </c>
       <c r="P62">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q62">
-        <v>2.26</v>
+        <v>2.75</v>
       </c>
       <c r="R62">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="S62">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U62">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V62">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W62">
         <v>1.08</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z62">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="AA62">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB62">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC62">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AD62">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE62">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF62">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>2.01</v>
+        <v>1.46</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,80 +17424,80 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.53</v>
+        <v>1.41</v>
       </c>
       <c r="O105">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="P105">
-        <v>2.55</v>
+        <v>5.26</v>
       </c>
       <c r="Q105">
-        <v>3.11</v>
+        <v>1.85</v>
       </c>
       <c r="R105">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="S105">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T105">
-        <v>3.26</v>
+        <v>4.8</v>
       </c>
       <c r="U105">
-        <v>2.32</v>
+        <v>1.99</v>
       </c>
       <c r="V105">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="W105">
+        <v>1.2</v>
+      </c>
+      <c r="X105">
+        <v>1.01</v>
+      </c>
+      <c r="Y105">
+        <v>1.06</v>
+      </c>
+      <c r="Z105">
+        <v>6.15</v>
+      </c>
+      <c r="AA105">
+        <v>1.32</v>
+      </c>
+      <c r="AB105">
+        <v>3.1</v>
+      </c>
+      <c r="AC105">
+        <v>1.91</v>
+      </c>
+      <c r="AD105">
+        <v>1.82</v>
+      </c>
+      <c r="AE105">
+        <v>1.31</v>
+      </c>
+      <c r="AF105">
+        <v>1.44</v>
+      </c>
+      <c r="AG105">
+        <v>2.5</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ105">
         <v>1.12</v>
       </c>
-      <c r="X105">
-        <v>1.02</v>
-      </c>
-      <c r="Y105">
-        <v>1.17</v>
-      </c>
-      <c r="Z105">
-        <v>4.05</v>
-      </c>
-      <c r="AA105">
-        <v>1.68</v>
-      </c>
-      <c r="AB105">
-        <v>2.11</v>
-      </c>
-      <c r="AC105">
-        <v>2.56</v>
-      </c>
-      <c r="AD105">
-        <v>1.45</v>
-      </c>
-      <c r="AE105">
-        <v>1.12</v>
-      </c>
-      <c r="AF105">
-        <v>1.53</v>
-      </c>
-      <c r="AG105">
-        <v>2.34</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ105">
-        <v>1.25</v>
-      </c>
       <c r="AK105">
-        <v>1.45</v>
+        <v>2.42</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.41</v>
+        <v>2.53</v>
       </c>
       <c r="O106">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P106">
-        <v>5.26</v>
+        <v>2.55</v>
       </c>
       <c r="Q106">
-        <v>1.85</v>
+        <v>3.11</v>
       </c>
       <c r="R106">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="S106">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T106">
-        <v>4.8</v>
+        <v>3.26</v>
       </c>
       <c r="U106">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="V106">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="W106">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="Z106">
-        <v>6.15</v>
+        <v>4.05</v>
       </c>
       <c r="AA106">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="AB106">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC106">
-        <v>1.91</v>
+        <v>2.56</v>
       </c>
       <c r="AD106">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="AE106">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AF106">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG106">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>2.42</v>
+        <v>1.45</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="O127">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="P127">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q127">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R127">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="S127">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="T127">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="U127">
-        <v>3.08</v>
+        <v>4.4</v>
       </c>
       <c r="V127">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="W127">
         <v>1.03</v>
       </c>
       <c r="X127">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y127">
-        <v>1.34</v>
+        <v>1.68</v>
       </c>
       <c r="Z127">
-        <v>2.78</v>
+        <v>2.02</v>
       </c>
       <c r="AA127">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
       <c r="AB127">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="AC127">
-        <v>3.88</v>
+        <v>7</v>
       </c>
       <c r="AD127">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AE127">
         <v>1.02</v>
       </c>
       <c r="AF127">
-        <v>1.85</v>
+        <v>2.44</v>
       </c>
       <c r="AG127">
-        <v>1.82</v>
+        <v>1.47</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AK127">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="O128">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="P128">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q128">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R128">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="S128">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="T128">
-        <v>2.04</v>
+        <v>2.41</v>
       </c>
       <c r="U128">
-        <v>4.4</v>
+        <v>3.08</v>
       </c>
       <c r="V128">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="W128">
         <v>1.03</v>
       </c>
       <c r="X128">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y128">
-        <v>1.68</v>
+        <v>1.34</v>
       </c>
       <c r="Z128">
-        <v>2.02</v>
+        <v>2.78</v>
       </c>
       <c r="AA128">
-        <v>3.14</v>
+        <v>2.3</v>
       </c>
       <c r="AB128">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="AC128">
-        <v>7</v>
+        <v>3.88</v>
       </c>
       <c r="AD128">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AE128">
         <v>1.02</v>
       </c>
       <c r="AF128">
-        <v>2.44</v>
+        <v>1.85</v>
       </c>
       <c r="AG128">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AK128">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="O135">
-        <v>3.72</v>
+        <v>3.16</v>
       </c>
       <c r="P135">
-        <v>3.86</v>
+        <v>3.24</v>
       </c>
       <c r="Q135">
+        <v>2.7</v>
+      </c>
+      <c r="R135">
         <v>2.1</v>
       </c>
-      <c r="R135">
-        <v>2.5</v>
-      </c>
       <c r="S135">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="T135">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="U135">
-        <v>2.13</v>
+        <v>2.73</v>
       </c>
       <c r="V135">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="W135">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y135">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="Z135">
-        <v>5.15</v>
+        <v>3.08</v>
       </c>
       <c r="AA135">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AB135">
-        <v>2.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC135">
-        <v>2.08</v>
+        <v>3.47</v>
       </c>
       <c r="AD135">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="AE135">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AF135">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="AG135">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AK135">
-        <v>1.99</v>
+        <v>1.56</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
+        <v>1.73</v>
+      </c>
+      <c r="O136">
+        <v>3.72</v>
+      </c>
+      <c r="P136">
+        <v>3.86</v>
+      </c>
+      <c r="Q136">
+        <v>2.1</v>
+      </c>
+      <c r="R136">
+        <v>2.5</v>
+      </c>
+      <c r="S136">
+        <v>1.2</v>
+      </c>
+      <c r="T136">
+        <v>4</v>
+      </c>
+      <c r="U136">
+        <v>2.13</v>
+      </c>
+      <c r="V136">
+        <v>1.68</v>
+      </c>
+      <c r="W136">
+        <v>1.15</v>
+      </c>
+      <c r="X136">
+        <v>1.02</v>
+      </c>
+      <c r="Y136">
+        <v>1.1</v>
+      </c>
+      <c r="Z136">
+        <v>5.15</v>
+      </c>
+      <c r="AA136">
+        <v>1.44</v>
+      </c>
+      <c r="AB136">
+        <v>2.66</v>
+      </c>
+      <c r="AC136">
         <v>2.08</v>
       </c>
-      <c r="O136">
-        <v>3.16</v>
-      </c>
-      <c r="P136">
-        <v>3.24</v>
-      </c>
-      <c r="Q136">
-        <v>2.7</v>
-      </c>
-      <c r="R136">
-        <v>2.1</v>
-      </c>
-      <c r="S136">
-        <v>1.36</v>
-      </c>
-      <c r="T136">
-        <v>2.88</v>
-      </c>
-      <c r="U136">
-        <v>2.73</v>
-      </c>
-      <c r="V136">
-        <v>1.36</v>
-      </c>
-      <c r="W136">
-        <v>1.08</v>
-      </c>
-      <c r="X136">
-        <v>1</v>
-      </c>
-      <c r="Y136">
-        <v>1.28</v>
-      </c>
-      <c r="Z136">
-        <v>3.08</v>
-      </c>
-      <c r="AA136">
-        <v>2.05</v>
-      </c>
-      <c r="AB136">
-        <v>1.75</v>
-      </c>
-      <c r="AC136">
-        <v>3.47</v>
-      </c>
       <c r="AD136">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AE136">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AF136">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AG136">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AK136">
-        <v>1.56</v>
+        <v>1.99</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>3.09</v>
+        <v>2.12</v>
       </c>
       <c r="O154">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P154">
-        <v>2.05</v>
+        <v>2.96</v>
       </c>
       <c r="Q154">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="R154">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S154">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T154">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U154">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="V154">
         <v>1.5</v>
       </c>
       <c r="W154">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X154">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z154">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="AA154">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB154">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AC154">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD154">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE154">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF154">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG154">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AK154">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="O155">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="P155">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="Q155">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="R155">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S155">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="T155">
-        <v>2.58</v>
+        <v>3.12</v>
       </c>
       <c r="U155">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V155">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W155">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X155">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y155">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="Z155">
+        <v>3.72</v>
+      </c>
+      <c r="AA155">
+        <v>1.7</v>
+      </c>
+      <c r="AB155">
+        <v>2.07</v>
+      </c>
+      <c r="AC155">
         <v>2.7</v>
       </c>
-      <c r="AA155">
-        <v>2.15</v>
-      </c>
-      <c r="AB155">
+      <c r="AD155">
+        <v>1.4</v>
+      </c>
+      <c r="AE155">
+        <v>1.11</v>
+      </c>
+      <c r="AF155">
         <v>1.6</v>
       </c>
-      <c r="AC155">
-        <v>3.86</v>
-      </c>
-      <c r="AD155">
-        <v>1.18</v>
-      </c>
-      <c r="AE155">
-        <v>1.03</v>
-      </c>
-      <c r="AF155">
-        <v>1.85</v>
-      </c>
       <c r="AG155">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AK155">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="O156">
-        <v>3.38</v>
+        <v>3.02</v>
       </c>
       <c r="P156">
-        <v>2.96</v>
+        <v>2.27</v>
       </c>
       <c r="Q156">
-        <v>2.72</v>
+        <v>3.86</v>
       </c>
       <c r="R156">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S156">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="T156">
-        <v>3.28</v>
+        <v>2.58</v>
       </c>
       <c r="U156">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="V156">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W156">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
+        <v>1.04</v>
+      </c>
+      <c r="Y156">
+        <v>1.36</v>
+      </c>
+      <c r="Z156">
+        <v>2.7</v>
+      </c>
+      <c r="AA156">
+        <v>2.15</v>
+      </c>
+      <c r="AB156">
+        <v>1.6</v>
+      </c>
+      <c r="AC156">
+        <v>3.86</v>
+      </c>
+      <c r="AD156">
+        <v>1.18</v>
+      </c>
+      <c r="AE156">
         <v>1.03</v>
       </c>
-      <c r="Y156">
-        <v>1.23</v>
-      </c>
-      <c r="Z156">
-        <v>3.78</v>
-      </c>
-      <c r="AA156">
-        <v>1.72</v>
-      </c>
-      <c r="AB156">
-        <v>1.98</v>
-      </c>
-      <c r="AC156">
-        <v>2.74</v>
-      </c>
-      <c r="AD156">
-        <v>1.35</v>
-      </c>
-      <c r="AE156">
-        <v>1.15</v>
-      </c>
       <c r="AF156">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AG156">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK156">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AL156">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="O8">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="Q8">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T8">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="U8">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
         <v>1.26</v>
       </c>
       <c r="Z8">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="AA8">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AB8">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC8">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD8">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE8">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,65 +1776,65 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.23</v>
+        <v>3.14</v>
       </c>
       <c r="O9">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q9">
-        <v>3.13</v>
+        <v>3.5</v>
       </c>
       <c r="R9">
+        <v>2.08</v>
+      </c>
+      <c r="S9">
+        <v>1.33</v>
+      </c>
+      <c r="T9">
+        <v>2.95</v>
+      </c>
+      <c r="U9">
+        <v>2.65</v>
+      </c>
+      <c r="V9">
+        <v>1.38</v>
+      </c>
+      <c r="W9">
+        <v>1.06</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1.26</v>
+      </c>
+      <c r="Z9">
+        <v>3.2</v>
+      </c>
+      <c r="AA9">
+        <v>1.99</v>
+      </c>
+      <c r="AB9">
+        <v>1.78</v>
+      </c>
+      <c r="AC9">
+        <v>3.2</v>
+      </c>
+      <c r="AD9">
+        <v>1.3</v>
+      </c>
+      <c r="AE9">
+        <v>1.11</v>
+      </c>
+      <c r="AF9">
+        <v>1.73</v>
+      </c>
+      <c r="AG9">
         <v>1.98</v>
       </c>
-      <c r="S9">
-        <v>1.45</v>
-      </c>
-      <c r="T9">
-        <v>2.42</v>
-      </c>
-      <c r="U9">
-        <v>3.22</v>
-      </c>
-      <c r="V9">
-        <v>1.35</v>
-      </c>
-      <c r="W9">
-        <v>1.07</v>
-      </c>
-      <c r="X9">
-        <v>1.04</v>
-      </c>
-      <c r="Y9">
-        <v>1.35</v>
-      </c>
-      <c r="Z9">
-        <v>2.74</v>
-      </c>
-      <c r="AA9">
-        <v>2.19</v>
-      </c>
-      <c r="AB9">
-        <v>1.61</v>
-      </c>
-      <c r="AC9">
-        <v>3.74</v>
-      </c>
-      <c r="AD9">
-        <v>1.19</v>
-      </c>
-      <c r="AE9">
-        <v>1.03</v>
-      </c>
-      <c r="AF9">
-        <v>1.84</v>
-      </c>
-      <c r="AG9">
-        <v>1.82</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="P10">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="R10">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T10">
-        <v>2.98</v>
+        <v>2.42</v>
       </c>
       <c r="U10">
-        <v>2.86</v>
+        <v>3.22</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z10">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="AA10">
-        <v>1.97</v>
+        <v>2.19</v>
       </c>
       <c r="AB10">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AC10">
-        <v>3.14</v>
+        <v>3.74</v>
       </c>
       <c r="AD10">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G35">
@@ -6023,55 +6023,55 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>2.19</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="S35">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="T35">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="U35">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="V35">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="W35">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AA35">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AB35">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AC35">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AD35">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AE35">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AF35">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="AG35">
-        <v>2.36</v>
+        <v>1.85</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="AK35">
-        <v>1.95</v>
+        <v>1.03</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G36">
@@ -6186,55 +6186,55 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>10</v>
+        <v>2.19</v>
       </c>
       <c r="R36">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="T36">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="U36">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="V36">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="W36">
+        <v>1.14</v>
+      </c>
+      <c r="X36">
+        <v>1.02</v>
+      </c>
+      <c r="Y36">
+        <v>1.13</v>
+      </c>
+      <c r="Z36">
+        <v>4.9</v>
+      </c>
+      <c r="AA36">
+        <v>1.46</v>
+      </c>
+      <c r="AB36">
+        <v>2.38</v>
+      </c>
+      <c r="AC36">
+        <v>2.2</v>
+      </c>
+      <c r="AD36">
+        <v>1.57</v>
+      </c>
+      <c r="AE36">
         <v>1.2</v>
       </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.11</v>
-      </c>
-      <c r="Z36">
-        <v>5.8</v>
-      </c>
-      <c r="AA36">
-        <v>1.38</v>
-      </c>
-      <c r="AB36">
-        <v>3</v>
-      </c>
-      <c r="AC36">
-        <v>1.96</v>
-      </c>
-      <c r="AD36">
-        <v>1.69</v>
-      </c>
-      <c r="AE36">
-        <v>1.27</v>
-      </c>
       <c r="AF36">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="AG36">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>4.5</v>
+        <v>1.16</v>
       </c>
       <c r="AK36">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O40">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="P40">
-        <v>4.79</v>
+        <v>4.49</v>
       </c>
       <c r="Q40">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="T40">
-        <v>3.16</v>
+        <v>3.46</v>
       </c>
       <c r="U40">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="V40">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
         <v>1.13</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>4.18</v>
+        <v>4.55</v>
       </c>
       <c r="AA40">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AB40">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AC40">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AD40">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF40">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AG40">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK40">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,61 +6992,61 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.62</v>
+        <v>1.55</v>
       </c>
       <c r="O41">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="P41">
-        <v>1.88</v>
+        <v>4.79</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S41">
         <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="U41">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>3.82</v>
+        <v>4.18</v>
       </c>
       <c r="AA41">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC41">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD41">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
         <v>2.1</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK41">
-        <v>1.19</v>
+        <v>2.14</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.6</v>
+        <v>3.62</v>
       </c>
       <c r="O42">
-        <v>3.88</v>
+        <v>3.68</v>
       </c>
       <c r="P42">
-        <v>4.49</v>
+        <v>1.88</v>
       </c>
       <c r="Q42">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R42">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
+        <v>1.32</v>
+      </c>
+      <c r="T42">
+        <v>3.12</v>
+      </c>
+      <c r="U42">
+        <v>2.48</v>
+      </c>
+      <c r="V42">
+        <v>1.43</v>
+      </c>
+      <c r="W42">
+        <v>1.1</v>
+      </c>
+      <c r="X42">
+        <v>1.03</v>
+      </c>
+      <c r="Y42">
         <v>1.23</v>
       </c>
-      <c r="T42">
-        <v>3.46</v>
-      </c>
-      <c r="U42">
-        <v>2.19</v>
-      </c>
-      <c r="V42">
-        <v>1.57</v>
-      </c>
-      <c r="W42">
-        <v>1.13</v>
-      </c>
-      <c r="X42">
-        <v>1.01</v>
-      </c>
-      <c r="Y42">
-        <v>1.2</v>
-      </c>
       <c r="Z42">
-        <v>4.55</v>
+        <v>3.82</v>
       </c>
       <c r="AA42">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AB42">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="AC42">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="AD42">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AE42">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AG42">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>2.15</v>
+        <v>1.19</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,49 +7970,49 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.63</v>
+        <v>2.92</v>
       </c>
       <c r="O47">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="P47">
-        <v>4.34</v>
+        <v>2.13</v>
       </c>
       <c r="Q47">
+        <v>3.26</v>
+      </c>
+      <c r="R47">
         <v>2.2</v>
       </c>
-      <c r="R47">
-        <v>2.22</v>
-      </c>
       <c r="S47">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="V47">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB47">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AC47">
         <v>2.7</v>
@@ -8021,13 +8021,13 @@
         <v>1.36</v>
       </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF47">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG47">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="AK47">
-        <v>2.03</v>
+        <v>1.33</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.73</v>
+        <v>1.74</v>
       </c>
       <c r="O48">
-        <v>3.02</v>
+        <v>3.68</v>
       </c>
       <c r="P48">
-        <v>2.58</v>
+        <v>4.3</v>
       </c>
       <c r="Q48">
-        <v>3.18</v>
+        <v>2.28</v>
       </c>
       <c r="R48">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U48">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="V48">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y48">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA48">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AB48">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC48">
-        <v>3.28</v>
+        <v>3.01</v>
       </c>
       <c r="AD48">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE48">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF48">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AK48">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="O49">
-        <v>2.91</v>
+        <v>3.62</v>
       </c>
       <c r="P49">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="Q49">
-        <v>3.24</v>
+        <v>2.43</v>
       </c>
       <c r="R49">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S49">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="U49">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="V49">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
         <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
         <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>4.07</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC49">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD49">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG49">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK49">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
       <c r="O50">
-        <v>3.74</v>
+        <v>3.02</v>
       </c>
       <c r="P50">
-        <v>2.13</v>
+        <v>2.58</v>
       </c>
       <c r="Q50">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="R50">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S50">
+        <v>1.38</v>
+      </c>
+      <c r="T50">
+        <v>2.75</v>
+      </c>
+      <c r="U50">
+        <v>2.96</v>
+      </c>
+      <c r="V50">
+        <v>1.4</v>
+      </c>
+      <c r="W50">
+        <v>1.06</v>
+      </c>
+      <c r="X50">
+        <v>1.03</v>
+      </c>
+      <c r="Y50">
         <v>1.3</v>
       </c>
-      <c r="T50">
-        <v>3.3</v>
-      </c>
-      <c r="U50">
-        <v>2.45</v>
-      </c>
-      <c r="V50">
-        <v>1.51</v>
-      </c>
-      <c r="W50">
-        <v>1.09</v>
-      </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.22</v>
-      </c>
       <c r="Z50">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA50">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="AB50">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC50">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF50">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AK50">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.74</v>
+        <v>2.83</v>
       </c>
       <c r="O51">
-        <v>3.68</v>
+        <v>2.91</v>
       </c>
       <c r="P51">
-        <v>4.3</v>
+        <v>2.57</v>
       </c>
       <c r="Q51">
-        <v>2.28</v>
+        <v>3.24</v>
       </c>
       <c r="R51">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W51">
         <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>4.07</v>
       </c>
       <c r="AA51">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AB51">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC51">
-        <v>3.01</v>
+        <v>2.74</v>
       </c>
       <c r="AD51">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF51">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AK51">
-        <v>1.91</v>
+        <v>1.43</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.19</v>
+        <v>1.63</v>
       </c>
       <c r="O52">
-        <v>3.62</v>
+        <v>4.25</v>
       </c>
       <c r="P52">
-        <v>2.88</v>
+        <v>4.34</v>
       </c>
       <c r="Q52">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="R52">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="S52">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T52">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U52">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z52">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AA52">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AB52">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AC52">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD52">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG52">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,25 +13512,25 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.59</v>
+        <v>2.32</v>
       </c>
       <c r="O81">
-        <v>3.52</v>
+        <v>3.14</v>
       </c>
       <c r="P81">
-        <v>5.13</v>
+        <v>2.68</v>
       </c>
       <c r="Q81">
-        <v>1.98</v>
+        <v>3</v>
       </c>
       <c r="R81">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="S81">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T81">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="U81">
         <v>2.89</v>
@@ -13539,37 +13539,37 @@
         <v>1.32</v>
       </c>
       <c r="W81">
+        <v>1.06</v>
+      </c>
+      <c r="X81">
+        <v>1</v>
+      </c>
+      <c r="Y81">
+        <v>1.28</v>
+      </c>
+      <c r="Z81">
+        <v>3.05</v>
+      </c>
+      <c r="AA81">
+        <v>1.98</v>
+      </c>
+      <c r="AB81">
+        <v>1.71</v>
+      </c>
+      <c r="AC81">
+        <v>3.5</v>
+      </c>
+      <c r="AD81">
+        <v>1.22</v>
+      </c>
+      <c r="AE81">
         <v>1.03</v>
       </c>
-      <c r="X81">
-        <v>1.01</v>
-      </c>
-      <c r="Y81">
-        <v>1.29</v>
-      </c>
-      <c r="Z81">
-        <v>3.04</v>
-      </c>
-      <c r="AA81">
-        <v>1.9</v>
-      </c>
-      <c r="AB81">
-        <v>1.78</v>
-      </c>
-      <c r="AC81">
-        <v>3.42</v>
-      </c>
-      <c r="AD81">
-        <v>1.23</v>
-      </c>
-      <c r="AE81">
-        <v>1.04</v>
-      </c>
       <c r="AF81">
-        <v>2.13</v>
+        <v>1.76</v>
       </c>
       <c r="AG81">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>2.46</v>
+        <v>1.46</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,25 +13675,25 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.32</v>
+        <v>1.59</v>
       </c>
       <c r="O82">
-        <v>3.14</v>
+        <v>3.52</v>
       </c>
       <c r="P82">
-        <v>2.68</v>
+        <v>5.13</v>
       </c>
       <c r="Q82">
-        <v>3</v>
+        <v>1.98</v>
       </c>
       <c r="R82">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S82">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="U82">
         <v>2.89</v>
@@ -13702,37 +13702,37 @@
         <v>1.32</v>
       </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X82">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z82">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA82">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB82">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AC82">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD82">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE82">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF82">
-        <v>1.76</v>
+        <v>2.13</v>
       </c>
       <c r="AG82">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK82">
-        <v>1.46</v>
+        <v>2.46</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.41</v>
+        <v>1.9</v>
       </c>
       <c r="O105">
-        <v>4.6</v>
+        <v>3.78</v>
       </c>
       <c r="P105">
-        <v>5.26</v>
+        <v>3.07</v>
       </c>
       <c r="Q105">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="R105">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="S105">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T105">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="U105">
-        <v>1.99</v>
+        <v>2.21</v>
       </c>
       <c r="V105">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="W105">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Z105">
-        <v>6.15</v>
+        <v>4.7</v>
       </c>
       <c r="AA105">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AB105">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC105">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="AD105">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AE105">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AF105">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG105">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK105">
-        <v>2.42</v>
+        <v>1.81</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,80 +17750,80 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="O107">
-        <v>3.78</v>
+        <v>4.6</v>
       </c>
       <c r="P107">
-        <v>3.07</v>
+        <v>5.26</v>
       </c>
       <c r="Q107">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="R107">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="S107">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T107">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="U107">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="V107">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="W107">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X107">
         <v>1.01</v>
       </c>
       <c r="Y107">
+        <v>1.06</v>
+      </c>
+      <c r="Z107">
+        <v>6.15</v>
+      </c>
+      <c r="AA107">
+        <v>1.32</v>
+      </c>
+      <c r="AB107">
+        <v>3.1</v>
+      </c>
+      <c r="AC107">
+        <v>1.91</v>
+      </c>
+      <c r="AD107">
+        <v>1.82</v>
+      </c>
+      <c r="AE107">
+        <v>1.31</v>
+      </c>
+      <c r="AF107">
+        <v>1.44</v>
+      </c>
+      <c r="AG107">
+        <v>2.5</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
         <v>1.12</v>
       </c>
-      <c r="Z107">
-        <v>4.7</v>
-      </c>
-      <c r="AA107">
-        <v>1.57</v>
-      </c>
-      <c r="AB107">
-        <v>2.35</v>
-      </c>
-      <c r="AC107">
-        <v>2.33</v>
-      </c>
-      <c r="AD107">
-        <v>1.48</v>
-      </c>
-      <c r="AE107">
-        <v>1.16</v>
-      </c>
-      <c r="AF107">
-        <v>1.5</v>
-      </c>
-      <c r="AG107">
-        <v>2.38</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.22</v>
-      </c>
       <c r="AK107">
-        <v>1.81</v>
+        <v>2.42</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="O154">
-        <v>3.38</v>
+        <v>3.02</v>
       </c>
       <c r="P154">
-        <v>2.96</v>
+        <v>2.27</v>
       </c>
       <c r="Q154">
-        <v>2.72</v>
+        <v>3.86</v>
       </c>
       <c r="R154">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S154">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="T154">
-        <v>3.28</v>
+        <v>2.58</v>
       </c>
       <c r="U154">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="V154">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W154">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X154">
+        <v>1.04</v>
+      </c>
+      <c r="Y154">
+        <v>1.36</v>
+      </c>
+      <c r="Z154">
+        <v>2.7</v>
+      </c>
+      <c r="AA154">
+        <v>2.15</v>
+      </c>
+      <c r="AB154">
+        <v>1.6</v>
+      </c>
+      <c r="AC154">
+        <v>3.86</v>
+      </c>
+      <c r="AD154">
+        <v>1.18</v>
+      </c>
+      <c r="AE154">
         <v>1.03</v>
       </c>
-      <c r="Y154">
-        <v>1.23</v>
-      </c>
-      <c r="Z154">
-        <v>3.78</v>
-      </c>
-      <c r="AA154">
-        <v>1.72</v>
-      </c>
-      <c r="AB154">
-        <v>1.98</v>
-      </c>
-      <c r="AC154">
-        <v>2.74</v>
-      </c>
-      <c r="AD154">
-        <v>1.35</v>
-      </c>
-      <c r="AE154">
-        <v>1.15</v>
-      </c>
       <c r="AF154">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AG154">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK154">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="O156">
-        <v>3.02</v>
+        <v>3.38</v>
       </c>
       <c r="P156">
-        <v>2.27</v>
+        <v>2.96</v>
       </c>
       <c r="Q156">
-        <v>3.86</v>
+        <v>2.72</v>
       </c>
       <c r="R156">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S156">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="T156">
-        <v>2.58</v>
+        <v>3.28</v>
       </c>
       <c r="U156">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="V156">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W156">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X156">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Z156">
-        <v>2.7</v>
+        <v>3.78</v>
       </c>
       <c r="AA156">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AB156">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AC156">
-        <v>3.86</v>
+        <v>2.74</v>
       </c>
       <c r="AD156">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AE156">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AF156">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AG156">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK156">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AL156">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.14</v>
+        <v>2.23</v>
       </c>
       <c r="O9">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="P9">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="R9">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T9">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="U9">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z9">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA9">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="AB9">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AC9">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD9">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG9">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,65 +1939,65 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.23</v>
+        <v>3.14</v>
       </c>
       <c r="O10">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="P10">
-        <v>3.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q10">
-        <v>3.13</v>
+        <v>3.5</v>
       </c>
       <c r="R10">
+        <v>2.08</v>
+      </c>
+      <c r="S10">
+        <v>1.33</v>
+      </c>
+      <c r="T10">
+        <v>2.95</v>
+      </c>
+      <c r="U10">
+        <v>2.65</v>
+      </c>
+      <c r="V10">
+        <v>1.38</v>
+      </c>
+      <c r="W10">
+        <v>1.06</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1.26</v>
+      </c>
+      <c r="Z10">
+        <v>3.2</v>
+      </c>
+      <c r="AA10">
+        <v>1.99</v>
+      </c>
+      <c r="AB10">
+        <v>1.78</v>
+      </c>
+      <c r="AC10">
+        <v>3.2</v>
+      </c>
+      <c r="AD10">
+        <v>1.3</v>
+      </c>
+      <c r="AE10">
+        <v>1.11</v>
+      </c>
+      <c r="AF10">
+        <v>1.73</v>
+      </c>
+      <c r="AG10">
         <v>1.98</v>
       </c>
-      <c r="S10">
-        <v>1.45</v>
-      </c>
-      <c r="T10">
-        <v>2.42</v>
-      </c>
-      <c r="U10">
-        <v>3.22</v>
-      </c>
-      <c r="V10">
-        <v>1.35</v>
-      </c>
-      <c r="W10">
-        <v>1.07</v>
-      </c>
-      <c r="X10">
-        <v>1.04</v>
-      </c>
-      <c r="Y10">
-        <v>1.35</v>
-      </c>
-      <c r="Z10">
-        <v>2.74</v>
-      </c>
-      <c r="AA10">
-        <v>2.19</v>
-      </c>
-      <c r="AB10">
-        <v>1.61</v>
-      </c>
-      <c r="AC10">
-        <v>3.74</v>
-      </c>
-      <c r="AD10">
-        <v>1.19</v>
-      </c>
-      <c r="AE10">
-        <v>1.03</v>
-      </c>
-      <c r="AF10">
-        <v>1.84</v>
-      </c>
-      <c r="AG10">
-        <v>1.82</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N22">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O30">
+        <v>3.2</v>
+      </c>
+      <c r="P30">
         <v>3.1</v>
       </c>
-      <c r="P30">
-        <v>3.21</v>
-      </c>
       <c r="Q30">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="R30">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="S30">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T30">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="U30">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="V30">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W30">
+        <v>1.06</v>
+      </c>
+      <c r="X30">
+        <v>1.02</v>
+      </c>
+      <c r="Y30">
+        <v>1.3</v>
+      </c>
+      <c r="Z30">
+        <v>3.04</v>
+      </c>
+      <c r="AA30">
+        <v>2</v>
+      </c>
+      <c r="AB30">
+        <v>1.72</v>
+      </c>
+      <c r="AC30">
+        <v>3.34</v>
+      </c>
+      <c r="AD30">
+        <v>1.24</v>
+      </c>
+      <c r="AE30">
         <v>1.05</v>
       </c>
-      <c r="X30">
-        <v>1.03</v>
-      </c>
-      <c r="Y30">
-        <v>1.35</v>
-      </c>
-      <c r="Z30">
-        <v>2.74</v>
-      </c>
-      <c r="AA30">
-        <v>2.2</v>
-      </c>
-      <c r="AB30">
-        <v>1.6</v>
-      </c>
-      <c r="AC30">
-        <v>3.82</v>
-      </c>
-      <c r="AD30">
-        <v>1.18</v>
-      </c>
-      <c r="AE30">
-        <v>1.03</v>
-      </c>
       <c r="AF30">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AG30">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK30">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="O31">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q31">
-        <v>4.88</v>
+        <v>4.8</v>
       </c>
       <c r="R31">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S31">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T31">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="U31">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="V31">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W31">
+        <v>1.06</v>
+      </c>
+      <c r="X31">
+        <v>1.03</v>
+      </c>
+      <c r="Y31">
+        <v>1.36</v>
+      </c>
+      <c r="Z31">
+        <v>2.82</v>
+      </c>
+      <c r="AA31">
+        <v>2.25</v>
+      </c>
+      <c r="AB31">
+        <v>1.58</v>
+      </c>
+      <c r="AC31">
+        <v>4</v>
+      </c>
+      <c r="AD31">
+        <v>1.17</v>
+      </c>
+      <c r="AE31">
         <v>1.02</v>
       </c>
-      <c r="X31">
-        <v>1.02</v>
-      </c>
-      <c r="Y31">
+      <c r="AF31">
+        <v>1.95</v>
+      </c>
+      <c r="AG31">
+        <v>1.73</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.33</v>
       </c>
-      <c r="Z31">
-        <v>2.83</v>
-      </c>
-      <c r="AA31">
-        <v>2.15</v>
-      </c>
-      <c r="AB31">
-        <v>1.6</v>
-      </c>
-      <c r="AC31">
-        <v>3.75</v>
-      </c>
-      <c r="AD31">
-        <v>1.19</v>
-      </c>
-      <c r="AE31">
-        <v>1.03</v>
-      </c>
-      <c r="AF31">
-        <v>1.9</v>
-      </c>
-      <c r="AG31">
-        <v>1.78</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.23</v>
-      </c>
       <c r="AK31">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="O32">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>3.41</v>
+        <v>2.84</v>
       </c>
       <c r="Q32">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R32">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="S32">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.55</v>
+        <v>2.77</v>
       </c>
       <c r="U32">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="V32">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W32">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
         <v>1.36</v>
       </c>
       <c r="Z32">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="AA32">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AB32">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AC32">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AD32">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE32">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG32">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK32">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,34 +6014,34 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q35">
-        <v>10</v>
+        <v>1.55</v>
       </c>
       <c r="R35">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="S35">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T35">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="U35">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="V35">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W35">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X35">
         <v>1.01</v>
@@ -6050,28 +6050,28 @@
         <v>1.11</v>
       </c>
       <c r="Z35">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA35">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AB35">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AC35">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AD35">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AE35">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF35">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AG35">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
+        <v>1.07</v>
+      </c>
+      <c r="AK35">
         <v>4.5</v>
-      </c>
-      <c r="AK35">
-        <v>1.03</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,34 +6340,34 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>1.55</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T37">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="U37">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="V37">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W37">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X37">
         <v>1.01</v>
@@ -6376,28 +6376,28 @@
         <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA37">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AB37">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="AC37">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AD37">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AE37">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF37">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AG37">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.07</v>
+        <v>4.5</v>
       </c>
       <c r="AK37">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="O38">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="P38">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.6</v>
+        <v>3.62</v>
       </c>
       <c r="O40">
-        <v>3.88</v>
+        <v>3.68</v>
       </c>
       <c r="P40">
-        <v>4.49</v>
+        <v>1.88</v>
       </c>
       <c r="Q40">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R40">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
+        <v>1.32</v>
+      </c>
+      <c r="T40">
+        <v>3.12</v>
+      </c>
+      <c r="U40">
+        <v>2.48</v>
+      </c>
+      <c r="V40">
+        <v>1.43</v>
+      </c>
+      <c r="W40">
+        <v>1.1</v>
+      </c>
+      <c r="X40">
+        <v>1.03</v>
+      </c>
+      <c r="Y40">
         <v>1.23</v>
       </c>
-      <c r="T40">
-        <v>3.46</v>
-      </c>
-      <c r="U40">
-        <v>2.19</v>
-      </c>
-      <c r="V40">
-        <v>1.57</v>
-      </c>
-      <c r="W40">
-        <v>1.13</v>
-      </c>
-      <c r="X40">
-        <v>1.01</v>
-      </c>
-      <c r="Y40">
-        <v>1.2</v>
-      </c>
       <c r="Z40">
-        <v>4.55</v>
+        <v>3.82</v>
       </c>
       <c r="AA40">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AB40">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="AC40">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="AD40">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AE40">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AG40">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>2.15</v>
+        <v>1.19</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.62</v>
+        <v>1.6</v>
       </c>
       <c r="O42">
-        <v>3.68</v>
+        <v>3.88</v>
       </c>
       <c r="P42">
-        <v>1.88</v>
+        <v>4.49</v>
       </c>
       <c r="Q42">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="T42">
-        <v>3.12</v>
+        <v>3.46</v>
       </c>
       <c r="U42">
-        <v>2.48</v>
+        <v>2.19</v>
       </c>
       <c r="V42">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>3.82</v>
+        <v>4.55</v>
       </c>
       <c r="AA42">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AB42">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="AC42">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="AD42">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF42">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AG42">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK42">
-        <v>1.19</v>
+        <v>2.15</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>4.11</v>
+        <v>1.48</v>
       </c>
       <c r="O43">
-        <v>3.62</v>
+        <v>4.6</v>
       </c>
       <c r="P43">
-        <v>1.79</v>
+        <v>5.36</v>
       </c>
       <c r="Q43">
-        <v>4.33</v>
+        <v>1.93</v>
       </c>
       <c r="R43">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S43">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="U43">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="V43">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z43">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA43">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AB43">
-        <v>1.94</v>
+        <v>2.19</v>
       </c>
       <c r="AC43">
-        <v>2.92</v>
+        <v>2.36</v>
       </c>
       <c r="AD43">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AE43">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF43">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG43">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK43">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,68 +7477,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="O44">
-        <v>4.6</v>
+        <v>3.26</v>
       </c>
       <c r="P44">
-        <v>5.36</v>
+        <v>3.54</v>
       </c>
       <c r="Q44">
-        <v>1.93</v>
+        <v>2.69</v>
       </c>
       <c r="R44">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="S44">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="T44">
-        <v>3.54</v>
+        <v>2.71</v>
       </c>
       <c r="U44">
-        <v>2.24</v>
+        <v>2.9</v>
       </c>
       <c r="V44">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="Z44">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="AA44">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="AB44">
-        <v>2.19</v>
+        <v>1.61</v>
       </c>
       <c r="AC44">
-        <v>2.36</v>
+        <v>3.76</v>
       </c>
       <c r="AD44">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AE44">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AF44">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AG44">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>2.45</v>
+        <v>1.66</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G45">
@@ -7640,68 +7640,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="O45">
-        <v>3.26</v>
+        <v>3.54</v>
       </c>
       <c r="P45">
-        <v>3.54</v>
+        <v>3.15</v>
       </c>
       <c r="Q45">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="R45">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="S45">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="T45">
-        <v>2.71</v>
+        <v>3.4</v>
       </c>
       <c r="U45">
-        <v>2.9</v>
+        <v>2.32</v>
       </c>
       <c r="V45">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X45">
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="Z45">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="AA45">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AB45">
-        <v>1.61</v>
+        <v>2.03</v>
       </c>
       <c r="AC45">
-        <v>3.76</v>
+        <v>2.77</v>
       </c>
       <c r="AD45">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AE45">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF45">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AG45">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK45">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="O46">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P46">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="Q46">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="R46">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S46">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T46">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U46">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="V46">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA46">
         <v>1.83</v>
       </c>
       <c r="AB46">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC46">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="AD46">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE46">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF46">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG46">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK46">
         <v>1.65</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O47">
-        <v>3.74</v>
+        <v>2.91</v>
       </c>
       <c r="P47">
-        <v>2.13</v>
+        <v>2.57</v>
       </c>
       <c r="Q47">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="R47">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T47">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="U47">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V47">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W47">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
         <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>4.2</v>
+        <v>4.07</v>
       </c>
       <c r="AA47">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="AB47">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AC47">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD47">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE47">
         <v>1.13</v>
       </c>
       <c r="AF47">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG47">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AK47">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.74</v>
+        <v>2.92</v>
       </c>
       <c r="O48">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="P48">
-        <v>4.3</v>
+        <v>2.13</v>
       </c>
       <c r="Q48">
-        <v>2.28</v>
+        <v>3.26</v>
       </c>
       <c r="R48">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S48">
         <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U48">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V48">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W48">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X48">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
         <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA48">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AB48">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="AC48">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="AD48">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE48">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG48">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="AK48">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.19</v>
+        <v>2.73</v>
       </c>
       <c r="O49">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="P49">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="Q49">
-        <v>2.43</v>
+        <v>3.18</v>
       </c>
       <c r="R49">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S49">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T49">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U49">
-        <v>2.47</v>
+        <v>2.96</v>
       </c>
       <c r="V49">
+        <v>1.4</v>
+      </c>
+      <c r="W49">
+        <v>1.06</v>
+      </c>
+      <c r="X49">
+        <v>1.03</v>
+      </c>
+      <c r="Y49">
+        <v>1.3</v>
+      </c>
+      <c r="Z49">
+        <v>3.2</v>
+      </c>
+      <c r="AA49">
+        <v>1.94</v>
+      </c>
+      <c r="AB49">
+        <v>1.8</v>
+      </c>
+      <c r="AC49">
+        <v>3.28</v>
+      </c>
+      <c r="AD49">
+        <v>1.25</v>
+      </c>
+      <c r="AE49">
+        <v>1.05</v>
+      </c>
+      <c r="AF49">
+        <v>1.73</v>
+      </c>
+      <c r="AG49">
+        <v>1.95</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.41</v>
+      </c>
+      <c r="AK49">
         <v>1.44</v>
-      </c>
-      <c r="W49">
-        <v>1.07</v>
-      </c>
-      <c r="X49">
-        <v>1.01</v>
-      </c>
-      <c r="Y49">
-        <v>1.22</v>
-      </c>
-      <c r="Z49">
-        <v>3.5</v>
-      </c>
-      <c r="AA49">
-        <v>1.83</v>
-      </c>
-      <c r="AB49">
-        <v>1.93</v>
-      </c>
-      <c r="AC49">
-        <v>2.83</v>
-      </c>
-      <c r="AD49">
-        <v>1.33</v>
-      </c>
-      <c r="AE49">
-        <v>1.12</v>
-      </c>
-      <c r="AF49">
-        <v>1.64</v>
-      </c>
-      <c r="AG49">
-        <v>2.13</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.27</v>
-      </c>
-      <c r="AK49">
-        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.73</v>
+        <v>4.11</v>
       </c>
       <c r="O50">
-        <v>3.02</v>
+        <v>3.62</v>
       </c>
       <c r="P50">
-        <v>2.58</v>
+        <v>1.79</v>
       </c>
       <c r="Q50">
-        <v>3.18</v>
+        <v>4.33</v>
       </c>
       <c r="R50">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T50">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U50">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="V50">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
+        <v>1.83</v>
+      </c>
+      <c r="AB50">
         <v>1.94</v>
       </c>
-      <c r="AB50">
-        <v>1.8</v>
-      </c>
       <c r="AC50">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AD50">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE50">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG50">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.83</v>
+        <v>1.74</v>
       </c>
       <c r="O51">
-        <v>2.91</v>
+        <v>3.68</v>
       </c>
       <c r="P51">
-        <v>2.57</v>
+        <v>4.3</v>
       </c>
       <c r="Q51">
-        <v>3.24</v>
+        <v>2.28</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S51">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V51">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
         <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.07</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AB51">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC51">
-        <v>2.74</v>
+        <v>3.01</v>
       </c>
       <c r="AD51">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG51">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>1.43</v>
+        <v>1.91</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.58</v>
+        <v>1.4</v>
       </c>
       <c r="O62">
-        <v>3.48</v>
+        <v>5</v>
       </c>
       <c r="P62">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q62">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="R62">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="S62">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="T62">
-        <v>3.08</v>
+        <v>4.3</v>
       </c>
       <c r="U62">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="W62">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="Z62">
-        <v>4.05</v>
+        <v>5.85</v>
       </c>
       <c r="AA62">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.1</v>
+        <v>2.87</v>
       </c>
       <c r="AC62">
-        <v>2.52</v>
+        <v>2.02</v>
       </c>
       <c r="AD62">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="AE62">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AF62">
         <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK62">
-        <v>1.46</v>
+        <v>3</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.4</v>
+        <v>2.58</v>
       </c>
       <c r="O63">
-        <v>5</v>
+        <v>3.48</v>
       </c>
       <c r="P63">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q63">
-        <v>1.74</v>
+        <v>2.75</v>
       </c>
       <c r="R63">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="S63">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="T63">
-        <v>4.3</v>
+        <v>3.08</v>
       </c>
       <c r="U63">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="V63">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="W63">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="Z63">
-        <v>5.85</v>
+        <v>4.05</v>
       </c>
       <c r="AA63">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB63">
-        <v>2.87</v>
+        <v>2.1</v>
       </c>
       <c r="AC63">
-        <v>2.02</v>
+        <v>2.52</v>
       </c>
       <c r="AD63">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="AE63">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AF63">
         <v>1.57</v>
       </c>
       <c r="AG63">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>3</v>
+        <v>1.46</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P64">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="O65">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P65">
-        <v>2.35</v>
+        <v>2.77</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="O66">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P66">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AB76">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="O77">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="P77">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB77">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N78">
@@ -13841,61 +13841,61 @@
         <v>2.2</v>
       </c>
       <c r="O83">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P83">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="Q83">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R83">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="S83">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T83">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="U83">
-        <v>3.12</v>
+        <v>2.93</v>
       </c>
       <c r="V83">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W83">
+        <v>1.07</v>
+      </c>
+      <c r="X83">
         <v>1.02</v>
       </c>
-      <c r="X83">
-        <v>1.03</v>
-      </c>
       <c r="Y83">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z83">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AA83">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AB83">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC83">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="AD83">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE83">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF83">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG83">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK83">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="O84">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P84">
-        <v>3.03</v>
+        <v>2.56</v>
       </c>
       <c r="Q84">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="R84">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S84">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T84">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="U84">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="V84">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W84">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X84">
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z84">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA84">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB84">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AC84">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="AD84">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE84">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF84">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG84">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AK84">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="O86">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P86">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q86">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="R86">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="S86">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="T86">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="U86">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="V86">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W86">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X86">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y86">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z86">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="AA86">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AB86">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC86">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="AD86">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AE86">
         <v>1.05</v>
       </c>
       <c r="AF86">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG86">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK86">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="O87">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="P87">
-        <v>2.9</v>
+        <v>4.37</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB87">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="O94">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P94">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15670,10 +15670,10 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB94">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC94">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="O95">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="P95">
-        <v>3.12</v>
+        <v>3.9</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AB95">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="O98">
-        <v>6.8</v>
+        <v>6.28</v>
       </c>
       <c r="P98">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB98">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="O99">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P99">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="O100">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P100">
-        <v>5.1</v>
+        <v>4.33</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB100">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,80 +17424,80 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="O105">
-        <v>3.78</v>
+        <v>4.6</v>
       </c>
       <c r="P105">
-        <v>3.07</v>
+        <v>5.26</v>
       </c>
       <c r="Q105">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="R105">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="S105">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T105">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="U105">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="V105">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="W105">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
+        <v>1.06</v>
+      </c>
+      <c r="Z105">
+        <v>6.15</v>
+      </c>
+      <c r="AA105">
+        <v>1.32</v>
+      </c>
+      <c r="AB105">
+        <v>3.1</v>
+      </c>
+      <c r="AC105">
+        <v>1.91</v>
+      </c>
+      <c r="AD105">
+        <v>1.82</v>
+      </c>
+      <c r="AE105">
+        <v>1.31</v>
+      </c>
+      <c r="AF105">
+        <v>1.44</v>
+      </c>
+      <c r="AG105">
+        <v>2.5</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ105">
         <v>1.12</v>
       </c>
-      <c r="Z105">
-        <v>4.7</v>
-      </c>
-      <c r="AA105">
-        <v>1.57</v>
-      </c>
-      <c r="AB105">
-        <v>2.35</v>
-      </c>
-      <c r="AC105">
-        <v>2.33</v>
-      </c>
-      <c r="AD105">
-        <v>1.48</v>
-      </c>
-      <c r="AE105">
-        <v>1.16</v>
-      </c>
-      <c r="AF105">
-        <v>1.5</v>
-      </c>
-      <c r="AG105">
-        <v>2.38</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ105">
-        <v>1.22</v>
-      </c>
       <c r="AK105">
-        <v>1.81</v>
+        <v>2.42</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.53</v>
+        <v>1.9</v>
       </c>
       <c r="O106">
+        <v>3.78</v>
+      </c>
+      <c r="P106">
+        <v>3.07</v>
+      </c>
+      <c r="Q106">
+        <v>2.4</v>
+      </c>
+      <c r="R106">
+        <v>2.4</v>
+      </c>
+      <c r="S106">
+        <v>1.25</v>
+      </c>
+      <c r="T106">
         <v>3.6</v>
       </c>
-      <c r="P106">
-        <v>2.55</v>
-      </c>
-      <c r="Q106">
-        <v>3.11</v>
-      </c>
-      <c r="R106">
-        <v>2.36</v>
-      </c>
-      <c r="S106">
-        <v>1.29</v>
-      </c>
-      <c r="T106">
-        <v>3.26</v>
-      </c>
       <c r="U106">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="V106">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W106">
         <v>1.12</v>
       </c>
       <c r="X106">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z106">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="AA106">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AB106">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="AC106">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="AD106">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE106">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF106">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG106">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>1.45</v>
+        <v>1.81</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.41</v>
+        <v>2.53</v>
       </c>
       <c r="O107">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P107">
-        <v>5.26</v>
+        <v>2.55</v>
       </c>
       <c r="Q107">
-        <v>1.85</v>
+        <v>3.11</v>
       </c>
       <c r="R107">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="S107">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T107">
-        <v>4.8</v>
+        <v>3.26</v>
       </c>
       <c r="U107">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="V107">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="W107">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="Z107">
-        <v>6.15</v>
+        <v>4.05</v>
       </c>
       <c r="AA107">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="AB107">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC107">
-        <v>1.91</v>
+        <v>2.56</v>
       </c>
       <c r="AD107">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="AE107">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AF107">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG107">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>2.42</v>
+        <v>1.45</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="O113">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P113">
-        <v>3.84</v>
+        <v>4.3</v>
       </c>
       <c r="Q113">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="R113">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="S113">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T113">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="U113">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V113">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W113">
         <v>1.06</v>
       </c>
       <c r="X113">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z113">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AA113">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AB113">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AC113">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="AD113">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE113">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF113">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AG113">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK113">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,80 +19869,80 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q120">
-        <v>2.75</v>
+        <v>3.48</v>
       </c>
       <c r="R120">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="S120">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T120">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="U120">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V120">
         <v>1.4</v>
       </c>
       <c r="W120">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X120">
         <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z120">
-        <v>3.86</v>
+        <v>3.2</v>
       </c>
       <c r="AA120">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AB120">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AC120">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AD120">
+        <v>1.31</v>
+      </c>
+      <c r="AE120">
+        <v>1.06</v>
+      </c>
+      <c r="AF120">
+        <v>1.69</v>
+      </c>
+      <c r="AG120">
+        <v>2.03</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ120">
+        <v>1.5</v>
+      </c>
+      <c r="AK120">
         <v>1.33</v>
-      </c>
-      <c r="AE120">
-        <v>1.09</v>
-      </c>
-      <c r="AF120">
-        <v>1.65</v>
-      </c>
-      <c r="AG120">
-        <v>2.16</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>1.25</v>
-      </c>
-      <c r="AK120">
-        <v>1.62</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121">
         <v>2.75</v>
       </c>
-      <c r="O121">
-        <v>3.2</v>
-      </c>
-      <c r="P121">
-        <v>2.47</v>
-      </c>
-      <c r="Q121">
-        <v>3.48</v>
-      </c>
       <c r="R121">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="S121">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T121">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="U121">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V121">
         <v>1.4</v>
       </c>
       <c r="W121">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X121">
         <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z121">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="AA121">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB121">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AC121">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="AD121">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE121">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF121">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AG121">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK121">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="O154">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="P154">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="Q154">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="R154">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S154">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="T154">
-        <v>2.58</v>
+        <v>3.12</v>
       </c>
       <c r="U154">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V154">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W154">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X154">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y154">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="Z154">
+        <v>3.72</v>
+      </c>
+      <c r="AA154">
+        <v>1.7</v>
+      </c>
+      <c r="AB154">
+        <v>2.07</v>
+      </c>
+      <c r="AC154">
         <v>2.7</v>
       </c>
-      <c r="AA154">
-        <v>2.15</v>
-      </c>
-      <c r="AB154">
+      <c r="AD154">
+        <v>1.4</v>
+      </c>
+      <c r="AE154">
+        <v>1.11</v>
+      </c>
+      <c r="AF154">
         <v>1.6</v>
       </c>
-      <c r="AC154">
-        <v>3.86</v>
-      </c>
-      <c r="AD154">
-        <v>1.18</v>
-      </c>
-      <c r="AE154">
-        <v>1.03</v>
-      </c>
-      <c r="AF154">
-        <v>1.85</v>
-      </c>
       <c r="AG154">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AK154">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>3.09</v>
+        <v>2.12</v>
       </c>
       <c r="O155">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P155">
-        <v>2.05</v>
+        <v>2.96</v>
       </c>
       <c r="Q155">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="R155">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S155">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T155">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U155">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="V155">
         <v>1.5</v>
       </c>
       <c r="W155">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X155">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y155">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z155">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="AA155">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB155">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AC155">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD155">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE155">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF155">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG155">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AK155">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="O156">
-        <v>3.38</v>
+        <v>3.02</v>
       </c>
       <c r="P156">
-        <v>2.96</v>
+        <v>2.27</v>
       </c>
       <c r="Q156">
-        <v>2.72</v>
+        <v>3.86</v>
       </c>
       <c r="R156">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S156">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="T156">
-        <v>3.28</v>
+        <v>2.58</v>
       </c>
       <c r="U156">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="V156">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W156">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
+        <v>1.04</v>
+      </c>
+      <c r="Y156">
+        <v>1.36</v>
+      </c>
+      <c r="Z156">
+        <v>2.7</v>
+      </c>
+      <c r="AA156">
+        <v>2.15</v>
+      </c>
+      <c r="AB156">
+        <v>1.6</v>
+      </c>
+      <c r="AC156">
+        <v>3.86</v>
+      </c>
+      <c r="AD156">
+        <v>1.18</v>
+      </c>
+      <c r="AE156">
         <v>1.03</v>
       </c>
-      <c r="Y156">
-        <v>1.23</v>
-      </c>
-      <c r="Z156">
-        <v>3.78</v>
-      </c>
-      <c r="AA156">
-        <v>1.72</v>
-      </c>
-      <c r="AB156">
-        <v>1.98</v>
-      </c>
-      <c r="AC156">
-        <v>2.74</v>
-      </c>
-      <c r="AD156">
-        <v>1.35</v>
-      </c>
-      <c r="AE156">
-        <v>1.15</v>
-      </c>
       <c r="AF156">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AG156">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK156">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AL156">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -603,139 +603,139 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.05</v>
+        <v>2.61</v>
       </c>
       <c r="O2">
+        <v>3.15</v>
+      </c>
+      <c r="P2">
+        <v>2.53</v>
+      </c>
+      <c r="Q2">
         <v>3.5</v>
       </c>
-      <c r="P2">
-        <v>3.25</v>
-      </c>
-      <c r="Q2">
-        <v>2.63</v>
-      </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="S2">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="T2">
-        <v>2.85</v>
+        <v>2.34</v>
       </c>
       <c r="U2">
-        <v>2.62</v>
+        <v>3.12</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
+        <v>1.05</v>
+      </c>
+      <c r="Y2">
+        <v>1.45</v>
+      </c>
+      <c r="Z2">
+        <v>2.51</v>
+      </c>
+      <c r="AA2">
+        <v>2.42</v>
+      </c>
+      <c r="AB2">
+        <v>1.53</v>
+      </c>
+      <c r="AC2">
+        <v>4.33</v>
+      </c>
+      <c r="AD2">
+        <v>1.14</v>
+      </c>
+      <c r="AE2">
         <v>1.03</v>
       </c>
-      <c r="Y2">
-        <v>1.24</v>
-      </c>
-      <c r="Z2">
-        <v>3.34</v>
-      </c>
-      <c r="AA2">
-        <v>1.89</v>
-      </c>
-      <c r="AB2">
-        <v>1.85</v>
-      </c>
-      <c r="AC2">
-        <v>3.2</v>
-      </c>
-      <c r="AD2">
-        <v>1.34</v>
-      </c>
-      <c r="AE2">
-        <v>1.08</v>
-      </c>
       <c r="AF2">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AG2">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK2">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -766,139 +766,139 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="O3">
+        <v>3.38</v>
+      </c>
+      <c r="P3">
+        <v>1.92</v>
+      </c>
+      <c r="Q3">
+        <v>4.1</v>
+      </c>
+      <c r="R3">
+        <v>2.11</v>
+      </c>
+      <c r="S3">
+        <v>1.38</v>
+      </c>
+      <c r="T3">
+        <v>2.73</v>
+      </c>
+      <c r="U3">
+        <v>2.57</v>
+      </c>
+      <c r="V3">
+        <v>1.4</v>
+      </c>
+      <c r="W3">
+        <v>1.06</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3">
+        <v>1.25</v>
+      </c>
+      <c r="Z3">
+        <v>3.6</v>
+      </c>
+      <c r="AA3">
+        <v>1.85</v>
+      </c>
+      <c r="AB3">
+        <v>1.89</v>
+      </c>
+      <c r="AC3">
+        <v>3.12</v>
+      </c>
+      <c r="AD3">
+        <v>1.32</v>
+      </c>
+      <c r="AE3">
+        <v>1.13</v>
+      </c>
+      <c r="AF3">
+        <v>1.67</v>
+      </c>
+      <c r="AG3">
+        <v>2.03</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>["34", "81"]</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <v>1.22</v>
+      </c>
+      <c r="AK3">
+        <v>1.25</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>4</v>
+      </c>
+      <c r="AN3">
         <v>3</v>
       </c>
-      <c r="P3">
-        <v>2.8</v>
-      </c>
-      <c r="Q3">
-        <v>3.5</v>
-      </c>
-      <c r="R3">
-        <v>1.92</v>
-      </c>
-      <c r="S3">
-        <v>1.51</v>
-      </c>
-      <c r="T3">
-        <v>2.35</v>
-      </c>
-      <c r="U3">
-        <v>3.12</v>
-      </c>
-      <c r="V3">
-        <v>1.29</v>
-      </c>
-      <c r="W3">
-        <v>1.03</v>
-      </c>
-      <c r="X3">
-        <v>1.05</v>
-      </c>
-      <c r="Y3">
-        <v>1.44</v>
-      </c>
-      <c r="Z3">
-        <v>2.52</v>
-      </c>
-      <c r="AA3">
-        <v>2.43</v>
-      </c>
-      <c r="AB3">
-        <v>1.52</v>
-      </c>
-      <c r="AC3">
-        <v>4.33</v>
-      </c>
-      <c r="AD3">
-        <v>1.14</v>
-      </c>
-      <c r="AE3">
-        <v>1.03</v>
-      </c>
-      <c r="AF3">
-        <v>1.95</v>
-      </c>
-      <c r="AG3">
-        <v>1.73</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.31</v>
-      </c>
-      <c r="AK3">
-        <v>1.36</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>-1</v>
-      </c>
-      <c r="AN3">
-        <v>-1</v>
-      </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -929,100 +929,100 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="O4">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="R4">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S4">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>2.73</v>
+        <v>3.19</v>
       </c>
       <c r="U4">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="AA4">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AB4">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AC4">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="AD4">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE4">
         <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AG4">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "57", "69", "87"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK4">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1092,139 +1092,139 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>2.37</v>
+        <v>1.5</v>
       </c>
       <c r="O5">
-        <v>3.45</v>
+        <v>3.98</v>
       </c>
       <c r="P5">
-        <v>2.75</v>
+        <v>6.4</v>
       </c>
       <c r="Q5">
-        <v>2.97</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T5">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="U5">
+        <v>2.85</v>
+      </c>
+      <c r="V5">
+        <v>1.33</v>
+      </c>
+      <c r="W5">
+        <v>1.05</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>1.27</v>
+      </c>
+      <c r="Z5">
+        <v>3.14</v>
+      </c>
+      <c r="AA5">
+        <v>1.94</v>
+      </c>
+      <c r="AB5">
+        <v>1.75</v>
+      </c>
+      <c r="AC5">
+        <v>3.42</v>
+      </c>
+      <c r="AD5">
+        <v>1.23</v>
+      </c>
+      <c r="AE5">
+        <v>1.06</v>
+      </c>
+      <c r="AF5">
+        <v>2.05</v>
+      </c>
+      <c r="AG5">
+        <v>1.75</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>["62"]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>["9", "69"]</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <v>1.17</v>
+      </c>
+      <c r="AK5">
         <v>2.45</v>
       </c>
-      <c r="V5">
-        <v>1.44</v>
-      </c>
-      <c r="W5">
-        <v>1.1</v>
-      </c>
-      <c r="X5">
-        <v>1.04</v>
-      </c>
-      <c r="Y5">
-        <v>1.2</v>
-      </c>
-      <c r="Z5">
-        <v>3.72</v>
-      </c>
-      <c r="AA5">
-        <v>1.81</v>
-      </c>
-      <c r="AB5">
-        <v>2.04</v>
-      </c>
-      <c r="AC5">
-        <v>3.07</v>
-      </c>
-      <c r="AD5">
-        <v>1.37</v>
-      </c>
-      <c r="AE5">
-        <v>1.13</v>
-      </c>
-      <c r="AF5">
-        <v>1.62</v>
-      </c>
-      <c r="AG5">
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>4</v>
+      </c>
+      <c r="AN5">
+        <v>6</v>
+      </c>
+      <c r="AO5">
+        <v>23</v>
+      </c>
+      <c r="AP5">
+        <v>18</v>
+      </c>
+      <c r="AQ5">
         <v>2.18</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.4</v>
-      </c>
-      <c r="AK5">
-        <v>1.48</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>-1</v>
-      </c>
-      <c r="AN5">
-        <v>-1</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>-1</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1255,139 +1255,139 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="O6">
-        <v>3.88</v>
+        <v>3.24</v>
       </c>
       <c r="P6">
-        <v>4.94</v>
+        <v>2.1</v>
       </c>
       <c r="Q6">
+        <v>3.9</v>
+      </c>
+      <c r="R6">
         <v>2.1</v>
       </c>
-      <c r="R6">
-        <v>2.3</v>
-      </c>
       <c r="S6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U6">
         <v>2.61</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA6">
+        <v>1.95</v>
+      </c>
+      <c r="AB6">
+        <v>1.88</v>
+      </c>
+      <c r="AC6">
+        <v>3.14</v>
+      </c>
+      <c r="AD6">
+        <v>1.29</v>
+      </c>
+      <c r="AE6">
+        <v>1.06</v>
+      </c>
+      <c r="AF6">
         <v>1.7</v>
       </c>
-      <c r="AB6">
-        <v>1.99</v>
-      </c>
-      <c r="AC6">
-        <v>2.66</v>
-      </c>
-      <c r="AD6">
-        <v>1.36</v>
-      </c>
-      <c r="AE6">
-        <v>1.15</v>
-      </c>
-      <c r="AF6">
-        <v>1.73</v>
-      </c>
       <c r="AG6">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43", "90+6"]</t>
         </is>
       </c>
       <c r="AJ6">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1418,139 +1418,139 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="O7">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="P7">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="Q7">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="R7">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="U7">
-        <v>3.32</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="Z7">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AA7">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AB7">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="AC7">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="AD7">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AE7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "40", "78"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82", "90+3"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,130 +1590,130 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="O8">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="P8">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
       </c>
       <c r="R8">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="S8">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T8">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U8">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="V8">
         <v>1.54</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z8">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA8">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB8">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AC8">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="AD8">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG8">
         <v>2.25</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "49", "90"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "25", "41"]</t>
         </is>
       </c>
       <c r="AJ8">
         <v>1.49</v>
       </c>
       <c r="AK8">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1744,90 +1744,90 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="O9">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
       <c r="P9">
-        <v>2.17</v>
+        <v>5.4</v>
       </c>
       <c r="Q9">
-        <v>3.8</v>
+        <v>2.07</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
         <v>1.33</v>
       </c>
       <c r="T9">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="U9">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AA9">
-        <v>1.99</v>
+        <v>1.68</v>
       </c>
       <c r="AB9">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AC9">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD9">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE9">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF9">
         <v>1.73</v>
@@ -1837,46 +1837,46 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "40", "50", "84", "90+3"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86"]</t>
         </is>
       </c>
       <c r="AJ9">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AK9">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1907,139 +1907,139 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>1.59</v>
+        <v>2.4</v>
       </c>
       <c r="O10">
-        <v>3.93</v>
+        <v>2.9</v>
       </c>
       <c r="P10">
-        <v>5.8</v>
+        <v>3.06</v>
       </c>
       <c r="Q10">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="S10">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="U10">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="V10">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W10">
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Z10">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AA10">
+        <v>2.25</v>
+      </c>
+      <c r="AB10">
+        <v>1.56</v>
+      </c>
+      <c r="AC10">
+        <v>4</v>
+      </c>
+      <c r="AD10">
+        <v>1.2</v>
+      </c>
+      <c r="AE10">
+        <v>1.02</v>
+      </c>
+      <c r="AF10">
         <v>1.92</v>
-      </c>
-      <c r="AB10">
-        <v>1.8</v>
-      </c>
-      <c r="AC10">
-        <v>3.34</v>
-      </c>
-      <c r="AD10">
-        <v>1.24</v>
-      </c>
-      <c r="AE10">
-        <v>1.08</v>
-      </c>
-      <c r="AF10">
-        <v>1.97</v>
       </c>
       <c r="AG10">
         <v>1.75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "69"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "89"]</t>
         </is>
       </c>
       <c r="AJ10">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2098,32 +2098,32 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="O11">
         <v>3.3</v>
       </c>
       <c r="P11">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q11">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="R11">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T11">
         <v>2.7</v>
       </c>
       <c r="U11">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="V11">
         <v>1.4</v>
@@ -2135,13 +2135,13 @@
         <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA11">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB11">
         <v>1.9</v>
@@ -2156,14 +2156,14 @@
         <v>1.07</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG11">
         <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "44"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2175,34 +2175,34 @@
         <v>1.29</v>
       </c>
       <c r="AK11">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,130 +2242,130 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="O12">
         <v>3.2</v>
       </c>
       <c r="P12">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="Q12">
+        <v>3.38</v>
+      </c>
+      <c r="R12">
+        <v>1.96</v>
+      </c>
+      <c r="S12">
+        <v>1.36</v>
+      </c>
+      <c r="T12">
+        <v>3</v>
+      </c>
+      <c r="U12">
+        <v>2.88</v>
+      </c>
+      <c r="V12">
+        <v>1.4</v>
+      </c>
+      <c r="W12">
+        <v>1.05</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>1.3</v>
+      </c>
+      <c r="Z12">
+        <v>3.56</v>
+      </c>
+      <c r="AA12">
+        <v>2.06</v>
+      </c>
+      <c r="AB12">
+        <v>1.84</v>
+      </c>
+      <c r="AC12">
         <v>3.42</v>
       </c>
-      <c r="R12">
-        <v>1.94</v>
-      </c>
-      <c r="S12">
-        <v>1.42</v>
-      </c>
-      <c r="T12">
-        <v>2.72</v>
-      </c>
-      <c r="U12">
-        <v>3.02</v>
-      </c>
-      <c r="V12">
-        <v>1.33</v>
-      </c>
-      <c r="W12">
-        <v>1.03</v>
-      </c>
-      <c r="X12">
-        <v>1.02</v>
-      </c>
-      <c r="Y12">
-        <v>1.33</v>
-      </c>
-      <c r="Z12">
-        <v>3.01</v>
-      </c>
-      <c r="AA12">
-        <v>2.17</v>
-      </c>
-      <c r="AB12">
-        <v>1.67</v>
-      </c>
-      <c r="AC12">
-        <v>4.05</v>
-      </c>
       <c r="AD12">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE12">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG12">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27"]</t>
         </is>
       </c>
       <c r="AJ12">
         <v>1.43</v>
       </c>
       <c r="AK12">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>3.2</v>
       </c>
       <c r="P20">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="Q20">
         <v>4.3</v>
@@ -3738,7 +3738,7 @@
         <v>4.2</v>
       </c>
       <c r="P21">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="Q21">
         <v>4.45</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P25">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q25">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R25">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S25">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U25">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V25">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z25">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AA25">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AB25">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC25">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD25">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE25">
         <v>1.08</v>
       </c>
       <c r="AF25">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG25">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="O33">
         <v>3.6</v>
@@ -5700,10 +5700,10 @@
         <v>2.32</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
         <v>2.88</v>
@@ -5721,16 +5721,16 @@
         <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
         <v>3.49</v>
       </c>
       <c r="AA33">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB33">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC33">
         <v>3.36</v>
@@ -5761,7 +5761,7 @@
         <v>1.19</v>
       </c>
       <c r="AK33">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q36">
-        <v>9.5</v>
+        <v>1.44</v>
       </c>
       <c r="R36">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="S36">
+        <v>1.2</v>
+      </c>
+      <c r="T36">
+        <v>4</v>
+      </c>
+      <c r="U36">
+        <v>1.96</v>
+      </c>
+      <c r="V36">
+        <v>1.72</v>
+      </c>
+      <c r="W36">
         <v>1.19</v>
-      </c>
-      <c r="T36">
-        <v>4.8</v>
-      </c>
-      <c r="U36">
-        <v>1.98</v>
-      </c>
-      <c r="V36">
-        <v>1.77</v>
-      </c>
-      <c r="W36">
-        <v>1.2</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z36">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AA36">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AB36">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AC36">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AD36">
         <v>1.71</v>
       </c>
       <c r="AE36">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF36">
-        <v>1.85</v>
+        <v>2.31</v>
       </c>
       <c r="AG36">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="AK36">
-        <v>1.03</v>
+        <v>5.85</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>1.44</v>
+        <v>9.5</v>
       </c>
       <c r="R37">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="S37">
+        <v>1.19</v>
+      </c>
+      <c r="T37">
+        <v>4.8</v>
+      </c>
+      <c r="U37">
+        <v>1.98</v>
+      </c>
+      <c r="V37">
+        <v>1.77</v>
+      </c>
+      <c r="W37">
         <v>1.2</v>
-      </c>
-      <c r="T37">
-        <v>4</v>
-      </c>
-      <c r="U37">
-        <v>1.96</v>
-      </c>
-      <c r="V37">
-        <v>1.72</v>
-      </c>
-      <c r="W37">
-        <v>1.19</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AA37">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AB37">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AC37">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AD37">
         <v>1.71</v>
       </c>
       <c r="AE37">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF37">
-        <v>2.31</v>
+        <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="AK37">
-        <v>5.85</v>
+        <v>1.03</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -7324,13 +7324,13 @@
         <v>4.2</v>
       </c>
       <c r="P43">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q43">
         <v>2</v>
       </c>
       <c r="R43">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="S43">
         <v>1.24</v>
@@ -7339,10 +7339,10 @@
         <v>3.5</v>
       </c>
       <c r="U43">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V43">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W43">
         <v>1.11</v>
@@ -7357,7 +7357,7 @@
         <v>4.75</v>
       </c>
       <c r="AA43">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB43">
         <v>2.17</v>
@@ -7677,7 +7677,7 @@
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z45">
         <v>4.1</v>
@@ -7689,10 +7689,10 @@
         <v>2.15</v>
       </c>
       <c r="AC45">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="AD45">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE45">
         <v>1.1</v>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="O46">
         <v>3.4</v>
@@ -7880,7 +7880,7 @@
         <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="O47">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
-        <v>3.24</v>
+        <v>2.7</v>
       </c>
       <c r="Q47">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
       <c r="R47">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S47">
+        <v>1.39</v>
+      </c>
+      <c r="T47">
+        <v>3.05</v>
+      </c>
+      <c r="U47">
+        <v>2.85</v>
+      </c>
+      <c r="V47">
+        <v>1.42</v>
+      </c>
+      <c r="W47">
+        <v>1.05</v>
+      </c>
+      <c r="X47">
+        <v>1.01</v>
+      </c>
+      <c r="Y47">
+        <v>1.24</v>
+      </c>
+      <c r="Z47">
+        <v>3.34</v>
+      </c>
+      <c r="AA47">
+        <v>1.83</v>
+      </c>
+      <c r="AB47">
+        <v>1.86</v>
+      </c>
+      <c r="AC47">
+        <v>3.2</v>
+      </c>
+      <c r="AD47">
         <v>1.34</v>
       </c>
-      <c r="T47">
-        <v>3.25</v>
-      </c>
-      <c r="U47">
-        <v>2.38</v>
-      </c>
-      <c r="V47">
-        <v>1.48</v>
-      </c>
-      <c r="W47">
-        <v>1.11</v>
-      </c>
-      <c r="X47">
-        <v>1</v>
-      </c>
-      <c r="Y47">
-        <v>1.22</v>
-      </c>
-      <c r="Z47">
-        <v>4.13</v>
-      </c>
-      <c r="AA47">
-        <v>1.75</v>
-      </c>
-      <c r="AB47">
-        <v>2.08</v>
-      </c>
-      <c r="AC47">
-        <v>2.74</v>
-      </c>
-      <c r="AD47">
-        <v>1.39</v>
-      </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF47">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG47">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK47">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P48">
-        <v>2.67</v>
+        <v>3.24</v>
       </c>
       <c r="Q48">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R48">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S48">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T48">
-        <v>2.88</v>
+        <v>3.27</v>
       </c>
       <c r="U48">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V48">
+        <v>1.48</v>
+      </c>
+      <c r="W48">
+        <v>1.11</v>
+      </c>
+      <c r="X48">
+        <v>1</v>
+      </c>
+      <c r="Y48">
+        <v>1.22</v>
+      </c>
+      <c r="Z48">
+        <v>4.16</v>
+      </c>
+      <c r="AA48">
+        <v>1.75</v>
+      </c>
+      <c r="AB48">
+        <v>2.09</v>
+      </c>
+      <c r="AC48">
+        <v>2.7</v>
+      </c>
+      <c r="AD48">
         <v>1.39</v>
       </c>
-      <c r="W48">
-        <v>1.05</v>
-      </c>
-      <c r="X48">
-        <v>1.05</v>
-      </c>
-      <c r="Y48">
-        <v>1.3</v>
-      </c>
-      <c r="Z48">
-        <v>3.14</v>
-      </c>
-      <c r="AA48">
-        <v>1.95</v>
-      </c>
-      <c r="AB48">
-        <v>1.78</v>
-      </c>
-      <c r="AC48">
-        <v>3.6</v>
-      </c>
-      <c r="AD48">
-        <v>1.29</v>
-      </c>
       <c r="AE48">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF48">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG48">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.29</v>
       </c>
       <c r="AK48">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="O49">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P49">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="Q49">
-        <v>4.6</v>
+        <v>3.02</v>
       </c>
       <c r="R49">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="S49">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T49">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U49">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W49">
+        <v>1.05</v>
+      </c>
+      <c r="X49">
+        <v>1.05</v>
+      </c>
+      <c r="Y49">
+        <v>1.31</v>
+      </c>
+      <c r="Z49">
+        <v>3.08</v>
+      </c>
+      <c r="AA49">
+        <v>1.98</v>
+      </c>
+      <c r="AB49">
+        <v>1.76</v>
+      </c>
+      <c r="AC49">
+        <v>3.6</v>
+      </c>
+      <c r="AD49">
+        <v>1.28</v>
+      </c>
+      <c r="AE49">
         <v>1.06</v>
       </c>
-      <c r="X49">
-        <v>1.02</v>
-      </c>
-      <c r="Y49">
-        <v>1.22</v>
-      </c>
-      <c r="Z49">
-        <v>3.5</v>
-      </c>
-      <c r="AA49">
-        <v>1.84</v>
-      </c>
-      <c r="AB49">
-        <v>1.94</v>
-      </c>
-      <c r="AC49">
-        <v>2.88</v>
-      </c>
-      <c r="AD49">
-        <v>1.32</v>
-      </c>
-      <c r="AE49">
-        <v>1.14</v>
-      </c>
       <c r="AF49">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG49">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,65 +8459,65 @@
         </is>
       </c>
       <c r="N50">
+        <v>3.65</v>
+      </c>
+      <c r="O50">
+        <v>3.35</v>
+      </c>
+      <c r="P50">
+        <v>1.85</v>
+      </c>
+      <c r="Q50">
+        <v>4.5</v>
+      </c>
+      <c r="R50">
+        <v>2.33</v>
+      </c>
+      <c r="S50">
+        <v>1.34</v>
+      </c>
+      <c r="T50">
+        <v>3.1</v>
+      </c>
+      <c r="U50">
         <v>2.6</v>
       </c>
-      <c r="O50">
-        <v>3.4</v>
-      </c>
-      <c r="P50">
-        <v>2.7</v>
-      </c>
-      <c r="Q50">
-        <v>3.08</v>
-      </c>
-      <c r="R50">
+      <c r="V50">
+        <v>1.44</v>
+      </c>
+      <c r="W50">
+        <v>1.06</v>
+      </c>
+      <c r="X50">
+        <v>1.02</v>
+      </c>
+      <c r="Y50">
+        <v>1.22</v>
+      </c>
+      <c r="Z50">
+        <v>3.5</v>
+      </c>
+      <c r="AA50">
+        <v>1.85</v>
+      </c>
+      <c r="AB50">
+        <v>1.94</v>
+      </c>
+      <c r="AC50">
+        <v>2.88</v>
+      </c>
+      <c r="AD50">
+        <v>1.32</v>
+      </c>
+      <c r="AE50">
+        <v>1.14</v>
+      </c>
+      <c r="AF50">
+        <v>1.7</v>
+      </c>
+      <c r="AG50">
         <v>2</v>
       </c>
-      <c r="S50">
-        <v>1.4</v>
-      </c>
-      <c r="T50">
-        <v>3.05</v>
-      </c>
-      <c r="U50">
-        <v>2.86</v>
-      </c>
-      <c r="V50">
-        <v>1.41</v>
-      </c>
-      <c r="W50">
-        <v>1.05</v>
-      </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.24</v>
-      </c>
-      <c r="Z50">
-        <v>3.34</v>
-      </c>
-      <c r="AA50">
-        <v>1.83</v>
-      </c>
-      <c r="AB50">
-        <v>1.85</v>
-      </c>
-      <c r="AC50">
-        <v>3.2</v>
-      </c>
-      <c r="AD50">
-        <v>1.34</v>
-      </c>
-      <c r="AE50">
-        <v>1.07</v>
-      </c>
-      <c r="AF50">
-        <v>1.62</v>
-      </c>
-      <c r="AG50">
-        <v>2.15</v>
-      </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8631,25 +8631,25 @@
         <v>2.15</v>
       </c>
       <c r="Q51">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="R51">
         <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T51">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="U51">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X51">
         <v>1.03</v>
@@ -8658,28 +8658,28 @@
         <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
       <c r="AA51">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AB51">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC51">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE51">
         <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG51">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8788,13 +8788,13 @@
         <v>1.7</v>
       </c>
       <c r="O52">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P52">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q52">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R52">
         <v>2.25</v>
@@ -8821,7 +8821,7 @@
         <v>1.3</v>
       </c>
       <c r="Z52">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AA52">
         <v>1.81</v>
@@ -8836,13 +8836,13 @@
         <v>1.31</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF52">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG52">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK52">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="O61">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="P61">
-        <v>2.45</v>
+        <v>7</v>
       </c>
       <c r="Q61">
-        <v>3.14</v>
+        <v>1.73</v>
       </c>
       <c r="R61">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="S61">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.12</v>
+        <v>4.4</v>
       </c>
       <c r="U61">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="V61">
-        <v>1.49</v>
+        <v>1.81</v>
       </c>
       <c r="W61">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="Z61">
-        <v>4.38</v>
+        <v>6.25</v>
       </c>
       <c r="AA61">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="AB61">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC61">
-        <v>2.49</v>
+        <v>1.88</v>
       </c>
       <c r="AD61">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AE61">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AF61">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG61">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK61">
-        <v>1.5</v>
+        <v>3.22</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="O62">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="P62">
-        <v>5.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q62">
-        <v>2.05</v>
+        <v>3.14</v>
       </c>
       <c r="R62">
         <v>2.4</v>
       </c>
       <c r="S62">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U62">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="V62">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="W62">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z62">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="AA62">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB62">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AC62">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AD62">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE62">
         <v>1.14</v>
       </c>
       <c r="AF62">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AG62">
-        <v>1.99</v>
+        <v>2.37</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="O63">
-        <v>5.8</v>
+        <v>4.33</v>
       </c>
       <c r="P63">
-        <v>7</v>
+        <v>5.35</v>
       </c>
       <c r="Q63">
+        <v>2.05</v>
+      </c>
+      <c r="R63">
+        <v>2.4</v>
+      </c>
+      <c r="S63">
+        <v>1.26</v>
+      </c>
+      <c r="T63">
+        <v>3.2</v>
+      </c>
+      <c r="U63">
+        <v>2.27</v>
+      </c>
+      <c r="V63">
+        <v>1.54</v>
+      </c>
+      <c r="W63">
+        <v>1.11</v>
+      </c>
+      <c r="X63">
+        <v>1.03</v>
+      </c>
+      <c r="Y63">
+        <v>1.21</v>
+      </c>
+      <c r="Z63">
+        <v>4.2</v>
+      </c>
+      <c r="AA63">
+        <v>1.63</v>
+      </c>
+      <c r="AB63">
+        <v>2.12</v>
+      </c>
+      <c r="AC63">
+        <v>2.46</v>
+      </c>
+      <c r="AD63">
+        <v>1.43</v>
+      </c>
+      <c r="AE63">
+        <v>1.14</v>
+      </c>
+      <c r="AF63">
         <v>1.73</v>
       </c>
-      <c r="R63">
-        <v>2.73</v>
-      </c>
-      <c r="S63">
-        <v>1.2</v>
-      </c>
-      <c r="T63">
-        <v>4.4</v>
-      </c>
-      <c r="U63">
-        <v>1.95</v>
-      </c>
-      <c r="V63">
-        <v>1.81</v>
-      </c>
-      <c r="W63">
-        <v>1.21</v>
-      </c>
-      <c r="X63">
-        <v>1.01</v>
-      </c>
-      <c r="Y63">
-        <v>1.06</v>
-      </c>
-      <c r="Z63">
-        <v>6.25</v>
-      </c>
-      <c r="AA63">
-        <v>1.37</v>
-      </c>
-      <c r="AB63">
-        <v>3.1</v>
-      </c>
-      <c r="AC63">
-        <v>1.88</v>
-      </c>
-      <c r="AD63">
-        <v>1.93</v>
-      </c>
-      <c r="AE63">
-        <v>1.33</v>
-      </c>
-      <c r="AF63">
-        <v>1.57</v>
-      </c>
       <c r="AG63">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AK63">
-        <v>3.22</v>
+        <v>2.4</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,16 +10741,16 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="O64">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P64">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="Q64">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="R64">
         <v>2</v>
@@ -10762,10 +10762,10 @@
         <v>2.61</v>
       </c>
       <c r="U64">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="V64">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W64">
         <v>1.05</v>
@@ -10774,22 +10774,22 @@
         <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z64">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA64">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB64">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC64">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="AD64">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE64">
         <v>1.05</v>
@@ -10798,7 +10798,7 @@
         <v>1.8</v>
       </c>
       <c r="AG64">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK64">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,65 +10904,65 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="O65">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P65">
-        <v>2.77</v>
+        <v>2.4</v>
       </c>
       <c r="Q65">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="R65">
         <v>2</v>
       </c>
       <c r="S65">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T65">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="U65">
-        <v>2.82</v>
+        <v>3.18</v>
       </c>
       <c r="V65">
+        <v>1.27</v>
+      </c>
+      <c r="W65">
+        <v>1.04</v>
+      </c>
+      <c r="X65">
+        <v>1.04</v>
+      </c>
+      <c r="Y65">
         <v>1.36</v>
       </c>
-      <c r="W65">
-        <v>1.05</v>
-      </c>
-      <c r="X65">
-        <v>1.03</v>
-      </c>
-      <c r="Y65">
-        <v>1.3</v>
-      </c>
       <c r="Z65">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="AA65">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="AB65">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AC65">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="AD65">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE65">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF65">
+        <v>1.87</v>
+      </c>
+      <c r="AG65">
         <v>1.8</v>
       </c>
-      <c r="AG65">
-        <v>1.9</v>
-      </c>
       <c r="AH65" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AK65">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="O66">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P66">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q66">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="R66">
         <v>2</v>
       </c>
       <c r="S66">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T66">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="U66">
-        <v>3.18</v>
+        <v>2.89</v>
       </c>
       <c r="V66">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W66">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X66">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z66">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="AA66">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AB66">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AC66">
-        <v>4.05</v>
+        <v>3.48</v>
       </c>
       <c r="AD66">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE66">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF66">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG66">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="AK66">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="O67">
+        <v>3.05</v>
+      </c>
+      <c r="P67">
+        <v>2.2</v>
+      </c>
+      <c r="Q67">
+        <v>3.62</v>
+      </c>
+      <c r="R67">
+        <v>2.1</v>
+      </c>
+      <c r="S67">
+        <v>1.3</v>
+      </c>
+      <c r="T67">
         <v>3</v>
       </c>
-      <c r="P67">
-        <v>2.55</v>
-      </c>
-      <c r="Q67">
-        <v>3.4</v>
-      </c>
-      <c r="R67">
-        <v>2</v>
-      </c>
-      <c r="S67">
-        <v>1.43</v>
-      </c>
-      <c r="T67">
-        <v>2.6</v>
-      </c>
       <c r="U67">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V67">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W67">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="Z67">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="AA67">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB67">
+        <v>1.85</v>
+      </c>
+      <c r="AC67">
+        <v>2.97</v>
+      </c>
+      <c r="AD67">
+        <v>1.3</v>
+      </c>
+      <c r="AE67">
+        <v>1.1</v>
+      </c>
+      <c r="AF67">
         <v>1.65</v>
       </c>
-      <c r="AC67">
-        <v>3.9</v>
-      </c>
-      <c r="AD67">
-        <v>1.2</v>
-      </c>
-      <c r="AE67">
-        <v>1.08</v>
-      </c>
-      <c r="AF67">
-        <v>1.85</v>
-      </c>
       <c r="AG67">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK67">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -14822,7 +14822,7 @@
         <v>3.4</v>
       </c>
       <c r="P89">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q89">
         <v>2.7</v>
@@ -14849,10 +14849,10 @@
         <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z89">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AA89">
         <v>1.77</v>
@@ -14861,13 +14861,13 @@
         <v>2.02</v>
       </c>
       <c r="AC89">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD89">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE89">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF89">
         <v>1.57</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,31 +17098,31 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="O103">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="P103">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q103">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="R103">
-        <v>2.96</v>
+        <v>2.55</v>
       </c>
       <c r="S103">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T103">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="U103">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="V103">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W103">
         <v>1.2</v>
@@ -17131,31 +17131,31 @@
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z103">
-        <v>7</v>
+        <v>6.05</v>
       </c>
       <c r="AA103">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB103">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AC103">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AD103">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AE103">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF103">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG103">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AK103">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="O104">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="P104">
-        <v>5.5</v>
+        <v>2.57</v>
       </c>
       <c r="Q104">
-        <v>1.95</v>
+        <v>3.07</v>
       </c>
       <c r="R104">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="S104">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T104">
+        <v>3.3</v>
+      </c>
+      <c r="U104">
+        <v>2.34</v>
+      </c>
+      <c r="V104">
+        <v>1.51</v>
+      </c>
+      <c r="W104">
+        <v>1.1</v>
+      </c>
+      <c r="X104">
+        <v>1.04</v>
+      </c>
+      <c r="Y104">
+        <v>1.16</v>
+      </c>
+      <c r="Z104">
         <v>4.2</v>
       </c>
-      <c r="U104">
-        <v>1.95</v>
-      </c>
-      <c r="V104">
-        <v>1.75</v>
-      </c>
-      <c r="W104">
-        <v>1.2</v>
-      </c>
-      <c r="X104">
-        <v>1.01</v>
-      </c>
-      <c r="Y104">
-        <v>1.06</v>
-      </c>
-      <c r="Z104">
-        <v>6.05</v>
-      </c>
       <c r="AA104">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="AB104">
-        <v>2.83</v>
+        <v>2.17</v>
       </c>
       <c r="AC104">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="AD104">
-        <v>1.81</v>
+        <v>1.46</v>
       </c>
       <c r="AE104">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF104">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG104">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AK104">
-        <v>2.4</v>
+        <v>1.47</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="O105">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="P105">
-        <v>3.07</v>
+        <v>6.75</v>
       </c>
       <c r="Q105">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="R105">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="S105">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="T105">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="U105">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="V105">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="W105">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z105">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA105">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AB105">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AC105">
-        <v>2.43</v>
+        <v>1.91</v>
       </c>
       <c r="AD105">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AE105">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AF105">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG105">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AK105">
-        <v>1.77</v>
+        <v>3.1</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,65 +17587,65 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="O106">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="P106">
-        <v>2.57</v>
+        <v>3.74</v>
       </c>
       <c r="Q106">
-        <v>3.07</v>
+        <v>2.16</v>
       </c>
       <c r="R106">
-        <v>2.18</v>
+        <v>2.8</v>
       </c>
       <c r="S106">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="T106">
+        <v>4.8</v>
+      </c>
+      <c r="U106">
+        <v>1.78</v>
+      </c>
+      <c r="V106">
+        <v>1.89</v>
+      </c>
+      <c r="W106">
+        <v>1.25</v>
+      </c>
+      <c r="X106">
+        <v>1.01</v>
+      </c>
+      <c r="Y106">
+        <v>1.05</v>
+      </c>
+      <c r="Z106">
+        <v>8.5</v>
+      </c>
+      <c r="AA106">
+        <v>1.24</v>
+      </c>
+      <c r="AB106">
+        <v>3.6</v>
+      </c>
+      <c r="AC106">
+        <v>1.73</v>
+      </c>
+      <c r="AD106">
+        <v>2.06</v>
+      </c>
+      <c r="AE106">
+        <v>1.45</v>
+      </c>
+      <c r="AF106">
+        <v>1.3</v>
+      </c>
+      <c r="AG106">
         <v>3.3</v>
       </c>
-      <c r="U106">
-        <v>2.34</v>
-      </c>
-      <c r="V106">
-        <v>1.51</v>
-      </c>
-      <c r="W106">
-        <v>1.1</v>
-      </c>
-      <c r="X106">
-        <v>1.04</v>
-      </c>
-      <c r="Y106">
-        <v>1.16</v>
-      </c>
-      <c r="Z106">
-        <v>4.2</v>
-      </c>
-      <c r="AA106">
-        <v>1.66</v>
-      </c>
-      <c r="AB106">
-        <v>2.17</v>
-      </c>
-      <c r="AC106">
-        <v>2.52</v>
-      </c>
-      <c r="AD106">
-        <v>1.46</v>
-      </c>
-      <c r="AE106">
-        <v>1.13</v>
-      </c>
-      <c r="AF106">
-        <v>1.53</v>
-      </c>
-      <c r="AG106">
-        <v>2.35</v>
-      </c>
       <c r="AH106" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>1.47</v>
+        <v>2.02</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,80 +17750,80 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="O107">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="P107">
-        <v>3.74</v>
+        <v>3.07</v>
       </c>
       <c r="Q107">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="R107">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="S107">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="T107">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="U107">
-        <v>1.78</v>
+        <v>2.26</v>
       </c>
       <c r="V107">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="W107">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="X107">
         <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="Z107">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="AA107">
+        <v>1.61</v>
+      </c>
+      <c r="AB107">
+        <v>2.25</v>
+      </c>
+      <c r="AC107">
+        <v>2.43</v>
+      </c>
+      <c r="AD107">
+        <v>1.44</v>
+      </c>
+      <c r="AE107">
+        <v>1.14</v>
+      </c>
+      <c r="AF107">
+        <v>1.5</v>
+      </c>
+      <c r="AG107">
+        <v>2.33</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
         <v>1.24</v>
       </c>
-      <c r="AB107">
-        <v>3.6</v>
-      </c>
-      <c r="AC107">
-        <v>1.73</v>
-      </c>
-      <c r="AD107">
-        <v>2.06</v>
-      </c>
-      <c r="AE107">
-        <v>1.45</v>
-      </c>
-      <c r="AF107">
-        <v>1.3</v>
-      </c>
-      <c r="AG107">
-        <v>3.3</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.25</v>
-      </c>
       <c r="AK107">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18921,13 +18921,13 @@
         <v>1.1</v>
       </c>
       <c r="X114">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z114">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="AA114">
         <v>1.8</v>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK114">
         <v>1.76</v>
@@ -19069,10 +19069,10 @@
         <v>2.05</v>
       </c>
       <c r="S115">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T115">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U115">
         <v>2.81</v>
@@ -19093,13 +19093,13 @@
         <v>2.92</v>
       </c>
       <c r="AA115">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AB115">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC115">
-        <v>3.77</v>
+        <v>3.81</v>
       </c>
       <c r="AD115">
         <v>1.22</v>
@@ -19220,10 +19220,10 @@
         <v>3</v>
       </c>
       <c r="O116">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P116">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q116">
         <v>3.48</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="O117">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="P117">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q117">
-        <v>3.28</v>
+        <v>3.47</v>
       </c>
       <c r="R117">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S117">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T117">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="U117">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V117">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W117">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X117">
         <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z117">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA117">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB117">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC117">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AD117">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE117">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF117">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG117">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK117">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="O118">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P118">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="Q118">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="R118">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S118">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T118">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="U118">
-        <v>2.48</v>
+        <v>3.12</v>
       </c>
       <c r="V118">
+        <v>1.28</v>
+      </c>
+      <c r="W118">
+        <v>1.01</v>
+      </c>
+      <c r="X118">
+        <v>1.03</v>
+      </c>
+      <c r="Y118">
         <v>1.4</v>
       </c>
-      <c r="W118">
-        <v>1.1</v>
-      </c>
-      <c r="X118">
-        <v>1.01</v>
-      </c>
-      <c r="Y118">
-        <v>1.22</v>
-      </c>
       <c r="Z118">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="AA118">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AB118">
-        <v>1.98</v>
+        <v>1.59</v>
       </c>
       <c r="AC118">
-        <v>2.88</v>
+        <v>3.95</v>
       </c>
       <c r="AD118">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AE118">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AF118">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AG118">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AK118">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O119">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P119">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="Q119">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="R119">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="S119">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T119">
-        <v>2.45</v>
+        <v>2.99</v>
       </c>
       <c r="U119">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="V119">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X119">
         <v>1.03</v>
       </c>
       <c r="Y119">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="Z119">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="AA119">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="AB119">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AC119">
-        <v>3.96</v>
+        <v>3.35</v>
       </c>
       <c r="AD119">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AE119">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF119">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AG119">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AK119">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,80 +19869,80 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O120">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P120">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q120">
-        <v>3.52</v>
+        <v>2.75</v>
       </c>
       <c r="R120">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="S120">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T120">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="U120">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="V120">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W120">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X120">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y120">
+        <v>1.22</v>
+      </c>
+      <c r="Z120">
+        <v>3.87</v>
+      </c>
+      <c r="AA120">
+        <v>1.78</v>
+      </c>
+      <c r="AB120">
+        <v>1.99</v>
+      </c>
+      <c r="AC120">
+        <v>2.96</v>
+      </c>
+      <c r="AD120">
+        <v>1.39</v>
+      </c>
+      <c r="AE120">
+        <v>1.08</v>
+      </c>
+      <c r="AF120">
+        <v>1.65</v>
+      </c>
+      <c r="AG120">
+        <v>2.14</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ120">
         <v>1.26</v>
       </c>
-      <c r="Z120">
-        <v>3.2</v>
-      </c>
-      <c r="AA120">
-        <v>1.9</v>
-      </c>
-      <c r="AB120">
-        <v>1.78</v>
-      </c>
-      <c r="AC120">
-        <v>3.33</v>
-      </c>
-      <c r="AD120">
-        <v>1.32</v>
-      </c>
-      <c r="AE120">
-        <v>1.11</v>
-      </c>
-      <c r="AF120">
-        <v>1.7</v>
-      </c>
-      <c r="AG120">
-        <v>2.03</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>1.42</v>
-      </c>
       <c r="AK120">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q121">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="R121">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S121">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T121">
+        <v>2.68</v>
+      </c>
+      <c r="U121">
+        <v>2.71</v>
+      </c>
+      <c r="V121">
+        <v>1.36</v>
+      </c>
+      <c r="W121">
+        <v>1.05</v>
+      </c>
+      <c r="X121">
+        <v>1.01</v>
+      </c>
+      <c r="Y121">
+        <v>1.29</v>
+      </c>
+      <c r="Z121">
+        <v>3.2</v>
+      </c>
+      <c r="AA121">
+        <v>1.95</v>
+      </c>
+      <c r="AB121">
+        <v>1.85</v>
+      </c>
+      <c r="AC121">
         <v>3.08</v>
       </c>
-      <c r="U121">
-        <v>2.6</v>
-      </c>
-      <c r="V121">
-        <v>1.4</v>
-      </c>
-      <c r="W121">
-        <v>1.07</v>
-      </c>
-      <c r="X121">
-        <v>1</v>
-      </c>
-      <c r="Y121">
-        <v>1.22</v>
-      </c>
-      <c r="Z121">
-        <v>3.87</v>
-      </c>
-      <c r="AA121">
-        <v>1.78</v>
-      </c>
-      <c r="AB121">
-        <v>1.99</v>
-      </c>
-      <c r="AC121">
-        <v>2.96</v>
-      </c>
       <c r="AD121">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AE121">
         <v>1.08</v>
       </c>
       <c r="AF121">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG121">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>1.26</v>
       </c>
       <c r="AK121">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O136">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="P136">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="Q136">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R136">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S136">
+        <v>1.33</v>
+      </c>
+      <c r="T136">
+        <v>2.84</v>
+      </c>
+      <c r="U136">
+        <v>3.01</v>
+      </c>
+      <c r="V136">
+        <v>1.38</v>
+      </c>
+      <c r="W136">
+        <v>1.05</v>
+      </c>
+      <c r="X136">
+        <v>1.04</v>
+      </c>
+      <c r="Y136">
         <v>1.3</v>
       </c>
-      <c r="T136">
+      <c r="Z136">
         <v>3.25</v>
       </c>
-      <c r="U136">
-        <v>2.4</v>
-      </c>
-      <c r="V136">
-        <v>1.46</v>
-      </c>
-      <c r="W136">
-        <v>1.08</v>
-      </c>
-      <c r="X136">
-        <v>1</v>
-      </c>
-      <c r="Y136">
-        <v>1.19</v>
-      </c>
-      <c r="Z136">
-        <v>4.1</v>
-      </c>
       <c r="AA136">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AB136">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="AC136">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="AD136">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AE136">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF136">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG136">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK136">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="O137">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="P137">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="Q137">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R137">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S137">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T137">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="U137">
-        <v>3.01</v>
+        <v>2.4</v>
       </c>
       <c r="V137">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W137">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X137">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y137">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z137">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="AA137">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AB137">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="AC137">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="AD137">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AE137">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF137">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG137">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK137">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AL137">
         <v>0</v>

--- a/jogos_2026-09-26.xlsx
+++ b/jogos_2026-09-26.xlsx
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -950,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>["40", "57", "69", "87"]</t>
+          <t>["40", "57", "69"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1046,16 +1046,16 @@
         <v>1</v>
       </c>
       <c r="AO4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="AR4">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AS4">
         <v>66</v>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2420,21 +2420,21 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="O13">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="P13">
-        <v>3.07</v>
+        <v>3.12</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2568,26 +2568,26 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2639,7 +2639,7 @@
         <v>2.62</v>
       </c>
       <c r="AD14">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
         <v>1.11</v>
@@ -2652,46 +2652,46 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "50", "85"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "67", "70", "87", "90+6"]</t>
         </is>
       </c>
       <c r="AJ14">
         <v>1.18</v>
       </c>
       <c r="AK14">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2746,11 +2746,11 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2763,98 +2763,98 @@
         <v>3.88</v>
       </c>
       <c r="Q15">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="R15">
+        <v>2.1</v>
+      </c>
+      <c r="S15">
+        <v>1.34</v>
+      </c>
+      <c r="T15">
+        <v>2.81</v>
+      </c>
+      <c r="U15">
+        <v>2.69</v>
+      </c>
+      <c r="V15">
+        <v>1.37</v>
+      </c>
+      <c r="W15">
+        <v>1.05</v>
+      </c>
+      <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
+        <v>1.27</v>
+      </c>
+      <c r="Z15">
+        <v>3.14</v>
+      </c>
+      <c r="AA15">
+        <v>1.95</v>
+      </c>
+      <c r="AB15">
+        <v>1.75</v>
+      </c>
+      <c r="AC15">
+        <v>3.25</v>
+      </c>
+      <c r="AD15">
+        <v>1.25</v>
+      </c>
+      <c r="AE15">
+        <v>1.08</v>
+      </c>
+      <c r="AF15">
+        <v>1.78</v>
+      </c>
+      <c r="AG15">
+        <v>1.86</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>["90+6"]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.22</v>
+      </c>
+      <c r="AK15">
+        <v>1.72</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>5</v>
+      </c>
+      <c r="AN15">
+        <v>3</v>
+      </c>
+      <c r="AO15">
+        <v>16</v>
+      </c>
+      <c r="AP15">
+        <v>7</v>
+      </c>
+      <c r="AQ15">
         <v>2.06</v>
       </c>
-      <c r="S15">
-        <v>1.37</v>
-      </c>
-      <c r="T15">
-        <v>2.69</v>
-      </c>
-      <c r="U15">
-        <v>2.81</v>
-      </c>
-      <c r="V15">
-        <v>1.34</v>
-      </c>
-      <c r="W15">
-        <v>1.04</v>
-      </c>
-      <c r="X15">
-        <v>1.04</v>
-      </c>
-      <c r="Y15">
-        <v>1.31</v>
-      </c>
-      <c r="Z15">
-        <v>2.92</v>
-      </c>
-      <c r="AA15">
-        <v>2.1</v>
-      </c>
-      <c r="AB15">
-        <v>1.66</v>
-      </c>
-      <c r="AC15">
-        <v>3.35</v>
-      </c>
-      <c r="AD15">
-        <v>1.22</v>
-      </c>
-      <c r="AE15">
-        <v>1.07</v>
-      </c>
-      <c r="AF15">
-        <v>1.97</v>
-      </c>
-      <c r="AG15">
-        <v>1.69</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.21</v>
-      </c>
-      <c r="AK15">
-        <v>2.04</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>-1</v>
-      </c>
-      <c r="AN15">
-        <v>-1</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>-1</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2906,14 +2906,14 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50", "85"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3060,33 +3060,33 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>5.32</v>
+        <v>5.8</v>
       </c>
       <c r="O17">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB17">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "51", "76", "82"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v